--- a/database/event/4566/event_4566_evp_summary.xlsx
+++ b/database/event/4566/event_4566_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>2.1854</v>
       </c>
       <c r="D2" t="n">
-        <v>3.4886</v>
+        <v>3.412</v>
       </c>
       <c r="E2" t="n">
         <v>9.678599999999999</v>
@@ -548,7 +548,7 @@
         <v>1.3924</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0698</v>
+        <v>2.0128</v>
       </c>
       <c r="E3" t="n">
         <v>6.1665</v>
@@ -594,7 +594,7 @@
         <v>0.978</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3285</v>
+        <v>1.2818</v>
       </c>
       <c r="E4" t="n">
         <v>4.3315</v>
@@ -640,7 +640,7 @@
         <v>0.9179</v>
       </c>
       <c r="D5" t="n">
-        <v>1.221</v>
+        <v>1.1757</v>
       </c>
       <c r="E5" t="n">
         <v>4.0654</v>
@@ -686,7 +686,7 @@
         <v>0.8659</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1279</v>
+        <v>1.0839</v>
       </c>
       <c r="E6" t="n">
         <v>3.8349</v>
@@ -732,7 +732,7 @@
         <v>0.8642</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1249</v>
+        <v>1.081</v>
       </c>
       <c r="E7" t="n">
         <v>3.8276</v>
@@ -778,7 +778,7 @@
         <v>0.83</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0637</v>
+        <v>1.0206</v>
       </c>
       <c r="E8" t="n">
         <v>3.676</v>
@@ -824,7 +824,7 @@
         <v>0.7964</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0035</v>
+        <v>0.9613</v>
       </c>
       <c r="E9" t="n">
         <v>3.5271</v>
@@ -870,7 +870,7 @@
         <v>0.6746</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7856</v>
+        <v>0.7464</v>
       </c>
       <c r="E10" t="n">
         <v>2.9877</v>
@@ -916,7 +916,7 @@
         <v>0.6344</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7137</v>
+        <v>0.6755</v>
       </c>
       <c r="E11" t="n">
         <v>2.8097</v>
@@ -962,7 +962,7 @@
         <v>0.6296</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7052</v>
+        <v>0.6671</v>
       </c>
       <c r="E12" t="n">
         <v>2.7886</v>
@@ -1008,7 +1008,7 @@
         <v>0.4912</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4575</v>
+        <v>0.4228</v>
       </c>
       <c r="E13" t="n">
         <v>2.1756</v>
@@ -1054,7 +1054,7 @@
         <v>0.4424</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3702</v>
+        <v>0.3367</v>
       </c>
       <c r="E14" t="n">
         <v>1.9594</v>
@@ -1100,7 +1100,7 @@
         <v>0.4259</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3407</v>
+        <v>0.3076</v>
       </c>
       <c r="E15" t="n">
         <v>1.8863</v>
@@ -1146,7 +1146,7 @@
         <v>0.3659</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2332</v>
+        <v>0.2016</v>
       </c>
       <c r="E16" t="n">
         <v>1.6203</v>
@@ -1192,7 +1192,7 @@
         <v>0.283</v>
       </c>
       <c r="D17" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.0554</v>
       </c>
       <c r="E17" t="n">
         <v>1.2534</v>
@@ -1238,7 +1238,7 @@
         <v>0.2266</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0159</v>
+        <v>-0.0441</v>
       </c>
       <c r="E18" t="n">
         <v>1.0036</v>
@@ -1284,7 +1284,7 @@
         <v>0.1218</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2034</v>
+        <v>-0.2289</v>
       </c>
       <c r="E19" t="n">
         <v>0.5396</v>
@@ -1330,7 +1330,7 @@
         <v>-0.0194</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.456</v>
+        <v>-0.4781</v>
       </c>
       <c r="E20" t="n">
         <v>-0.0858</v>
@@ -1376,7 +1376,7 @@
         <v>-0.0365</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4866</v>
+        <v>-0.5083</v>
       </c>
       <c r="E21" t="n">
         <v>-0.1616</v>
@@ -1422,7 +1422,7 @@
         <v>-0.0603</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.5292</v>
+        <v>-0.5503</v>
       </c>
       <c r="E22" t="n">
         <v>-0.267</v>
@@ -1468,7 +1468,7 @@
         <v>-0.082</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.5679999999999999</v>
+        <v>-0.5886</v>
       </c>
       <c r="E23" t="n">
         <v>-0.3631</v>
@@ -1514,7 +1514,7 @@
         <v>-0.1254</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.6458</v>
+        <v>-0.6652</v>
       </c>
       <c r="E24" t="n">
         <v>-0.5555</v>
@@ -1560,7 +1560,7 @@
         <v>-0.1546</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.698</v>
+        <v>-0.7167</v>
       </c>
       <c r="E25" t="n">
         <v>-0.6848</v>
@@ -1606,7 +1606,7 @@
         <v>-0.156</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.7004</v>
+        <v>-0.7191</v>
       </c>
       <c r="E26" t="n">
         <v>-0.6908</v>
@@ -1652,7 +1652,7 @@
         <v>-0.2647</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.895</v>
+        <v>-0.911</v>
       </c>
       <c r="E27" t="n">
         <v>-1.1724</v>
@@ -1698,7 +1698,7 @@
         <v>-0.2662</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.8976</v>
+        <v>-0.9136</v>
       </c>
       <c r="E28" t="n">
         <v>-1.1789</v>
@@ -1744,7 +1744,7 @@
         <v>-0.3596</v>
       </c>
       <c r="D29" t="n">
-        <v>-1.0648</v>
+        <v>-1.0785</v>
       </c>
       <c r="E29" t="n">
         <v>-1.5928</v>
@@ -1790,7 +1790,7 @@
         <v>-0.6484</v>
       </c>
       <c r="D30" t="n">
-        <v>-1.5815</v>
+        <v>-1.588</v>
       </c>
       <c r="E30" t="n">
         <v>-2.8717</v>
@@ -1836,7 +1836,7 @@
         <v>-0.8445</v>
       </c>
       <c r="D31" t="n">
-        <v>-1.9324</v>
+        <v>-1.934</v>
       </c>
       <c r="E31" t="n">
         <v>-3.7403</v>

--- a/database/event/4566/event_4566_evp_summary.xlsx
+++ b/database/event/4566/event_4566_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.678599999999999</v>
+        <v>8.7082</v>
       </c>
       <c r="C2" t="n">
-        <v>2.1854</v>
+        <v>1.9663</v>
       </c>
       <c r="D2" t="n">
-        <v>3.412</v>
+        <v>3.2933</v>
       </c>
       <c r="E2" t="n">
-        <v>9.678599999999999</v>
+        <v>8.7082</v>
       </c>
       <c r="F2" t="n">
-        <v>4.8663</v>
+        <v>4.4518</v>
       </c>
       <c r="G2" t="n">
-        <v>4.8123</v>
+        <v>4.2564</v>
       </c>
       <c r="H2" t="n">
-        <v>7.6156</v>
+        <v>13.1512</v>
       </c>
       <c r="I2" t="n">
-        <v>6.1727</v>
+        <v>6.838</v>
       </c>
       <c r="J2" t="n">
-        <v>4.8123</v>
+        <v>4.2564</v>
       </c>
       <c r="K2" t="n">
         <v>286</v>
@@ -529,7 +529,7 @@
         <v>142</v>
       </c>
       <c r="M2" t="n">
-        <v>10.985</v>
+        <v>11.0944</v>
       </c>
       <c r="N2" t="n">
         <v>428</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.1665</v>
+        <v>5.7059</v>
       </c>
       <c r="C3" t="n">
-        <v>1.3924</v>
+        <v>1.2884</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0128</v>
+        <v>1.9379</v>
       </c>
       <c r="E3" t="n">
-        <v>6.1665</v>
+        <v>5.7059</v>
       </c>
       <c r="F3" t="n">
-        <v>4.6406</v>
+        <v>4.4217</v>
       </c>
       <c r="G3" t="n">
-        <v>1.5259</v>
+        <v>1.2842</v>
       </c>
       <c r="H3" t="n">
-        <v>6.1098</v>
+        <v>10.093</v>
       </c>
       <c r="I3" t="n">
-        <v>4.9522</v>
+        <v>5.2479</v>
       </c>
       <c r="J3" t="n">
-        <v>1.5259</v>
+        <v>1.2842</v>
       </c>
       <c r="K3" t="n">
         <v>257</v>
@@ -575,7 +575,7 @@
         <v>102</v>
       </c>
       <c r="M3" t="n">
-        <v>6.4781</v>
+        <v>6.5321</v>
       </c>
       <c r="N3" t="n">
         <v>359</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.3315</v>
+        <v>3.9677</v>
       </c>
       <c r="C4" t="n">
-        <v>0.978</v>
+        <v>0.8959</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2818</v>
+        <v>1.1532</v>
       </c>
       <c r="E4" t="n">
-        <v>4.3315</v>
+        <v>3.9677</v>
       </c>
       <c r="F4" t="n">
-        <v>3.8</v>
+        <v>3.3824</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5315</v>
+        <v>0.5853</v>
       </c>
       <c r="H4" t="n">
-        <v>3.8</v>
+        <v>6.4311</v>
       </c>
       <c r="I4" t="n">
-        <v>3.08</v>
+        <v>3.3439</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5315</v>
+        <v>0.5853</v>
       </c>
       <c r="K4" t="n">
         <v>286</v>
@@ -621,7 +621,7 @@
         <v>142</v>
       </c>
       <c r="M4" t="n">
-        <v>3.6115</v>
+        <v>3.9292</v>
       </c>
       <c r="N4" t="n">
         <v>428</v>
@@ -630,127 +630,127 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CeRq</t>
+          <t>sergej</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.0654</v>
+        <v>3.9604</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9179</v>
+        <v>0.8942</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1757</v>
+        <v>1.1499</v>
       </c>
       <c r="E5" t="n">
-        <v>4.0654</v>
+        <v>3.9604</v>
       </c>
       <c r="F5" t="n">
-        <v>4.0282</v>
+        <v>2.7632</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0372</v>
+        <v>1.1972</v>
       </c>
       <c r="H5" t="n">
-        <v>4.0282</v>
+        <v>4.2496</v>
       </c>
       <c r="I5" t="n">
-        <v>3.265</v>
+        <v>2.2096</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0372</v>
+        <v>1.1972</v>
       </c>
       <c r="K5" t="n">
-        <v>269</v>
+        <v>255</v>
       </c>
       <c r="L5" t="n">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="M5" t="n">
-        <v>3.3022</v>
+        <v>3.4068</v>
       </c>
       <c r="N5" t="n">
-        <v>317</v>
+        <v>343</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>sergej</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.8349</v>
+        <v>3.8983</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8659</v>
+        <v>0.8802</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0839</v>
+        <v>1.1219</v>
       </c>
       <c r="E6" t="n">
-        <v>3.8349</v>
+        <v>3.8983</v>
       </c>
       <c r="F6" t="n">
-        <v>2.5805</v>
+        <v>2.4659</v>
       </c>
       <c r="G6" t="n">
-        <v>1.2544</v>
+        <v>1.4324</v>
       </c>
       <c r="H6" t="n">
-        <v>2.5805</v>
+        <v>3.202</v>
       </c>
       <c r="I6" t="n">
-        <v>2.0916</v>
+        <v>1.6649</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2544</v>
+        <v>1.4324</v>
       </c>
       <c r="K6" t="n">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="L6" t="n">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="M6" t="n">
-        <v>3.346</v>
+        <v>3.0973</v>
       </c>
       <c r="N6" t="n">
-        <v>343</v>
+        <v>359</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>CeRq</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.8276</v>
+        <v>3.6587</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8642</v>
+        <v>0.8260999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>1.081</v>
+        <v>1.0137</v>
       </c>
       <c r="E7" t="n">
-        <v>3.8276</v>
+        <v>3.6587</v>
       </c>
       <c r="F7" t="n">
-        <v>4.1656</v>
+        <v>3.565</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.338</v>
+        <v>0.09370000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>4.1985</v>
+        <v>7.0747</v>
       </c>
       <c r="I7" t="n">
-        <v>3.403</v>
+        <v>3.6785</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.338</v>
+        <v>0.09370000000000001</v>
       </c>
       <c r="K7" t="n">
         <v>269</v>
@@ -759,7 +759,7 @@
         <v>48</v>
       </c>
       <c r="M7" t="n">
-        <v>3.065</v>
+        <v>3.7722</v>
       </c>
       <c r="N7" t="n">
         <v>317</v>
@@ -768,219 +768,219 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>NBK-</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.676</v>
+        <v>3.6241</v>
       </c>
       <c r="C8" t="n">
-        <v>0.83</v>
+        <v>0.8183</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0206</v>
+        <v>0.9981</v>
       </c>
       <c r="E8" t="n">
-        <v>3.676</v>
+        <v>3.6241</v>
       </c>
       <c r="F8" t="n">
-        <v>1.8159</v>
+        <v>2.4465</v>
       </c>
       <c r="G8" t="n">
-        <v>1.8601</v>
+        <v>1.1776</v>
       </c>
       <c r="H8" t="n">
-        <v>1.8159</v>
+        <v>3.1335</v>
       </c>
       <c r="I8" t="n">
-        <v>1.4718</v>
+        <v>1.6293</v>
       </c>
       <c r="J8" t="n">
-        <v>1.8601</v>
+        <v>1.1776</v>
       </c>
       <c r="K8" t="n">
-        <v>257</v>
+        <v>286</v>
       </c>
       <c r="L8" t="n">
-        <v>102</v>
+        <v>142</v>
       </c>
       <c r="M8" t="n">
-        <v>3.3319</v>
+        <v>2.8069</v>
       </c>
       <c r="N8" t="n">
-        <v>359</v>
+        <v>428</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>Brehze</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.5271</v>
+        <v>3.5426</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7964</v>
+        <v>0.7999000000000001</v>
       </c>
       <c r="D9" t="n">
         <v>0.9613</v>
       </c>
       <c r="E9" t="n">
-        <v>3.5271</v>
+        <v>3.5426</v>
       </c>
       <c r="F9" t="n">
-        <v>4.2657</v>
+        <v>3.2054</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.7386</v>
+        <v>0.3372</v>
       </c>
       <c r="H9" t="n">
-        <v>4.6012</v>
+        <v>5.8076</v>
       </c>
       <c r="I9" t="n">
-        <v>3.7294</v>
+        <v>3.0197</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.7386</v>
+        <v>0.3372</v>
       </c>
       <c r="K9" t="n">
-        <v>286</v>
+        <v>269</v>
       </c>
       <c r="L9" t="n">
-        <v>142</v>
+        <v>48</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9908</v>
+        <v>3.3569</v>
       </c>
       <c r="N9" t="n">
-        <v>428</v>
+        <v>317</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Brehze</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.9877</v>
+        <v>3.4898</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6746</v>
+        <v>0.788</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7464</v>
+        <v>0.9375</v>
       </c>
       <c r="E10" t="n">
-        <v>2.9877</v>
+        <v>3.4898</v>
       </c>
       <c r="F10" t="n">
-        <v>2.6744</v>
+        <v>3.1921</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3133</v>
+        <v>0.2977</v>
       </c>
       <c r="H10" t="n">
-        <v>2.6744</v>
+        <v>5.7605</v>
       </c>
       <c r="I10" t="n">
-        <v>2.1676</v>
+        <v>2.9952</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3133</v>
+        <v>0.2977</v>
       </c>
       <c r="K10" t="n">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="L10" t="n">
-        <v>48</v>
+        <v>102</v>
       </c>
       <c r="M10" t="n">
-        <v>2.4809</v>
+        <v>3.2929</v>
       </c>
       <c r="N10" t="n">
-        <v>317</v>
+        <v>359</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NBK-</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.8097</v>
+        <v>3.4455</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6344</v>
+        <v>0.778</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6755</v>
+        <v>0.9175</v>
       </c>
       <c r="E11" t="n">
-        <v>2.8097</v>
+        <v>3.4455</v>
       </c>
       <c r="F11" t="n">
-        <v>1.6384</v>
+        <v>3.7036</v>
       </c>
       <c r="G11" t="n">
-        <v>1.1713</v>
+        <v>-0.2581</v>
       </c>
       <c r="H11" t="n">
-        <v>1.6384</v>
+        <v>7.5628</v>
       </c>
       <c r="I11" t="n">
-        <v>1.328</v>
+        <v>3.9323</v>
       </c>
       <c r="J11" t="n">
-        <v>1.1713</v>
+        <v>-0.2581</v>
       </c>
       <c r="K11" t="n">
-        <v>286</v>
+        <v>269</v>
       </c>
       <c r="L11" t="n">
-        <v>142</v>
+        <v>48</v>
       </c>
       <c r="M11" t="n">
-        <v>2.4993</v>
+        <v>3.6742</v>
       </c>
       <c r="N11" t="n">
-        <v>428</v>
+        <v>317</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.7886</v>
+        <v>3.4275</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6296</v>
+        <v>0.7739</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6671</v>
+        <v>0.9093</v>
       </c>
       <c r="E12" t="n">
-        <v>2.7886</v>
+        <v>3.4275</v>
       </c>
       <c r="F12" t="n">
-        <v>2.6137</v>
+        <v>2.2073</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1749</v>
+        <v>1.2202</v>
       </c>
       <c r="H12" t="n">
-        <v>2.6137</v>
+        <v>2.291</v>
       </c>
       <c r="I12" t="n">
-        <v>2.1185</v>
+        <v>1.1912</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1749</v>
+        <v>1.2202</v>
       </c>
       <c r="K12" t="n">
         <v>257</v>
@@ -989,7 +989,7 @@
         <v>102</v>
       </c>
       <c r="M12" t="n">
-        <v>2.2934</v>
+        <v>2.4114</v>
       </c>
       <c r="N12" t="n">
         <v>359</v>
@@ -998,415 +998,415 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>freakazoid</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.1756</v>
+        <v>3.2577</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4912</v>
+        <v>0.7356</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4228</v>
+        <v>0.8327</v>
       </c>
       <c r="E13" t="n">
-        <v>2.1756</v>
+        <v>3.2577</v>
       </c>
       <c r="F13" t="n">
-        <v>2.1756</v>
+        <v>3.7645</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>-0.5068</v>
       </c>
       <c r="H13" t="n">
-        <v>2.1756</v>
+        <v>7.7774</v>
       </c>
       <c r="I13" t="n">
-        <v>2.1756</v>
+        <v>4.0439</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>-0.5068</v>
       </c>
       <c r="K13" t="n">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>142</v>
       </c>
       <c r="M13" t="n">
-        <v>2.1756</v>
+        <v>3.5371</v>
       </c>
       <c r="N13" t="n">
-        <v>277</v>
+        <v>428</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>jks</t>
+          <t>RpK</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.9594</v>
+        <v>2.5517</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4424</v>
+        <v>0.5762</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3367</v>
+        <v>0.514</v>
       </c>
       <c r="E14" t="n">
-        <v>1.9594</v>
+        <v>2.5517</v>
       </c>
       <c r="F14" t="n">
-        <v>1.9594</v>
+        <v>2.3174</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>0.2343</v>
       </c>
       <c r="H14" t="n">
-        <v>1.9594</v>
+        <v>2.6789</v>
       </c>
       <c r="I14" t="n">
-        <v>1.9594</v>
+        <v>1.3929</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>0.2343</v>
       </c>
       <c r="K14" t="n">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>142</v>
       </c>
       <c r="M14" t="n">
-        <v>1.9594</v>
+        <v>1.6272</v>
       </c>
       <c r="N14" t="n">
-        <v>280</v>
+        <v>428</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>jks</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.8863</v>
+        <v>2.4686</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4259</v>
+        <v>0.5574</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3076</v>
+        <v>0.4764</v>
       </c>
       <c r="E15" t="n">
-        <v>1.8863</v>
+        <v>2.4686</v>
       </c>
       <c r="F15" t="n">
-        <v>2.7983</v>
+        <v>2.4686</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.912</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2.7983</v>
+        <v>2.4686</v>
       </c>
       <c r="I15" t="n">
-        <v>2.2681</v>
+        <v>2.4686</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.912</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="L15" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.3561</v>
+        <v>2.4686</v>
       </c>
       <c r="N15" t="n">
-        <v>317</v>
+        <v>280</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>allu</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.6203</v>
+        <v>2.3695</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3659</v>
+        <v>0.535</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2016</v>
+        <v>0.4317</v>
       </c>
       <c r="E16" t="n">
-        <v>1.6203</v>
+        <v>2.3695</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3754</v>
+        <v>2.2741</v>
       </c>
       <c r="G16" t="n">
-        <v>1.2449</v>
+        <v>0.0954</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3754</v>
+        <v>2.5264</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3043</v>
+        <v>1.3136</v>
       </c>
       <c r="J16" t="n">
-        <v>1.2449</v>
+        <v>0.0954</v>
       </c>
       <c r="K16" t="n">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="L16" t="n">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="M16" t="n">
-        <v>1.5492</v>
+        <v>1.409</v>
       </c>
       <c r="N16" t="n">
-        <v>359</v>
+        <v>343</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>RpK</t>
+          <t>freakazoid</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.2534</v>
+        <v>2.3615</v>
       </c>
       <c r="C17" t="n">
-        <v>0.283</v>
+        <v>0.5332</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0554</v>
+        <v>0.4281</v>
       </c>
       <c r="E17" t="n">
-        <v>1.2534</v>
+        <v>2.3615</v>
       </c>
       <c r="F17" t="n">
-        <v>1.3713</v>
+        <v>2.3615</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.1179</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.3713</v>
+        <v>2.3615</v>
       </c>
       <c r="I17" t="n">
-        <v>1.1115</v>
+        <v>2.3615</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.1179</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="L17" t="n">
-        <v>142</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.9935999999999999</v>
+        <v>2.3615</v>
       </c>
       <c r="N17" t="n">
-        <v>428</v>
+        <v>277</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>allu</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.0036</v>
+        <v>2.2971</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2266</v>
+        <v>0.5187</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0441</v>
+        <v>0.399</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0036</v>
+        <v>2.2971</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0336</v>
+        <v>2.89</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.03</v>
+        <v>-0.5929</v>
       </c>
       <c r="H18" t="n">
-        <v>1.0336</v>
+        <v>4.6962</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8378</v>
+        <v>2.4418</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.03</v>
+        <v>-0.5929</v>
       </c>
       <c r="K18" t="n">
-        <v>255</v>
+        <v>269</v>
       </c>
       <c r="L18" t="n">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="M18" t="n">
-        <v>0.8078</v>
+        <v>1.8489</v>
       </c>
       <c r="N18" t="n">
-        <v>343</v>
+        <v>317</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>smooya</t>
+          <t>Aerial</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.5396</v>
+        <v>0.9441000000000001</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1218</v>
+        <v>0.2132</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2289</v>
+        <v>-0.2118</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5396</v>
+        <v>0.9441000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5396</v>
+        <v>0.7406</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>0.2035</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5396</v>
+        <v>0.7406</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5396</v>
+        <v>0.3851</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>0.2035</v>
       </c>
       <c r="K19" t="n">
-        <v>280</v>
+        <v>255</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="M19" t="n">
-        <v>0.5396</v>
+        <v>0.5886</v>
       </c>
       <c r="N19" t="n">
-        <v>280</v>
+        <v>343</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>WARDELL</t>
+          <t>smooya</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.0858</v>
+        <v>0.802</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.0194</v>
+        <v>0.1811</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4781</v>
+        <v>-0.276</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0858</v>
+        <v>0.802</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0858</v>
+        <v>0.802</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.0858</v>
+        <v>0.802</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0858</v>
+        <v>0.802</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.0858</v>
+        <v>0.802</v>
       </c>
       <c r="N20" t="n">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Aerial</t>
+          <t>daps</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.1616</v>
+        <v>0.6105</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.0365</v>
+        <v>0.1378</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5083</v>
+        <v>-0.3624</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.1616</v>
+        <v>0.6105</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1967</v>
+        <v>1.2853</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0351</v>
+        <v>-0.6748</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.1967</v>
+        <v>1.2853</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1594</v>
+        <v>0.6683</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0351</v>
+        <v>-0.6748</v>
       </c>
       <c r="K21" t="n">
-        <v>255</v>
+        <v>269</v>
       </c>
       <c r="L21" t="n">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1243</v>
+        <v>-0.00649999999999995</v>
       </c>
       <c r="N21" t="n">
-        <v>343</v>
+        <v>317</v>
       </c>
     </row>
     <row r="22">
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.267</v>
+        <v>0.5288</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.0603</v>
+        <v>0.1194</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.5503</v>
+        <v>-0.3993</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.267</v>
+        <v>0.5288</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.267</v>
+        <v>0.5288</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.267</v>
+        <v>0.5288</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.267</v>
+        <v>0.5288</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.267</v>
+        <v>0.5288</v>
       </c>
       <c r="N22" t="n">
         <v>280</v>
@@ -1458,32 +1458,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>steel</t>
+          <t>WARDELL</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.3631</v>
+        <v>0.3944</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.082</v>
+        <v>0.0891</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.5886</v>
+        <v>-0.46</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.3631</v>
+        <v>0.3944</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.3631</v>
+        <v>0.3944</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.3631</v>
+        <v>0.3944</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.3631</v>
+        <v>0.3944</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.3631</v>
+        <v>0.3944</v>
       </c>
       <c r="N23" t="n">
         <v>277</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.5555</v>
+        <v>0.3452</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.1254</v>
+        <v>0.0779</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.6652</v>
+        <v>-0.4822</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.5555</v>
+        <v>0.3452</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.5555</v>
+        <v>0.3452</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.5555</v>
+        <v>0.3452</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.5555</v>
+        <v>0.3452</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.5555</v>
+        <v>0.3452</v>
       </c>
       <c r="N24" t="n">
         <v>280</v>
@@ -1550,47 +1550,47 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AZR</t>
+          <t>steel</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.6848</v>
+        <v>0.2927</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.1546</v>
+        <v>0.06610000000000001</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.7167</v>
+        <v>-0.5059</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.6848</v>
+        <v>0.2927</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.6848</v>
+        <v>0.2927</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.6848</v>
+        <v>0.2927</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.6848</v>
+        <v>0.2927</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.6848</v>
+        <v>0.2927</v>
       </c>
       <c r="N25" t="n">
-        <v>280</v>
+        <v>277</v>
       </c>
     </row>
     <row r="26">
@@ -1600,31 +1600,31 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.6908</v>
+        <v>0.1164</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.156</v>
+        <v>0.0263</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.7191</v>
+        <v>-0.5855</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.6908</v>
+        <v>0.1164</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.4311</v>
+        <v>0.1942</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.2597</v>
+        <v>-0.07779999999999999</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.4311</v>
+        <v>0.1942</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.3494</v>
+        <v>0.101</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.2597</v>
+        <v>-0.07779999999999999</v>
       </c>
       <c r="K26" t="n">
         <v>255</v>
@@ -1633,7 +1633,7 @@
         <v>88</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.6091</v>
+        <v>0.02320000000000001</v>
       </c>
       <c r="N26" t="n">
         <v>343</v>
@@ -1642,93 +1642,93 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>AZR</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-1.1724</v>
+        <v>-0.02</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.2647</v>
+        <v>-0.0045</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.911</v>
+        <v>-0.647</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.1724</v>
+        <v>-0.02</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.3506</v>
+        <v>-0.02</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1782</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-1.3506</v>
+        <v>-0.02</v>
       </c>
       <c r="I27" t="n">
-        <v>-1.0947</v>
+        <v>-0.02</v>
       </c>
       <c r="J27" t="n">
-        <v>0.1782</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>257</v>
+        <v>280</v>
       </c>
       <c r="L27" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.9165</v>
+        <v>-0.02</v>
       </c>
       <c r="N27" t="n">
-        <v>359</v>
+        <v>280</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>daps</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-1.1789</v>
+        <v>-0.4124</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.2662</v>
+        <v>-0.0931</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.9136</v>
+        <v>-0.8242</v>
       </c>
       <c r="E28" t="n">
-        <v>-1.1789</v>
+        <v>-0.4124</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.1812</v>
+        <v>-1.0018</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.9977</v>
+        <v>0.5894</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.1812</v>
+        <v>-1.0018</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.1469</v>
+        <v>-0.5209</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.9977</v>
+        <v>0.5894</v>
       </c>
       <c r="K28" t="n">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="L28" t="n">
-        <v>48</v>
+        <v>102</v>
       </c>
       <c r="M28" t="n">
-        <v>-1.1446</v>
+        <v>0.06850000000000001</v>
       </c>
       <c r="N28" t="n">
-        <v>317</v>
+        <v>359</v>
       </c>
     </row>
     <row r="29">
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-1.5928</v>
+        <v>-0.9492</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.3596</v>
+        <v>-0.2143</v>
       </c>
       <c r="D29" t="n">
-        <v>-1.0785</v>
+        <v>-1.0665</v>
       </c>
       <c r="E29" t="n">
-        <v>-1.5928</v>
+        <v>-0.9492</v>
       </c>
       <c r="F29" t="n">
-        <v>-1.5928</v>
+        <v>-0.9492</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-1.5928</v>
+        <v>-0.9492</v>
       </c>
       <c r="I29" t="n">
-        <v>-1.5928</v>
+        <v>-0.9492</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-1.5928</v>
+        <v>-0.9492</v>
       </c>
       <c r="N29" t="n">
         <v>277</v>
@@ -1784,31 +1784,31 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-2.8717</v>
+        <v>-2.3648</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.6484</v>
+        <v>-0.534</v>
       </c>
       <c r="D30" t="n">
-        <v>-1.588</v>
+        <v>-1.7056</v>
       </c>
       <c r="E30" t="n">
-        <v>-2.8717</v>
+        <v>-2.3648</v>
       </c>
       <c r="F30" t="n">
-        <v>-2.2042</v>
+        <v>-1.9986</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.6675</v>
+        <v>-0.3662</v>
       </c>
       <c r="H30" t="n">
-        <v>-2.2042</v>
+        <v>-1.9986</v>
       </c>
       <c r="I30" t="n">
-        <v>-1.7866</v>
+        <v>-1.0392</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.6675</v>
+        <v>-0.3662</v>
       </c>
       <c r="K30" t="n">
         <v>255</v>
@@ -1817,7 +1817,7 @@
         <v>88</v>
       </c>
       <c r="M30" t="n">
-        <v>-2.4541</v>
+        <v>-1.4054</v>
       </c>
       <c r="N30" t="n">
         <v>343</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-3.7403</v>
+        <v>-2.7489</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.8445</v>
+        <v>-0.6207</v>
       </c>
       <c r="D31" t="n">
-        <v>-1.934</v>
+        <v>-1.879</v>
       </c>
       <c r="E31" t="n">
-        <v>-3.7403</v>
+        <v>-2.7489</v>
       </c>
       <c r="F31" t="n">
-        <v>-3.7403</v>
+        <v>-2.7489</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-3.7403</v>
+        <v>-2.7489</v>
       </c>
       <c r="I31" t="n">
-        <v>-3.7403</v>
+        <v>-2.7489</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-3.7403</v>
+        <v>-2.7489</v>
       </c>
       <c r="N31" t="n">
         <v>277</v>
@@ -1969,10 +1969,10 @@
         <v>1.61</v>
       </c>
       <c r="I2" t="n">
-        <v>1.4171</v>
+        <v>1.2698</v>
       </c>
       <c r="J2" t="n">
-        <v>35.4275</v>
+        <v>31.745</v>
       </c>
     </row>
     <row r="3">
@@ -2009,10 +2009,10 @@
         <v>1.29</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7432</v>
+        <v>0.7608</v>
       </c>
       <c r="J3" t="n">
-        <v>18.58</v>
+        <v>19.02</v>
       </c>
     </row>
     <row r="4">
@@ -2049,10 +2049,10 @@
         <v>1.19</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4623</v>
+        <v>0.5295</v>
       </c>
       <c r="J4" t="n">
-        <v>11.5575</v>
+        <v>13.2375</v>
       </c>
     </row>
     <row r="5">
@@ -2089,10 +2089,10 @@
         <v>1.06</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0994</v>
+        <v>0.1744</v>
       </c>
       <c r="J5" t="n">
-        <v>2.485</v>
+        <v>4.36</v>
       </c>
     </row>
     <row r="6">
@@ -2129,10 +2129,10 @@
         <v>1.05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.06759999999999999</v>
+        <v>0.1425</v>
       </c>
       <c r="J6" t="n">
-        <v>1.69</v>
+        <v>3.5625</v>
       </c>
     </row>
     <row r="7">
@@ -2169,10 +2169,10 @@
         <v>1.04</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1939</v>
+        <v>0.1777</v>
       </c>
       <c r="J7" t="n">
-        <v>4.8475</v>
+        <v>4.4425</v>
       </c>
     </row>
     <row r="8">
@@ -2209,10 +2209,10 @@
         <v>0.99</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0569</v>
+        <v>0.0132</v>
       </c>
       <c r="J8" t="n">
-        <v>1.4225</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="9">
@@ -2249,10 +2249,10 @@
         <v>0.86</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1952</v>
+        <v>-0.1567</v>
       </c>
       <c r="J9" t="n">
-        <v>-4.88</v>
+        <v>-3.9175</v>
       </c>
     </row>
     <row r="10">
@@ -2289,10 +2289,10 @@
         <v>0.68</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5011</v>
+        <v>-0.3306</v>
       </c>
       <c r="J10" t="n">
-        <v>-12.5275</v>
+        <v>-8.265000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -2329,10 +2329,10 @@
         <v>0.47</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7725</v>
+        <v>-0.526</v>
       </c>
       <c r="J11" t="n">
-        <v>-19.3125</v>
+        <v>-13.15</v>
       </c>
     </row>
     <row r="12">
@@ -2369,10 +2369,10 @@
         <v>1.3</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8867</v>
+        <v>0.8573</v>
       </c>
       <c r="J12" t="n">
-        <v>25.7143</v>
+        <v>24.8617</v>
       </c>
     </row>
     <row r="13">
@@ -2409,10 +2409,10 @@
         <v>1.26</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7942</v>
+        <v>0.7589</v>
       </c>
       <c r="J13" t="n">
-        <v>23.0318</v>
+        <v>22.0081</v>
       </c>
     </row>
     <row r="14">
@@ -2449,10 +2449,10 @@
         <v>0.93</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3219</v>
+        <v>-0.2688</v>
       </c>
       <c r="J14" t="n">
-        <v>-9.335100000000001</v>
+        <v>-7.7952</v>
       </c>
     </row>
     <row r="15">
@@ -2489,10 +2489,10 @@
         <v>0.87</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4979</v>
+        <v>-0.443</v>
       </c>
       <c r="J15" t="n">
-        <v>-14.4391</v>
+        <v>-12.847</v>
       </c>
     </row>
     <row r="16">
@@ -2529,10 +2529,10 @@
         <v>0.8</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6798</v>
+        <v>-0.6307</v>
       </c>
       <c r="J16" t="n">
-        <v>-19.7142</v>
+        <v>-18.2903</v>
       </c>
     </row>
     <row r="17">
@@ -2569,10 +2569,10 @@
         <v>1.28</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4872</v>
+        <v>0.575</v>
       </c>
       <c r="J17" t="n">
-        <v>14.1288</v>
+        <v>16.675</v>
       </c>
     </row>
     <row r="18">
@@ -2609,10 +2609,10 @@
         <v>1.2</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3767</v>
+        <v>0.4325</v>
       </c>
       <c r="J18" t="n">
-        <v>10.9243</v>
+        <v>12.5425</v>
       </c>
     </row>
     <row r="19">
@@ -2649,10 +2649,10 @@
         <v>0.92</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1993</v>
+        <v>-0.1138</v>
       </c>
       <c r="J19" t="n">
-        <v>-5.7797</v>
+        <v>-3.3002</v>
       </c>
     </row>
     <row r="20">
@@ -2689,10 +2689,10 @@
         <v>0.87</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.283</v>
+        <v>-0.1691</v>
       </c>
       <c r="J20" t="n">
-        <v>-8.207000000000001</v>
+        <v>-4.9039</v>
       </c>
     </row>
     <row r="21">
@@ -2729,10 +2729,10 @@
         <v>0.83</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3444</v>
+        <v>-0.2109</v>
       </c>
       <c r="J21" t="n">
-        <v>-9.9876</v>
+        <v>-6.1161</v>
       </c>
     </row>
     <row r="22">
@@ -2769,10 +2769,10 @@
         <v>1.6</v>
       </c>
       <c r="I22" t="n">
-        <v>1.4251</v>
+        <v>0.999</v>
       </c>
       <c r="J22" t="n">
-        <v>34.2024</v>
+        <v>23.976</v>
       </c>
     </row>
     <row r="23">
@@ -2809,10 +2809,10 @@
         <v>1.17</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4473</v>
+        <v>0.4263</v>
       </c>
       <c r="J23" t="n">
-        <v>10.7352</v>
+        <v>10.2312</v>
       </c>
     </row>
     <row r="24">
@@ -2849,10 +2849,10 @@
         <v>1.09</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2148</v>
+        <v>0.2778</v>
       </c>
       <c r="J24" t="n">
-        <v>5.1552</v>
+        <v>6.6672</v>
       </c>
     </row>
     <row r="25">
@@ -2889,10 +2889,10 @@
         <v>1.03</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0214</v>
+        <v>0.0885</v>
       </c>
       <c r="J25" t="n">
-        <v>0.5135999999999999</v>
+        <v>2.124</v>
       </c>
     </row>
     <row r="26">
@@ -2929,10 +2929,10 @@
         <v>1.03</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0214</v>
+        <v>0.0885</v>
       </c>
       <c r="J26" t="n">
-        <v>0.5135999999999999</v>
+        <v>2.124</v>
       </c>
     </row>
     <row r="27">
@@ -2969,10 +2969,10 @@
         <v>1.34</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5783</v>
+        <v>0.5464</v>
       </c>
       <c r="J27" t="n">
-        <v>13.8792</v>
+        <v>13.1136</v>
       </c>
     </row>
     <row r="28">
@@ -3009,10 +3009,10 @@
         <v>1.11</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2524</v>
+        <v>0.272</v>
       </c>
       <c r="J28" t="n">
-        <v>6.0576</v>
+        <v>6.528</v>
       </c>
     </row>
     <row r="29">
@@ -3049,10 +3049,10 @@
         <v>0.99</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.0216</v>
+        <v>-0.0194</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.5184</v>
+        <v>-0.4656</v>
       </c>
     </row>
     <row r="30">
@@ -3089,10 +3089,10 @@
         <v>0.84</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.319</v>
+        <v>-0.196</v>
       </c>
       <c r="J30" t="n">
-        <v>-7.656</v>
+        <v>-4.704</v>
       </c>
     </row>
     <row r="31">
@@ -3129,10 +3129,10 @@
         <v>0.62</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.6183</v>
+        <v>-0.4087</v>
       </c>
       <c r="J31" t="n">
-        <v>-14.8392</v>
+        <v>-9.8088</v>
       </c>
     </row>
     <row r="32">
@@ -3169,10 +3169,10 @@
         <v>1.51</v>
       </c>
       <c r="I32" t="n">
-        <v>1.1677</v>
+        <v>0.8493000000000001</v>
       </c>
       <c r="J32" t="n">
-        <v>28.0248</v>
+        <v>20.3832</v>
       </c>
     </row>
     <row r="33">
@@ -3209,10 +3209,10 @@
         <v>1.43</v>
       </c>
       <c r="I33" t="n">
-        <v>0.999</v>
+        <v>0.7507</v>
       </c>
       <c r="J33" t="n">
-        <v>23.976</v>
+        <v>18.0168</v>
       </c>
     </row>
     <row r="34">
@@ -3249,10 +3249,10 @@
         <v>1.4</v>
       </c>
       <c r="I34" t="n">
-        <v>0.9315</v>
+        <v>0.7134</v>
       </c>
       <c r="J34" t="n">
-        <v>22.356</v>
+        <v>17.1216</v>
       </c>
     </row>
     <row r="35">
@@ -3289,10 +3289,10 @@
         <v>1.26</v>
       </c>
       <c r="I35" t="n">
-        <v>0.5774</v>
+        <v>0.534</v>
       </c>
       <c r="J35" t="n">
-        <v>13.8576</v>
+        <v>12.816</v>
       </c>
     </row>
     <row r="36">
@@ -3329,10 +3329,10 @@
         <v>1.17</v>
       </c>
       <c r="I36" t="n">
-        <v>0.3592</v>
+        <v>0.4051</v>
       </c>
       <c r="J36" t="n">
-        <v>8.620799999999999</v>
+        <v>9.7224</v>
       </c>
     </row>
     <row r="37">
@@ -3369,10 +3369,10 @@
         <v>0.83</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.2152</v>
+        <v>-0.1783</v>
       </c>
       <c r="J37" t="n">
-        <v>-5.1648</v>
+        <v>-4.2792</v>
       </c>
     </row>
     <row r="38">
@@ -3409,10 +3409,10 @@
         <v>0.8</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.265</v>
+        <v>-0.2092</v>
       </c>
       <c r="J38" t="n">
-        <v>-6.36</v>
+        <v>-5.0208</v>
       </c>
     </row>
     <row r="39">
@@ -3449,10 +3449,10 @@
         <v>0.77</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.3164</v>
+        <v>-0.2387</v>
       </c>
       <c r="J39" t="n">
-        <v>-7.5936</v>
+        <v>-5.7288</v>
       </c>
     </row>
     <row r="40">
@@ -3489,10 +3489,10 @@
         <v>0.74</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.3794</v>
+        <v>-0.2661</v>
       </c>
       <c r="J40" t="n">
-        <v>-9.105600000000001</v>
+        <v>-6.3864</v>
       </c>
     </row>
     <row r="41">
@@ -3529,10 +3529,10 @@
         <v>0.6</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.593</v>
+        <v>-0.3969</v>
       </c>
       <c r="J41" t="n">
-        <v>-14.232</v>
+        <v>-9.525600000000001</v>
       </c>
     </row>
     <row r="42">
@@ -3569,10 +3569,10 @@
         <v>1.15</v>
       </c>
       <c r="I42" t="n">
-        <v>0.3301</v>
+        <v>0.2782</v>
       </c>
       <c r="J42" t="n">
-        <v>9.903</v>
+        <v>8.346</v>
       </c>
     </row>
     <row r="43">
@@ -3609,10 +3609,10 @@
         <v>1.06</v>
       </c>
       <c r="I43" t="n">
-        <v>0.179</v>
+        <v>0.1348</v>
       </c>
       <c r="J43" t="n">
-        <v>5.37</v>
+        <v>4.044</v>
       </c>
     </row>
     <row r="44">
@@ -3649,10 +3649,10 @@
         <v>1.03</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1183</v>
+        <v>0.0799</v>
       </c>
       <c r="J44" t="n">
-        <v>3.549</v>
+        <v>2.397</v>
       </c>
     </row>
     <row r="45">
@@ -3689,10 +3689,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.3538</v>
+        <v>-0.222</v>
       </c>
       <c r="J45" t="n">
-        <v>-10.614</v>
+        <v>-6.66</v>
       </c>
     </row>
     <row r="46">
@@ -3729,10 +3729,10 @@
         <v>0.66</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.5612</v>
+        <v>-0.3672</v>
       </c>
       <c r="J46" t="n">
-        <v>-16.836</v>
+        <v>-11.016</v>
       </c>
     </row>
     <row r="47">
@@ -3769,10 +3769,10 @@
         <v>1.28</v>
       </c>
       <c r="I47" t="n">
-        <v>0.4473</v>
+        <v>0.3637</v>
       </c>
       <c r="J47" t="n">
-        <v>13.419</v>
+        <v>10.911</v>
       </c>
     </row>
     <row r="48">
@@ -3809,10 +3809,10 @@
         <v>1.22</v>
       </c>
       <c r="I48" t="n">
-        <v>0.3629</v>
+        <v>0.3115</v>
       </c>
       <c r="J48" t="n">
-        <v>10.887</v>
+        <v>9.345000000000001</v>
       </c>
     </row>
     <row r="49">
@@ -3849,10 +3849,10 @@
         <v>1.19</v>
       </c>
       <c r="I49" t="n">
-        <v>0.3175</v>
+        <v>0.2749</v>
       </c>
       <c r="J49" t="n">
-        <v>9.525</v>
+        <v>8.247</v>
       </c>
     </row>
     <row r="50">
@@ -3889,10 +3889,10 @@
         <v>1.04</v>
       </c>
       <c r="I50" t="n">
-        <v>0.0439</v>
+        <v>0.0672</v>
       </c>
       <c r="J50" t="n">
-        <v>1.317</v>
+        <v>2.016</v>
       </c>
     </row>
     <row r="51">
@@ -3929,10 +3929,10 @@
         <v>0.98</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.1157</v>
+        <v>-0.05</v>
       </c>
       <c r="J51" t="n">
-        <v>-3.471</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="52">
@@ -3969,10 +3969,10 @@
         <v>2.18</v>
       </c>
       <c r="I52" t="n">
-        <v>2.0713</v>
+        <v>1.642</v>
       </c>
       <c r="J52" t="n">
-        <v>49.7112</v>
+        <v>39.408</v>
       </c>
     </row>
     <row r="53">
@@ -4009,10 +4009,10 @@
         <v>1.27</v>
       </c>
       <c r="I53" t="n">
-        <v>0.617</v>
+        <v>0.5511</v>
       </c>
       <c r="J53" t="n">
-        <v>14.808</v>
+        <v>13.2264</v>
       </c>
     </row>
     <row r="54">
@@ -4049,10 +4049,10 @@
         <v>1.14</v>
       </c>
       <c r="I54" t="n">
-        <v>0.2936</v>
+        <v>0.363</v>
       </c>
       <c r="J54" t="n">
-        <v>7.0464</v>
+        <v>8.712</v>
       </c>
     </row>
     <row r="55">
@@ -4089,10 +4089,10 @@
         <v>1.05</v>
       </c>
       <c r="I55" t="n">
-        <v>0.0396</v>
+        <v>0.1227</v>
       </c>
       <c r="J55" t="n">
-        <v>0.9504</v>
+        <v>2.9448</v>
       </c>
     </row>
     <row r="56">
@@ -4129,10 +4129,10 @@
         <v>0.98</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.2613</v>
+        <v>-0.1744</v>
       </c>
       <c r="J56" t="n">
-        <v>-6.2712</v>
+        <v>-4.1856</v>
       </c>
     </row>
     <row r="57">
@@ -4169,10 +4169,10 @@
         <v>1.23</v>
       </c>
       <c r="I57" t="n">
-        <v>0.4905</v>
+        <v>0.4747</v>
       </c>
       <c r="J57" t="n">
-        <v>11.772</v>
+        <v>11.3928</v>
       </c>
     </row>
     <row r="58">
@@ -4209,10 +4209,10 @@
         <v>0.89</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.1514</v>
+        <v>-0.1269</v>
       </c>
       <c r="J58" t="n">
-        <v>-3.6336</v>
+        <v>-3.0456</v>
       </c>
     </row>
     <row r="59">
@@ -4249,10 +4249,10 @@
         <v>0.79</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.3412</v>
+        <v>-0.2276</v>
       </c>
       <c r="J59" t="n">
-        <v>-8.188800000000001</v>
+        <v>-5.4624</v>
       </c>
     </row>
     <row r="60">
@@ -4289,10 +4289,10 @@
         <v>0.68</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.5067</v>
+        <v>-0.3332</v>
       </c>
       <c r="J60" t="n">
-        <v>-12.1608</v>
+        <v>-7.9968</v>
       </c>
     </row>
     <row r="61">
@@ -4329,10 +4329,10 @@
         <v>0.54</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.6902</v>
+        <v>-0.464</v>
       </c>
       <c r="J61" t="n">
-        <v>-16.5648</v>
+        <v>-11.136</v>
       </c>
     </row>
     <row r="62">
@@ -4369,10 +4369,10 @@
         <v>1.38</v>
       </c>
       <c r="I62" t="n">
-        <v>1.0505</v>
+        <v>0.7483</v>
       </c>
       <c r="J62" t="n">
-        <v>35.717</v>
+        <v>25.4422</v>
       </c>
     </row>
     <row r="63">
@@ -4409,10 +4409,10 @@
         <v>1.16</v>
       </c>
       <c r="I63" t="n">
-        <v>0.5304</v>
+        <v>0.429</v>
       </c>
       <c r="J63" t="n">
-        <v>18.0336</v>
+        <v>14.586</v>
       </c>
     </row>
     <row r="64">
@@ -4449,10 +4449,10 @@
         <v>0.97</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.1971</v>
+        <v>-0.1437</v>
       </c>
       <c r="J64" t="n">
-        <v>-6.7014</v>
+        <v>-4.8858</v>
       </c>
     </row>
     <row r="65">
@@ -4489,10 +4489,10 @@
         <v>0.97</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.1971</v>
+        <v>-0.1437</v>
       </c>
       <c r="J65" t="n">
-        <v>-6.7014</v>
+        <v>-4.8858</v>
       </c>
     </row>
     <row r="66">
@@ -4529,10 +4529,10 @@
         <v>0.79</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.7121</v>
+        <v>-0.6629</v>
       </c>
       <c r="J66" t="n">
-        <v>-24.2114</v>
+        <v>-22.5386</v>
       </c>
     </row>
     <row r="67">
@@ -4569,10 +4569,10 @@
         <v>1.26</v>
       </c>
       <c r="I67" t="n">
-        <v>0.4464</v>
+        <v>0.4476</v>
       </c>
       <c r="J67" t="n">
-        <v>15.1776</v>
+        <v>15.2184</v>
       </c>
     </row>
     <row r="68">
@@ -4609,10 +4609,10 @@
         <v>1.18</v>
       </c>
       <c r="I68" t="n">
-        <v>0.3324</v>
+        <v>0.3639</v>
       </c>
       <c r="J68" t="n">
-        <v>11.3016</v>
+        <v>12.3726</v>
       </c>
     </row>
     <row r="69">
@@ -4649,10 +4649,10 @@
         <v>1.12</v>
       </c>
       <c r="I69" t="n">
-        <v>0.2371</v>
+        <v>0.2723</v>
       </c>
       <c r="J69" t="n">
-        <v>8.061400000000001</v>
+        <v>9.2582</v>
       </c>
     </row>
     <row r="70">
@@ -4689,10 +4689,10 @@
         <v>0.97</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.1159</v>
+        <v>-0.0561</v>
       </c>
       <c r="J70" t="n">
-        <v>-3.9406</v>
+        <v>-1.9074</v>
       </c>
     </row>
     <row r="71">
@@ -4729,10 +4729,10 @@
         <v>0.78</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.4246</v>
+        <v>-0.2659</v>
       </c>
       <c r="J71" t="n">
-        <v>-14.4364</v>
+        <v>-9.0406</v>
       </c>
     </row>
     <row r="72">
@@ -4769,10 +4769,10 @@
         <v>1.63</v>
       </c>
       <c r="I72" t="n">
-        <v>0.862</v>
+        <v>0.7776</v>
       </c>
       <c r="J72" t="n">
-        <v>24.998</v>
+        <v>22.5504</v>
       </c>
     </row>
     <row r="73">
@@ -4809,10 +4809,10 @@
         <v>1.41</v>
       </c>
       <c r="I73" t="n">
-        <v>0.6114000000000001</v>
+        <v>0.5343</v>
       </c>
       <c r="J73" t="n">
-        <v>17.7306</v>
+        <v>15.4947</v>
       </c>
     </row>
     <row r="74">
@@ -4849,10 +4849,10 @@
         <v>1.1</v>
       </c>
       <c r="I74" t="n">
-        <v>0.1526</v>
+        <v>0.1581</v>
       </c>
       <c r="J74" t="n">
-        <v>4.4254</v>
+        <v>4.5849</v>
       </c>
     </row>
     <row r="75">
@@ -4889,10 +4889,10 @@
         <v>0.89</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.2801</v>
+        <v>-0.1612</v>
       </c>
       <c r="J75" t="n">
-        <v>-8.1229</v>
+        <v>-4.6748</v>
       </c>
     </row>
     <row r="76">
@@ -4929,10 +4929,10 @@
         <v>0.71</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.5302</v>
+        <v>-0.3418</v>
       </c>
       <c r="J76" t="n">
-        <v>-15.3758</v>
+        <v>-9.9122</v>
       </c>
     </row>
     <row r="77">
@@ -4969,10 +4969,10 @@
         <v>1.43</v>
       </c>
       <c r="I77" t="n">
-        <v>0.6866</v>
+        <v>0.8445</v>
       </c>
       <c r="J77" t="n">
-        <v>19.9114</v>
+        <v>24.4905</v>
       </c>
     </row>
     <row r="78">
@@ -5009,10 +5009,10 @@
         <v>1.06</v>
       </c>
       <c r="I78" t="n">
-        <v>0.1612</v>
+        <v>0.1648</v>
       </c>
       <c r="J78" t="n">
-        <v>4.6748</v>
+        <v>4.7792</v>
       </c>
     </row>
     <row r="79">
@@ -5049,10 +5049,10 @@
         <v>0.88</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.2571</v>
+        <v>-0.1545</v>
       </c>
       <c r="J79" t="n">
-        <v>-7.4559</v>
+        <v>-4.4805</v>
       </c>
     </row>
     <row r="80">
@@ -5089,10 +5089,10 @@
         <v>0.84</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.3207</v>
+        <v>-0.1967</v>
       </c>
       <c r="J80" t="n">
-        <v>-9.3003</v>
+        <v>-5.7043</v>
       </c>
     </row>
     <row r="81">
@@ -5129,10 +5129,10 @@
         <v>0.72</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.4913</v>
+        <v>-0.3156</v>
       </c>
       <c r="J81" t="n">
-        <v>-14.2477</v>
+        <v>-9.1524</v>
       </c>
     </row>
     <row r="82">
@@ -5169,10 +5169,10 @@
         <v>1.37</v>
       </c>
       <c r="I82" t="n">
-        <v>0.5794</v>
+        <v>0.5004999999999999</v>
       </c>
       <c r="J82" t="n">
-        <v>16.2232</v>
+        <v>14.014</v>
       </c>
     </row>
     <row r="83">
@@ -5209,10 +5209,10 @@
         <v>1.21</v>
       </c>
       <c r="I83" t="n">
-        <v>0.3661</v>
+        <v>0.3071</v>
       </c>
       <c r="J83" t="n">
-        <v>10.2508</v>
+        <v>8.598800000000001</v>
       </c>
     </row>
     <row r="84">
@@ -5249,10 +5249,10 @@
         <v>1.05</v>
       </c>
       <c r="I84" t="n">
-        <v>0.0809</v>
+        <v>0.0897</v>
       </c>
       <c r="J84" t="n">
-        <v>2.2652</v>
+        <v>2.5116</v>
       </c>
     </row>
     <row r="85">
@@ -5289,10 +5289,10 @@
         <v>1</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.0434</v>
+        <v>-0.008</v>
       </c>
       <c r="J85" t="n">
-        <v>-1.2152</v>
+        <v>-0.224</v>
       </c>
     </row>
     <row r="86">
@@ -5329,10 +5329,10 @@
         <v>0.83</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.3597</v>
+        <v>-0.2189</v>
       </c>
       <c r="J86" t="n">
-        <v>-10.0716</v>
+        <v>-6.1292</v>
       </c>
     </row>
     <row r="87">
@@ -5369,10 +5369,10 @@
         <v>1.49</v>
       </c>
       <c r="I87" t="n">
-        <v>0.7391</v>
+        <v>0.9175</v>
       </c>
       <c r="J87" t="n">
-        <v>20.6948</v>
+        <v>25.69</v>
       </c>
     </row>
     <row r="88">
@@ -5409,10 +5409,10 @@
         <v>1.06</v>
       </c>
       <c r="I88" t="n">
-        <v>0.1363</v>
+        <v>0.1544</v>
       </c>
       <c r="J88" t="n">
-        <v>3.8164</v>
+        <v>4.3232</v>
       </c>
     </row>
     <row r="89">
@@ -5449,10 +5449,10 @@
         <v>1</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.0247</v>
+        <v>-0.003</v>
       </c>
       <c r="J89" t="n">
-        <v>-0.6916</v>
+        <v>-0.08400000000000001</v>
       </c>
     </row>
     <row r="90">
@@ -5489,10 +5489,10 @@
         <v>0.97</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.1085</v>
+        <v>-0.0539</v>
       </c>
       <c r="J90" t="n">
-        <v>-3.038</v>
+        <v>-1.5092</v>
       </c>
     </row>
     <row r="91">
@@ -5529,10 +5529,10 @@
         <v>0.68</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.5527</v>
+        <v>-0.3594</v>
       </c>
       <c r="J91" t="n">
-        <v>-15.4756</v>
+        <v>-10.0632</v>
       </c>
     </row>
     <row r="92">
@@ -5569,10 +5569,10 @@
         <v>1.08</v>
       </c>
       <c r="I92" t="n">
-        <v>0.2411</v>
+        <v>0.2431</v>
       </c>
       <c r="J92" t="n">
-        <v>6.5097</v>
+        <v>6.5637</v>
       </c>
     </row>
     <row r="93">
@@ -5609,10 +5609,10 @@
         <v>0.86</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.2454</v>
+        <v>-0.1636</v>
       </c>
       <c r="J93" t="n">
-        <v>-6.6258</v>
+        <v>-4.4172</v>
       </c>
     </row>
     <row r="94">
@@ -5649,10 +5649,10 @@
         <v>0.85</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.2638</v>
+        <v>-0.1737</v>
       </c>
       <c r="J94" t="n">
-        <v>-7.1226</v>
+        <v>-4.6899</v>
       </c>
     </row>
     <row r="95">
@@ -5689,10 +5689,10 @@
         <v>0.8</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.3471</v>
+        <v>-0.2239</v>
       </c>
       <c r="J95" t="n">
-        <v>-9.371700000000001</v>
+        <v>-6.0453</v>
       </c>
     </row>
     <row r="96">
@@ -5729,10 +5729,10 @@
         <v>0.79</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.3627</v>
+        <v>-0.2338</v>
       </c>
       <c r="J96" t="n">
-        <v>-9.792899999999999</v>
+        <v>-6.3126</v>
       </c>
     </row>
     <row r="97">
@@ -5769,10 +5769,10 @@
         <v>1.72</v>
       </c>
       <c r="I97" t="n">
-        <v>1.6567</v>
+        <v>1.4286</v>
       </c>
       <c r="J97" t="n">
-        <v>44.7309</v>
+        <v>38.5722</v>
       </c>
     </row>
     <row r="98">
@@ -5809,10 +5809,10 @@
         <v>1.21</v>
       </c>
       <c r="I98" t="n">
-        <v>0.5891</v>
+        <v>0.59</v>
       </c>
       <c r="J98" t="n">
-        <v>15.9057</v>
+        <v>15.93</v>
       </c>
     </row>
     <row r="99">
@@ -5849,10 +5849,10 @@
         <v>1.01</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.0512</v>
+        <v>0.0149</v>
       </c>
       <c r="J99" t="n">
-        <v>-1.3824</v>
+        <v>0.4023</v>
       </c>
     </row>
     <row r="100">
@@ -5889,10 +5889,10 @@
         <v>0.98</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.2111</v>
+        <v>-0.136</v>
       </c>
       <c r="J100" t="n">
-        <v>-5.6997</v>
+        <v>-3.672</v>
       </c>
     </row>
     <row r="101">
@@ -5929,10 +5929,10 @@
         <v>0.91</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.4375</v>
+        <v>-0.3656</v>
       </c>
       <c r="J101" t="n">
-        <v>-11.8125</v>
+        <v>-9.8712</v>
       </c>
     </row>
     <row r="102">
@@ -5969,10 +5969,10 @@
         <v>1.43</v>
       </c>
       <c r="I102" t="n">
-        <v>1.0557</v>
+        <v>1.0404</v>
       </c>
       <c r="J102" t="n">
-        <v>25.3368</v>
+        <v>24.9696</v>
       </c>
     </row>
     <row r="103">
@@ -6009,10 +6009,10 @@
         <v>1.39</v>
       </c>
       <c r="I103" t="n">
-        <v>0.97</v>
+        <v>0.9759</v>
       </c>
       <c r="J103" t="n">
-        <v>23.28</v>
+        <v>23.4216</v>
       </c>
     </row>
     <row r="104">
@@ -6049,10 +6049,10 @@
         <v>1.2</v>
       </c>
       <c r="I104" t="n">
-        <v>0.4852</v>
+        <v>0.5527</v>
       </c>
       <c r="J104" t="n">
-        <v>11.6448</v>
+        <v>13.2648</v>
       </c>
     </row>
     <row r="105">
@@ -6089,10 +6089,10 @@
         <v>1.15</v>
       </c>
       <c r="I105" t="n">
-        <v>0.3526</v>
+        <v>0.4271</v>
       </c>
       <c r="J105" t="n">
-        <v>8.462400000000001</v>
+        <v>10.2504</v>
       </c>
     </row>
     <row r="106">
@@ -6129,10 +6129,10 @@
         <v>1.06</v>
       </c>
       <c r="I106" t="n">
-        <v>0.09710000000000001</v>
+        <v>0.1729</v>
       </c>
       <c r="J106" t="n">
-        <v>2.3304</v>
+        <v>4.1496</v>
       </c>
     </row>
     <row r="107">
@@ -6169,10 +6169,10 @@
         <v>1.1</v>
       </c>
       <c r="I107" t="n">
-        <v>0.287</v>
+        <v>0.2995</v>
       </c>
       <c r="J107" t="n">
-        <v>6.888</v>
+        <v>7.188</v>
       </c>
     </row>
     <row r="108">
@@ -6209,10 +6209,10 @@
         <v>1.02</v>
       </c>
       <c r="I108" t="n">
-        <v>0.1351</v>
+        <v>0.1081</v>
       </c>
       <c r="J108" t="n">
-        <v>3.2424</v>
+        <v>2.5944</v>
       </c>
     </row>
     <row r="109">
@@ -6249,10 +6249,10 @@
         <v>0.87</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.1984</v>
+        <v>-0.151</v>
       </c>
       <c r="J109" t="n">
-        <v>-4.7616</v>
+        <v>-3.624</v>
       </c>
     </row>
     <row r="110">
@@ -6289,10 +6289,10 @@
         <v>0.74</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.4273</v>
+        <v>-0.2786</v>
       </c>
       <c r="J110" t="n">
-        <v>-10.2552</v>
+        <v>-6.6864</v>
       </c>
     </row>
     <row r="111">
@@ -6329,10 +6329,10 @@
         <v>0.5</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.7427</v>
+        <v>-0.5032</v>
       </c>
       <c r="J111" t="n">
-        <v>-17.8248</v>
+        <v>-12.0768</v>
       </c>
     </row>
     <row r="112">
@@ -6369,10 +6369,10 @@
         <v>1.33</v>
       </c>
       <c r="I112" t="n">
-        <v>0.5158</v>
+        <v>0.4449</v>
       </c>
       <c r="J112" t="n">
-        <v>14.9582</v>
+        <v>12.9021</v>
       </c>
     </row>
     <row r="113">
@@ -6409,10 +6409,10 @@
         <v>1.2</v>
       </c>
       <c r="I113" t="n">
-        <v>0.3361</v>
+        <v>0.2883</v>
       </c>
       <c r="J113" t="n">
-        <v>9.7469</v>
+        <v>8.3607</v>
       </c>
     </row>
     <row r="114">
@@ -6449,10 +6449,10 @@
         <v>1.17</v>
       </c>
       <c r="I114" t="n">
-        <v>0.2891</v>
+        <v>0.2507</v>
       </c>
       <c r="J114" t="n">
-        <v>8.383900000000001</v>
+        <v>7.2703</v>
       </c>
     </row>
     <row r="115">
@@ -6489,10 +6489,10 @@
         <v>1.07</v>
       </c>
       <c r="I115" t="n">
-        <v>0.1038</v>
+        <v>0.116</v>
       </c>
       <c r="J115" t="n">
-        <v>3.0102</v>
+        <v>3.364</v>
       </c>
     </row>
     <row r="116">
@@ -6529,10 +6529,10 @@
         <v>0.9</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.2614</v>
+        <v>-0.1487</v>
       </c>
       <c r="J116" t="n">
-        <v>-7.5806</v>
+        <v>-4.3123</v>
       </c>
     </row>
     <row r="117">
@@ -6569,10 +6569,10 @@
         <v>1.21</v>
       </c>
       <c r="I117" t="n">
-        <v>0.4049</v>
+        <v>0.4638</v>
       </c>
       <c r="J117" t="n">
-        <v>11.7421</v>
+        <v>13.4502</v>
       </c>
     </row>
     <row r="118">
@@ -6609,10 +6609,10 @@
         <v>1.18</v>
       </c>
       <c r="I118" t="n">
-        <v>0.3615</v>
+        <v>0.408</v>
       </c>
       <c r="J118" t="n">
-        <v>10.4835</v>
+        <v>11.832</v>
       </c>
     </row>
     <row r="119">
@@ -6649,10 +6649,10 @@
         <v>1.01</v>
       </c>
       <c r="I119" t="n">
-        <v>0.052</v>
+        <v>0.0409</v>
       </c>
       <c r="J119" t="n">
-        <v>1.508</v>
+        <v>1.1861</v>
       </c>
     </row>
     <row r="120">
@@ -6689,10 +6689,10 @@
         <v>0.8</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.3788</v>
+        <v>-0.2367</v>
       </c>
       <c r="J120" t="n">
-        <v>-10.9852</v>
+        <v>-6.8643</v>
       </c>
     </row>
     <row r="121">
@@ -6729,10 +6729,10 @@
         <v>0.7</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.5165</v>
+        <v>-0.334</v>
       </c>
       <c r="J121" t="n">
-        <v>-14.9785</v>
+        <v>-9.686</v>
       </c>
     </row>
     <row r="122">
@@ -6769,10 +6769,10 @@
         <v>1.34</v>
       </c>
       <c r="I122" t="n">
-        <v>0.5249</v>
+        <v>0.4543</v>
       </c>
       <c r="J122" t="n">
-        <v>15.747</v>
+        <v>13.629</v>
       </c>
     </row>
     <row r="123">
@@ -6809,10 +6809,10 @@
         <v>1.18</v>
       </c>
       <c r="I123" t="n">
-        <v>0.3</v>
+        <v>0.262</v>
       </c>
       <c r="J123" t="n">
-        <v>9</v>
+        <v>7.86</v>
       </c>
     </row>
     <row r="124">
@@ -6849,10 +6849,10 @@
         <v>1.14</v>
       </c>
       <c r="I124" t="n">
-        <v>0.225</v>
+        <v>0.2119</v>
       </c>
       <c r="J124" t="n">
-        <v>6.75</v>
+        <v>6.357</v>
       </c>
     </row>
     <row r="125">
@@ -6889,10 +6889,10 @@
         <v>1.08</v>
       </c>
       <c r="I125" t="n">
-        <v>0.1179</v>
+        <v>0.1296</v>
       </c>
       <c r="J125" t="n">
-        <v>3.537</v>
+        <v>3.888</v>
       </c>
     </row>
     <row r="126">
@@ -6929,10 +6929,10 @@
         <v>0.99</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.09229999999999999</v>
+        <v>-0.0345</v>
       </c>
       <c r="J126" t="n">
-        <v>-2.769</v>
+        <v>-1.035</v>
       </c>
     </row>
     <row r="127">
@@ -6969,10 +6969,10 @@
         <v>1.08</v>
       </c>
       <c r="I127" t="n">
-        <v>0.2186</v>
+        <v>0.2228</v>
       </c>
       <c r="J127" t="n">
-        <v>6.558</v>
+        <v>6.684</v>
       </c>
     </row>
     <row r="128">
@@ -7009,10 +7009,10 @@
         <v>1.01</v>
       </c>
       <c r="I128" t="n">
-        <v>0.07340000000000001</v>
+        <v>0.0508</v>
       </c>
       <c r="J128" t="n">
-        <v>2.202</v>
+        <v>1.524</v>
       </c>
     </row>
     <row r="129">
@@ -7049,10 +7049,10 @@
         <v>0.98</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.0231</v>
+        <v>-0.0305</v>
       </c>
       <c r="J129" t="n">
-        <v>-0.6929999999999999</v>
+        <v>-0.915</v>
       </c>
     </row>
     <row r="130">
@@ -7089,10 +7089,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.3514</v>
+        <v>-0.2211</v>
       </c>
       <c r="J130" t="n">
-        <v>-10.542</v>
+        <v>-6.633</v>
       </c>
     </row>
     <row r="131">
@@ -7129,10 +7129,10 @@
         <v>0.79</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.3813</v>
+        <v>-0.2411</v>
       </c>
       <c r="J131" t="n">
-        <v>-11.439</v>
+        <v>-7.233</v>
       </c>
     </row>
     <row r="132">
@@ -7169,10 +7169,10 @@
         <v>1.48</v>
       </c>
       <c r="I132" t="n">
-        <v>0.6949</v>
+        <v>0.6135</v>
       </c>
       <c r="J132" t="n">
-        <v>20.847</v>
+        <v>18.405</v>
       </c>
     </row>
     <row r="133">
@@ -7209,10 +7209,10 @@
         <v>1.18</v>
       </c>
       <c r="I133" t="n">
-        <v>0.3</v>
+        <v>0.262</v>
       </c>
       <c r="J133" t="n">
-        <v>9</v>
+        <v>7.86</v>
       </c>
     </row>
     <row r="134">
@@ -7249,10 +7249,10 @@
         <v>1.1</v>
       </c>
       <c r="I134" t="n">
-        <v>0.1534</v>
+        <v>0.1583</v>
       </c>
       <c r="J134" t="n">
-        <v>4.602</v>
+        <v>4.749</v>
       </c>
     </row>
     <row r="135">
@@ -7289,10 +7289,10 @@
         <v>1.02</v>
       </c>
       <c r="I135" t="n">
-        <v>0.0001</v>
+        <v>0.0307</v>
       </c>
       <c r="J135" t="n">
-        <v>0.003</v>
+        <v>0.921</v>
       </c>
     </row>
     <row r="136">
@@ -7329,10 +7329,10 @@
         <v>0.95</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.1778</v>
+        <v>-0.091</v>
       </c>
       <c r="J136" t="n">
-        <v>-5.334</v>
+        <v>-2.73</v>
       </c>
     </row>
     <row r="137">
@@ -7369,10 +7369,10 @@
         <v>1.24</v>
       </c>
       <c r="I137" t="n">
-        <v>0.4338</v>
+        <v>0.5052</v>
       </c>
       <c r="J137" t="n">
-        <v>13.014</v>
+        <v>15.156</v>
       </c>
     </row>
     <row r="138">
@@ -7409,10 +7409,10 @@
         <v>1.11</v>
       </c>
       <c r="I138" t="n">
-        <v>0.2379</v>
+        <v>0.2622</v>
       </c>
       <c r="J138" t="n">
-        <v>7.137</v>
+        <v>7.866</v>
       </c>
     </row>
     <row r="139">
@@ -7449,10 +7449,10 @@
         <v>1.09</v>
       </c>
       <c r="I139" t="n">
-        <v>0.2033</v>
+        <v>0.2217</v>
       </c>
       <c r="J139" t="n">
-        <v>6.099</v>
+        <v>6.651</v>
       </c>
     </row>
     <row r="140">
@@ -7489,10 +7489,10 @@
         <v>0.95</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.1423</v>
+        <v>-0.07770000000000001</v>
       </c>
       <c r="J140" t="n">
-        <v>-4.269</v>
+        <v>-2.331</v>
       </c>
     </row>
     <row r="141">
@@ -7529,10 +7529,10 @@
         <v>0.7</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.5234</v>
+        <v>-0.3382</v>
       </c>
       <c r="J141" t="n">
-        <v>-15.702</v>
+        <v>-10.146</v>
       </c>
     </row>
     <row r="142">
@@ -7569,10 +7569,10 @@
         <v>1.91</v>
       </c>
       <c r="I142" t="n">
-        <v>1.0869</v>
+        <v>0.9955000000000001</v>
       </c>
       <c r="J142" t="n">
-        <v>23.9118</v>
+        <v>21.901</v>
       </c>
     </row>
     <row r="143">
@@ -7609,10 +7609,10 @@
         <v>1.68</v>
       </c>
       <c r="I143" t="n">
-        <v>0.8532999999999999</v>
+        <v>0.7784</v>
       </c>
       <c r="J143" t="n">
-        <v>18.7726</v>
+        <v>17.1248</v>
       </c>
     </row>
     <row r="144">
@@ -7649,10 +7649,10 @@
         <v>1.18</v>
       </c>
       <c r="I144" t="n">
-        <v>0.2154</v>
+        <v>0.2386</v>
       </c>
       <c r="J144" t="n">
-        <v>4.7388</v>
+        <v>5.2492</v>
       </c>
     </row>
     <row r="145">
@@ -7689,10 +7689,10 @@
         <v>1.17</v>
       </c>
       <c r="I145" t="n">
-        <v>0.2012</v>
+        <v>0.2258</v>
       </c>
       <c r="J145" t="n">
-        <v>4.4264</v>
+        <v>4.9676</v>
       </c>
     </row>
     <row r="146">
@@ -7729,10 +7729,10 @@
         <v>0.96</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.1984</v>
+        <v>-0.09959999999999999</v>
       </c>
       <c r="J146" t="n">
-        <v>-4.3648</v>
+        <v>-2.1912</v>
       </c>
     </row>
     <row r="147">
@@ -7769,10 +7769,10 @@
         <v>0.93</v>
       </c>
       <c r="I147" t="n">
-        <v>-0.0378</v>
+        <v>-0.0606</v>
       </c>
       <c r="J147" t="n">
-        <v>-0.8316</v>
+        <v>-1.3332</v>
       </c>
     </row>
     <row r="148">
@@ -7809,10 +7809,10 @@
         <v>0.9</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.0915</v>
+        <v>-0.0975</v>
       </c>
       <c r="J148" t="n">
-        <v>-2.013</v>
+        <v>-2.145</v>
       </c>
     </row>
     <row r="149">
@@ -7849,10 +7849,10 @@
         <v>0.74</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.3636</v>
+        <v>-0.2652</v>
       </c>
       <c r="J149" t="n">
-        <v>-7.9992</v>
+        <v>-5.8344</v>
       </c>
     </row>
     <row r="150">
@@ -7889,10 +7889,10 @@
         <v>0.58</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.6163999999999999</v>
+        <v>-0.4137</v>
       </c>
       <c r="J150" t="n">
-        <v>-13.5608</v>
+        <v>-9.1014</v>
       </c>
     </row>
     <row r="151">
@@ -7929,10 +7929,10 @@
         <v>0.53</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.6826</v>
+        <v>-0.4604</v>
       </c>
       <c r="J151" t="n">
-        <v>-15.0172</v>
+        <v>-10.1288</v>
       </c>
     </row>
     <row r="152">
@@ -7969,10 +7969,10 @@
         <v>1.52</v>
       </c>
       <c r="I152" t="n">
-        <v>0.7935</v>
+        <v>0.987</v>
       </c>
       <c r="J152" t="n">
-        <v>19.8375</v>
+        <v>24.675</v>
       </c>
     </row>
     <row r="153">
@@ -8009,10 +8009,10 @@
         <v>0.98</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.0526</v>
+        <v>-0.0346</v>
       </c>
       <c r="J153" t="n">
-        <v>-1.315</v>
+        <v>-0.865</v>
       </c>
     </row>
     <row r="154">
@@ -8049,10 +8049,10 @@
         <v>0.98</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.0526</v>
+        <v>-0.0346</v>
       </c>
       <c r="J154" t="n">
-        <v>-1.315</v>
+        <v>-0.865</v>
       </c>
     </row>
     <row r="155">
@@ -8089,10 +8089,10 @@
         <v>0.77</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.4217</v>
+        <v>-0.2664</v>
       </c>
       <c r="J155" t="n">
-        <v>-10.5425</v>
+        <v>-6.66</v>
       </c>
     </row>
     <row r="156">
@@ -8129,10 +8129,10 @@
         <v>0.65</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.5808</v>
+        <v>-0.381</v>
       </c>
       <c r="J156" t="n">
-        <v>-14.52</v>
+        <v>-9.525</v>
       </c>
     </row>
     <row r="157">
@@ -8169,10 +8169,10 @@
         <v>1.66</v>
       </c>
       <c r="I157" t="n">
-        <v>0.8878</v>
+        <v>0.8037</v>
       </c>
       <c r="J157" t="n">
-        <v>22.195</v>
+        <v>20.0925</v>
       </c>
     </row>
     <row r="158">
@@ -8209,10 +8209,10 @@
         <v>1.31</v>
       </c>
       <c r="I158" t="n">
-        <v>0.4783</v>
+        <v>0.4152</v>
       </c>
       <c r="J158" t="n">
-        <v>11.9575</v>
+        <v>10.38</v>
       </c>
     </row>
     <row r="159">
@@ -8249,10 +8249,10 @@
         <v>1.29</v>
       </c>
       <c r="I159" t="n">
-        <v>0.4516</v>
+        <v>0.3918</v>
       </c>
       <c r="J159" t="n">
-        <v>11.29</v>
+        <v>9.795</v>
       </c>
     </row>
     <row r="160">
@@ -8289,10 +8289,10 @@
         <v>0.8</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.4152</v>
+        <v>-0.257</v>
       </c>
       <c r="J160" t="n">
-        <v>-10.38</v>
+        <v>-6.425</v>
       </c>
     </row>
     <row r="161">
@@ -8329,10 +8329,10 @@
         <v>0.79</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.4288</v>
+        <v>-0.2669</v>
       </c>
       <c r="J161" t="n">
-        <v>-10.72</v>
+        <v>-6.6725</v>
       </c>
     </row>
     <row r="162">
@@ -8369,10 +8369,10 @@
         <v>1.15</v>
       </c>
       <c r="I162" t="n">
-        <v>0.3665</v>
+        <v>0.4039</v>
       </c>
       <c r="J162" t="n">
-        <v>8.429500000000001</v>
+        <v>9.2897</v>
       </c>
     </row>
     <row r="163">
@@ -8409,10 +8409,10 @@
         <v>0.97</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.007</v>
+        <v>-0.0318</v>
       </c>
       <c r="J163" t="n">
-        <v>-0.161</v>
+        <v>-0.7314000000000001</v>
       </c>
     </row>
     <row r="164">
@@ -8449,10 +8449,10 @@
         <v>0.97</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.007</v>
+        <v>-0.0318</v>
       </c>
       <c r="J164" t="n">
-        <v>-0.161</v>
+        <v>-0.7314000000000001</v>
       </c>
     </row>
     <row r="165">
@@ -8489,10 +8489,10 @@
         <v>0.67</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.5262</v>
+        <v>-0.3455</v>
       </c>
       <c r="J165" t="n">
-        <v>-12.1026</v>
+        <v>-7.9465</v>
       </c>
     </row>
     <row r="166">
@@ -8529,10 +8529,10 @@
         <v>0.47</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.7786</v>
+        <v>-0.5306</v>
       </c>
       <c r="J166" t="n">
-        <v>-17.9078</v>
+        <v>-12.2038</v>
       </c>
     </row>
     <row r="167">
@@ -8569,10 +8569,10 @@
         <v>1.46</v>
       </c>
       <c r="I167" t="n">
-        <v>0.6301</v>
+        <v>0.5641</v>
       </c>
       <c r="J167" t="n">
-        <v>14.4923</v>
+        <v>12.9743</v>
       </c>
     </row>
     <row r="168">
@@ -8609,10 +8609,10 @@
         <v>1.37</v>
       </c>
       <c r="I168" t="n">
-        <v>0.5181</v>
+        <v>0.4663</v>
       </c>
       <c r="J168" t="n">
-        <v>11.9163</v>
+        <v>10.7249</v>
       </c>
     </row>
     <row r="169">
@@ -8649,10 +8649,10 @@
         <v>1.35</v>
       </c>
       <c r="I169" t="n">
-        <v>0.4916</v>
+        <v>0.4443</v>
       </c>
       <c r="J169" t="n">
-        <v>11.3068</v>
+        <v>10.2189</v>
       </c>
     </row>
     <row r="170">
@@ -8689,10 +8689,10 @@
         <v>1.3</v>
       </c>
       <c r="I170" t="n">
-        <v>0.4199</v>
+        <v>0.3893</v>
       </c>
       <c r="J170" t="n">
-        <v>9.6577</v>
+        <v>8.953900000000001</v>
       </c>
     </row>
     <row r="171">
@@ -8729,10 +8729,10 @@
         <v>0.97</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.166</v>
+        <v>-0.0784</v>
       </c>
       <c r="J171" t="n">
-        <v>-3.818</v>
+        <v>-1.8032</v>
       </c>
     </row>
     <row r="172">
@@ -8769,10 +8769,10 @@
         <v>1.12</v>
       </c>
       <c r="I172" t="n">
-        <v>0.4375</v>
+        <v>0.3965</v>
       </c>
       <c r="J172" t="n">
-        <v>12.6875</v>
+        <v>11.4985</v>
       </c>
     </row>
     <row r="173">
@@ -8809,10 +8809,10 @@
         <v>1.08</v>
       </c>
       <c r="I173" t="n">
-        <v>0.3164</v>
+        <v>0.2822</v>
       </c>
       <c r="J173" t="n">
-        <v>9.175599999999999</v>
+        <v>8.1838</v>
       </c>
     </row>
     <row r="174">
@@ -8849,10 +8849,10 @@
         <v>1.07</v>
       </c>
       <c r="I174" t="n">
-        <v>0.2837</v>
+        <v>0.2524</v>
       </c>
       <c r="J174" t="n">
-        <v>8.2273</v>
+        <v>7.3196</v>
       </c>
     </row>
     <row r="175">
@@ -8889,10 +8889,10 @@
         <v>0.95</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.2525</v>
+        <v>-0.2041</v>
       </c>
       <c r="J175" t="n">
-        <v>-7.3225</v>
+        <v>-5.9189</v>
       </c>
     </row>
     <row r="176">
@@ -8929,10 +8929,10 @@
         <v>0.91</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.3805</v>
+        <v>-0.3272</v>
       </c>
       <c r="J176" t="n">
-        <v>-11.0345</v>
+        <v>-9.488799999999999</v>
       </c>
     </row>
     <row r="177">
@@ -8969,10 +8969,10 @@
         <v>1.25</v>
       </c>
       <c r="I177" t="n">
-        <v>0.3997</v>
+        <v>0.4856</v>
       </c>
       <c r="J177" t="n">
-        <v>11.5913</v>
+        <v>14.0824</v>
       </c>
     </row>
     <row r="178">
@@ -9009,10 +9009,10 @@
         <v>1.18</v>
       </c>
       <c r="I178" t="n">
-        <v>0.2934</v>
+        <v>0.3659</v>
       </c>
       <c r="J178" t="n">
-        <v>8.508599999999999</v>
+        <v>10.6111</v>
       </c>
     </row>
     <row r="179">
@@ -9049,10 +9049,10 @@
         <v>1.18</v>
       </c>
       <c r="I179" t="n">
-        <v>0.2934</v>
+        <v>0.3659</v>
       </c>
       <c r="J179" t="n">
-        <v>8.508599999999999</v>
+        <v>10.6111</v>
       </c>
     </row>
     <row r="180">
@@ -9089,10 +9089,10 @@
         <v>1.12</v>
       </c>
       <c r="I180" t="n">
-        <v>0.1826</v>
+        <v>0.2589</v>
       </c>
       <c r="J180" t="n">
-        <v>5.2954</v>
+        <v>7.5081</v>
       </c>
     </row>
     <row r="181">
@@ -9129,10 +9129,10 @@
         <v>1.07</v>
       </c>
       <c r="I181" t="n">
-        <v>0.0955</v>
+        <v>0.1586</v>
       </c>
       <c r="J181" t="n">
-        <v>2.7695</v>
+        <v>4.5994</v>
       </c>
     </row>
     <row r="182">
@@ -9169,10 +9169,10 @@
         <v>1.49</v>
       </c>
       <c r="I182" t="n">
-        <v>0.7113</v>
+        <v>0.8827</v>
       </c>
       <c r="J182" t="n">
-        <v>21.339</v>
+        <v>26.481</v>
       </c>
     </row>
     <row r="183">
@@ -9209,10 +9209,10 @@
         <v>1.32</v>
       </c>
       <c r="I183" t="n">
-        <v>0.5041</v>
+        <v>0.6093</v>
       </c>
       <c r="J183" t="n">
-        <v>15.123</v>
+        <v>18.279</v>
       </c>
     </row>
     <row r="184">
@@ -9249,10 +9249,10 @@
         <v>1.07</v>
       </c>
       <c r="I184" t="n">
-        <v>0.1052</v>
+        <v>0.1636</v>
       </c>
       <c r="J184" t="n">
-        <v>3.156</v>
+        <v>4.908</v>
       </c>
     </row>
     <row r="185">
@@ -9289,10 +9289,10 @@
         <v>0.92</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.2276</v>
+        <v>-0.1255</v>
       </c>
       <c r="J185" t="n">
-        <v>-6.828</v>
+        <v>-3.765</v>
       </c>
     </row>
     <row r="186">
@@ -9329,10 +9329,10 @@
         <v>0.85</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.3376</v>
+        <v>-0.2021</v>
       </c>
       <c r="J186" t="n">
-        <v>-10.128</v>
+        <v>-6.063</v>
       </c>
     </row>
     <row r="187">
@@ -9369,10 +9369,10 @@
         <v>1.22</v>
       </c>
       <c r="I187" t="n">
-        <v>0.7206</v>
+        <v>0.6757</v>
       </c>
       <c r="J187" t="n">
-        <v>21.618</v>
+        <v>20.271</v>
       </c>
     </row>
     <row r="188">
@@ -9409,10 +9409,10 @@
         <v>1.14</v>
       </c>
       <c r="I188" t="n">
-        <v>0.5144</v>
+        <v>0.4636</v>
       </c>
       <c r="J188" t="n">
-        <v>15.432</v>
+        <v>13.908</v>
       </c>
     </row>
     <row r="189">
@@ -9449,10 +9449,10 @@
         <v>1.08</v>
       </c>
       <c r="I189" t="n">
-        <v>0.3395</v>
+        <v>0.2922</v>
       </c>
       <c r="J189" t="n">
-        <v>10.185</v>
+        <v>8.766</v>
       </c>
     </row>
     <row r="190">
@@ -9489,10 +9489,10 @@
         <v>0.78</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.7147</v>
+        <v>-0.671</v>
       </c>
       <c r="J190" t="n">
-        <v>-21.441</v>
+        <v>-20.13</v>
       </c>
     </row>
     <row r="191">
@@ -9529,10 +9529,10 @@
         <v>0.75</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.7872</v>
+        <v>-0.7474</v>
       </c>
       <c r="J191" t="n">
-        <v>-23.616</v>
+        <v>-22.422</v>
       </c>
     </row>
     <row r="192">
@@ -9569,10 +9569,10 @@
         <v>1.09</v>
       </c>
       <c r="I192" t="n">
-        <v>0.2514</v>
+        <v>0.2581</v>
       </c>
       <c r="J192" t="n">
-        <v>6.285</v>
+        <v>6.4525</v>
       </c>
     </row>
     <row r="193">
@@ -9609,10 +9609,10 @@
         <v>0.9</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.1718</v>
+        <v>-0.124</v>
       </c>
       <c r="J193" t="n">
-        <v>-4.295</v>
+        <v>-3.1</v>
       </c>
     </row>
     <row r="194">
@@ -9649,10 +9649,10 @@
         <v>0.86</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.2554</v>
+        <v>-0.1654</v>
       </c>
       <c r="J194" t="n">
-        <v>-6.385</v>
+        <v>-4.135</v>
       </c>
     </row>
     <row r="195">
@@ -9689,10 +9689,10 @@
         <v>0.84</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.2897</v>
+        <v>-0.1859</v>
       </c>
       <c r="J195" t="n">
-        <v>-7.2425</v>
+        <v>-4.6475</v>
       </c>
     </row>
     <row r="196">
@@ -9729,10 +9729,10 @@
         <v>0.78</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.384</v>
+        <v>-0.2459</v>
       </c>
       <c r="J196" t="n">
-        <v>-9.6</v>
+        <v>-6.1475</v>
       </c>
     </row>
     <row r="197">
@@ -9769,10 +9769,10 @@
         <v>1.94</v>
       </c>
       <c r="I197" t="n">
-        <v>1.9516</v>
+        <v>1.6491</v>
       </c>
       <c r="J197" t="n">
-        <v>48.79</v>
+        <v>41.2275</v>
       </c>
     </row>
     <row r="198">
@@ -9809,10 +9809,10 @@
         <v>1.27</v>
       </c>
       <c r="I198" t="n">
-        <v>0.6335</v>
+        <v>0.7071</v>
       </c>
       <c r="J198" t="n">
-        <v>15.8375</v>
+        <v>17.6775</v>
       </c>
     </row>
     <row r="199">
@@ -9849,10 +9849,10 @@
         <v>1.11</v>
       </c>
       <c r="I199" t="n">
-        <v>0.223</v>
+        <v>0.3076</v>
       </c>
       <c r="J199" t="n">
-        <v>5.575</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="200">
@@ -9889,10 +9889,10 @@
         <v>1.1</v>
       </c>
       <c r="I200" t="n">
-        <v>0.1954</v>
+        <v>0.2795</v>
       </c>
       <c r="J200" t="n">
-        <v>4.885</v>
+        <v>6.9875</v>
       </c>
     </row>
     <row r="201">
@@ -9929,10 +9929,10 @@
         <v>1.07</v>
       </c>
       <c r="I201" t="n">
-        <v>0.1092</v>
+        <v>0.1915</v>
       </c>
       <c r="J201" t="n">
-        <v>2.73</v>
+        <v>4.7875</v>
       </c>
     </row>
     <row r="202">
@@ -9969,10 +9969,10 @@
         <v>1.52</v>
       </c>
       <c r="I202" t="n">
-        <v>1.2157</v>
+        <v>1.1457</v>
       </c>
       <c r="J202" t="n">
-        <v>25.5297</v>
+        <v>24.0597</v>
       </c>
     </row>
     <row r="203">
@@ -10009,10 +10009,10 @@
         <v>1.44</v>
       </c>
       <c r="I203" t="n">
-        <v>1.0514</v>
+        <v>1.0446</v>
       </c>
       <c r="J203" t="n">
-        <v>22.0794</v>
+        <v>21.9366</v>
       </c>
     </row>
     <row r="204">
@@ -10049,10 +10049,10 @@
         <v>1.41</v>
       </c>
       <c r="I204" t="n">
-        <v>0.987</v>
+        <v>0.9996</v>
       </c>
       <c r="J204" t="n">
-        <v>20.727</v>
+        <v>20.9916</v>
       </c>
     </row>
     <row r="205">
@@ -10089,10 +10089,10 @@
         <v>1.18</v>
       </c>
       <c r="I205" t="n">
-        <v>0.4075</v>
+        <v>0.4928</v>
       </c>
       <c r="J205" t="n">
-        <v>8.557499999999999</v>
+        <v>10.3488</v>
       </c>
     </row>
     <row r="206">
@@ -10129,10 +10129,10 @@
         <v>0.93</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.4175</v>
+        <v>-0.3369</v>
       </c>
       <c r="J206" t="n">
-        <v>-8.7675</v>
+        <v>-7.0749</v>
       </c>
     </row>
     <row r="207">
@@ -10169,10 +10169,10 @@
         <v>1.16</v>
       </c>
       <c r="I207" t="n">
-        <v>0.3793</v>
+        <v>0.4212</v>
       </c>
       <c r="J207" t="n">
-        <v>7.9653</v>
+        <v>8.8452</v>
       </c>
     </row>
     <row r="208">
@@ -10209,10 +10209,10 @@
         <v>1.07</v>
       </c>
       <c r="I208" t="n">
-        <v>0.2328</v>
+        <v>0.2304</v>
       </c>
       <c r="J208" t="n">
-        <v>4.8888</v>
+        <v>4.8384</v>
       </c>
     </row>
     <row r="209">
@@ -10249,10 +10249,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.07099999999999999</v>
+        <v>-0.0725</v>
       </c>
       <c r="J209" t="n">
-        <v>-1.491</v>
+        <v>-1.5225</v>
       </c>
     </row>
     <row r="210">
@@ -10289,10 +10289,10 @@
         <v>0.55</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.6828</v>
+        <v>-0.4581</v>
       </c>
       <c r="J210" t="n">
-        <v>-14.3388</v>
+        <v>-9.620100000000001</v>
       </c>
     </row>
     <row r="211">
@@ -10329,10 +10329,10 @@
         <v>0.54</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.6951000000000001</v>
+        <v>-0.4673</v>
       </c>
       <c r="J211" t="n">
-        <v>-14.5971</v>
+        <v>-9.8133</v>
       </c>
     </row>
     <row r="212">
@@ -10369,10 +10369,10 @@
         <v>0.88</v>
       </c>
       <c r="I212" t="n">
-        <v>-0.1017</v>
+        <v>-0.1076</v>
       </c>
       <c r="J212" t="n">
-        <v>-1.9323</v>
+        <v>-2.0444</v>
       </c>
     </row>
     <row r="213">
@@ -10409,10 +10409,10 @@
         <v>0.76</v>
       </c>
       <c r="I213" t="n">
-        <v>-0.296</v>
+        <v>-0.2382</v>
       </c>
       <c r="J213" t="n">
-        <v>-5.624</v>
+        <v>-4.5258</v>
       </c>
     </row>
     <row r="214">
@@ -10449,10 +10449,10 @@
         <v>0.68</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.4413</v>
+        <v>-0.3136</v>
       </c>
       <c r="J214" t="n">
-        <v>-8.3847</v>
+        <v>-5.9584</v>
       </c>
     </row>
     <row r="215">
@@ -10489,10 +10489,10 @@
         <v>0.62</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.5409</v>
+        <v>-0.3683</v>
       </c>
       <c r="J215" t="n">
-        <v>-10.2771</v>
+        <v>-6.9977</v>
       </c>
     </row>
     <row r="216">
@@ -10529,10 +10529,10 @@
         <v>0.49</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.7212</v>
+        <v>-0.4898</v>
       </c>
       <c r="J216" t="n">
-        <v>-13.7028</v>
+        <v>-9.3062</v>
       </c>
     </row>
     <row r="217">
@@ -10569,10 +10569,10 @@
         <v>1.71</v>
       </c>
       <c r="I217" t="n">
-        <v>0.8541</v>
+        <v>0.7893</v>
       </c>
       <c r="J217" t="n">
-        <v>16.2279</v>
+        <v>14.9967</v>
       </c>
     </row>
     <row r="218">
@@ -10609,10 +10609,10 @@
         <v>1.66</v>
       </c>
       <c r="I218" t="n">
-        <v>0.8001</v>
+        <v>0.7403</v>
       </c>
       <c r="J218" t="n">
-        <v>15.2019</v>
+        <v>14.0657</v>
       </c>
     </row>
     <row r="219">
@@ -10649,10 +10649,10 @@
         <v>1.44</v>
       </c>
       <c r="I219" t="n">
-        <v>0.5242</v>
+        <v>0.5222</v>
       </c>
       <c r="J219" t="n">
-        <v>9.9598</v>
+        <v>9.921799999999999</v>
       </c>
     </row>
     <row r="220">
@@ -10689,10 +10689,10 @@
         <v>1.37</v>
       </c>
       <c r="I220" t="n">
-        <v>0.4377</v>
+        <v>0.4477</v>
       </c>
       <c r="J220" t="n">
-        <v>8.3163</v>
+        <v>8.5063</v>
       </c>
     </row>
     <row r="221">
@@ -10729,10 +10729,10 @@
         <v>1.35</v>
       </c>
       <c r="I221" t="n">
-        <v>0.413</v>
+        <v>0.4258</v>
       </c>
       <c r="J221" t="n">
-        <v>7.847</v>
+        <v>8.090199999999999</v>
       </c>
     </row>
     <row r="222">
@@ -10769,10 +10769,10 @@
         <v>1.17</v>
       </c>
       <c r="I222" t="n">
-        <v>0.3758</v>
+        <v>0.419</v>
       </c>
       <c r="J222" t="n">
-        <v>10.8982</v>
+        <v>12.151</v>
       </c>
     </row>
     <row r="223">
@@ -10809,10 +10809,10 @@
         <v>0.89</v>
       </c>
       <c r="I223" t="n">
-        <v>-0.2023</v>
+        <v>-0.1347</v>
       </c>
       <c r="J223" t="n">
-        <v>-5.8667</v>
+        <v>-3.9063</v>
       </c>
     </row>
     <row r="224">
@@ -10849,10 +10849,10 @@
         <v>0.88</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.222</v>
+        <v>-0.1452</v>
       </c>
       <c r="J224" t="n">
-        <v>-6.438</v>
+        <v>-4.2108</v>
       </c>
     </row>
     <row r="225">
@@ -10889,10 +10889,10 @@
         <v>0.79</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.3709</v>
+        <v>-0.2368</v>
       </c>
       <c r="J225" t="n">
-        <v>-10.7561</v>
+        <v>-6.8672</v>
       </c>
     </row>
     <row r="226">
@@ -10929,10 +10929,10 @@
         <v>0.77</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.4007</v>
+        <v>-0.2565</v>
       </c>
       <c r="J226" t="n">
-        <v>-11.6203</v>
+        <v>-7.4385</v>
       </c>
     </row>
     <row r="227">
@@ -10969,10 +10969,10 @@
         <v>1.48</v>
       </c>
       <c r="I227" t="n">
-        <v>0.6991000000000001</v>
+        <v>0.6168</v>
       </c>
       <c r="J227" t="n">
-        <v>20.2739</v>
+        <v>17.8872</v>
       </c>
     </row>
     <row r="228">
@@ -11009,10 +11009,10 @@
         <v>1.37</v>
       </c>
       <c r="I228" t="n">
-        <v>0.5671</v>
+        <v>0.4918</v>
       </c>
       <c r="J228" t="n">
-        <v>16.4459</v>
+        <v>14.2622</v>
       </c>
     </row>
     <row r="229">
@@ -11049,10 +11049,10 @@
         <v>1.27</v>
       </c>
       <c r="I229" t="n">
-        <v>0.437</v>
+        <v>0.3741</v>
       </c>
       <c r="J229" t="n">
-        <v>12.673</v>
+        <v>10.8489</v>
       </c>
     </row>
     <row r="230">
@@ -11089,10 +11089,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.3953</v>
+        <v>-0.2433</v>
       </c>
       <c r="J230" t="n">
-        <v>-11.4637</v>
+        <v>-7.0557</v>
       </c>
     </row>
     <row r="231">
@@ -11129,10 +11129,10 @@
         <v>0.73</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.5024999999999999</v>
+        <v>-0.3214</v>
       </c>
       <c r="J231" t="n">
-        <v>-14.5725</v>
+        <v>-9.320600000000001</v>
       </c>
     </row>
     <row r="232">
@@ -11169,10 +11169,10 @@
         <v>1.05</v>
       </c>
       <c r="I232" t="n">
-        <v>0.2533</v>
+        <v>0.2534</v>
       </c>
       <c r="J232" t="n">
-        <v>4.8127</v>
+        <v>4.8146</v>
       </c>
     </row>
     <row r="233">
@@ -11209,10 +11209,10 @@
         <v>0.79</v>
       </c>
       <c r="I233" t="n">
-        <v>-0.2651</v>
+        <v>-0.2141</v>
       </c>
       <c r="J233" t="n">
-        <v>-5.0369</v>
+        <v>-4.0679</v>
       </c>
     </row>
     <row r="234">
@@ -11249,10 +11249,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.4474</v>
+        <v>-0.3084</v>
       </c>
       <c r="J234" t="n">
-        <v>-8.5006</v>
+        <v>-5.8596</v>
       </c>
     </row>
     <row r="235">
@@ -11289,10 +11289,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.6379</v>
+        <v>-0.4296</v>
       </c>
       <c r="J235" t="n">
-        <v>-12.1201</v>
+        <v>-8.1624</v>
       </c>
     </row>
     <row r="236">
@@ -11329,10 +11329,10 @@
         <v>0.5</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.7167</v>
+        <v>-0.4856</v>
       </c>
       <c r="J236" t="n">
-        <v>-13.6173</v>
+        <v>-9.2264</v>
       </c>
     </row>
     <row r="237">
@@ -11369,10 +11369,10 @@
         <v>2.34</v>
       </c>
       <c r="I237" t="n">
-        <v>1.4686</v>
+        <v>1.2368</v>
       </c>
       <c r="J237" t="n">
-        <v>27.9034</v>
+        <v>23.4992</v>
       </c>
     </row>
     <row r="238">
@@ -11409,10 +11409,10 @@
         <v>1.51</v>
       </c>
       <c r="I238" t="n">
-        <v>0.646</v>
+        <v>0.5977</v>
       </c>
       <c r="J238" t="n">
-        <v>12.274</v>
+        <v>11.3563</v>
       </c>
     </row>
     <row r="239">
@@ -11449,10 +11449,10 @@
         <v>1.27</v>
       </c>
       <c r="I239" t="n">
-        <v>0.3251</v>
+        <v>0.3416</v>
       </c>
       <c r="J239" t="n">
-        <v>6.1769</v>
+        <v>6.4904</v>
       </c>
     </row>
     <row r="240">
@@ -11489,10 +11489,10 @@
         <v>1.12</v>
       </c>
       <c r="I240" t="n">
-        <v>0.1182</v>
+        <v>0.1528</v>
       </c>
       <c r="J240" t="n">
-        <v>2.2458</v>
+        <v>2.9032</v>
       </c>
     </row>
     <row r="241">
@@ -11529,10 +11529,10 @@
         <v>0.96</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.2058</v>
+        <v>-0.1043</v>
       </c>
       <c r="J241" t="n">
-        <v>-3.9102</v>
+        <v>-1.9817</v>
       </c>
     </row>
     <row r="242">
@@ -11569,10 +11569,10 @@
         <v>1.25</v>
       </c>
       <c r="I242" t="n">
-        <v>0.4557</v>
+        <v>0.5313</v>
       </c>
       <c r="J242" t="n">
-        <v>13.671</v>
+        <v>15.939</v>
       </c>
     </row>
     <row r="243">
@@ -11609,10 +11609,10 @@
         <v>1.08</v>
       </c>
       <c r="I243" t="n">
-        <v>0.1951</v>
+        <v>0.2063</v>
       </c>
       <c r="J243" t="n">
-        <v>5.853</v>
+        <v>6.189</v>
       </c>
     </row>
     <row r="244">
@@ -11649,10 +11649,10 @@
         <v>1.04</v>
       </c>
       <c r="I244" t="n">
-        <v>0.1173</v>
+        <v>0.1172</v>
       </c>
       <c r="J244" t="n">
-        <v>3.519</v>
+        <v>3.516</v>
       </c>
     </row>
     <row r="245">
@@ -11689,10 +11689,10 @@
         <v>0.97</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.0893</v>
+        <v>-0.0495</v>
       </c>
       <c r="J245" t="n">
-        <v>-2.679</v>
+        <v>-1.485</v>
       </c>
     </row>
     <row r="246">
@@ -11729,10 +11729,10 @@
         <v>0.63</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.6081</v>
+        <v>-0.401</v>
       </c>
       <c r="J246" t="n">
-        <v>-18.243</v>
+        <v>-12.03</v>
       </c>
     </row>
     <row r="247">
@@ -11769,10 +11769,10 @@
         <v>1.17</v>
       </c>
       <c r="I247" t="n">
-        <v>0.3054</v>
+        <v>0.2559</v>
       </c>
       <c r="J247" t="n">
-        <v>9.162000000000001</v>
+        <v>7.677</v>
       </c>
     </row>
     <row r="248">
@@ -11809,10 +11809,10 @@
         <v>1.15</v>
       </c>
       <c r="I248" t="n">
-        <v>0.2737</v>
+        <v>0.2298</v>
       </c>
       <c r="J248" t="n">
-        <v>8.211</v>
+        <v>6.894</v>
       </c>
     </row>
     <row r="249">
@@ -11849,10 +11849,10 @@
         <v>1.1</v>
       </c>
       <c r="I249" t="n">
-        <v>0.1849</v>
+        <v>0.1628</v>
       </c>
       <c r="J249" t="n">
-        <v>5.547</v>
+        <v>4.884</v>
       </c>
     </row>
     <row r="250">
@@ -11889,10 +11889,10 @@
         <v>1.09</v>
       </c>
       <c r="I250" t="n">
-        <v>0.1605</v>
+        <v>0.1492</v>
       </c>
       <c r="J250" t="n">
-        <v>4.815</v>
+        <v>4.476</v>
       </c>
     </row>
     <row r="251">
@@ -11929,10 +11929,10 @@
         <v>0.96</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.1459</v>
+        <v>-0.0728</v>
       </c>
       <c r="J251" t="n">
-        <v>-4.377</v>
+        <v>-2.184</v>
       </c>
     </row>
     <row r="252">
@@ -11969,10 +11969,10 @@
         <v>1.79</v>
       </c>
       <c r="I252" t="n">
-        <v>1.8217</v>
+        <v>1.546</v>
       </c>
       <c r="J252" t="n">
-        <v>51.0076</v>
+        <v>43.288</v>
       </c>
     </row>
     <row r="253">
@@ -12009,10 +12009,10 @@
         <v>1.01</v>
       </c>
       <c r="I253" t="n">
-        <v>-0.0143</v>
+        <v>0.0343</v>
       </c>
       <c r="J253" t="n">
-        <v>-0.4004</v>
+        <v>0.9604</v>
       </c>
     </row>
     <row r="254">
@@ -12049,10 +12049,10 @@
         <v>0.97</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.2161</v>
+        <v>-0.1532</v>
       </c>
       <c r="J254" t="n">
-        <v>-6.0508</v>
+        <v>-4.2896</v>
       </c>
     </row>
     <row r="255">
@@ -12089,10 +12089,10 @@
         <v>0.88</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.4942</v>
+        <v>-0.4316</v>
       </c>
       <c r="J255" t="n">
-        <v>-13.8376</v>
+        <v>-12.0848</v>
       </c>
     </row>
     <row r="256">
@@ -12129,10 +12129,10 @@
         <v>0.8</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.6995</v>
+        <v>-0.6471</v>
       </c>
       <c r="J256" t="n">
-        <v>-19.586</v>
+        <v>-18.1188</v>
       </c>
     </row>
     <row r="257">
@@ -12169,10 +12169,10 @@
         <v>1.21</v>
       </c>
       <c r="I257" t="n">
-        <v>0.4119</v>
+        <v>0.471</v>
       </c>
       <c r="J257" t="n">
-        <v>11.5332</v>
+        <v>13.188</v>
       </c>
     </row>
     <row r="258">
@@ -12209,10 +12209,10 @@
         <v>1.15</v>
       </c>
       <c r="I258" t="n">
-        <v>0.3235</v>
+        <v>0.3573</v>
       </c>
       <c r="J258" t="n">
-        <v>9.058</v>
+        <v>10.0044</v>
       </c>
     </row>
     <row r="259">
@@ -12249,10 +12249,10 @@
         <v>0.97</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.062</v>
+        <v>-0.0472</v>
       </c>
       <c r="J259" t="n">
-        <v>-1.736</v>
+        <v>-1.3216</v>
       </c>
     </row>
     <row r="260">
@@ -12289,10 +12289,10 @@
         <v>0.83</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.3287</v>
+        <v>-0.2039</v>
       </c>
       <c r="J260" t="n">
-        <v>-9.2036</v>
+        <v>-5.7092</v>
       </c>
     </row>
     <row r="261">
@@ -12329,10 +12329,10 @@
         <v>0.64</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.59</v>
+        <v>-0.388</v>
       </c>
       <c r="J261" t="n">
-        <v>-16.52</v>
+        <v>-10.864</v>
       </c>
     </row>
     <row r="262">
@@ -12369,10 +12369,10 @@
         <v>0.67</v>
       </c>
       <c r="I262" t="n">
-        <v>-0.3782</v>
+        <v>-0.3048</v>
       </c>
       <c r="J262" t="n">
-        <v>-7.1858</v>
+        <v>-5.7912</v>
       </c>
     </row>
     <row r="263">
@@ -12409,10 +12409,10 @@
         <v>0.67</v>
       </c>
       <c r="I263" t="n">
-        <v>-0.3782</v>
+        <v>-0.3048</v>
       </c>
       <c r="J263" t="n">
-        <v>-7.1858</v>
+        <v>-5.7912</v>
       </c>
     </row>
     <row r="264">
@@ -12449,10 +12449,10 @@
         <v>0.66</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.3939</v>
+        <v>-0.3148</v>
       </c>
       <c r="J264" t="n">
-        <v>-7.4841</v>
+        <v>-5.9812</v>
       </c>
     </row>
     <row r="265">
@@ -12489,10 +12489,10 @@
         <v>0.55</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.5941</v>
+        <v>-0.4155</v>
       </c>
       <c r="J265" t="n">
-        <v>-11.2879</v>
+        <v>-7.8945</v>
       </c>
     </row>
     <row r="266">
@@ -12529,10 +12529,10 @@
         <v>0.37</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.8491</v>
+        <v>-0.5859</v>
       </c>
       <c r="J266" t="n">
-        <v>-16.1329</v>
+        <v>-11.1321</v>
       </c>
     </row>
     <row r="267">
@@ -12569,10 +12569,10 @@
         <v>2.18</v>
       </c>
       <c r="I267" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J267" t="n">
-        <v>39.1267</v>
+        <v>34.8422</v>
       </c>
     </row>
     <row r="268">
@@ -12609,10 +12609,10 @@
         <v>2.01</v>
       </c>
       <c r="I268" t="n">
-        <v>1.9581</v>
+        <v>1.6618</v>
       </c>
       <c r="J268" t="n">
-        <v>37.2039</v>
+        <v>31.5742</v>
       </c>
     </row>
     <row r="269">
@@ -12649,10 +12649,10 @@
         <v>1.46</v>
       </c>
       <c r="I269" t="n">
-        <v>0.931</v>
+        <v>1.0406</v>
       </c>
       <c r="J269" t="n">
-        <v>17.689</v>
+        <v>19.7714</v>
       </c>
     </row>
     <row r="270">
@@ -12689,10 +12689,10 @@
         <v>1.42</v>
       </c>
       <c r="I270" t="n">
-        <v>0.8477</v>
+        <v>0.9797</v>
       </c>
       <c r="J270" t="n">
-        <v>16.1063</v>
+        <v>18.6143</v>
       </c>
     </row>
     <row r="271">
@@ -12729,10 +12729,10 @@
         <v>0.72</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.9668</v>
+        <v>-0.9399</v>
       </c>
       <c r="J271" t="n">
-        <v>-18.3692</v>
+        <v>-17.8581</v>
       </c>
     </row>
     <row r="272">
@@ -12769,10 +12769,10 @@
         <v>1.35</v>
       </c>
       <c r="I272" t="n">
-        <v>0.652</v>
+        <v>0.8031</v>
       </c>
       <c r="J272" t="n">
-        <v>15.648</v>
+        <v>19.2744</v>
       </c>
     </row>
     <row r="273">
@@ -12809,10 +12809,10 @@
         <v>0.95</v>
       </c>
       <c r="I273" t="n">
-        <v>-0.0363</v>
+        <v>-0.0537</v>
       </c>
       <c r="J273" t="n">
-        <v>-0.8712</v>
+        <v>-1.2888</v>
       </c>
     </row>
     <row r="274">
@@ -12849,10 +12849,10 @@
         <v>0.78</v>
       </c>
       <c r="I274" t="n">
-        <v>-0.3538</v>
+        <v>-0.2363</v>
       </c>
       <c r="J274" t="n">
-        <v>-8.491199999999999</v>
+        <v>-5.6712</v>
       </c>
     </row>
     <row r="275">
@@ -12889,10 +12889,10 @@
         <v>0.61</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.5991</v>
+        <v>-0.3979</v>
       </c>
       <c r="J275" t="n">
-        <v>-14.3784</v>
+        <v>-9.5496</v>
       </c>
     </row>
     <row r="276">
@@ -12929,10 +12929,10 @@
         <v>0.4</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.8565</v>
+        <v>-0.5909</v>
       </c>
       <c r="J276" t="n">
-        <v>-20.556</v>
+        <v>-14.1816</v>
       </c>
     </row>
     <row r="277">
@@ -12969,10 +12969,10 @@
         <v>1.61</v>
       </c>
       <c r="I277" t="n">
-        <v>1.3827</v>
+        <v>1.2525</v>
       </c>
       <c r="J277" t="n">
-        <v>33.1848</v>
+        <v>30.06</v>
       </c>
     </row>
     <row r="278">
@@ -13009,10 +13009,10 @@
         <v>1.58</v>
       </c>
       <c r="I278" t="n">
-        <v>1.3252</v>
+        <v>1.216</v>
       </c>
       <c r="J278" t="n">
-        <v>31.8048</v>
+        <v>29.184</v>
       </c>
     </row>
     <row r="279">
@@ -13049,10 +13049,10 @@
         <v>1.36</v>
       </c>
       <c r="I279" t="n">
-        <v>0.8637</v>
+        <v>0.9002</v>
       </c>
       <c r="J279" t="n">
-        <v>20.7288</v>
+        <v>21.6048</v>
       </c>
     </row>
     <row r="280">
@@ -13089,10 +13089,10 @@
         <v>1.11</v>
       </c>
       <c r="I280" t="n">
-        <v>0.2173</v>
+        <v>0.304</v>
       </c>
       <c r="J280" t="n">
-        <v>5.2152</v>
+        <v>7.296</v>
       </c>
     </row>
     <row r="281">
@@ -13129,10 +13129,10 @@
         <v>0.91</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.4787</v>
+        <v>-0.4011</v>
       </c>
       <c r="J281" t="n">
-        <v>-11.4888</v>
+        <v>-9.6264</v>
       </c>
     </row>
     <row r="282">
@@ -13169,10 +13169,10 @@
         <v>1.23</v>
       </c>
       <c r="I282" t="n">
-        <v>0.7035</v>
+        <v>0.6707</v>
       </c>
       <c r="J282" t="n">
-        <v>20.4015</v>
+        <v>19.4503</v>
       </c>
     </row>
     <row r="283">
@@ -13209,10 +13209,10 @@
         <v>1.16</v>
       </c>
       <c r="I283" t="n">
-        <v>0.524</v>
+        <v>0.4919</v>
       </c>
       <c r="J283" t="n">
-        <v>15.196</v>
+        <v>14.2651</v>
       </c>
     </row>
     <row r="284">
@@ -13249,10 +13249,10 @@
         <v>1.01</v>
       </c>
       <c r="I284" t="n">
-        <v>0.0016</v>
+        <v>0.0408</v>
       </c>
       <c r="J284" t="n">
-        <v>0.0464</v>
+        <v>1.1832</v>
       </c>
     </row>
     <row r="285">
@@ -13289,10 +13289,10 @@
         <v>0.98</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.1636</v>
+        <v>-0.1092</v>
       </c>
       <c r="J285" t="n">
-        <v>-4.7444</v>
+        <v>-3.1668</v>
       </c>
     </row>
     <row r="286">
@@ -13329,10 +13329,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.3064</v>
+        <v>-0.2465</v>
       </c>
       <c r="J286" t="n">
-        <v>-8.8856</v>
+        <v>-7.1485</v>
       </c>
     </row>
     <row r="287">
@@ -13369,10 +13369,10 @@
         <v>1.27</v>
       </c>
       <c r="I287" t="n">
-        <v>0.4692</v>
+        <v>0.5528</v>
       </c>
       <c r="J287" t="n">
-        <v>13.6068</v>
+        <v>16.0312</v>
       </c>
     </row>
     <row r="288">
@@ -13409,10 +13409,10 @@
         <v>1.05</v>
       </c>
       <c r="I288" t="n">
-        <v>0.1184</v>
+        <v>0.1334</v>
       </c>
       <c r="J288" t="n">
-        <v>3.4336</v>
+        <v>3.8686</v>
       </c>
     </row>
     <row r="289">
@@ -13449,10 +13449,10 @@
         <v>0.99</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.0576</v>
+        <v>-0.0234</v>
       </c>
       <c r="J289" t="n">
-        <v>-1.6704</v>
+        <v>-0.6786</v>
       </c>
     </row>
     <row r="290">
@@ -13489,10 +13489,10 @@
         <v>0.98</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.0834</v>
+        <v>-0.0391</v>
       </c>
       <c r="J290" t="n">
-        <v>-2.4186</v>
+        <v>-1.1339</v>
       </c>
     </row>
     <row r="291">
@@ -13529,10 +13529,10 @@
         <v>0.88</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.2707</v>
+        <v>-0.16</v>
       </c>
       <c r="J291" t="n">
-        <v>-7.8503</v>
+        <v>-4.64</v>
       </c>
     </row>
     <row r="292">
@@ -13569,10 +13569,10 @@
         <v>1.21</v>
       </c>
       <c r="I292" t="n">
-        <v>0.3938</v>
+        <v>0.4532</v>
       </c>
       <c r="J292" t="n">
-        <v>11.0264</v>
+        <v>12.6896</v>
       </c>
     </row>
     <row r="293">
@@ -13609,10 +13609,10 @@
         <v>1.11</v>
       </c>
       <c r="I293" t="n">
-        <v>0.2402</v>
+        <v>0.2636</v>
       </c>
       <c r="J293" t="n">
-        <v>6.7256</v>
+        <v>7.3808</v>
       </c>
     </row>
     <row r="294">
@@ -13649,10 +13649,10 @@
         <v>1.01</v>
       </c>
       <c r="I294" t="n">
-        <v>0.0282</v>
+        <v>0.0365</v>
       </c>
       <c r="J294" t="n">
-        <v>0.7896</v>
+        <v>1.022</v>
       </c>
     </row>
     <row r="295">
@@ -13689,10 +13689,10 @@
         <v>0.93</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.1785</v>
+        <v>-0.1013</v>
       </c>
       <c r="J295" t="n">
-        <v>-4.998</v>
+        <v>-2.8364</v>
       </c>
     </row>
     <row r="296">
@@ -13729,10 +13729,10 @@
         <v>0.8</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.3863</v>
+        <v>-0.2404</v>
       </c>
       <c r="J296" t="n">
-        <v>-10.8164</v>
+        <v>-6.7312</v>
       </c>
     </row>
     <row r="297">
@@ -13769,10 +13769,10 @@
         <v>1.36</v>
       </c>
       <c r="I297" t="n">
-        <v>0.5651</v>
+        <v>0.4874</v>
       </c>
       <c r="J297" t="n">
-        <v>15.8228</v>
+        <v>13.6472</v>
       </c>
     </row>
     <row r="298">
@@ -13809,10 +13809,10 @@
         <v>1.34</v>
       </c>
       <c r="I298" t="n">
-        <v>0.5399</v>
+        <v>0.4639</v>
       </c>
       <c r="J298" t="n">
-        <v>15.1172</v>
+        <v>12.9892</v>
       </c>
     </row>
     <row r="299">
@@ -13849,10 +13849,10 @@
         <v>1.03</v>
       </c>
       <c r="I299" t="n">
-        <v>0.0368</v>
+        <v>0.0553</v>
       </c>
       <c r="J299" t="n">
-        <v>1.0304</v>
+        <v>1.5484</v>
       </c>
     </row>
     <row r="300">
@@ -13889,10 +13889,10 @@
         <v>1.02</v>
       </c>
       <c r="I300" t="n">
-        <v>0.0142</v>
+        <v>0.0368</v>
       </c>
       <c r="J300" t="n">
-        <v>0.3976</v>
+        <v>1.0304</v>
       </c>
     </row>
     <row r="301">
@@ -13929,10 +13929,10 @@
         <v>0.74</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.4845</v>
+        <v>-0.3085</v>
       </c>
       <c r="J301" t="n">
-        <v>-13.566</v>
+        <v>-8.638</v>
       </c>
     </row>
     <row r="302">
@@ -13969,10 +13969,10 @@
         <v>1.07</v>
       </c>
       <c r="I302" t="n">
-        <v>0.1841</v>
+        <v>0.1893</v>
       </c>
       <c r="J302" t="n">
-        <v>5.523</v>
+        <v>5.679</v>
       </c>
     </row>
     <row r="303">
@@ -14009,10 +14009,10 @@
         <v>1.07</v>
       </c>
       <c r="I303" t="n">
-        <v>0.1841</v>
+        <v>0.1893</v>
       </c>
       <c r="J303" t="n">
-        <v>5.523</v>
+        <v>5.679</v>
       </c>
     </row>
     <row r="304">
@@ -14049,10 +14049,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.1452</v>
+        <v>-0.0857</v>
       </c>
       <c r="J304" t="n">
-        <v>-4.356</v>
+        <v>-2.571</v>
       </c>
     </row>
     <row r="305">
@@ -14089,10 +14089,10 @@
         <v>0.93</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.1649</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="J305" t="n">
-        <v>-4.947</v>
+        <v>-2.928</v>
       </c>
     </row>
     <row r="306">
@@ -14129,10 +14129,10 @@
         <v>0.87</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.2703</v>
+        <v>-0.1641</v>
       </c>
       <c r="J306" t="n">
-        <v>-8.109</v>
+        <v>-4.923</v>
       </c>
     </row>
     <row r="307">
@@ -14169,10 +14169,10 @@
         <v>1.26</v>
       </c>
       <c r="I307" t="n">
-        <v>0.4158</v>
+        <v>0.3586</v>
       </c>
       <c r="J307" t="n">
-        <v>12.474</v>
+        <v>10.758</v>
       </c>
     </row>
     <row r="308">
@@ -14209,10 +14209,10 @@
         <v>1.21</v>
       </c>
       <c r="I308" t="n">
-        <v>0.3434</v>
+        <v>0.2981</v>
       </c>
       <c r="J308" t="n">
-        <v>10.302</v>
+        <v>8.943</v>
       </c>
     </row>
     <row r="309">
@@ -14249,10 +14249,10 @@
         <v>1.19</v>
       </c>
       <c r="I309" t="n">
-        <v>0.3125</v>
+        <v>0.2735</v>
       </c>
       <c r="J309" t="n">
-        <v>9.375</v>
+        <v>8.205</v>
       </c>
     </row>
     <row r="310">
@@ -14289,10 +14289,10 @@
         <v>1.08</v>
       </c>
       <c r="I310" t="n">
-        <v>0.1153</v>
+        <v>0.1286</v>
       </c>
       <c r="J310" t="n">
-        <v>3.459</v>
+        <v>3.858</v>
       </c>
     </row>
     <row r="311">
@@ -14329,10 +14329,10 @@
         <v>1.03</v>
       </c>
       <c r="I311" t="n">
-        <v>0.0199</v>
+        <v>0.0483</v>
       </c>
       <c r="J311" t="n">
-        <v>0.597</v>
+        <v>1.449</v>
       </c>
     </row>
     <row r="312">
@@ -14369,10 +14369,10 @@
         <v>1.7</v>
       </c>
       <c r="I312" t="n">
-        <v>1.5443</v>
+        <v>1.3578</v>
       </c>
       <c r="J312" t="n">
-        <v>35.5189</v>
+        <v>31.2294</v>
       </c>
     </row>
     <row r="313">
@@ -14409,10 +14409,10 @@
         <v>1.34</v>
       </c>
       <c r="I313" t="n">
-        <v>0.8037</v>
+        <v>0.855</v>
       </c>
       <c r="J313" t="n">
-        <v>18.4851</v>
+        <v>19.665</v>
       </c>
     </row>
     <row r="314">
@@ -14449,10 +14449,10 @@
         <v>1.29</v>
       </c>
       <c r="I314" t="n">
-        <v>0.6641</v>
+        <v>0.747</v>
       </c>
       <c r="J314" t="n">
-        <v>15.2743</v>
+        <v>17.181</v>
       </c>
     </row>
     <row r="315">
@@ -14489,10 +14489,10 @@
         <v>1.21</v>
       </c>
       <c r="I315" t="n">
-        <v>0.4683</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J315" t="n">
-        <v>10.7709</v>
+        <v>12.88</v>
       </c>
     </row>
     <row r="316">
@@ -14529,10 +14529,10 @@
         <v>1.1</v>
       </c>
       <c r="I316" t="n">
-        <v>0.1851</v>
+        <v>0.2726</v>
       </c>
       <c r="J316" t="n">
-        <v>4.2573</v>
+        <v>6.2698</v>
       </c>
     </row>
     <row r="317">
@@ -14569,10 +14569,10 @@
         <v>1.12</v>
       </c>
       <c r="I317" t="n">
-        <v>0.3261</v>
+        <v>0.3498</v>
       </c>
       <c r="J317" t="n">
-        <v>7.5003</v>
+        <v>8.045400000000001</v>
       </c>
     </row>
     <row r="318">
@@ -14609,10 +14609,10 @@
         <v>0.88</v>
       </c>
       <c r="I318" t="n">
-        <v>-0.1713</v>
+        <v>-0.1384</v>
       </c>
       <c r="J318" t="n">
-        <v>-3.9399</v>
+        <v>-3.1832</v>
       </c>
     </row>
     <row r="319">
@@ -14649,10 +14649,10 @@
         <v>0.78</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.3596</v>
+        <v>-0.2378</v>
       </c>
       <c r="J319" t="n">
-        <v>-8.270799999999999</v>
+        <v>-5.4694</v>
       </c>
     </row>
     <row r="320">
@@ -14689,10 +14689,10 @@
         <v>0.73</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.4365</v>
+        <v>-0.2861</v>
       </c>
       <c r="J320" t="n">
-        <v>-10.0395</v>
+        <v>-6.5803</v>
       </c>
     </row>
     <row r="321">
@@ -14729,10 +14729,10 @@
         <v>0.64</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.5624</v>
+        <v>-0.3715</v>
       </c>
       <c r="J321" t="n">
-        <v>-12.9352</v>
+        <v>-8.544499999999999</v>
       </c>
     </row>
     <row r="322">
@@ -14769,10 +14769,10 @@
         <v>1.11</v>
       </c>
       <c r="I322" t="n">
-        <v>0.2471</v>
+        <v>0.2682</v>
       </c>
       <c r="J322" t="n">
-        <v>10.3782</v>
+        <v>11.2644</v>
       </c>
     </row>
     <row r="323">
@@ -14809,10 +14809,10 @@
         <v>1.06</v>
       </c>
       <c r="I323" t="n">
-        <v>0.1578</v>
+        <v>0.1631</v>
       </c>
       <c r="J323" t="n">
-        <v>6.6276</v>
+        <v>6.8502</v>
       </c>
     </row>
     <row r="324">
@@ -14849,10 +14849,10 @@
         <v>1.02</v>
       </c>
       <c r="I324" t="n">
-        <v>0.0713</v>
+        <v>0.067</v>
       </c>
       <c r="J324" t="n">
-        <v>2.9946</v>
+        <v>2.814</v>
       </c>
     </row>
     <row r="325">
@@ -14889,10 +14889,10 @@
         <v>1</v>
       </c>
       <c r="I325" t="n">
-        <v>0.0065</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="J325" t="n">
-        <v>0.273</v>
+        <v>0.0252</v>
       </c>
     </row>
     <row r="326">
@@ -14929,10 +14929,10 @@
         <v>0.78</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.4108</v>
+        <v>-0.2582</v>
       </c>
       <c r="J326" t="n">
-        <v>-17.2536</v>
+        <v>-10.8444</v>
       </c>
     </row>
     <row r="327">
@@ -14969,10 +14969,10 @@
         <v>1.31</v>
       </c>
       <c r="I327" t="n">
-        <v>0.8789</v>
+        <v>0.8567</v>
       </c>
       <c r="J327" t="n">
-        <v>36.9138</v>
+        <v>35.9814</v>
       </c>
     </row>
     <row r="328">
@@ -15009,10 +15009,10 @@
         <v>1.09</v>
       </c>
       <c r="I328" t="n">
-        <v>0.2951</v>
+        <v>0.2976</v>
       </c>
       <c r="J328" t="n">
-        <v>12.3942</v>
+        <v>12.4992</v>
       </c>
     </row>
     <row r="329">
@@ -15049,10 +15049,10 @@
         <v>1.08</v>
       </c>
       <c r="I329" t="n">
-        <v>0.252</v>
+        <v>0.2699</v>
       </c>
       <c r="J329" t="n">
-        <v>10.584</v>
+        <v>11.3358</v>
       </c>
     </row>
     <row r="330">
@@ -15089,10 +15089,10 @@
         <v>1.01</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.012</v>
+        <v>0.0354</v>
       </c>
       <c r="J330" t="n">
-        <v>-0.504</v>
+        <v>1.4868</v>
       </c>
     </row>
     <row r="331">
@@ -15129,10 +15129,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.3167</v>
+        <v>-0.2526</v>
       </c>
       <c r="J331" t="n">
-        <v>-13.3014</v>
+        <v>-10.6092</v>
       </c>
     </row>
     <row r="332">
@@ -15169,10 +15169,10 @@
         <v>1.35</v>
       </c>
       <c r="I332" t="n">
-        <v>0.9042</v>
+        <v>0.9061</v>
       </c>
       <c r="J332" t="n">
-        <v>22.605</v>
+        <v>22.6525</v>
       </c>
     </row>
     <row r="333">
@@ -15209,10 +15209,10 @@
         <v>1.22</v>
       </c>
       <c r="I333" t="n">
-        <v>0.5864</v>
+        <v>0.6063</v>
       </c>
       <c r="J333" t="n">
-        <v>14.66</v>
+        <v>15.1575</v>
       </c>
     </row>
     <row r="334">
@@ -15249,10 +15249,10 @@
         <v>1.21</v>
       </c>
       <c r="I334" t="n">
-        <v>0.5566</v>
+        <v>0.5829</v>
       </c>
       <c r="J334" t="n">
-        <v>13.915</v>
+        <v>14.5725</v>
       </c>
     </row>
     <row r="335">
@@ -15289,10 +15289,10 @@
         <v>1.15</v>
       </c>
       <c r="I335" t="n">
-        <v>0.3754</v>
+        <v>0.4363</v>
       </c>
       <c r="J335" t="n">
-        <v>9.385</v>
+        <v>10.9075</v>
       </c>
     </row>
     <row r="336">
@@ -15329,10 +15329,10 @@
         <v>1.09</v>
       </c>
       <c r="I336" t="n">
-        <v>0.2051</v>
+        <v>0.273</v>
       </c>
       <c r="J336" t="n">
-        <v>5.1275</v>
+        <v>6.825</v>
       </c>
     </row>
     <row r="337">
@@ -15369,10 +15369,10 @@
         <v>1.12</v>
       </c>
       <c r="I337" t="n">
-        <v>0.2792</v>
+        <v>0.3006</v>
       </c>
       <c r="J337" t="n">
-        <v>6.98</v>
+        <v>7.515</v>
       </c>
     </row>
     <row r="338">
@@ -15409,10 +15409,10 @@
         <v>1.06</v>
       </c>
       <c r="I338" t="n">
-        <v>0.175</v>
+        <v>0.1734</v>
       </c>
       <c r="J338" t="n">
-        <v>4.375</v>
+        <v>4.335</v>
       </c>
     </row>
     <row r="339">
@@ -15449,10 +15449,10 @@
         <v>0.98</v>
       </c>
       <c r="I339" t="n">
-        <v>-0.0323</v>
+        <v>-0.0325</v>
       </c>
       <c r="J339" t="n">
-        <v>-0.8075</v>
+        <v>-0.8125</v>
       </c>
     </row>
     <row r="340">
@@ -15489,10 +15489,10 @@
         <v>0.82</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.3416</v>
+        <v>-0.2131</v>
       </c>
       <c r="J340" t="n">
-        <v>-8.539999999999999</v>
+        <v>-5.3275</v>
       </c>
     </row>
     <row r="341">
@@ -15529,10 +15529,10 @@
         <v>0.78</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.4007</v>
+        <v>-0.2532</v>
       </c>
       <c r="J341" t="n">
-        <v>-10.0175</v>
+        <v>-6.33</v>
       </c>
     </row>
     <row r="342">
@@ -15569,10 +15569,10 @@
         <v>1.28</v>
       </c>
       <c r="I342" t="n">
-        <v>0.4859</v>
+        <v>0.5736</v>
       </c>
       <c r="J342" t="n">
-        <v>20.4078</v>
+        <v>24.0912</v>
       </c>
     </row>
     <row r="343">
@@ -15609,10 +15609,10 @@
         <v>1.19</v>
       </c>
       <c r="I343" t="n">
-        <v>0.3607</v>
+        <v>0.413</v>
       </c>
       <c r="J343" t="n">
-        <v>15.1494</v>
+        <v>17.346</v>
       </c>
     </row>
     <row r="344">
@@ -15649,10 +15649,10 @@
         <v>1.13</v>
       </c>
       <c r="I344" t="n">
-        <v>0.2686</v>
+        <v>0.3</v>
       </c>
       <c r="J344" t="n">
-        <v>11.2812</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="345">
@@ -15689,10 +15689,10 @@
         <v>0.76</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.4448</v>
+        <v>-0.2813</v>
       </c>
       <c r="J345" t="n">
-        <v>-18.6816</v>
+        <v>-11.8146</v>
       </c>
     </row>
     <row r="346">
@@ -15729,10 +15729,10 @@
         <v>0.76</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.4448</v>
+        <v>-0.2813</v>
       </c>
       <c r="J346" t="n">
-        <v>-18.6816</v>
+        <v>-11.8146</v>
       </c>
     </row>
     <row r="347">
@@ -15769,10 +15769,10 @@
         <v>1.35</v>
       </c>
       <c r="I347" t="n">
-        <v>0.9646</v>
+        <v>0.946</v>
       </c>
       <c r="J347" t="n">
-        <v>40.5132</v>
+        <v>39.732</v>
       </c>
     </row>
     <row r="348">
@@ -15809,10 +15809,10 @@
         <v>1.28</v>
       </c>
       <c r="I348" t="n">
-        <v>0.8066</v>
+        <v>0.7824</v>
       </c>
       <c r="J348" t="n">
-        <v>33.8772</v>
+        <v>32.8608</v>
       </c>
     </row>
     <row r="349">
@@ -15849,10 +15849,10 @@
         <v>1.24</v>
       </c>
       <c r="I349" t="n">
-        <v>0.7114</v>
+        <v>0.6851</v>
       </c>
       <c r="J349" t="n">
-        <v>29.8788</v>
+        <v>28.7742</v>
       </c>
     </row>
     <row r="350">
@@ -15889,10 +15889,10 @@
         <v>0.85</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.5748</v>
+        <v>-0.515</v>
       </c>
       <c r="J350" t="n">
-        <v>-24.1416</v>
+        <v>-21.63</v>
       </c>
     </row>
     <row r="351">
@@ -15929,10 +15929,10 @@
         <v>0.74</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.8413</v>
+        <v>-0.8002</v>
       </c>
       <c r="J351" t="n">
-        <v>-35.3346</v>
+        <v>-33.6084</v>
       </c>
     </row>
     <row r="352">
@@ -15969,10 +15969,10 @@
         <v>1.62</v>
       </c>
       <c r="I352" t="n">
-        <v>1.4699</v>
+        <v>1.3022</v>
       </c>
       <c r="J352" t="n">
-        <v>39.6873</v>
+        <v>35.1594</v>
       </c>
     </row>
     <row r="353">
@@ -16009,10 +16009,10 @@
         <v>1.56</v>
       </c>
       <c r="I353" t="n">
-        <v>1.3552</v>
+        <v>1.2261</v>
       </c>
       <c r="J353" t="n">
-        <v>36.5904</v>
+        <v>33.1047</v>
       </c>
     </row>
     <row r="354">
@@ -16049,10 +16049,10 @@
         <v>1.18</v>
       </c>
       <c r="I354" t="n">
-        <v>0.5009</v>
+        <v>0.5164</v>
       </c>
       <c r="J354" t="n">
-        <v>13.5243</v>
+        <v>13.9428</v>
       </c>
     </row>
     <row r="355">
@@ -16089,10 +16089,10 @@
         <v>0.77</v>
       </c>
       <c r="I355" t="n">
-        <v>-0.7927</v>
+        <v>-0.7445000000000001</v>
       </c>
       <c r="J355" t="n">
-        <v>-21.4029</v>
+        <v>-20.1015</v>
       </c>
     </row>
     <row r="356">
@@ -16129,10 +16129,10 @@
         <v>0.72</v>
       </c>
       <c r="I356" t="n">
-        <v>-0.9054</v>
+        <v>-0.869</v>
       </c>
       <c r="J356" t="n">
-        <v>-24.4458</v>
+        <v>-23.463</v>
       </c>
     </row>
     <row r="357">
@@ -16169,10 +16169,10 @@
         <v>1.03</v>
       </c>
       <c r="I357" t="n">
-        <v>0.1307</v>
+        <v>0.1128</v>
       </c>
       <c r="J357" t="n">
-        <v>3.5289</v>
+        <v>3.0456</v>
       </c>
     </row>
     <row r="358">
@@ -16209,10 +16209,10 @@
         <v>0.99</v>
       </c>
       <c r="I358" t="n">
-        <v>0.0128</v>
+        <v>-0.0118</v>
       </c>
       <c r="J358" t="n">
-        <v>0.3456</v>
+        <v>-0.3186</v>
       </c>
     </row>
     <row r="359">
@@ -16249,10 +16249,10 @@
         <v>0.97</v>
       </c>
       <c r="I359" t="n">
-        <v>-0.0362</v>
+        <v>-0.0421</v>
       </c>
       <c r="J359" t="n">
-        <v>-0.9774</v>
+        <v>-1.1367</v>
       </c>
     </row>
     <row r="360">
@@ -16289,10 +16289,10 @@
         <v>0.93</v>
       </c>
       <c r="I360" t="n">
-        <v>-0.1211</v>
+        <v>-0.09229999999999999</v>
       </c>
       <c r="J360" t="n">
-        <v>-3.2697</v>
+        <v>-2.4921</v>
       </c>
     </row>
     <row r="361">
@@ -16329,10 +16329,10 @@
         <v>0.64</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.581</v>
+        <v>-0.3823</v>
       </c>
       <c r="J361" t="n">
-        <v>-15.687</v>
+        <v>-10.3221</v>
       </c>
     </row>
     <row r="362">
@@ -16369,10 +16369,10 @@
         <v>1.35</v>
       </c>
       <c r="I362" t="n">
-        <v>0.6203</v>
+        <v>0.7524</v>
       </c>
       <c r="J362" t="n">
-        <v>16.1278</v>
+        <v>19.5624</v>
       </c>
     </row>
     <row r="363">
@@ -16409,10 +16409,10 @@
         <v>0.83</v>
       </c>
       <c r="I363" t="n">
-        <v>-0.3078</v>
+        <v>-0.1965</v>
       </c>
       <c r="J363" t="n">
-        <v>-8.002800000000001</v>
+        <v>-5.109</v>
       </c>
     </row>
     <row r="364">
@@ -16449,10 +16449,10 @@
         <v>0.8</v>
       </c>
       <c r="I364" t="n">
-        <v>-0.3551</v>
+        <v>-0.2266</v>
       </c>
       <c r="J364" t="n">
-        <v>-9.2326</v>
+        <v>-5.8916</v>
       </c>
     </row>
     <row r="365">
@@ -16489,10 +16489,10 @@
         <v>0.76</v>
       </c>
       <c r="I365" t="n">
-        <v>-0.4147</v>
+        <v>-0.2661</v>
       </c>
       <c r="J365" t="n">
-        <v>-10.7822</v>
+        <v>-6.9186</v>
       </c>
     </row>
     <row r="366">
@@ -16529,10 +16529,10 @@
         <v>0.75</v>
       </c>
       <c r="I366" t="n">
-        <v>-0.4291</v>
+        <v>-0.2758</v>
       </c>
       <c r="J366" t="n">
-        <v>-11.1566</v>
+        <v>-7.1708</v>
       </c>
     </row>
     <row r="367">
@@ -16569,10 +16569,10 @@
         <v>1.51</v>
       </c>
       <c r="I367" t="n">
-        <v>1.2611</v>
+        <v>1.1642</v>
       </c>
       <c r="J367" t="n">
-        <v>32.7886</v>
+        <v>30.2692</v>
       </c>
     </row>
     <row r="368">
@@ -16609,10 +16609,10 @@
         <v>1.25</v>
       </c>
       <c r="I368" t="n">
-        <v>0.6942</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="J368" t="n">
-        <v>18.0492</v>
+        <v>17.862</v>
       </c>
     </row>
     <row r="369">
@@ -16649,10 +16649,10 @@
         <v>1.09</v>
       </c>
       <c r="I369" t="n">
-        <v>0.2267</v>
+        <v>0.2829</v>
       </c>
       <c r="J369" t="n">
-        <v>5.8942</v>
+        <v>7.3554</v>
       </c>
     </row>
     <row r="370">
@@ -16689,10 +16689,10 @@
         <v>1.05</v>
       </c>
       <c r="I370" t="n">
-        <v>0.1006</v>
+        <v>0.1617</v>
       </c>
       <c r="J370" t="n">
-        <v>2.6156</v>
+        <v>4.2042</v>
       </c>
     </row>
     <row r="371">
@@ -16729,10 +16729,10 @@
         <v>0.91</v>
       </c>
       <c r="I371" t="n">
-        <v>-0.4362</v>
+        <v>-0.3645</v>
       </c>
       <c r="J371" t="n">
-        <v>-11.3412</v>
+        <v>-9.477</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/4566/event_4566_evp_summary.xlsx
+++ b/database/event/4566/event_4566_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.7082</v>
+        <v>9.0229</v>
       </c>
       <c r="C2" t="n">
-        <v>1.9663</v>
+        <v>2.0373</v>
       </c>
       <c r="D2" t="n">
-        <v>3.2933</v>
+        <v>3.4832</v>
       </c>
       <c r="E2" t="n">
-        <v>8.7082</v>
+        <v>9.0229</v>
       </c>
       <c r="F2" t="n">
-        <v>4.4518</v>
+        <v>4.5807</v>
       </c>
       <c r="G2" t="n">
-        <v>4.2564</v>
+        <v>4.4423</v>
       </c>
       <c r="H2" t="n">
-        <v>13.1512</v>
+        <v>12.3807</v>
       </c>
       <c r="I2" t="n">
-        <v>6.838</v>
+        <v>6.6855</v>
       </c>
       <c r="J2" t="n">
-        <v>4.2564</v>
+        <v>4.4423</v>
       </c>
       <c r="K2" t="n">
         <v>286</v>
@@ -529,7 +529,7 @@
         <v>142</v>
       </c>
       <c r="M2" t="n">
-        <v>11.0944</v>
+        <v>11.1278</v>
       </c>
       <c r="N2" t="n">
         <v>428</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.7059</v>
+        <v>5.7861</v>
       </c>
       <c r="C3" t="n">
-        <v>1.2884</v>
+        <v>1.3065</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9379</v>
+        <v>2.0097</v>
       </c>
       <c r="E3" t="n">
-        <v>5.7059</v>
+        <v>5.7861</v>
       </c>
       <c r="F3" t="n">
-        <v>4.4217</v>
+        <v>4.3852</v>
       </c>
       <c r="G3" t="n">
-        <v>1.2842</v>
+        <v>1.4009</v>
       </c>
       <c r="H3" t="n">
-        <v>10.093</v>
+        <v>9.574199999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>5.2479</v>
+        <v>5.17</v>
       </c>
       <c r="J3" t="n">
-        <v>1.2842</v>
+        <v>1.4009</v>
       </c>
       <c r="K3" t="n">
         <v>257</v>
@@ -575,7 +575,7 @@
         <v>102</v>
       </c>
       <c r="M3" t="n">
-        <v>6.5321</v>
+        <v>6.5709</v>
       </c>
       <c r="N3" t="n">
         <v>359</v>
@@ -584,93 +584,93 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ALEX</t>
+          <t>sergej</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.9677</v>
+        <v>4.0311</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8959</v>
+        <v>0.9102</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1532</v>
+        <v>1.2108</v>
       </c>
       <c r="E4" t="n">
-        <v>3.9677</v>
+        <v>4.0311</v>
       </c>
       <c r="F4" t="n">
-        <v>3.3824</v>
+        <v>2.7267</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5853</v>
+        <v>1.3044</v>
       </c>
       <c r="H4" t="n">
-        <v>6.4311</v>
+        <v>4.1023</v>
       </c>
       <c r="I4" t="n">
-        <v>3.3439</v>
+        <v>2.2152</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5853</v>
+        <v>1.3044</v>
       </c>
       <c r="K4" t="n">
-        <v>286</v>
+        <v>255</v>
       </c>
       <c r="L4" t="n">
-        <v>142</v>
+        <v>88</v>
       </c>
       <c r="M4" t="n">
-        <v>3.9292</v>
+        <v>3.5196</v>
       </c>
       <c r="N4" t="n">
-        <v>428</v>
+        <v>343</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>sergej</t>
+          <t>ALEX</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.9604</v>
+        <v>4.0043</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8942</v>
+        <v>0.9041</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1499</v>
+        <v>1.1986</v>
       </c>
       <c r="E5" t="n">
-        <v>3.9604</v>
+        <v>4.0043</v>
       </c>
       <c r="F5" t="n">
-        <v>2.7632</v>
+        <v>3.3208</v>
       </c>
       <c r="G5" t="n">
-        <v>1.1972</v>
+        <v>0.6835</v>
       </c>
       <c r="H5" t="n">
-        <v>4.2496</v>
+        <v>6.0625</v>
       </c>
       <c r="I5" t="n">
-        <v>2.2096</v>
+        <v>3.2737</v>
       </c>
       <c r="J5" t="n">
-        <v>1.1972</v>
+        <v>0.6835</v>
       </c>
       <c r="K5" t="n">
-        <v>255</v>
+        <v>286</v>
       </c>
       <c r="L5" t="n">
-        <v>88</v>
+        <v>142</v>
       </c>
       <c r="M5" t="n">
-        <v>3.4068</v>
+        <v>3.9572</v>
       </c>
       <c r="N5" t="n">
-        <v>343</v>
+        <v>428</v>
       </c>
     </row>
     <row r="6">
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.8983</v>
+        <v>3.9624</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8802</v>
+        <v>0.8947000000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1219</v>
+        <v>1.1796</v>
       </c>
       <c r="E6" t="n">
-        <v>3.8983</v>
+        <v>3.9624</v>
       </c>
       <c r="F6" t="n">
-        <v>2.4659</v>
+        <v>2.3984</v>
       </c>
       <c r="G6" t="n">
-        <v>1.4324</v>
+        <v>1.564</v>
       </c>
       <c r="H6" t="n">
-        <v>3.202</v>
+        <v>3.0189</v>
       </c>
       <c r="I6" t="n">
-        <v>1.6649</v>
+        <v>1.6302</v>
       </c>
       <c r="J6" t="n">
-        <v>1.4324</v>
+        <v>1.564</v>
       </c>
       <c r="K6" t="n">
         <v>257</v>
@@ -713,7 +713,7 @@
         <v>102</v>
       </c>
       <c r="M6" t="n">
-        <v>3.0973</v>
+        <v>3.1942</v>
       </c>
       <c r="N6" t="n">
         <v>359</v>
@@ -722,93 +722,93 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CeRq</t>
+          <t>NBK-</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.6587</v>
+        <v>3.6154</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8260999999999999</v>
+        <v>0.8163</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0137</v>
+        <v>1.0216</v>
       </c>
       <c r="E7" t="n">
-        <v>3.6587</v>
+        <v>3.6154</v>
       </c>
       <c r="F7" t="n">
-        <v>3.565</v>
+        <v>2.4031</v>
       </c>
       <c r="G7" t="n">
-        <v>0.09370000000000001</v>
+        <v>1.2123</v>
       </c>
       <c r="H7" t="n">
-        <v>7.0747</v>
+        <v>3.0345</v>
       </c>
       <c r="I7" t="n">
-        <v>3.6785</v>
+        <v>1.6386</v>
       </c>
       <c r="J7" t="n">
-        <v>0.09370000000000001</v>
+        <v>1.2123</v>
       </c>
       <c r="K7" t="n">
-        <v>269</v>
+        <v>286</v>
       </c>
       <c r="L7" t="n">
-        <v>48</v>
+        <v>142</v>
       </c>
       <c r="M7" t="n">
-        <v>3.7722</v>
+        <v>2.8509</v>
       </c>
       <c r="N7" t="n">
-        <v>317</v>
+        <v>428</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NBK-</t>
+          <t>CeRq</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.6241</v>
+        <v>3.5941</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8183</v>
+        <v>0.8115</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9981</v>
+        <v>1.0119</v>
       </c>
       <c r="E8" t="n">
-        <v>3.6241</v>
+        <v>3.5941</v>
       </c>
       <c r="F8" t="n">
-        <v>2.4465</v>
+        <v>3.5172</v>
       </c>
       <c r="G8" t="n">
-        <v>1.1776</v>
+        <v>0.0769</v>
       </c>
       <c r="H8" t="n">
-        <v>3.1335</v>
+        <v>6.7105</v>
       </c>
       <c r="I8" t="n">
-        <v>1.6293</v>
+        <v>3.6236</v>
       </c>
       <c r="J8" t="n">
-        <v>1.1776</v>
+        <v>0.0769</v>
       </c>
       <c r="K8" t="n">
-        <v>286</v>
+        <v>269</v>
       </c>
       <c r="L8" t="n">
-        <v>142</v>
+        <v>48</v>
       </c>
       <c r="M8" t="n">
-        <v>2.8069</v>
+        <v>3.7005</v>
       </c>
       <c r="N8" t="n">
-        <v>428</v>
+        <v>317</v>
       </c>
     </row>
     <row r="9">
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.5426</v>
+        <v>3.535</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7999000000000001</v>
+        <v>0.7982</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9613</v>
+        <v>0.985</v>
       </c>
       <c r="E9" t="n">
-        <v>3.5426</v>
+        <v>3.535</v>
       </c>
       <c r="F9" t="n">
-        <v>3.2054</v>
+        <v>3.1577</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3372</v>
+        <v>0.3773</v>
       </c>
       <c r="H9" t="n">
-        <v>5.8076</v>
+        <v>5.5243</v>
       </c>
       <c r="I9" t="n">
-        <v>3.0197</v>
+        <v>2.9831</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3372</v>
+        <v>0.3773</v>
       </c>
       <c r="K9" t="n">
         <v>269</v>
@@ -851,7 +851,7 @@
         <v>48</v>
       </c>
       <c r="M9" t="n">
-        <v>3.3569</v>
+        <v>3.3604</v>
       </c>
       <c r="N9" t="n">
         <v>317</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.4898</v>
+        <v>3.4636</v>
       </c>
       <c r="C10" t="n">
-        <v>0.788</v>
+        <v>0.7821</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9375</v>
+        <v>0.9525</v>
       </c>
       <c r="E10" t="n">
-        <v>3.4898</v>
+        <v>3.4636</v>
       </c>
       <c r="F10" t="n">
-        <v>3.1921</v>
+        <v>3.0912</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2977</v>
+        <v>0.3724</v>
       </c>
       <c r="H10" t="n">
-        <v>5.7605</v>
+        <v>5.3047</v>
       </c>
       <c r="I10" t="n">
-        <v>2.9952</v>
+        <v>2.8645</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2977</v>
+        <v>0.3724</v>
       </c>
       <c r="K10" t="n">
         <v>257</v>
@@ -897,7 +897,7 @@
         <v>102</v>
       </c>
       <c r="M10" t="n">
-        <v>3.2929</v>
+        <v>3.2369</v>
       </c>
       <c r="N10" t="n">
         <v>359</v>
@@ -906,93 +906,93 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.4455</v>
+        <v>3.4322</v>
       </c>
       <c r="C11" t="n">
-        <v>0.778</v>
+        <v>0.775</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9175</v>
+        <v>0.9382</v>
       </c>
       <c r="E11" t="n">
-        <v>3.4455</v>
+        <v>3.4322</v>
       </c>
       <c r="F11" t="n">
-        <v>3.7036</v>
+        <v>2.1444</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.2581</v>
+        <v>1.2878</v>
       </c>
       <c r="H11" t="n">
-        <v>7.5628</v>
+        <v>2.181</v>
       </c>
       <c r="I11" t="n">
-        <v>3.9323</v>
+        <v>1.1777</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.2581</v>
+        <v>1.2878</v>
       </c>
       <c r="K11" t="n">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="L11" t="n">
-        <v>48</v>
+        <v>102</v>
       </c>
       <c r="M11" t="n">
-        <v>3.6742</v>
+        <v>2.4655</v>
       </c>
       <c r="N11" t="n">
-        <v>317</v>
+        <v>359</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.4275</v>
+        <v>3.3099</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7739</v>
+        <v>0.7474</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9093</v>
+        <v>0.8825</v>
       </c>
       <c r="E12" t="n">
-        <v>3.4275</v>
+        <v>3.3099</v>
       </c>
       <c r="F12" t="n">
-        <v>2.2073</v>
+        <v>3.5928</v>
       </c>
       <c r="G12" t="n">
-        <v>1.2202</v>
+        <v>-0.2829</v>
       </c>
       <c r="H12" t="n">
-        <v>2.291</v>
+        <v>6.9597</v>
       </c>
       <c r="I12" t="n">
-        <v>1.1912</v>
+        <v>3.7582</v>
       </c>
       <c r="J12" t="n">
-        <v>1.2202</v>
+        <v>-0.2829</v>
       </c>
       <c r="K12" t="n">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="L12" t="n">
-        <v>102</v>
+        <v>48</v>
       </c>
       <c r="M12" t="n">
-        <v>2.4114</v>
+        <v>3.4753</v>
       </c>
       <c r="N12" t="n">
-        <v>359</v>
+        <v>317</v>
       </c>
     </row>
     <row r="13">
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.2577</v>
+        <v>3.2921</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7356</v>
+        <v>0.7433</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8327</v>
+        <v>0.8744</v>
       </c>
       <c r="E13" t="n">
-        <v>3.2577</v>
+        <v>3.2921</v>
       </c>
       <c r="F13" t="n">
-        <v>3.7645</v>
+        <v>3.7401</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.5068</v>
+        <v>-0.448</v>
       </c>
       <c r="H13" t="n">
-        <v>7.7774</v>
+        <v>7.4459</v>
       </c>
       <c r="I13" t="n">
-        <v>4.0439</v>
+        <v>4.0207</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.5068</v>
+        <v>-0.448</v>
       </c>
       <c r="K13" t="n">
         <v>286</v>
@@ -1035,7 +1035,7 @@
         <v>142</v>
       </c>
       <c r="M13" t="n">
-        <v>3.5371</v>
+        <v>3.5727</v>
       </c>
       <c r="N13" t="n">
         <v>428</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.5517</v>
+        <v>2.564</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5762</v>
+        <v>0.5789</v>
       </c>
       <c r="D14" t="n">
-        <v>0.514</v>
+        <v>0.543</v>
       </c>
       <c r="E14" t="n">
-        <v>2.5517</v>
+        <v>2.564</v>
       </c>
       <c r="F14" t="n">
-        <v>2.3174</v>
+        <v>2.2994</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2343</v>
+        <v>0.2646</v>
       </c>
       <c r="H14" t="n">
-        <v>2.6789</v>
+        <v>2.6923</v>
       </c>
       <c r="I14" t="n">
-        <v>1.3929</v>
+        <v>1.4538</v>
       </c>
       <c r="J14" t="n">
-        <v>0.2343</v>
+        <v>0.2646</v>
       </c>
       <c r="K14" t="n">
         <v>286</v>
@@ -1081,7 +1081,7 @@
         <v>142</v>
       </c>
       <c r="M14" t="n">
-        <v>1.6272</v>
+        <v>1.7184</v>
       </c>
       <c r="N14" t="n">
         <v>428</v>
@@ -1094,28 +1094,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.4686</v>
+        <v>2.3424</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5574</v>
+        <v>0.5289</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4764</v>
+        <v>0.4421</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4686</v>
+        <v>2.3424</v>
       </c>
       <c r="F15" t="n">
-        <v>2.4686</v>
+        <v>2.3424</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2.4686</v>
+        <v>2.4019</v>
       </c>
       <c r="I15" t="n">
-        <v>2.4686</v>
+        <v>2.4019</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.4686</v>
+        <v>2.4019</v>
       </c>
       <c r="N15" t="n">
         <v>280</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.3695</v>
+        <v>2.2824</v>
       </c>
       <c r="C16" t="n">
-        <v>0.535</v>
+        <v>0.5154</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4317</v>
+        <v>0.4148</v>
       </c>
       <c r="E16" t="n">
-        <v>2.3695</v>
+        <v>2.2824</v>
       </c>
       <c r="F16" t="n">
-        <v>2.2741</v>
+        <v>2.1995</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0954</v>
+        <v>0.0829</v>
       </c>
       <c r="H16" t="n">
-        <v>2.5264</v>
+        <v>2.3628</v>
       </c>
       <c r="I16" t="n">
-        <v>1.3136</v>
+        <v>1.2759</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0954</v>
+        <v>0.0829</v>
       </c>
       <c r="K16" t="n">
         <v>255</v>
@@ -1173,7 +1173,7 @@
         <v>88</v>
       </c>
       <c r="M16" t="n">
-        <v>1.409</v>
+        <v>1.3588</v>
       </c>
       <c r="N16" t="n">
         <v>343</v>
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.3615</v>
+        <v>2.262</v>
       </c>
       <c r="C17" t="n">
-        <v>0.5332</v>
+        <v>0.5107</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4281</v>
+        <v>0.4055</v>
       </c>
       <c r="E17" t="n">
-        <v>2.3615</v>
+        <v>2.262</v>
       </c>
       <c r="F17" t="n">
-        <v>2.3615</v>
+        <v>2.262</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>2.3615</v>
+        <v>2.262</v>
       </c>
       <c r="I17" t="n">
-        <v>2.3615</v>
+        <v>2.262</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>2.3615</v>
+        <v>2.262</v>
       </c>
       <c r="N17" t="n">
         <v>277</v>
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.2971</v>
+        <v>2.2279</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5187</v>
+        <v>0.503</v>
       </c>
       <c r="D18" t="n">
-        <v>0.399</v>
+        <v>0.39</v>
       </c>
       <c r="E18" t="n">
-        <v>2.2971</v>
+        <v>2.2279</v>
       </c>
       <c r="F18" t="n">
-        <v>2.89</v>
+        <v>2.8498</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.5929</v>
+        <v>-0.6219</v>
       </c>
       <c r="H18" t="n">
-        <v>4.6962</v>
+        <v>4.5082</v>
       </c>
       <c r="I18" t="n">
-        <v>2.4418</v>
+        <v>2.4344</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.5929</v>
+        <v>-0.6219</v>
       </c>
       <c r="K18" t="n">
         <v>269</v>
@@ -1265,7 +1265,7 @@
         <v>48</v>
       </c>
       <c r="M18" t="n">
-        <v>1.8489</v>
+        <v>1.8125</v>
       </c>
       <c r="N18" t="n">
         <v>317</v>
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9441000000000001</v>
+        <v>0.8749</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2132</v>
+        <v>0.1975</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2118</v>
+        <v>-0.2259</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9441000000000001</v>
+        <v>0.8749</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7406</v>
+        <v>0.6526</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2035</v>
+        <v>0.2223</v>
       </c>
       <c r="H19" t="n">
-        <v>0.7406</v>
+        <v>0.6526</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3851</v>
+        <v>0.3524</v>
       </c>
       <c r="J19" t="n">
-        <v>0.2035</v>
+        <v>0.2223</v>
       </c>
       <c r="K19" t="n">
         <v>255</v>
@@ -1311,7 +1311,7 @@
         <v>88</v>
       </c>
       <c r="M19" t="n">
-        <v>0.5886</v>
+        <v>0.5747</v>
       </c>
       <c r="N19" t="n">
         <v>343</v>
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.802</v>
+        <v>0.8007</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1811</v>
+        <v>0.1808</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.276</v>
+        <v>-0.2597</v>
       </c>
       <c r="E20" t="n">
-        <v>0.802</v>
+        <v>0.8007</v>
       </c>
       <c r="F20" t="n">
-        <v>0.802</v>
+        <v>0.8007</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.802</v>
+        <v>0.8007</v>
       </c>
       <c r="I20" t="n">
-        <v>0.802</v>
+        <v>0.8007</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.802</v>
+        <v>0.8007</v>
       </c>
       <c r="N20" t="n">
         <v>280</v>
@@ -1366,93 +1366,93 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>daps</t>
+          <t>jkaem</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6105</v>
+        <v>0.5145</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1378</v>
+        <v>0.1162</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3624</v>
+        <v>-0.39</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6105</v>
+        <v>0.5145</v>
       </c>
       <c r="F21" t="n">
-        <v>1.2853</v>
+        <v>0.5145</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.6748</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.2853</v>
+        <v>0.5145</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6683</v>
+        <v>0.5145</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.6748</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="L21" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.00649999999999995</v>
+        <v>0.5145</v>
       </c>
       <c r="N21" t="n">
-        <v>317</v>
+        <v>280</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>jkaem</t>
+          <t>daps</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.5288</v>
+        <v>0.4174</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1194</v>
+        <v>0.09420000000000001</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3993</v>
+        <v>-0.4342</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5288</v>
+        <v>0.4174</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5288</v>
+        <v>1.1211</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>-0.7037</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5288</v>
+        <v>1.1211</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5288</v>
+        <v>0.6054</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>-0.7037</v>
       </c>
       <c r="K22" t="n">
-        <v>280</v>
+        <v>269</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M22" t="n">
-        <v>0.5288</v>
+        <v>-0.09829999999999994</v>
       </c>
       <c r="N22" t="n">
-        <v>280</v>
+        <v>317</v>
       </c>
     </row>
     <row r="23">
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.3944</v>
+        <v>0.3036</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0891</v>
+        <v>0.06859999999999999</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.46</v>
+        <v>-0.486</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3944</v>
+        <v>0.3036</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3944</v>
+        <v>0.3036</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3944</v>
+        <v>0.3036</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3944</v>
+        <v>0.3036</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.3944</v>
+        <v>0.3036</v>
       </c>
       <c r="N23" t="n">
         <v>277</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.3452</v>
+        <v>0.2887</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0779</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4822</v>
+        <v>-0.4928</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3452</v>
+        <v>0.2887</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3452</v>
+        <v>0.2887</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.3452</v>
+        <v>0.2887</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3452</v>
+        <v>0.2887</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.3452</v>
+        <v>0.2887</v>
       </c>
       <c r="N24" t="n">
         <v>280</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.2927</v>
+        <v>0.2373</v>
       </c>
       <c r="C25" t="n">
-        <v>0.06610000000000001</v>
+        <v>0.0536</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.5059</v>
+        <v>-0.5162</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2927</v>
+        <v>0.2373</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2927</v>
+        <v>0.2373</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2927</v>
+        <v>0.2373</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2927</v>
+        <v>0.2373</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.2927</v>
+        <v>0.2373</v>
       </c>
       <c r="N25" t="n">
         <v>277</v>
@@ -1600,31 +1600,31 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.1164</v>
+        <v>-0.0005</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0263</v>
+        <v>-0.0001</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.5855</v>
+        <v>-0.6244</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1164</v>
+        <v>-0.0005</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1942</v>
+        <v>0.0839</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.07779999999999999</v>
+        <v>-0.0844</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1942</v>
+        <v>0.0839</v>
       </c>
       <c r="I26" t="n">
-        <v>0.101</v>
+        <v>0.0453</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.07779999999999999</v>
+        <v>-0.0844</v>
       </c>
       <c r="K26" t="n">
         <v>255</v>
@@ -1633,7 +1633,7 @@
         <v>88</v>
       </c>
       <c r="M26" t="n">
-        <v>0.02320000000000001</v>
+        <v>-0.0391</v>
       </c>
       <c r="N26" t="n">
         <v>343</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.02</v>
+        <v>-0.0706</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.0045</v>
+        <v>-0.0159</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.647</v>
+        <v>-0.6563</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.02</v>
+        <v>-0.0706</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.02</v>
+        <v>-0.0706</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.02</v>
+        <v>-0.0706</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.02</v>
+        <v>-0.0706</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.02</v>
+        <v>-0.0706</v>
       </c>
       <c r="N27" t="n">
         <v>280</v>
@@ -1692,31 +1692,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.4124</v>
+        <v>-0.2543</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0931</v>
+        <v>-0.0574</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.8242</v>
+        <v>-0.74</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.4124</v>
+        <v>-0.2543</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.0018</v>
+        <v>-0.8887</v>
       </c>
       <c r="G28" t="n">
-        <v>0.5894</v>
+        <v>0.6344</v>
       </c>
       <c r="H28" t="n">
-        <v>-1.0018</v>
+        <v>-0.8887</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.5209</v>
+        <v>-0.4799</v>
       </c>
       <c r="J28" t="n">
-        <v>0.5894</v>
+        <v>0.6344</v>
       </c>
       <c r="K28" t="n">
         <v>257</v>
@@ -1725,7 +1725,7 @@
         <v>102</v>
       </c>
       <c r="M28" t="n">
-        <v>0.06850000000000001</v>
+        <v>0.1545</v>
       </c>
       <c r="N28" t="n">
         <v>359</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.9492</v>
+        <v>-0.9989</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.2143</v>
+        <v>-0.2255</v>
       </c>
       <c r="D29" t="n">
-        <v>-1.0665</v>
+        <v>-1.0789</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.9492</v>
+        <v>-0.9989</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.9492</v>
+        <v>-0.9989</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.9492</v>
+        <v>-0.9989</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.9492</v>
+        <v>-0.9989</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.9492</v>
+        <v>-0.9989</v>
       </c>
       <c r="N29" t="n">
         <v>277</v>
@@ -1784,31 +1784,31 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-2.3648</v>
+        <v>-2.397</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.534</v>
+        <v>-0.5412</v>
       </c>
       <c r="D30" t="n">
-        <v>-1.7056</v>
+        <v>-1.7154</v>
       </c>
       <c r="E30" t="n">
-        <v>-2.3648</v>
+        <v>-2.397</v>
       </c>
       <c r="F30" t="n">
-        <v>-1.9986</v>
+        <v>-2.0432</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.3662</v>
+        <v>-0.3538</v>
       </c>
       <c r="H30" t="n">
-        <v>-1.9986</v>
+        <v>-2.0432</v>
       </c>
       <c r="I30" t="n">
-        <v>-1.0392</v>
+        <v>-1.1033</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.3662</v>
+        <v>-0.3538</v>
       </c>
       <c r="K30" t="n">
         <v>255</v>
@@ -1817,7 +1817,7 @@
         <v>88</v>
       </c>
       <c r="M30" t="n">
-        <v>-1.4054</v>
+        <v>-1.4571</v>
       </c>
       <c r="N30" t="n">
         <v>343</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-2.7489</v>
+        <v>-2.8064</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.6207</v>
+        <v>-0.6337</v>
       </c>
       <c r="D31" t="n">
-        <v>-1.879</v>
+        <v>-1.9017</v>
       </c>
       <c r="E31" t="n">
-        <v>-2.7489</v>
+        <v>-2.8064</v>
       </c>
       <c r="F31" t="n">
-        <v>-2.7489</v>
+        <v>-2.8064</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-2.7489</v>
+        <v>-2.8064</v>
       </c>
       <c r="I31" t="n">
-        <v>-2.7489</v>
+        <v>-2.8064</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-2.7489</v>
+        <v>-2.8064</v>
       </c>
       <c r="N31" t="n">
         <v>277</v>
@@ -1969,10 +1969,10 @@
         <v>1.61</v>
       </c>
       <c r="I2" t="n">
-        <v>1.2698</v>
+        <v>1.3276</v>
       </c>
       <c r="J2" t="n">
-        <v>31.745</v>
+        <v>33.19</v>
       </c>
     </row>
     <row r="3">
@@ -2009,10 +2009,10 @@
         <v>1.29</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7608</v>
+        <v>0.726</v>
       </c>
       <c r="J3" t="n">
-        <v>19.02</v>
+        <v>18.15</v>
       </c>
     </row>
     <row r="4">
@@ -2049,10 +2049,10 @@
         <v>1.19</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5295</v>
+        <v>0.519</v>
       </c>
       <c r="J4" t="n">
-        <v>13.2375</v>
+        <v>12.975</v>
       </c>
     </row>
     <row r="5">
@@ -2089,10 +2089,10 @@
         <v>1.06</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1744</v>
+        <v>0.1929</v>
       </c>
       <c r="J5" t="n">
-        <v>4.36</v>
+        <v>4.8225</v>
       </c>
     </row>
     <row r="6">
@@ -2129,10 +2129,10 @@
         <v>1.05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1425</v>
+        <v>0.1627</v>
       </c>
       <c r="J6" t="n">
-        <v>3.5625</v>
+        <v>4.0675</v>
       </c>
     </row>
     <row r="7">
@@ -2169,10 +2169,10 @@
         <v>1.04</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1777</v>
+        <v>0.1695</v>
       </c>
       <c r="J7" t="n">
-        <v>4.4425</v>
+        <v>4.2375</v>
       </c>
     </row>
     <row r="8">
@@ -2209,10 +2209,10 @@
         <v>0.99</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0132</v>
+        <v>-0.0038</v>
       </c>
       <c r="J8" t="n">
-        <v>0.33</v>
+        <v>-0.095</v>
       </c>
     </row>
     <row r="9">
@@ -2249,10 +2249,10 @@
         <v>0.86</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1567</v>
+        <v>-0.175</v>
       </c>
       <c r="J9" t="n">
-        <v>-3.9175</v>
+        <v>-4.375</v>
       </c>
     </row>
     <row r="10">
@@ -2289,10 +2289,10 @@
         <v>0.68</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3306</v>
+        <v>-0.3468</v>
       </c>
       <c r="J10" t="n">
-        <v>-8.265000000000001</v>
+        <v>-8.67</v>
       </c>
     </row>
     <row r="11">
@@ -2329,10 +2329,10 @@
         <v>0.47</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.526</v>
+        <v>-0.5322</v>
       </c>
       <c r="J11" t="n">
-        <v>-13.15</v>
+        <v>-13.305</v>
       </c>
     </row>
     <row r="12">
@@ -2369,10 +2369,10 @@
         <v>1.3</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8573</v>
+        <v>0.7975</v>
       </c>
       <c r="J12" t="n">
-        <v>24.8617</v>
+        <v>23.1275</v>
       </c>
     </row>
     <row r="13">
@@ -2409,10 +2409,10 @@
         <v>1.26</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7589</v>
+        <v>0.7116</v>
       </c>
       <c r="J13" t="n">
-        <v>22.0081</v>
+        <v>20.6364</v>
       </c>
     </row>
     <row r="14">
@@ -2449,10 +2449,10 @@
         <v>0.93</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2688</v>
+        <v>-0.2656</v>
       </c>
       <c r="J14" t="n">
-        <v>-7.7952</v>
+        <v>-7.7024</v>
       </c>
     </row>
     <row r="15">
@@ -2489,10 +2489,10 @@
         <v>0.87</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.443</v>
+        <v>-0.4259</v>
       </c>
       <c r="J15" t="n">
-        <v>-12.847</v>
+        <v>-12.3511</v>
       </c>
     </row>
     <row r="16">
@@ -2529,10 +2529,10 @@
         <v>0.8</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6307</v>
+        <v>-0.5941</v>
       </c>
       <c r="J16" t="n">
-        <v>-18.2903</v>
+        <v>-17.2289</v>
       </c>
     </row>
     <row r="17">
@@ -2569,10 +2569,10 @@
         <v>1.28</v>
       </c>
       <c r="I17" t="n">
-        <v>0.575</v>
+        <v>0.5603</v>
       </c>
       <c r="J17" t="n">
-        <v>16.675</v>
+        <v>16.2487</v>
       </c>
     </row>
     <row r="18">
@@ -2609,10 +2609,10 @@
         <v>1.2</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4325</v>
+        <v>0.4292</v>
       </c>
       <c r="J18" t="n">
-        <v>12.5425</v>
+        <v>12.4468</v>
       </c>
     </row>
     <row r="19">
@@ -2649,10 +2649,10 @@
         <v>0.92</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1138</v>
+        <v>-0.1253</v>
       </c>
       <c r="J19" t="n">
-        <v>-3.3002</v>
+        <v>-3.6337</v>
       </c>
     </row>
     <row r="20">
@@ -2689,10 +2689,10 @@
         <v>0.87</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1691</v>
+        <v>-0.182</v>
       </c>
       <c r="J20" t="n">
-        <v>-4.9039</v>
+        <v>-5.278</v>
       </c>
     </row>
     <row r="21">
@@ -2729,10 +2729,10 @@
         <v>0.83</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2109</v>
+        <v>-0.224</v>
       </c>
       <c r="J21" t="n">
-        <v>-6.1161</v>
+        <v>-6.496</v>
       </c>
     </row>
     <row r="22">
@@ -2769,10 +2769,10 @@
         <v>1.6</v>
       </c>
       <c r="I22" t="n">
-        <v>0.999</v>
+        <v>1.0963</v>
       </c>
       <c r="J22" t="n">
-        <v>23.976</v>
+        <v>26.3112</v>
       </c>
     </row>
     <row r="23">
@@ -2809,10 +2809,10 @@
         <v>1.17</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4263</v>
+        <v>0.4702</v>
       </c>
       <c r="J23" t="n">
-        <v>10.2312</v>
+        <v>11.2848</v>
       </c>
     </row>
     <row r="24">
@@ -2849,10 +2849,10 @@
         <v>1.09</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2778</v>
+        <v>0.2864</v>
       </c>
       <c r="J24" t="n">
-        <v>6.6672</v>
+        <v>6.8736</v>
       </c>
     </row>
     <row r="25">
@@ -2889,10 +2889,10 @@
         <v>1.03</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0885</v>
+        <v>0.1069</v>
       </c>
       <c r="J25" t="n">
-        <v>2.124</v>
+        <v>2.5656</v>
       </c>
     </row>
     <row r="26">
@@ -2929,10 +2929,10 @@
         <v>1.03</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0885</v>
+        <v>0.1069</v>
       </c>
       <c r="J26" t="n">
-        <v>2.124</v>
+        <v>2.5656</v>
       </c>
     </row>
     <row r="27">
@@ -2969,10 +2969,10 @@
         <v>1.34</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5464</v>
+        <v>0.6068</v>
       </c>
       <c r="J27" t="n">
-        <v>13.1136</v>
+        <v>14.5632</v>
       </c>
     </row>
     <row r="28">
@@ -3009,10 +3009,10 @@
         <v>1.11</v>
       </c>
       <c r="I28" t="n">
-        <v>0.272</v>
+        <v>0.2758</v>
       </c>
       <c r="J28" t="n">
-        <v>6.528</v>
+        <v>6.6192</v>
       </c>
     </row>
     <row r="29">
@@ -3049,10 +3049,10 @@
         <v>0.99</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.0194</v>
+        <v>-0.0244</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.4656</v>
+        <v>-0.5856</v>
       </c>
     </row>
     <row r="30">
@@ -3089,10 +3089,10 @@
         <v>0.84</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.196</v>
+        <v>-0.2101</v>
       </c>
       <c r="J30" t="n">
-        <v>-4.704</v>
+        <v>-5.0424</v>
       </c>
     </row>
     <row r="31">
@@ -3129,10 +3129,10 @@
         <v>0.62</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4087</v>
+        <v>-0.418</v>
       </c>
       <c r="J31" t="n">
-        <v>-9.8088</v>
+        <v>-10.032</v>
       </c>
     </row>
     <row r="32">
@@ -3169,10 +3169,10 @@
         <v>1.51</v>
       </c>
       <c r="I32" t="n">
-        <v>0.8493000000000001</v>
+        <v>0.9432</v>
       </c>
       <c r="J32" t="n">
-        <v>20.3832</v>
+        <v>22.6368</v>
       </c>
     </row>
     <row r="33">
@@ -3209,10 +3209,10 @@
         <v>1.43</v>
       </c>
       <c r="I33" t="n">
-        <v>0.7507</v>
+        <v>0.8363</v>
       </c>
       <c r="J33" t="n">
-        <v>18.0168</v>
+        <v>20.0712</v>
       </c>
     </row>
     <row r="34">
@@ -3249,10 +3249,10 @@
         <v>1.4</v>
       </c>
       <c r="I34" t="n">
-        <v>0.7134</v>
+        <v>0.7956</v>
       </c>
       <c r="J34" t="n">
-        <v>17.1216</v>
+        <v>19.0944</v>
       </c>
     </row>
     <row r="35">
@@ -3289,10 +3289,10 @@
         <v>1.26</v>
       </c>
       <c r="I35" t="n">
-        <v>0.534</v>
+        <v>0.5968</v>
       </c>
       <c r="J35" t="n">
-        <v>12.816</v>
+        <v>14.3232</v>
       </c>
     </row>
     <row r="36">
@@ -3329,10 +3329,10 @@
         <v>1.17</v>
       </c>
       <c r="I36" t="n">
-        <v>0.4051</v>
+        <v>0.451</v>
       </c>
       <c r="J36" t="n">
-        <v>9.7224</v>
+        <v>10.824</v>
       </c>
     </row>
     <row r="37">
@@ -3369,10 +3369,10 @@
         <v>0.83</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.1783</v>
+        <v>-0.1989</v>
       </c>
       <c r="J37" t="n">
-        <v>-4.2792</v>
+        <v>-4.7736</v>
       </c>
     </row>
     <row r="38">
@@ -3409,10 +3409,10 @@
         <v>0.8</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.2092</v>
+        <v>-0.2295</v>
       </c>
       <c r="J38" t="n">
-        <v>-5.0208</v>
+        <v>-5.508</v>
       </c>
     </row>
     <row r="39">
@@ -3449,10 +3449,10 @@
         <v>0.77</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.2387</v>
+        <v>-0.2585</v>
       </c>
       <c r="J39" t="n">
-        <v>-5.7288</v>
+        <v>-6.204</v>
       </c>
     </row>
     <row r="40">
@@ -3489,10 +3489,10 @@
         <v>0.74</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.2661</v>
+        <v>-0.2857</v>
       </c>
       <c r="J40" t="n">
-        <v>-6.3864</v>
+        <v>-6.8568</v>
       </c>
     </row>
     <row r="41">
@@ -3529,10 +3529,10 @@
         <v>0.6</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.3969</v>
+        <v>-0.4118</v>
       </c>
       <c r="J41" t="n">
-        <v>-9.525600000000001</v>
+        <v>-9.8832</v>
       </c>
     </row>
     <row r="42">
@@ -3569,10 +3569,10 @@
         <v>1.15</v>
       </c>
       <c r="I42" t="n">
-        <v>0.2782</v>
+        <v>0.2818</v>
       </c>
       <c r="J42" t="n">
-        <v>8.346</v>
+        <v>8.454000000000001</v>
       </c>
     </row>
     <row r="43">
@@ -3609,10 +3609,10 @@
         <v>1.06</v>
       </c>
       <c r="I43" t="n">
-        <v>0.1348</v>
+        <v>0.1414</v>
       </c>
       <c r="J43" t="n">
-        <v>4.044</v>
+        <v>4.242</v>
       </c>
     </row>
     <row r="44">
@@ -3649,10 +3649,10 @@
         <v>1.03</v>
       </c>
       <c r="I44" t="n">
-        <v>0.0799</v>
+        <v>0.0854</v>
       </c>
       <c r="J44" t="n">
-        <v>2.397</v>
+        <v>2.562</v>
       </c>
     </row>
     <row r="45">
@@ -3689,10 +3689,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.222</v>
+        <v>-0.2371</v>
       </c>
       <c r="J45" t="n">
-        <v>-6.66</v>
+        <v>-7.113</v>
       </c>
     </row>
     <row r="46">
@@ -3729,10 +3729,10 @@
         <v>0.66</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.3672</v>
+        <v>-0.3788</v>
       </c>
       <c r="J46" t="n">
-        <v>-11.016</v>
+        <v>-11.364</v>
       </c>
     </row>
     <row r="47">
@@ -3769,10 +3769,10 @@
         <v>1.28</v>
       </c>
       <c r="I47" t="n">
-        <v>0.3637</v>
+        <v>0.3972</v>
       </c>
       <c r="J47" t="n">
-        <v>10.911</v>
+        <v>11.916</v>
       </c>
     </row>
     <row r="48">
@@ -3809,10 +3809,10 @@
         <v>1.22</v>
       </c>
       <c r="I48" t="n">
-        <v>0.3115</v>
+        <v>0.3273</v>
       </c>
       <c r="J48" t="n">
-        <v>9.345000000000001</v>
+        <v>9.819000000000001</v>
       </c>
     </row>
     <row r="49">
@@ -3849,10 +3849,10 @@
         <v>1.19</v>
       </c>
       <c r="I49" t="n">
-        <v>0.2749</v>
+        <v>0.2911</v>
       </c>
       <c r="J49" t="n">
-        <v>8.247</v>
+        <v>8.733000000000001</v>
       </c>
     </row>
     <row r="50">
@@ -3889,10 +3889,10 @@
         <v>1.04</v>
       </c>
       <c r="I50" t="n">
-        <v>0.0672</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="J50" t="n">
-        <v>2.016</v>
+        <v>2.433</v>
       </c>
     </row>
     <row r="51">
@@ -3929,10 +3929,10 @@
         <v>0.98</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.05</v>
+        <v>-0.0535</v>
       </c>
       <c r="J51" t="n">
-        <v>-1.5</v>
+        <v>-1.605</v>
       </c>
     </row>
     <row r="52">
@@ -3969,10 +3969,10 @@
         <v>2.18</v>
       </c>
       <c r="I52" t="n">
-        <v>1.642</v>
+        <v>1.7759</v>
       </c>
       <c r="J52" t="n">
-        <v>39.408</v>
+        <v>42.6216</v>
       </c>
     </row>
     <row r="53">
@@ -4009,10 +4009,10 @@
         <v>1.27</v>
       </c>
       <c r="I53" t="n">
-        <v>0.5511</v>
+        <v>0.6149</v>
       </c>
       <c r="J53" t="n">
-        <v>13.2264</v>
+        <v>14.7576</v>
       </c>
     </row>
     <row r="54">
@@ -4049,10 +4049,10 @@
         <v>1.14</v>
       </c>
       <c r="I54" t="n">
-        <v>0.363</v>
+        <v>0.3906</v>
       </c>
       <c r="J54" t="n">
-        <v>8.712</v>
+        <v>9.3744</v>
       </c>
     </row>
     <row r="55">
@@ -4089,10 +4089,10 @@
         <v>1.05</v>
       </c>
       <c r="I55" t="n">
-        <v>0.1227</v>
+        <v>0.1488</v>
       </c>
       <c r="J55" t="n">
-        <v>2.9448</v>
+        <v>3.5712</v>
       </c>
     </row>
     <row r="56">
@@ -4129,10 +4129,10 @@
         <v>0.98</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.1744</v>
+        <v>-0.1556</v>
       </c>
       <c r="J56" t="n">
-        <v>-4.1856</v>
+        <v>-3.7344</v>
       </c>
     </row>
     <row r="57">
@@ -4169,10 +4169,10 @@
         <v>1.23</v>
       </c>
       <c r="I57" t="n">
-        <v>0.4747</v>
+        <v>0.5155999999999999</v>
       </c>
       <c r="J57" t="n">
-        <v>11.3928</v>
+        <v>12.3744</v>
       </c>
     </row>
     <row r="58">
@@ -4209,10 +4209,10 @@
         <v>0.89</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.1269</v>
+        <v>-0.1442</v>
       </c>
       <c r="J58" t="n">
-        <v>-3.0456</v>
+        <v>-3.4608</v>
       </c>
     </row>
     <row r="59">
@@ -4249,10 +4249,10 @@
         <v>0.79</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.2276</v>
+        <v>-0.2457</v>
       </c>
       <c r="J59" t="n">
-        <v>-5.4624</v>
+        <v>-5.8968</v>
       </c>
     </row>
     <row r="60">
@@ -4289,10 +4289,10 @@
         <v>0.68</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.3332</v>
+        <v>-0.3488</v>
       </c>
       <c r="J60" t="n">
-        <v>-7.9968</v>
+        <v>-8.3712</v>
       </c>
     </row>
     <row r="61">
@@ -4329,10 +4329,10 @@
         <v>0.54</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.464</v>
+        <v>-0.4735</v>
       </c>
       <c r="J61" t="n">
-        <v>-11.136</v>
+        <v>-11.364</v>
       </c>
     </row>
     <row r="62">
@@ -4369,10 +4369,10 @@
         <v>1.38</v>
       </c>
       <c r="I62" t="n">
-        <v>0.7483</v>
+        <v>0.8206</v>
       </c>
       <c r="J62" t="n">
-        <v>25.4422</v>
+        <v>27.9004</v>
       </c>
     </row>
     <row r="63">
@@ -4409,10 +4409,10 @@
         <v>1.16</v>
       </c>
       <c r="I63" t="n">
-        <v>0.429</v>
+        <v>0.4684</v>
       </c>
       <c r="J63" t="n">
-        <v>14.586</v>
+        <v>15.9256</v>
       </c>
     </row>
     <row r="64">
@@ -4449,10 +4449,10 @@
         <v>0.97</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.1437</v>
+        <v>-0.1448</v>
       </c>
       <c r="J64" t="n">
-        <v>-4.8858</v>
+        <v>-4.9232</v>
       </c>
     </row>
     <row r="65">
@@ -4489,10 +4489,10 @@
         <v>0.97</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.1437</v>
+        <v>-0.1448</v>
       </c>
       <c r="J65" t="n">
-        <v>-4.8858</v>
+        <v>-4.9232</v>
       </c>
     </row>
     <row r="66">
@@ -4529,10 +4529,10 @@
         <v>0.79</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.6629</v>
+        <v>-0.6215000000000001</v>
       </c>
       <c r="J66" t="n">
-        <v>-22.5386</v>
+        <v>-21.131</v>
       </c>
     </row>
     <row r="67">
@@ -4569,10 +4569,10 @@
         <v>1.26</v>
       </c>
       <c r="I67" t="n">
-        <v>0.4476</v>
+        <v>0.4977</v>
       </c>
       <c r="J67" t="n">
-        <v>15.2184</v>
+        <v>16.9218</v>
       </c>
     </row>
     <row r="68">
@@ -4609,10 +4609,10 @@
         <v>1.18</v>
       </c>
       <c r="I68" t="n">
-        <v>0.3639</v>
+        <v>0.3869</v>
       </c>
       <c r="J68" t="n">
-        <v>12.3726</v>
+        <v>13.1546</v>
       </c>
     </row>
     <row r="69">
@@ -4649,10 +4649,10 @@
         <v>1.12</v>
       </c>
       <c r="I69" t="n">
-        <v>0.2723</v>
+        <v>0.2806</v>
       </c>
       <c r="J69" t="n">
-        <v>9.2582</v>
+        <v>9.5404</v>
       </c>
     </row>
     <row r="70">
@@ -4689,10 +4689,10 @@
         <v>0.97</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.0561</v>
+        <v>-0.0629</v>
       </c>
       <c r="J70" t="n">
-        <v>-1.9074</v>
+        <v>-2.1386</v>
       </c>
     </row>
     <row r="71">
@@ -4729,10 +4729,10 @@
         <v>0.78</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.2659</v>
+        <v>-0.2775</v>
       </c>
       <c r="J71" t="n">
-        <v>-9.0406</v>
+        <v>-9.435</v>
       </c>
     </row>
     <row r="72">
@@ -4769,10 +4769,10 @@
         <v>1.63</v>
       </c>
       <c r="I72" t="n">
-        <v>0.7776</v>
+        <v>0.7657</v>
       </c>
       <c r="J72" t="n">
-        <v>22.5504</v>
+        <v>22.2053</v>
       </c>
     </row>
     <row r="73">
@@ -4809,10 +4809,10 @@
         <v>1.41</v>
       </c>
       <c r="I73" t="n">
-        <v>0.5343</v>
+        <v>0.5396</v>
       </c>
       <c r="J73" t="n">
-        <v>15.4947</v>
+        <v>15.6484</v>
       </c>
     </row>
     <row r="74">
@@ -4849,10 +4849,10 @@
         <v>1.1</v>
       </c>
       <c r="I74" t="n">
-        <v>0.1581</v>
+        <v>0.1747</v>
       </c>
       <c r="J74" t="n">
-        <v>4.5849</v>
+        <v>5.0663</v>
       </c>
     </row>
     <row r="75">
@@ -4889,10 +4889,10 @@
         <v>0.89</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.1612</v>
+        <v>-0.1707</v>
       </c>
       <c r="J75" t="n">
-        <v>-4.6748</v>
+        <v>-4.9503</v>
       </c>
     </row>
     <row r="76">
@@ -4929,10 +4929,10 @@
         <v>0.71</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.3418</v>
+        <v>-0.3503</v>
       </c>
       <c r="J76" t="n">
-        <v>-9.9122</v>
+        <v>-10.1587</v>
       </c>
     </row>
     <row r="77">
@@ -4969,10 +4969,10 @@
         <v>1.43</v>
       </c>
       <c r="I77" t="n">
-        <v>0.8445</v>
+        <v>0.8008999999999999</v>
       </c>
       <c r="J77" t="n">
-        <v>24.4905</v>
+        <v>23.2261</v>
       </c>
     </row>
     <row r="78">
@@ -5009,10 +5009,10 @@
         <v>1.06</v>
       </c>
       <c r="I78" t="n">
-        <v>0.1648</v>
+        <v>0.1724</v>
       </c>
       <c r="J78" t="n">
-        <v>4.7792</v>
+        <v>4.9996</v>
       </c>
     </row>
     <row r="79">
@@ -5049,10 +5049,10 @@
         <v>0.88</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.1545</v>
+        <v>-0.1681</v>
       </c>
       <c r="J79" t="n">
-        <v>-4.4805</v>
+        <v>-4.8749</v>
       </c>
     </row>
     <row r="80">
@@ -5089,10 +5089,10 @@
         <v>0.84</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.1967</v>
+        <v>-0.2106</v>
       </c>
       <c r="J80" t="n">
-        <v>-5.7043</v>
+        <v>-6.1074</v>
       </c>
     </row>
     <row r="81">
@@ -5129,10 +5129,10 @@
         <v>0.72</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.3156</v>
+        <v>-0.3279</v>
       </c>
       <c r="J81" t="n">
-        <v>-9.1524</v>
+        <v>-9.5091</v>
       </c>
     </row>
     <row r="82">
@@ -5169,10 +5169,10 @@
         <v>1.37</v>
       </c>
       <c r="I82" t="n">
-        <v>0.5004999999999999</v>
+        <v>0.5057</v>
       </c>
       <c r="J82" t="n">
-        <v>14.014</v>
+        <v>14.1596</v>
       </c>
     </row>
     <row r="83">
@@ -5209,10 +5209,10 @@
         <v>1.21</v>
       </c>
       <c r="I83" t="n">
-        <v>0.3071</v>
+        <v>0.321</v>
       </c>
       <c r="J83" t="n">
-        <v>8.598800000000001</v>
+        <v>8.988</v>
       </c>
     </row>
     <row r="84">
@@ -5249,10 +5249,10 @@
         <v>1.05</v>
       </c>
       <c r="I84" t="n">
-        <v>0.0897</v>
+        <v>0.1029</v>
       </c>
       <c r="J84" t="n">
-        <v>2.5116</v>
+        <v>2.8812</v>
       </c>
     </row>
     <row r="85">
@@ -5289,10 +5289,10 @@
         <v>1</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.008</v>
+        <v>-0.0061</v>
       </c>
       <c r="J85" t="n">
-        <v>-0.224</v>
+        <v>-0.1708</v>
       </c>
     </row>
     <row r="86">
@@ -5329,10 +5329,10 @@
         <v>0.83</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.2189</v>
+        <v>-0.2302</v>
       </c>
       <c r="J86" t="n">
-        <v>-6.1292</v>
+        <v>-6.4456</v>
       </c>
     </row>
     <row r="87">
@@ -5369,10 +5369,10 @@
         <v>1.49</v>
       </c>
       <c r="I87" t="n">
-        <v>0.9175</v>
+        <v>0.8702</v>
       </c>
       <c r="J87" t="n">
-        <v>25.69</v>
+        <v>24.3656</v>
       </c>
     </row>
     <row r="88">
@@ -5409,10 +5409,10 @@
         <v>1.06</v>
       </c>
       <c r="I88" t="n">
-        <v>0.1544</v>
+        <v>0.1649</v>
       </c>
       <c r="J88" t="n">
-        <v>4.3232</v>
+        <v>4.6172</v>
       </c>
     </row>
     <row r="89">
@@ -5449,10 +5449,10 @@
         <v>1</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.003</v>
+        <v>-0.0023</v>
       </c>
       <c r="J89" t="n">
-        <v>-0.08400000000000001</v>
+        <v>-0.0644</v>
       </c>
     </row>
     <row r="90">
@@ -5489,10 +5489,10 @@
         <v>0.97</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.0539</v>
+        <v>-0.0611</v>
       </c>
       <c r="J90" t="n">
-        <v>-1.5092</v>
+        <v>-1.7108</v>
       </c>
     </row>
     <row r="91">
@@ -5529,10 +5529,10 @@
         <v>0.68</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.3594</v>
+        <v>-0.3694</v>
       </c>
       <c r="J91" t="n">
-        <v>-10.0632</v>
+        <v>-10.3432</v>
       </c>
     </row>
     <row r="92">
@@ -5569,10 +5569,10 @@
         <v>1.08</v>
       </c>
       <c r="I92" t="n">
-        <v>0.2431</v>
+        <v>0.2403</v>
       </c>
       <c r="J92" t="n">
-        <v>6.5637</v>
+        <v>6.4881</v>
       </c>
     </row>
     <row r="93">
@@ -5609,10 +5609,10 @@
         <v>0.86</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.1636</v>
+        <v>-0.1802</v>
       </c>
       <c r="J93" t="n">
-        <v>-4.4172</v>
+        <v>-4.8654</v>
       </c>
     </row>
     <row r="94">
@@ -5649,10 +5649,10 @@
         <v>0.85</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.1737</v>
+        <v>-0.1905</v>
       </c>
       <c r="J94" t="n">
-        <v>-4.6899</v>
+        <v>-5.1435</v>
       </c>
     </row>
     <row r="95">
@@ -5689,10 +5689,10 @@
         <v>0.8</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.2239</v>
+        <v>-0.2406</v>
       </c>
       <c r="J95" t="n">
-        <v>-6.0453</v>
+        <v>-6.4962</v>
       </c>
     </row>
     <row r="96">
@@ -5729,10 +5729,10 @@
         <v>0.79</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.2338</v>
+        <v>-0.2504</v>
       </c>
       <c r="J96" t="n">
-        <v>-6.3126</v>
+        <v>-6.7608</v>
       </c>
     </row>
     <row r="97">
@@ -5769,10 +5769,10 @@
         <v>1.72</v>
       </c>
       <c r="I97" t="n">
-        <v>1.4286</v>
+        <v>1.4074</v>
       </c>
       <c r="J97" t="n">
-        <v>38.5722</v>
+        <v>37.9998</v>
       </c>
     </row>
     <row r="98">
@@ -5809,10 +5809,10 @@
         <v>1.21</v>
       </c>
       <c r="I98" t="n">
-        <v>0.59</v>
+        <v>0.5707</v>
       </c>
       <c r="J98" t="n">
-        <v>15.93</v>
+        <v>15.4089</v>
       </c>
     </row>
     <row r="99">
@@ -5849,10 +5849,10 @@
         <v>1.01</v>
       </c>
       <c r="I99" t="n">
-        <v>0.0149</v>
+        <v>0.0322</v>
       </c>
       <c r="J99" t="n">
-        <v>0.4023</v>
+        <v>0.8694</v>
       </c>
     </row>
     <row r="100">
@@ -5889,10 +5889,10 @@
         <v>0.98</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.136</v>
+        <v>-0.1288</v>
       </c>
       <c r="J100" t="n">
-        <v>-3.672</v>
+        <v>-3.4776</v>
       </c>
     </row>
     <row r="101">
@@ -5929,10 +5929,10 @@
         <v>0.91</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.3656</v>
+        <v>-0.3471</v>
       </c>
       <c r="J101" t="n">
-        <v>-9.8712</v>
+        <v>-9.371700000000001</v>
       </c>
     </row>
     <row r="102">
@@ -5969,10 +5969,10 @@
         <v>1.43</v>
       </c>
       <c r="I102" t="n">
-        <v>1.0404</v>
+        <v>0.9912</v>
       </c>
       <c r="J102" t="n">
-        <v>24.9696</v>
+        <v>23.7888</v>
       </c>
     </row>
     <row r="103">
@@ -6009,10 +6009,10 @@
         <v>1.39</v>
       </c>
       <c r="I103" t="n">
-        <v>0.9759</v>
+        <v>0.9203</v>
       </c>
       <c r="J103" t="n">
-        <v>23.4216</v>
+        <v>22.0872</v>
       </c>
     </row>
     <row r="104">
@@ -6049,10 +6049,10 @@
         <v>1.2</v>
       </c>
       <c r="I104" t="n">
-        <v>0.5527</v>
+        <v>0.5402</v>
       </c>
       <c r="J104" t="n">
-        <v>13.2648</v>
+        <v>12.9648</v>
       </c>
     </row>
     <row r="105">
@@ -6089,10 +6089,10 @@
         <v>1.15</v>
       </c>
       <c r="I105" t="n">
-        <v>0.4271</v>
+        <v>0.4267</v>
       </c>
       <c r="J105" t="n">
-        <v>10.2504</v>
+        <v>10.2408</v>
       </c>
     </row>
     <row r="106">
@@ -6129,10 +6129,10 @@
         <v>1.06</v>
       </c>
       <c r="I106" t="n">
-        <v>0.1729</v>
+        <v>0.1919</v>
       </c>
       <c r="J106" t="n">
-        <v>4.1496</v>
+        <v>4.6056</v>
       </c>
     </row>
     <row r="107">
@@ -6169,10 +6169,10 @@
         <v>1.1</v>
       </c>
       <c r="I107" t="n">
-        <v>0.2995</v>
+        <v>0.2913</v>
       </c>
       <c r="J107" t="n">
-        <v>7.188</v>
+        <v>6.9912</v>
       </c>
     </row>
     <row r="108">
@@ -6209,10 +6209,10 @@
         <v>1.02</v>
       </c>
       <c r="I108" t="n">
-        <v>0.1081</v>
+        <v>0.1039</v>
       </c>
       <c r="J108" t="n">
-        <v>2.5944</v>
+        <v>2.4936</v>
       </c>
     </row>
     <row r="109">
@@ -6249,10 +6249,10 @@
         <v>0.87</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.151</v>
+        <v>-0.1681</v>
       </c>
       <c r="J109" t="n">
-        <v>-3.624</v>
+        <v>-4.0344</v>
       </c>
     </row>
     <row r="110">
@@ -6289,10 +6289,10 @@
         <v>0.74</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.2786</v>
+        <v>-0.2953</v>
       </c>
       <c r="J110" t="n">
-        <v>-6.6864</v>
+        <v>-7.0872</v>
       </c>
     </row>
     <row r="111">
@@ -6329,10 +6329,10 @@
         <v>0.5</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.5032</v>
+        <v>-0.5102</v>
       </c>
       <c r="J111" t="n">
-        <v>-12.0768</v>
+        <v>-12.2448</v>
       </c>
     </row>
     <row r="112">
@@ -6369,10 +6369,10 @@
         <v>1.33</v>
       </c>
       <c r="I112" t="n">
-        <v>0.4449</v>
+        <v>0.4547</v>
       </c>
       <c r="J112" t="n">
-        <v>12.9021</v>
+        <v>13.1863</v>
       </c>
     </row>
     <row r="113">
@@ -6409,10 +6409,10 @@
         <v>1.2</v>
       </c>
       <c r="I113" t="n">
-        <v>0.2883</v>
+        <v>0.304</v>
       </c>
       <c r="J113" t="n">
-        <v>8.3607</v>
+        <v>8.816000000000001</v>
       </c>
     </row>
     <row r="114">
@@ -6449,10 +6449,10 @@
         <v>1.17</v>
       </c>
       <c r="I114" t="n">
-        <v>0.2507</v>
+        <v>0.2671</v>
       </c>
       <c r="J114" t="n">
-        <v>7.2703</v>
+        <v>7.7459</v>
       </c>
     </row>
     <row r="115">
@@ -6489,10 +6489,10 @@
         <v>1.07</v>
       </c>
       <c r="I115" t="n">
-        <v>0.116</v>
+        <v>0.1314</v>
       </c>
       <c r="J115" t="n">
-        <v>3.364</v>
+        <v>3.8106</v>
       </c>
     </row>
     <row r="116">
@@ -6529,10 +6529,10 @@
         <v>0.9</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.1487</v>
+        <v>-0.1582</v>
       </c>
       <c r="J116" t="n">
-        <v>-4.3123</v>
+        <v>-4.5878</v>
       </c>
     </row>
     <row r="117">
@@ -6569,10 +6569,10 @@
         <v>1.21</v>
       </c>
       <c r="I117" t="n">
-        <v>0.4638</v>
+        <v>0.4556</v>
       </c>
       <c r="J117" t="n">
-        <v>13.4502</v>
+        <v>13.2124</v>
       </c>
     </row>
     <row r="118">
@@ -6609,10 +6609,10 @@
         <v>1.18</v>
       </c>
       <c r="I118" t="n">
-        <v>0.408</v>
+        <v>0.404</v>
       </c>
       <c r="J118" t="n">
-        <v>11.832</v>
+        <v>11.716</v>
       </c>
     </row>
     <row r="119">
@@ -6649,10 +6649,10 @@
         <v>1.01</v>
       </c>
       <c r="I119" t="n">
-        <v>0.0409</v>
+        <v>0.0456</v>
       </c>
       <c r="J119" t="n">
-        <v>1.1861</v>
+        <v>1.3224</v>
       </c>
     </row>
     <row r="120">
@@ -6689,10 +6689,10 @@
         <v>0.8</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.2367</v>
+        <v>-0.2506</v>
       </c>
       <c r="J120" t="n">
-        <v>-6.8643</v>
+        <v>-7.2674</v>
       </c>
     </row>
     <row r="121">
@@ -6729,10 +6729,10 @@
         <v>0.7</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.334</v>
+        <v>-0.3459</v>
       </c>
       <c r="J121" t="n">
-        <v>-9.686</v>
+        <v>-10.0311</v>
       </c>
     </row>
     <row r="122">
@@ -6769,10 +6769,10 @@
         <v>1.34</v>
       </c>
       <c r="I122" t="n">
-        <v>0.4543</v>
+        <v>0.464</v>
       </c>
       <c r="J122" t="n">
-        <v>13.629</v>
+        <v>13.92</v>
       </c>
     </row>
     <row r="123">
@@ -6809,10 +6809,10 @@
         <v>1.18</v>
       </c>
       <c r="I123" t="n">
-        <v>0.262</v>
+        <v>0.2785</v>
       </c>
       <c r="J123" t="n">
-        <v>7.86</v>
+        <v>8.355</v>
       </c>
     </row>
     <row r="124">
@@ -6849,10 +6849,10 @@
         <v>1.14</v>
       </c>
       <c r="I124" t="n">
-        <v>0.2119</v>
+        <v>0.2287</v>
       </c>
       <c r="J124" t="n">
-        <v>6.357</v>
+        <v>6.861</v>
       </c>
     </row>
     <row r="125">
@@ -6889,10 +6889,10 @@
         <v>1.08</v>
       </c>
       <c r="I125" t="n">
-        <v>0.1296</v>
+        <v>0.1457</v>
       </c>
       <c r="J125" t="n">
-        <v>3.888</v>
+        <v>4.371</v>
       </c>
     </row>
     <row r="126">
@@ -6929,10 +6929,10 @@
         <v>0.99</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.0345</v>
+        <v>-0.036</v>
       </c>
       <c r="J126" t="n">
-        <v>-1.035</v>
+        <v>-1.08</v>
       </c>
     </row>
     <row r="127">
@@ -6969,10 +6969,10 @@
         <v>1.08</v>
       </c>
       <c r="I127" t="n">
-        <v>0.2228</v>
+        <v>0.2254</v>
       </c>
       <c r="J127" t="n">
-        <v>6.684</v>
+        <v>6.762</v>
       </c>
     </row>
     <row r="128">
@@ -7009,10 +7009,10 @@
         <v>1.01</v>
       </c>
       <c r="I128" t="n">
-        <v>0.0508</v>
+        <v>0.0527</v>
       </c>
       <c r="J128" t="n">
-        <v>1.524</v>
+        <v>1.581</v>
       </c>
     </row>
     <row r="129">
@@ -7049,10 +7049,10 @@
         <v>0.98</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.0305</v>
+        <v>-0.0386</v>
       </c>
       <c r="J129" t="n">
-        <v>-0.915</v>
+        <v>-1.158</v>
       </c>
     </row>
     <row r="130">
@@ -7089,10 +7089,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.2211</v>
+        <v>-0.2363</v>
       </c>
       <c r="J130" t="n">
-        <v>-6.633</v>
+        <v>-7.089</v>
       </c>
     </row>
     <row r="131">
@@ -7129,10 +7129,10 @@
         <v>0.79</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.2411</v>
+        <v>-0.2561</v>
       </c>
       <c r="J131" t="n">
-        <v>-7.233</v>
+        <v>-7.683</v>
       </c>
     </row>
     <row r="132">
@@ -7169,10 +7169,10 @@
         <v>1.48</v>
       </c>
       <c r="I132" t="n">
-        <v>0.6135</v>
+        <v>0.6137</v>
       </c>
       <c r="J132" t="n">
-        <v>18.405</v>
+        <v>18.411</v>
       </c>
     </row>
     <row r="133">
@@ -7209,10 +7209,10 @@
         <v>1.18</v>
       </c>
       <c r="I133" t="n">
-        <v>0.262</v>
+        <v>0.2785</v>
       </c>
       <c r="J133" t="n">
-        <v>7.86</v>
+        <v>8.355</v>
       </c>
     </row>
     <row r="134">
@@ -7249,10 +7249,10 @@
         <v>1.1</v>
       </c>
       <c r="I134" t="n">
-        <v>0.1583</v>
+        <v>0.1748</v>
       </c>
       <c r="J134" t="n">
-        <v>4.749</v>
+        <v>5.244</v>
       </c>
     </row>
     <row r="135">
@@ -7289,10 +7289,10 @@
         <v>1.02</v>
       </c>
       <c r="I135" t="n">
-        <v>0.0307</v>
+        <v>0.0423</v>
       </c>
       <c r="J135" t="n">
-        <v>0.921</v>
+        <v>1.269</v>
       </c>
     </row>
     <row r="136">
@@ -7329,10 +7329,10 @@
         <v>0.95</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.091</v>
+        <v>-0.0978</v>
       </c>
       <c r="J136" t="n">
-        <v>-2.73</v>
+        <v>-2.934</v>
       </c>
     </row>
     <row r="137">
@@ -7369,10 +7369,10 @@
         <v>1.24</v>
       </c>
       <c r="I137" t="n">
-        <v>0.5052</v>
+        <v>0.4963</v>
       </c>
       <c r="J137" t="n">
-        <v>15.156</v>
+        <v>14.889</v>
       </c>
     </row>
     <row r="138">
@@ -7409,10 +7409,10 @@
         <v>1.11</v>
       </c>
       <c r="I138" t="n">
-        <v>0.2622</v>
+        <v>0.2687</v>
       </c>
       <c r="J138" t="n">
-        <v>7.866</v>
+        <v>8.061</v>
       </c>
     </row>
     <row r="139">
@@ -7449,10 +7449,10 @@
         <v>1.09</v>
       </c>
       <c r="I139" t="n">
-        <v>0.2217</v>
+        <v>0.2297</v>
       </c>
       <c r="J139" t="n">
-        <v>6.651</v>
+        <v>6.891</v>
       </c>
     </row>
     <row r="140">
@@ -7489,10 +7489,10 @@
         <v>0.95</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.07770000000000001</v>
+        <v>-0.08749999999999999</v>
       </c>
       <c r="J140" t="n">
-        <v>-2.331</v>
+        <v>-2.625</v>
       </c>
     </row>
     <row r="141">
@@ -7529,10 +7529,10 @@
         <v>0.7</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.3382</v>
+        <v>-0.3492</v>
       </c>
       <c r="J141" t="n">
-        <v>-10.146</v>
+        <v>-10.476</v>
       </c>
     </row>
     <row r="142">
@@ -7569,10 +7569,10 @@
         <v>1.91</v>
       </c>
       <c r="I142" t="n">
-        <v>0.9955000000000001</v>
+        <v>0.9798</v>
       </c>
       <c r="J142" t="n">
-        <v>21.901</v>
+        <v>21.5556</v>
       </c>
     </row>
     <row r="143">
@@ -7609,10 +7609,10 @@
         <v>1.68</v>
       </c>
       <c r="I143" t="n">
-        <v>0.7784</v>
+        <v>0.7743</v>
       </c>
       <c r="J143" t="n">
-        <v>17.1248</v>
+        <v>17.0346</v>
       </c>
     </row>
     <row r="144">
@@ -7649,10 +7649,10 @@
         <v>1.18</v>
       </c>
       <c r="I144" t="n">
-        <v>0.2386</v>
+        <v>0.261</v>
       </c>
       <c r="J144" t="n">
-        <v>5.2492</v>
+        <v>5.742</v>
       </c>
     </row>
     <row r="145">
@@ -7689,10 +7689,10 @@
         <v>1.17</v>
       </c>
       <c r="I145" t="n">
-        <v>0.2258</v>
+        <v>0.2484</v>
       </c>
       <c r="J145" t="n">
-        <v>4.9676</v>
+        <v>5.4648</v>
       </c>
     </row>
     <row r="146">
@@ -7729,10 +7729,10 @@
         <v>0.96</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.09959999999999999</v>
+        <v>-0.1008</v>
       </c>
       <c r="J146" t="n">
-        <v>-2.1912</v>
+        <v>-2.2176</v>
       </c>
     </row>
     <row r="147">
@@ -7769,10 +7769,10 @@
         <v>0.93</v>
       </c>
       <c r="I147" t="n">
-        <v>-0.0606</v>
+        <v>-0.081</v>
       </c>
       <c r="J147" t="n">
-        <v>-1.3332</v>
+        <v>-1.782</v>
       </c>
     </row>
     <row r="148">
@@ -7809,10 +7809,10 @@
         <v>0.9</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.0975</v>
+        <v>-0.1186</v>
       </c>
       <c r="J148" t="n">
-        <v>-2.145</v>
+        <v>-2.6092</v>
       </c>
     </row>
     <row r="149">
@@ -7849,10 +7849,10 @@
         <v>0.74</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.2652</v>
+        <v>-0.285</v>
       </c>
       <c r="J149" t="n">
-        <v>-5.8344</v>
+        <v>-6.27</v>
       </c>
     </row>
     <row r="150">
@@ -7889,10 +7889,10 @@
         <v>0.58</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.4137</v>
+        <v>-0.4281</v>
       </c>
       <c r="J150" t="n">
-        <v>-9.1014</v>
+        <v>-9.418200000000001</v>
       </c>
     </row>
     <row r="151">
@@ -7929,10 +7929,10 @@
         <v>0.53</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.4604</v>
+        <v>-0.4722</v>
       </c>
       <c r="J151" t="n">
-        <v>-10.1288</v>
+        <v>-10.3884</v>
       </c>
     </row>
     <row r="152">
@@ -7969,10 +7969,10 @@
         <v>1.52</v>
       </c>
       <c r="I152" t="n">
-        <v>0.987</v>
+        <v>0.9344</v>
       </c>
       <c r="J152" t="n">
-        <v>24.675</v>
+        <v>23.36</v>
       </c>
     </row>
     <row r="153">
@@ -8009,10 +8009,10 @@
         <v>0.98</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.0346</v>
+        <v>-0.0417</v>
       </c>
       <c r="J153" t="n">
-        <v>-0.865</v>
+        <v>-1.0425</v>
       </c>
     </row>
     <row r="154">
@@ -8049,10 +8049,10 @@
         <v>0.98</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.0346</v>
+        <v>-0.0417</v>
       </c>
       <c r="J154" t="n">
-        <v>-0.865</v>
+        <v>-1.0425</v>
       </c>
     </row>
     <row r="155">
@@ -8089,10 +8089,10 @@
         <v>0.77</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.2664</v>
+        <v>-0.2799</v>
       </c>
       <c r="J155" t="n">
-        <v>-6.66</v>
+        <v>-6.9975</v>
       </c>
     </row>
     <row r="156">
@@ -8129,10 +8129,10 @@
         <v>0.65</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.381</v>
+        <v>-0.3913</v>
       </c>
       <c r="J156" t="n">
-        <v>-9.525</v>
+        <v>-9.782500000000001</v>
       </c>
     </row>
     <row r="157">
@@ -8169,10 +8169,10 @@
         <v>1.66</v>
       </c>
       <c r="I157" t="n">
-        <v>0.8037</v>
+        <v>0.7906</v>
       </c>
       <c r="J157" t="n">
-        <v>20.0925</v>
+        <v>19.765</v>
       </c>
     </row>
     <row r="158">
@@ -8209,10 +8209,10 @@
         <v>1.31</v>
       </c>
       <c r="I158" t="n">
-        <v>0.4152</v>
+        <v>0.4276</v>
       </c>
       <c r="J158" t="n">
-        <v>10.38</v>
+        <v>10.69</v>
       </c>
     </row>
     <row r="159">
@@ -8249,10 +8249,10 @@
         <v>1.29</v>
       </c>
       <c r="I159" t="n">
-        <v>0.3918</v>
+        <v>0.4052</v>
       </c>
       <c r="J159" t="n">
-        <v>9.795</v>
+        <v>10.13</v>
       </c>
     </row>
     <row r="160">
@@ -8289,10 +8289,10 @@
         <v>0.8</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.257</v>
+        <v>-0.2665</v>
       </c>
       <c r="J160" t="n">
-        <v>-6.425</v>
+        <v>-6.6625</v>
       </c>
     </row>
     <row r="161">
@@ -8329,10 +8329,10 @@
         <v>0.79</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.2669</v>
+        <v>-0.2763</v>
       </c>
       <c r="J161" t="n">
-        <v>-6.6725</v>
+        <v>-6.9075</v>
       </c>
     </row>
     <row r="162">
@@ -8369,10 +8369,10 @@
         <v>1.15</v>
       </c>
       <c r="I162" t="n">
-        <v>0.4039</v>
+        <v>0.3895</v>
       </c>
       <c r="J162" t="n">
-        <v>9.2897</v>
+        <v>8.958500000000001</v>
       </c>
     </row>
     <row r="163">
@@ -8409,10 +8409,10 @@
         <v>0.97</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.0318</v>
+        <v>-0.0442</v>
       </c>
       <c r="J163" t="n">
-        <v>-0.7314000000000001</v>
+        <v>-1.0166</v>
       </c>
     </row>
     <row r="164">
@@ -8449,10 +8449,10 @@
         <v>0.97</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.0318</v>
+        <v>-0.0442</v>
       </c>
       <c r="J164" t="n">
-        <v>-0.7314000000000001</v>
+        <v>-1.0166</v>
       </c>
     </row>
     <row r="165">
@@ -8489,10 +8489,10 @@
         <v>0.67</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.3455</v>
+        <v>-0.3601</v>
       </c>
       <c r="J165" t="n">
-        <v>-7.9465</v>
+        <v>-8.282299999999999</v>
       </c>
     </row>
     <row r="166">
@@ -8529,10 +8529,10 @@
         <v>0.47</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.5306</v>
+        <v>-0.5358000000000001</v>
       </c>
       <c r="J166" t="n">
-        <v>-12.2038</v>
+        <v>-12.3234</v>
       </c>
     </row>
     <row r="167">
@@ -8569,10 +8569,10 @@
         <v>1.46</v>
       </c>
       <c r="I167" t="n">
-        <v>0.5641</v>
+        <v>0.5722</v>
       </c>
       <c r="J167" t="n">
-        <v>12.9743</v>
+        <v>13.1606</v>
       </c>
     </row>
     <row r="168">
@@ -8609,10 +8609,10 @@
         <v>1.37</v>
       </c>
       <c r="I168" t="n">
-        <v>0.4663</v>
+        <v>0.4797</v>
       </c>
       <c r="J168" t="n">
-        <v>10.7249</v>
+        <v>11.0331</v>
       </c>
     </row>
     <row r="169">
@@ -8649,10 +8649,10 @@
         <v>1.35</v>
       </c>
       <c r="I169" t="n">
-        <v>0.4443</v>
+        <v>0.4587</v>
       </c>
       <c r="J169" t="n">
-        <v>10.2189</v>
+        <v>10.5501</v>
       </c>
     </row>
     <row r="170">
@@ -8689,10 +8689,10 @@
         <v>1.3</v>
       </c>
       <c r="I170" t="n">
-        <v>0.3893</v>
+        <v>0.4058</v>
       </c>
       <c r="J170" t="n">
-        <v>8.953900000000001</v>
+        <v>9.333399999999999</v>
       </c>
     </row>
     <row r="171">
@@ -8729,10 +8729,10 @@
         <v>0.97</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.0784</v>
+        <v>-0.0803</v>
       </c>
       <c r="J171" t="n">
-        <v>-1.8032</v>
+        <v>-1.8469</v>
       </c>
     </row>
     <row r="172">
@@ -8769,10 +8769,10 @@
         <v>1.12</v>
       </c>
       <c r="I172" t="n">
-        <v>0.3965</v>
+        <v>0.3876</v>
       </c>
       <c r="J172" t="n">
-        <v>11.4985</v>
+        <v>11.2404</v>
       </c>
     </row>
     <row r="173">
@@ -8849,10 +8849,10 @@
         <v>1.07</v>
       </c>
       <c r="I174" t="n">
-        <v>0.2524</v>
+        <v>0.2543</v>
       </c>
       <c r="J174" t="n">
-        <v>7.3196</v>
+        <v>7.3747</v>
       </c>
     </row>
     <row r="175">
@@ -8889,10 +8889,10 @@
         <v>0.95</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.2041</v>
+        <v>-0.205</v>
       </c>
       <c r="J175" t="n">
-        <v>-5.9189</v>
+        <v>-5.945</v>
       </c>
     </row>
     <row r="176">
@@ -8929,10 +8929,10 @@
         <v>0.91</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.3272</v>
+        <v>-0.3203</v>
       </c>
       <c r="J176" t="n">
-        <v>-9.488799999999999</v>
+        <v>-9.2887</v>
       </c>
     </row>
     <row r="177">
@@ -8969,10 +8969,10 @@
         <v>1.25</v>
       </c>
       <c r="I177" t="n">
-        <v>0.4856</v>
+        <v>0.4854</v>
       </c>
       <c r="J177" t="n">
-        <v>14.0824</v>
+        <v>14.0766</v>
       </c>
     </row>
     <row r="178">
@@ -9009,10 +9009,10 @@
         <v>1.18</v>
       </c>
       <c r="I178" t="n">
-        <v>0.3659</v>
+        <v>0.3734</v>
       </c>
       <c r="J178" t="n">
-        <v>10.6111</v>
+        <v>10.8286</v>
       </c>
     </row>
     <row r="179">
@@ -9049,10 +9049,10 @@
         <v>1.18</v>
       </c>
       <c r="I179" t="n">
-        <v>0.3659</v>
+        <v>0.3734</v>
       </c>
       <c r="J179" t="n">
-        <v>10.6111</v>
+        <v>10.8286</v>
       </c>
     </row>
     <row r="180">
@@ -9089,10 +9089,10 @@
         <v>1.12</v>
       </c>
       <c r="I180" t="n">
-        <v>0.2589</v>
+        <v>0.2711</v>
       </c>
       <c r="J180" t="n">
-        <v>7.5081</v>
+        <v>7.8619</v>
       </c>
     </row>
     <row r="181">
@@ -9129,10 +9129,10 @@
         <v>1.07</v>
       </c>
       <c r="I181" t="n">
-        <v>0.1586</v>
+        <v>0.1738</v>
       </c>
       <c r="J181" t="n">
-        <v>4.5994</v>
+        <v>5.0402</v>
       </c>
     </row>
     <row r="182">
@@ -9169,10 +9169,10 @@
         <v>1.49</v>
       </c>
       <c r="I182" t="n">
-        <v>0.8827</v>
+        <v>0.844</v>
       </c>
       <c r="J182" t="n">
-        <v>26.481</v>
+        <v>25.32</v>
       </c>
     </row>
     <row r="183">
@@ -9209,10 +9209,10 @@
         <v>1.32</v>
       </c>
       <c r="I183" t="n">
-        <v>0.6093</v>
+        <v>0.5977</v>
       </c>
       <c r="J183" t="n">
-        <v>18.279</v>
+        <v>17.931</v>
       </c>
     </row>
     <row r="184">
@@ -9249,10 +9249,10 @@
         <v>1.07</v>
       </c>
       <c r="I184" t="n">
-        <v>0.1636</v>
+        <v>0.1774</v>
       </c>
       <c r="J184" t="n">
-        <v>4.908</v>
+        <v>5.322</v>
       </c>
     </row>
     <row r="185">
@@ -9289,10 +9289,10 @@
         <v>0.92</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.1255</v>
+        <v>-0.1344</v>
       </c>
       <c r="J185" t="n">
-        <v>-3.765</v>
+        <v>-4.032</v>
       </c>
     </row>
     <row r="186">
@@ -9329,10 +9329,10 @@
         <v>0.85</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.2021</v>
+        <v>-0.2126</v>
       </c>
       <c r="J186" t="n">
-        <v>-6.063</v>
+        <v>-6.378</v>
       </c>
     </row>
     <row r="187">
@@ -9369,10 +9369,10 @@
         <v>1.22</v>
       </c>
       <c r="I187" t="n">
-        <v>0.6757</v>
+        <v>0.6352</v>
       </c>
       <c r="J187" t="n">
-        <v>20.271</v>
+        <v>19.056</v>
       </c>
     </row>
     <row r="188">
@@ -9409,10 +9409,10 @@
         <v>1.14</v>
       </c>
       <c r="I188" t="n">
-        <v>0.4636</v>
+        <v>0.446</v>
       </c>
       <c r="J188" t="n">
-        <v>13.908</v>
+        <v>13.38</v>
       </c>
     </row>
     <row r="189">
@@ -9449,10 +9449,10 @@
         <v>1.08</v>
       </c>
       <c r="I189" t="n">
-        <v>0.2922</v>
+        <v>0.2891</v>
       </c>
       <c r="J189" t="n">
-        <v>8.766</v>
+        <v>8.673</v>
       </c>
     </row>
     <row r="190">
@@ -9489,10 +9489,10 @@
         <v>0.78</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.671</v>
+        <v>-0.6319</v>
       </c>
       <c r="J190" t="n">
-        <v>-20.13</v>
+        <v>-18.957</v>
       </c>
     </row>
     <row r="191">
@@ -9529,10 +9529,10 @@
         <v>0.75</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.7474</v>
+        <v>-0.6991000000000001</v>
       </c>
       <c r="J191" t="n">
-        <v>-22.422</v>
+        <v>-20.973</v>
       </c>
     </row>
     <row r="192">
@@ -9569,10 +9569,10 @@
         <v>1.09</v>
       </c>
       <c r="I192" t="n">
-        <v>0.2581</v>
+        <v>0.2562</v>
       </c>
       <c r="J192" t="n">
-        <v>6.4525</v>
+        <v>6.405</v>
       </c>
     </row>
     <row r="193">
@@ -9609,10 +9609,10 @@
         <v>0.9</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.124</v>
+        <v>-0.1391</v>
       </c>
       <c r="J193" t="n">
-        <v>-3.1</v>
+        <v>-3.4775</v>
       </c>
     </row>
     <row r="194">
@@ -9649,10 +9649,10 @@
         <v>0.86</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.1654</v>
+        <v>-0.1816</v>
       </c>
       <c r="J194" t="n">
-        <v>-4.135</v>
+        <v>-4.54</v>
       </c>
     </row>
     <row r="195">
@@ -9689,10 +9689,10 @@
         <v>0.84</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.1859</v>
+        <v>-0.2022</v>
       </c>
       <c r="J195" t="n">
-        <v>-4.6475</v>
+        <v>-5.055</v>
       </c>
     </row>
     <row r="196">
@@ -9729,10 +9729,10 @@
         <v>0.78</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.2459</v>
+        <v>-0.2619</v>
       </c>
       <c r="J196" t="n">
-        <v>-6.1475</v>
+        <v>-6.5475</v>
       </c>
     </row>
     <row r="197">
@@ -9769,10 +9769,10 @@
         <v>1.94</v>
       </c>
       <c r="I197" t="n">
-        <v>1.6491</v>
+        <v>1.6452</v>
       </c>
       <c r="J197" t="n">
-        <v>41.2275</v>
+        <v>41.13</v>
       </c>
     </row>
     <row r="198">
@@ -9809,10 +9809,10 @@
         <v>1.27</v>
       </c>
       <c r="I198" t="n">
-        <v>0.7071</v>
+        <v>0.6802</v>
       </c>
       <c r="J198" t="n">
-        <v>17.6775</v>
+        <v>17.005</v>
       </c>
     </row>
     <row r="199">
@@ -9849,10 +9849,10 @@
         <v>1.11</v>
       </c>
       <c r="I199" t="n">
-        <v>0.3076</v>
+        <v>0.3202</v>
       </c>
       <c r="J199" t="n">
-        <v>7.69</v>
+        <v>8.005000000000001</v>
       </c>
     </row>
     <row r="200">
@@ -9889,10 +9889,10 @@
         <v>1.1</v>
       </c>
       <c r="I200" t="n">
-        <v>0.2795</v>
+        <v>0.2943</v>
       </c>
       <c r="J200" t="n">
-        <v>6.9875</v>
+        <v>7.3575</v>
       </c>
     </row>
     <row r="201">
@@ -9929,10 +9929,10 @@
         <v>1.07</v>
       </c>
       <c r="I201" t="n">
-        <v>0.1915</v>
+        <v>0.2124</v>
       </c>
       <c r="J201" t="n">
-        <v>4.7875</v>
+        <v>5.31</v>
       </c>
     </row>
     <row r="202">
@@ -9969,10 +9969,10 @@
         <v>1.52</v>
       </c>
       <c r="I202" t="n">
-        <v>1.1457</v>
+        <v>1.1128</v>
       </c>
       <c r="J202" t="n">
-        <v>24.0597</v>
+        <v>23.3688</v>
       </c>
     </row>
     <row r="203">
@@ -10009,10 +10009,10 @@
         <v>1.44</v>
       </c>
       <c r="I203" t="n">
-        <v>1.0446</v>
+        <v>0.9984</v>
       </c>
       <c r="J203" t="n">
-        <v>21.9366</v>
+        <v>20.9664</v>
       </c>
     </row>
     <row r="204">
@@ -10049,10 +10049,10 @@
         <v>1.41</v>
       </c>
       <c r="I204" t="n">
-        <v>0.9996</v>
+        <v>0.9475</v>
       </c>
       <c r="J204" t="n">
-        <v>20.9916</v>
+        <v>19.8975</v>
       </c>
     </row>
     <row r="205">
@@ -10089,10 +10089,10 @@
         <v>1.18</v>
       </c>
       <c r="I205" t="n">
-        <v>0.4928</v>
+        <v>0.4885</v>
       </c>
       <c r="J205" t="n">
-        <v>10.3488</v>
+        <v>10.2585</v>
       </c>
     </row>
     <row r="206">
@@ -10129,10 +10129,10 @@
         <v>0.93</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.3369</v>
+        <v>-0.3133</v>
       </c>
       <c r="J206" t="n">
-        <v>-7.0749</v>
+        <v>-6.5793</v>
       </c>
     </row>
     <row r="207">
@@ -10169,10 +10169,10 @@
         <v>1.16</v>
       </c>
       <c r="I207" t="n">
-        <v>0.4212</v>
+        <v>0.4061</v>
       </c>
       <c r="J207" t="n">
-        <v>8.8452</v>
+        <v>8.5281</v>
       </c>
     </row>
     <row r="208">
@@ -10209,10 +10209,10 @@
         <v>1.07</v>
       </c>
       <c r="I208" t="n">
-        <v>0.2304</v>
+        <v>0.2257</v>
       </c>
       <c r="J208" t="n">
-        <v>4.8384</v>
+        <v>4.7397</v>
       </c>
     </row>
     <row r="209">
@@ -10249,10 +10249,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.0725</v>
+        <v>-0.0871</v>
       </c>
       <c r="J209" t="n">
-        <v>-1.5225</v>
+        <v>-1.8291</v>
       </c>
     </row>
     <row r="210">
@@ -10289,10 +10289,10 @@
         <v>0.55</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.4581</v>
+        <v>-0.4675</v>
       </c>
       <c r="J210" t="n">
-        <v>-9.620100000000001</v>
+        <v>-9.817500000000001</v>
       </c>
     </row>
     <row r="211">
@@ -10329,10 +10329,10 @@
         <v>0.54</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.4673</v>
+        <v>-0.4762</v>
       </c>
       <c r="J211" t="n">
-        <v>-9.8133</v>
+        <v>-10.0002</v>
       </c>
     </row>
     <row r="212">
@@ -10369,10 +10369,10 @@
         <v>0.88</v>
       </c>
       <c r="I212" t="n">
-        <v>-0.1076</v>
+        <v>-0.1317</v>
       </c>
       <c r="J212" t="n">
-        <v>-2.0444</v>
+        <v>-2.5023</v>
       </c>
     </row>
     <row r="213">
@@ -10409,10 +10409,10 @@
         <v>0.76</v>
       </c>
       <c r="I213" t="n">
-        <v>-0.2382</v>
+        <v>-0.2603</v>
       </c>
       <c r="J213" t="n">
-        <v>-4.5258</v>
+        <v>-4.9457</v>
       </c>
     </row>
     <row r="214">
@@ -10449,10 +10449,10 @@
         <v>0.68</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.3136</v>
+        <v>-0.3336</v>
       </c>
       <c r="J214" t="n">
-        <v>-5.9584</v>
+        <v>-6.3384</v>
       </c>
     </row>
     <row r="215">
@@ -10489,10 +10489,10 @@
         <v>0.62</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.3683</v>
+        <v>-0.3863</v>
       </c>
       <c r="J215" t="n">
-        <v>-6.9977</v>
+        <v>-7.3397</v>
       </c>
     </row>
     <row r="216">
@@ -10529,10 +10529,10 @@
         <v>0.49</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.4898</v>
+        <v>-0.501</v>
       </c>
       <c r="J216" t="n">
-        <v>-9.3062</v>
+        <v>-9.519</v>
       </c>
     </row>
     <row r="217">
@@ -10569,10 +10569,10 @@
         <v>1.71</v>
       </c>
       <c r="I217" t="n">
-        <v>0.7893</v>
+        <v>0.7874</v>
       </c>
       <c r="J217" t="n">
-        <v>14.9967</v>
+        <v>14.9606</v>
       </c>
     </row>
     <row r="218">
@@ -10609,10 +10609,10 @@
         <v>1.66</v>
       </c>
       <c r="I218" t="n">
-        <v>0.7403</v>
+        <v>0.742</v>
       </c>
       <c r="J218" t="n">
-        <v>14.0657</v>
+        <v>14.098</v>
       </c>
     </row>
     <row r="219">
@@ -10649,10 +10649,10 @@
         <v>1.44</v>
       </c>
       <c r="I219" t="n">
-        <v>0.5222</v>
+        <v>0.5367</v>
       </c>
       <c r="J219" t="n">
-        <v>9.921799999999999</v>
+        <v>10.1973</v>
       </c>
     </row>
     <row r="220">
@@ -10689,10 +10689,10 @@
         <v>1.37</v>
       </c>
       <c r="I220" t="n">
-        <v>0.4477</v>
+        <v>0.4659</v>
       </c>
       <c r="J220" t="n">
-        <v>8.5063</v>
+        <v>8.8521</v>
       </c>
     </row>
     <row r="221">
@@ -10729,10 +10729,10 @@
         <v>1.35</v>
       </c>
       <c r="I221" t="n">
-        <v>0.4258</v>
+        <v>0.4449</v>
       </c>
       <c r="J221" t="n">
-        <v>8.090199999999999</v>
+        <v>8.453099999999999</v>
       </c>
     </row>
     <row r="222">
@@ -10769,10 +10769,10 @@
         <v>1.17</v>
       </c>
       <c r="I222" t="n">
-        <v>0.419</v>
+        <v>0.4082</v>
       </c>
       <c r="J222" t="n">
-        <v>12.151</v>
+        <v>11.8378</v>
       </c>
     </row>
     <row r="223">
@@ -10809,10 +10809,10 @@
         <v>0.89</v>
       </c>
       <c r="I223" t="n">
-        <v>-0.1347</v>
+        <v>-0.1501</v>
       </c>
       <c r="J223" t="n">
-        <v>-3.9063</v>
+        <v>-4.3529</v>
       </c>
     </row>
     <row r="224">
@@ -10849,10 +10849,10 @@
         <v>0.88</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.1452</v>
+        <v>-0.1609</v>
       </c>
       <c r="J224" t="n">
-        <v>-4.2108</v>
+        <v>-4.6661</v>
       </c>
     </row>
     <row r="225">
@@ -10889,10 +10889,10 @@
         <v>0.79</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.2368</v>
+        <v>-0.2528</v>
       </c>
       <c r="J225" t="n">
-        <v>-6.8672</v>
+        <v>-7.3312</v>
       </c>
     </row>
     <row r="226">
@@ -10929,10 +10929,10 @@
         <v>0.77</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.2565</v>
+        <v>-0.2722</v>
       </c>
       <c r="J226" t="n">
-        <v>-7.4385</v>
+        <v>-7.8938</v>
       </c>
     </row>
     <row r="227">
@@ -10969,10 +10969,10 @@
         <v>1.48</v>
       </c>
       <c r="I227" t="n">
-        <v>0.6168</v>
+        <v>0.6163</v>
       </c>
       <c r="J227" t="n">
-        <v>17.8872</v>
+        <v>17.8727</v>
       </c>
     </row>
     <row r="228">
@@ -11009,10 +11009,10 @@
         <v>1.37</v>
       </c>
       <c r="I228" t="n">
-        <v>0.4918</v>
+        <v>0.499</v>
       </c>
       <c r="J228" t="n">
-        <v>14.2622</v>
+        <v>14.471</v>
       </c>
     </row>
     <row r="229">
@@ -11049,10 +11049,10 @@
         <v>1.27</v>
       </c>
       <c r="I229" t="n">
-        <v>0.3741</v>
+        <v>0.387</v>
       </c>
       <c r="J229" t="n">
-        <v>10.8489</v>
+        <v>11.223</v>
       </c>
     </row>
     <row r="230">
@@ -11089,10 +11089,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.2433</v>
+        <v>-0.2537</v>
       </c>
       <c r="J230" t="n">
-        <v>-7.0557</v>
+        <v>-7.3573</v>
       </c>
     </row>
     <row r="231">
@@ -11129,10 +11129,10 @@
         <v>0.73</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.3214</v>
+        <v>-0.3307</v>
       </c>
       <c r="J231" t="n">
-        <v>-9.320600000000001</v>
+        <v>-9.590299999999999</v>
       </c>
     </row>
     <row r="232">
@@ -11169,10 +11169,10 @@
         <v>1.05</v>
       </c>
       <c r="I232" t="n">
-        <v>0.2534</v>
+        <v>0.2316</v>
       </c>
       <c r="J232" t="n">
-        <v>4.8146</v>
+        <v>4.4004</v>
       </c>
     </row>
     <row r="233">
@@ -11209,10 +11209,10 @@
         <v>0.79</v>
       </c>
       <c r="I233" t="n">
-        <v>-0.2141</v>
+        <v>-0.2354</v>
       </c>
       <c r="J233" t="n">
-        <v>-4.0679</v>
+        <v>-4.4726</v>
       </c>
     </row>
     <row r="234">
@@ -11249,10 +11249,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.3084</v>
+        <v>-0.3277</v>
       </c>
       <c r="J234" t="n">
-        <v>-5.8596</v>
+        <v>-6.2263</v>
       </c>
     </row>
     <row r="235">
@@ -11289,10 +11289,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.4296</v>
+        <v>-0.4435</v>
       </c>
       <c r="J235" t="n">
-        <v>-8.1624</v>
+        <v>-8.426500000000001</v>
       </c>
     </row>
     <row r="236">
@@ -11329,10 +11329,10 @@
         <v>0.5</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.4856</v>
+        <v>-0.4963</v>
       </c>
       <c r="J236" t="n">
-        <v>-9.2264</v>
+        <v>-9.4297</v>
       </c>
     </row>
     <row r="237">
@@ -11369,10 +11369,10 @@
         <v>2.34</v>
       </c>
       <c r="I237" t="n">
-        <v>1.2368</v>
+        <v>1.2537</v>
       </c>
       <c r="J237" t="n">
-        <v>23.4992</v>
+        <v>23.8203</v>
       </c>
     </row>
     <row r="238">
@@ -11409,10 +11409,10 @@
         <v>1.51</v>
       </c>
       <c r="I238" t="n">
-        <v>0.5977</v>
+        <v>0.6073</v>
       </c>
       <c r="J238" t="n">
-        <v>11.3563</v>
+        <v>11.5387</v>
       </c>
     </row>
     <row r="239">
@@ -11449,10 +11449,10 @@
         <v>1.27</v>
       </c>
       <c r="I239" t="n">
-        <v>0.3416</v>
+        <v>0.3626</v>
       </c>
       <c r="J239" t="n">
-        <v>6.4904</v>
+        <v>6.8894</v>
       </c>
     </row>
     <row r="240">
@@ -11489,10 +11489,10 @@
         <v>1.12</v>
       </c>
       <c r="I240" t="n">
-        <v>0.1528</v>
+        <v>0.1775</v>
       </c>
       <c r="J240" t="n">
-        <v>2.9032</v>
+        <v>3.3725</v>
       </c>
     </row>
     <row r="241">
@@ -11529,10 +11529,10 @@
         <v>0.96</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.1043</v>
+        <v>-0.1045</v>
       </c>
       <c r="J241" t="n">
-        <v>-1.9817</v>
+        <v>-1.9855</v>
       </c>
     </row>
     <row r="242">
@@ -11569,10 +11569,10 @@
         <v>1.25</v>
       </c>
       <c r="I242" t="n">
-        <v>0.5313</v>
+        <v>0.5187</v>
       </c>
       <c r="J242" t="n">
-        <v>15.939</v>
+        <v>15.561</v>
       </c>
     </row>
     <row r="243">
@@ -11609,10 +11609,10 @@
         <v>1.08</v>
       </c>
       <c r="I243" t="n">
-        <v>0.2063</v>
+        <v>0.2134</v>
       </c>
       <c r="J243" t="n">
-        <v>6.189</v>
+        <v>6.402</v>
       </c>
     </row>
     <row r="244">
@@ -11649,10 +11649,10 @@
         <v>1.04</v>
       </c>
       <c r="I244" t="n">
-        <v>0.1172</v>
+        <v>0.1254</v>
       </c>
       <c r="J244" t="n">
-        <v>3.516</v>
+        <v>3.762</v>
       </c>
     </row>
     <row r="245">
@@ -11689,10 +11689,10 @@
         <v>0.97</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.0495</v>
+        <v>-0.0578</v>
       </c>
       <c r="J245" t="n">
-        <v>-1.485</v>
+        <v>-1.734</v>
       </c>
     </row>
     <row r="246">
@@ -11729,10 +11729,10 @@
         <v>0.63</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.401</v>
+        <v>-0.4103</v>
       </c>
       <c r="J246" t="n">
-        <v>-12.03</v>
+        <v>-12.309</v>
       </c>
     </row>
     <row r="247">
@@ -11769,10 +11769,10 @@
         <v>1.17</v>
       </c>
       <c r="I247" t="n">
-        <v>0.2559</v>
+        <v>0.271</v>
       </c>
       <c r="J247" t="n">
-        <v>7.677</v>
+        <v>8.130000000000001</v>
       </c>
     </row>
     <row r="248">
@@ -11809,10 +11809,10 @@
         <v>1.15</v>
       </c>
       <c r="I248" t="n">
-        <v>0.2298</v>
+        <v>0.2453</v>
       </c>
       <c r="J248" t="n">
-        <v>6.894</v>
+        <v>7.359</v>
       </c>
     </row>
     <row r="249">
@@ -11849,10 +11849,10 @@
         <v>1.1</v>
       </c>
       <c r="I249" t="n">
-        <v>0.1628</v>
+        <v>0.1782</v>
       </c>
       <c r="J249" t="n">
-        <v>4.884</v>
+        <v>5.346</v>
       </c>
     </row>
     <row r="250">
@@ -11889,10 +11889,10 @@
         <v>1.09</v>
       </c>
       <c r="I250" t="n">
-        <v>0.1492</v>
+        <v>0.1642</v>
       </c>
       <c r="J250" t="n">
-        <v>4.476</v>
+        <v>4.926</v>
       </c>
     </row>
     <row r="251">
@@ -11929,10 +11929,10 @@
         <v>0.96</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.0728</v>
+        <v>-0.0799</v>
       </c>
       <c r="J251" t="n">
-        <v>-2.184</v>
+        <v>-2.397</v>
       </c>
     </row>
     <row r="252">
@@ -11969,10 +11969,10 @@
         <v>1.79</v>
       </c>
       <c r="I252" t="n">
-        <v>1.546</v>
+        <v>1.5257</v>
       </c>
       <c r="J252" t="n">
-        <v>43.288</v>
+        <v>42.7196</v>
       </c>
     </row>
     <row r="253">
@@ -12009,10 +12009,10 @@
         <v>1.01</v>
       </c>
       <c r="I253" t="n">
-        <v>0.0343</v>
+        <v>0.0457</v>
       </c>
       <c r="J253" t="n">
-        <v>0.9604</v>
+        <v>1.2796</v>
       </c>
     </row>
     <row r="254">
@@ -12049,10 +12049,10 @@
         <v>0.97</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.1532</v>
+        <v>-0.1515</v>
       </c>
       <c r="J254" t="n">
-        <v>-4.2896</v>
+        <v>-4.242</v>
       </c>
     </row>
     <row r="255">
@@ -12089,10 +12089,10 @@
         <v>0.88</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.4316</v>
+        <v>-0.412</v>
       </c>
       <c r="J255" t="n">
-        <v>-12.0848</v>
+        <v>-11.536</v>
       </c>
     </row>
     <row r="256">
@@ -12129,10 +12129,10 @@
         <v>0.8</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.6471</v>
+        <v>-0.6056</v>
       </c>
       <c r="J256" t="n">
-        <v>-18.1188</v>
+        <v>-16.9568</v>
       </c>
     </row>
     <row r="257">
@@ -12169,10 +12169,10 @@
         <v>1.21</v>
       </c>
       <c r="I257" t="n">
-        <v>0.471</v>
+        <v>0.461</v>
       </c>
       <c r="J257" t="n">
-        <v>13.188</v>
+        <v>12.908</v>
       </c>
     </row>
     <row r="258">
@@ -12209,10 +12209,10 @@
         <v>1.15</v>
       </c>
       <c r="I258" t="n">
-        <v>0.3573</v>
+        <v>0.3552</v>
       </c>
       <c r="J258" t="n">
-        <v>10.0044</v>
+        <v>9.945600000000001</v>
       </c>
     </row>
     <row r="259">
@@ -12249,10 +12249,10 @@
         <v>0.97</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.0472</v>
+        <v>-0.0561</v>
       </c>
       <c r="J259" t="n">
-        <v>-1.3216</v>
+        <v>-1.5708</v>
       </c>
     </row>
     <row r="260">
@@ -12289,10 +12289,10 @@
         <v>0.83</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.2039</v>
+        <v>-0.2185</v>
       </c>
       <c r="J260" t="n">
-        <v>-5.7092</v>
+        <v>-6.118</v>
       </c>
     </row>
     <row r="261">
@@ -12329,10 +12329,10 @@
         <v>0.64</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.388</v>
+        <v>-0.3984</v>
       </c>
       <c r="J261" t="n">
-        <v>-10.864</v>
+        <v>-11.1552</v>
       </c>
     </row>
     <row r="262">
@@ -12369,10 +12369,10 @@
         <v>0.67</v>
       </c>
       <c r="I262" t="n">
-        <v>-0.3048</v>
+        <v>-0.3287</v>
       </c>
       <c r="J262" t="n">
-        <v>-5.7912</v>
+        <v>-6.2453</v>
       </c>
     </row>
     <row r="263">
@@ -12409,10 +12409,10 @@
         <v>0.67</v>
       </c>
       <c r="I263" t="n">
-        <v>-0.3048</v>
+        <v>-0.3287</v>
       </c>
       <c r="J263" t="n">
-        <v>-5.7912</v>
+        <v>-6.2453</v>
       </c>
     </row>
     <row r="264">
@@ -12449,10 +12449,10 @@
         <v>0.66</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.3148</v>
+        <v>-0.3382</v>
       </c>
       <c r="J264" t="n">
-        <v>-5.9812</v>
+        <v>-6.4258</v>
       </c>
     </row>
     <row r="265">
@@ -12489,10 +12489,10 @@
         <v>0.55</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.4155</v>
+        <v>-0.4341</v>
       </c>
       <c r="J265" t="n">
-        <v>-7.8945</v>
+        <v>-8.2479</v>
       </c>
     </row>
     <row r="266">
@@ -12529,10 +12529,10 @@
         <v>0.37</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.5859</v>
+        <v>-0.5925</v>
       </c>
       <c r="J266" t="n">
-        <v>-11.1321</v>
+        <v>-11.2575</v>
       </c>
     </row>
     <row r="267">
@@ -12569,10 +12569,10 @@
         <v>2.18</v>
       </c>
       <c r="I267" t="n">
-        <v>1.8338</v>
+        <v>1.8613</v>
       </c>
       <c r="J267" t="n">
-        <v>34.8422</v>
+        <v>35.3647</v>
       </c>
     </row>
     <row r="268">
@@ -12609,10 +12609,10 @@
         <v>2.01</v>
       </c>
       <c r="I268" t="n">
-        <v>1.6618</v>
+        <v>1.6689</v>
       </c>
       <c r="J268" t="n">
-        <v>31.5742</v>
+        <v>31.7091</v>
       </c>
     </row>
     <row r="269">
@@ -12649,10 +12649,10 @@
         <v>1.46</v>
       </c>
       <c r="I269" t="n">
-        <v>1.0406</v>
+        <v>1.0012</v>
       </c>
       <c r="J269" t="n">
-        <v>19.7714</v>
+        <v>19.0228</v>
       </c>
     </row>
     <row r="270">
@@ -12689,10 +12689,10 @@
         <v>1.42</v>
       </c>
       <c r="I270" t="n">
-        <v>0.9797</v>
+        <v>0.9349</v>
       </c>
       <c r="J270" t="n">
-        <v>18.6143</v>
+        <v>17.7631</v>
       </c>
     </row>
     <row r="271">
@@ -12729,10 +12729,10 @@
         <v>0.72</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.9399</v>
+        <v>-0.8478</v>
       </c>
       <c r="J271" t="n">
-        <v>-17.8581</v>
+        <v>-16.1082</v>
       </c>
     </row>
     <row r="272">
@@ -12769,10 +12769,10 @@
         <v>1.35</v>
       </c>
       <c r="I272" t="n">
-        <v>0.8031</v>
+        <v>0.7493</v>
       </c>
       <c r="J272" t="n">
-        <v>19.2744</v>
+        <v>17.9832</v>
       </c>
     </row>
     <row r="273">
@@ -12809,10 +12809,10 @@
         <v>0.95</v>
       </c>
       <c r="I273" t="n">
-        <v>-0.0537</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="J273" t="n">
-        <v>-1.2888</v>
+        <v>-1.656</v>
       </c>
     </row>
     <row r="274">
@@ -12849,10 +12849,10 @@
         <v>0.78</v>
       </c>
       <c r="I274" t="n">
-        <v>-0.2363</v>
+        <v>-0.2545</v>
       </c>
       <c r="J274" t="n">
-        <v>-5.6712</v>
+        <v>-6.108</v>
       </c>
     </row>
     <row r="275">
@@ -12889,10 +12889,10 @@
         <v>0.61</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.3979</v>
+        <v>-0.411</v>
       </c>
       <c r="J275" t="n">
-        <v>-9.5496</v>
+        <v>-9.864000000000001</v>
       </c>
     </row>
     <row r="276">
@@ -12929,10 +12929,10 @@
         <v>0.4</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.5909</v>
+        <v>-0.5927</v>
       </c>
       <c r="J276" t="n">
-        <v>-14.1816</v>
+        <v>-14.2248</v>
       </c>
     </row>
     <row r="277">
@@ -12969,10 +12969,10 @@
         <v>1.61</v>
       </c>
       <c r="I277" t="n">
-        <v>1.2525</v>
+        <v>1.228</v>
       </c>
       <c r="J277" t="n">
-        <v>30.06</v>
+        <v>29.472</v>
       </c>
     </row>
     <row r="278">
@@ -13009,10 +13009,10 @@
         <v>1.58</v>
       </c>
       <c r="I278" t="n">
-        <v>1.216</v>
+        <v>1.1889</v>
       </c>
       <c r="J278" t="n">
-        <v>29.184</v>
+        <v>28.5336</v>
       </c>
     </row>
     <row r="279">
@@ -13049,10 +13049,10 @@
         <v>1.36</v>
       </c>
       <c r="I279" t="n">
-        <v>0.9002</v>
+        <v>0.8518</v>
       </c>
       <c r="J279" t="n">
-        <v>21.6048</v>
+        <v>20.4432</v>
       </c>
     </row>
     <row r="280">
@@ -13089,10 +13089,10 @@
         <v>1.11</v>
       </c>
       <c r="I280" t="n">
-        <v>0.304</v>
+        <v>0.3176</v>
       </c>
       <c r="J280" t="n">
-        <v>7.296</v>
+        <v>7.6224</v>
       </c>
     </row>
     <row r="281">
@@ -13129,10 +13129,10 @@
         <v>0.91</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.4011</v>
+        <v>-0.3721</v>
       </c>
       <c r="J281" t="n">
-        <v>-9.6264</v>
+        <v>-8.930400000000001</v>
       </c>
     </row>
     <row r="282">
@@ -13169,10 +13169,10 @@
         <v>1.23</v>
       </c>
       <c r="I282" t="n">
-        <v>0.6707</v>
+        <v>0.6364</v>
       </c>
       <c r="J282" t="n">
-        <v>19.4503</v>
+        <v>18.4556</v>
       </c>
     </row>
     <row r="283">
@@ -13209,10 +13209,10 @@
         <v>1.16</v>
       </c>
       <c r="I283" t="n">
-        <v>0.4919</v>
+        <v>0.4768</v>
       </c>
       <c r="J283" t="n">
-        <v>14.2651</v>
+        <v>13.8272</v>
       </c>
     </row>
     <row r="284">
@@ -13249,10 +13249,10 @@
         <v>1.01</v>
       </c>
       <c r="I284" t="n">
-        <v>0.0408</v>
+        <v>0.0502</v>
       </c>
       <c r="J284" t="n">
-        <v>1.1832</v>
+        <v>1.4558</v>
       </c>
     </row>
     <row r="285">
@@ -13289,10 +13289,10 @@
         <v>0.98</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.1092</v>
+        <v>-0.1102</v>
       </c>
       <c r="J285" t="n">
-        <v>-3.1668</v>
+        <v>-3.1958</v>
       </c>
     </row>
     <row r="286">
@@ -13329,10 +13329,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.2465</v>
+        <v>-0.2425</v>
       </c>
       <c r="J286" t="n">
-        <v>-7.1485</v>
+        <v>-7.0325</v>
       </c>
     </row>
     <row r="287">
@@ -13369,10 +13369,10 @@
         <v>1.27</v>
       </c>
       <c r="I287" t="n">
-        <v>0.5528</v>
+        <v>0.5409</v>
       </c>
       <c r="J287" t="n">
-        <v>16.0312</v>
+        <v>15.6861</v>
       </c>
     </row>
     <row r="288">
@@ -13409,10 +13409,10 @@
         <v>1.05</v>
       </c>
       <c r="I288" t="n">
-        <v>0.1334</v>
+        <v>0.1437</v>
       </c>
       <c r="J288" t="n">
-        <v>3.8686</v>
+        <v>4.1673</v>
       </c>
     </row>
     <row r="289">
@@ -13449,10 +13449,10 @@
         <v>0.99</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.0234</v>
+        <v>-0.0274</v>
       </c>
       <c r="J289" t="n">
-        <v>-0.6786</v>
+        <v>-0.7946</v>
       </c>
     </row>
     <row r="290">
@@ -13489,10 +13489,10 @@
         <v>0.98</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.0391</v>
+        <v>-0.0451</v>
       </c>
       <c r="J290" t="n">
-        <v>-1.1339</v>
+        <v>-1.3079</v>
       </c>
     </row>
     <row r="291">
@@ -13529,10 +13529,10 @@
         <v>0.88</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.16</v>
+        <v>-0.1723</v>
       </c>
       <c r="J291" t="n">
-        <v>-4.64</v>
+        <v>-4.9967</v>
       </c>
     </row>
     <row r="292">
@@ -13569,10 +13569,10 @@
         <v>1.21</v>
       </c>
       <c r="I292" t="n">
-        <v>0.4532</v>
+        <v>0.4479</v>
       </c>
       <c r="J292" t="n">
-        <v>12.6896</v>
+        <v>12.5412</v>
       </c>
     </row>
     <row r="293">
@@ -13609,10 +13609,10 @@
         <v>1.11</v>
       </c>
       <c r="I293" t="n">
-        <v>0.2636</v>
+        <v>0.2697</v>
       </c>
       <c r="J293" t="n">
-        <v>7.3808</v>
+        <v>7.5516</v>
       </c>
     </row>
     <row r="294">
@@ -13649,10 +13649,10 @@
         <v>1.01</v>
       </c>
       <c r="I294" t="n">
-        <v>0.0365</v>
+        <v>0.0425</v>
       </c>
       <c r="J294" t="n">
-        <v>1.022</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="295">
@@ -13689,10 +13689,10 @@
         <v>0.93</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.1013</v>
+        <v>-0.1125</v>
       </c>
       <c r="J295" t="n">
-        <v>-2.8364</v>
+        <v>-3.15</v>
       </c>
     </row>
     <row r="296">
@@ -13729,10 +13729,10 @@
         <v>0.8</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.2404</v>
+        <v>-0.2535</v>
       </c>
       <c r="J296" t="n">
-        <v>-6.7312</v>
+        <v>-7.098</v>
       </c>
     </row>
     <row r="297">
@@ -13769,10 +13769,10 @@
         <v>1.36</v>
       </c>
       <c r="I297" t="n">
-        <v>0.4874</v>
+        <v>0.4936</v>
       </c>
       <c r="J297" t="n">
-        <v>13.6472</v>
+        <v>13.8208</v>
       </c>
     </row>
     <row r="298">
@@ -13809,10 +13809,10 @@
         <v>1.34</v>
       </c>
       <c r="I298" t="n">
-        <v>0.4639</v>
+        <v>0.4714</v>
       </c>
       <c r="J298" t="n">
-        <v>12.9892</v>
+        <v>13.1992</v>
       </c>
     </row>
     <row r="299">
@@ -13849,10 +13849,10 @@
         <v>1.03</v>
       </c>
       <c r="I299" t="n">
-        <v>0.0553</v>
+        <v>0.0668</v>
       </c>
       <c r="J299" t="n">
-        <v>1.5484</v>
+        <v>1.8704</v>
       </c>
     </row>
     <row r="300">
@@ -13889,10 +13889,10 @@
         <v>1.02</v>
       </c>
       <c r="I300" t="n">
-        <v>0.0368</v>
+        <v>0.0469</v>
       </c>
       <c r="J300" t="n">
-        <v>1.0304</v>
+        <v>1.3132</v>
       </c>
     </row>
     <row r="301">
@@ -13929,10 +13929,10 @@
         <v>0.74</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.3085</v>
+        <v>-0.3187</v>
       </c>
       <c r="J301" t="n">
-        <v>-8.638</v>
+        <v>-8.9236</v>
       </c>
     </row>
     <row r="302">
@@ -13969,10 +13969,10 @@
         <v>1.07</v>
       </c>
       <c r="I302" t="n">
-        <v>0.1893</v>
+        <v>0.1957</v>
       </c>
       <c r="J302" t="n">
-        <v>5.679</v>
+        <v>5.871</v>
       </c>
     </row>
     <row r="303">
@@ -14009,10 +14009,10 @@
         <v>1.07</v>
       </c>
       <c r="I303" t="n">
-        <v>0.1893</v>
+        <v>0.1957</v>
       </c>
       <c r="J303" t="n">
-        <v>5.679</v>
+        <v>5.871</v>
       </c>
     </row>
     <row r="304">
@@ -14049,10 +14049,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.0857</v>
+        <v>-0.09719999999999999</v>
       </c>
       <c r="J304" t="n">
-        <v>-2.571</v>
+        <v>-2.916</v>
       </c>
     </row>
     <row r="305">
@@ -14089,10 +14089,10 @@
         <v>0.93</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.09760000000000001</v>
+        <v>-0.1096</v>
       </c>
       <c r="J305" t="n">
-        <v>-2.928</v>
+        <v>-3.288</v>
       </c>
     </row>
     <row r="306">
@@ -14129,10 +14129,10 @@
         <v>0.87</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.1641</v>
+        <v>-0.1781</v>
       </c>
       <c r="J306" t="n">
-        <v>-4.923</v>
+        <v>-5.343</v>
       </c>
     </row>
     <row r="307">
@@ -14169,10 +14169,10 @@
         <v>1.26</v>
       </c>
       <c r="I307" t="n">
-        <v>0.3586</v>
+        <v>0.3729</v>
       </c>
       <c r="J307" t="n">
-        <v>10.758</v>
+        <v>11.187</v>
       </c>
     </row>
     <row r="308">
@@ -14209,10 +14209,10 @@
         <v>1.21</v>
       </c>
       <c r="I308" t="n">
-        <v>0.2981</v>
+        <v>0.3142</v>
       </c>
       <c r="J308" t="n">
-        <v>8.943</v>
+        <v>9.426</v>
       </c>
     </row>
     <row r="309">
@@ -14249,10 +14249,10 @@
         <v>1.19</v>
       </c>
       <c r="I309" t="n">
-        <v>0.2735</v>
+        <v>0.2901</v>
       </c>
       <c r="J309" t="n">
-        <v>8.205</v>
+        <v>8.702999999999999</v>
       </c>
     </row>
     <row r="310">
@@ -14289,10 +14289,10 @@
         <v>1.08</v>
       </c>
       <c r="I310" t="n">
-        <v>0.1286</v>
+        <v>0.145</v>
       </c>
       <c r="J310" t="n">
-        <v>3.858</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="311">
@@ -14329,10 +14329,10 @@
         <v>1.03</v>
       </c>
       <c r="I311" t="n">
-        <v>0.0483</v>
+        <v>0.0615</v>
       </c>
       <c r="J311" t="n">
-        <v>1.449</v>
+        <v>1.845</v>
       </c>
     </row>
     <row r="312">
@@ -14369,10 +14369,10 @@
         <v>1.7</v>
       </c>
       <c r="I312" t="n">
-        <v>1.3578</v>
+        <v>1.3405</v>
       </c>
       <c r="J312" t="n">
-        <v>31.2294</v>
+        <v>30.8315</v>
       </c>
     </row>
     <row r="313">
@@ -14409,10 +14409,10 @@
         <v>1.34</v>
       </c>
       <c r="I313" t="n">
-        <v>0.855</v>
+        <v>0.8124</v>
       </c>
       <c r="J313" t="n">
-        <v>19.665</v>
+        <v>18.6852</v>
       </c>
     </row>
     <row r="314">
@@ -14449,10 +14449,10 @@
         <v>1.29</v>
       </c>
       <c r="I314" t="n">
-        <v>0.747</v>
+        <v>0.7167</v>
       </c>
       <c r="J314" t="n">
-        <v>17.181</v>
+        <v>16.4841</v>
       </c>
     </row>
     <row r="315">
@@ -14489,10 +14489,10 @@
         <v>1.21</v>
       </c>
       <c r="I315" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5503</v>
       </c>
       <c r="J315" t="n">
-        <v>12.88</v>
+        <v>12.6569</v>
       </c>
     </row>
     <row r="316">
@@ -14529,10 +14529,10 @@
         <v>1.1</v>
       </c>
       <c r="I316" t="n">
-        <v>0.2726</v>
+        <v>0.2895</v>
       </c>
       <c r="J316" t="n">
-        <v>6.2698</v>
+        <v>6.6585</v>
       </c>
     </row>
     <row r="317">
@@ -14569,10 +14569,10 @@
         <v>1.12</v>
       </c>
       <c r="I317" t="n">
-        <v>0.3498</v>
+        <v>0.3373</v>
       </c>
       <c r="J317" t="n">
-        <v>8.045400000000001</v>
+        <v>7.7579</v>
       </c>
     </row>
     <row r="318">
@@ -14609,10 +14609,10 @@
         <v>0.88</v>
       </c>
       <c r="I318" t="n">
-        <v>-0.1384</v>
+        <v>-0.1557</v>
       </c>
       <c r="J318" t="n">
-        <v>-3.1832</v>
+        <v>-3.5811</v>
       </c>
     </row>
     <row r="319">
@@ -14649,10 +14649,10 @@
         <v>0.78</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.2378</v>
+        <v>-0.2557</v>
       </c>
       <c r="J319" t="n">
-        <v>-5.4694</v>
+        <v>-5.8811</v>
       </c>
     </row>
     <row r="320">
@@ -14689,10 +14689,10 @@
         <v>0.73</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.2861</v>
+        <v>-0.303</v>
       </c>
       <c r="J320" t="n">
-        <v>-6.5803</v>
+        <v>-6.969</v>
       </c>
     </row>
     <row r="321">
@@ -14729,10 +14729,10 @@
         <v>0.64</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.3715</v>
+        <v>-0.3855</v>
       </c>
       <c r="J321" t="n">
-        <v>-8.544499999999999</v>
+        <v>-8.8665</v>
       </c>
     </row>
     <row r="322">
@@ -14769,10 +14769,10 @@
         <v>1.11</v>
       </c>
       <c r="I322" t="n">
-        <v>0.2682</v>
+        <v>0.273</v>
       </c>
       <c r="J322" t="n">
-        <v>11.2644</v>
+        <v>11.466</v>
       </c>
     </row>
     <row r="323">
@@ -14809,10 +14809,10 @@
         <v>1.06</v>
       </c>
       <c r="I323" t="n">
-        <v>0.1631</v>
+        <v>0.1711</v>
       </c>
       <c r="J323" t="n">
-        <v>6.8502</v>
+        <v>7.1862</v>
       </c>
     </row>
     <row r="324">
@@ -14849,10 +14849,10 @@
         <v>1.02</v>
       </c>
       <c r="I324" t="n">
-        <v>0.067</v>
+        <v>0.0741</v>
       </c>
       <c r="J324" t="n">
-        <v>2.814</v>
+        <v>3.1122</v>
       </c>
     </row>
     <row r="325">
@@ -14889,10 +14889,10 @@
         <v>1</v>
       </c>
       <c r="I325" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0004</v>
       </c>
       <c r="J325" t="n">
-        <v>0.0252</v>
+        <v>0.0168</v>
       </c>
     </row>
     <row r="326">
@@ -14929,10 +14929,10 @@
         <v>0.78</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.2582</v>
+        <v>-0.2715</v>
       </c>
       <c r="J326" t="n">
-        <v>-10.8444</v>
+        <v>-11.403</v>
       </c>
     </row>
     <row r="327">
@@ -14969,10 +14969,10 @@
         <v>1.31</v>
       </c>
       <c r="I327" t="n">
-        <v>0.8567</v>
+        <v>0.8011</v>
       </c>
       <c r="J327" t="n">
-        <v>35.9814</v>
+        <v>33.6462</v>
       </c>
     </row>
     <row r="328">
@@ -15009,10 +15009,10 @@
         <v>1.09</v>
       </c>
       <c r="I328" t="n">
-        <v>0.2976</v>
+        <v>0.2999</v>
       </c>
       <c r="J328" t="n">
-        <v>12.4992</v>
+        <v>12.5958</v>
       </c>
     </row>
     <row r="329">
@@ -15049,10 +15049,10 @@
         <v>1.08</v>
       </c>
       <c r="I329" t="n">
-        <v>0.2699</v>
+        <v>0.2739</v>
       </c>
       <c r="J329" t="n">
-        <v>11.3358</v>
+        <v>11.5038</v>
       </c>
     </row>
     <row r="330">
@@ -15089,10 +15089,10 @@
         <v>1.01</v>
       </c>
       <c r="I330" t="n">
-        <v>0.0354</v>
+        <v>0.0464</v>
       </c>
       <c r="J330" t="n">
-        <v>1.4868</v>
+        <v>1.9488</v>
       </c>
     </row>
     <row r="331">
@@ -15129,10 +15129,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.2526</v>
+        <v>-0.2467</v>
       </c>
       <c r="J331" t="n">
-        <v>-10.6092</v>
+        <v>-10.3614</v>
       </c>
     </row>
     <row r="332">
@@ -15169,10 +15169,10 @@
         <v>1.35</v>
       </c>
       <c r="I332" t="n">
-        <v>0.9061</v>
+        <v>0.8519</v>
       </c>
       <c r="J332" t="n">
-        <v>22.6525</v>
+        <v>21.2975</v>
       </c>
     </row>
     <row r="333">
@@ -15209,10 +15209,10 @@
         <v>1.22</v>
       </c>
       <c r="I333" t="n">
-        <v>0.6063</v>
+        <v>0.587</v>
       </c>
       <c r="J333" t="n">
-        <v>15.1575</v>
+        <v>14.675</v>
       </c>
     </row>
     <row r="334">
@@ -15249,10 +15249,10 @@
         <v>1.21</v>
       </c>
       <c r="I334" t="n">
-        <v>0.5829</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="J334" t="n">
-        <v>14.5725</v>
+        <v>14.15</v>
       </c>
     </row>
     <row r="335">
@@ -15289,10 +15289,10 @@
         <v>1.15</v>
       </c>
       <c r="I335" t="n">
-        <v>0.4363</v>
+        <v>0.433</v>
       </c>
       <c r="J335" t="n">
-        <v>10.9075</v>
+        <v>10.825</v>
       </c>
     </row>
     <row r="336">
@@ -15329,10 +15329,10 @@
         <v>1.09</v>
       </c>
       <c r="I336" t="n">
-        <v>0.273</v>
+        <v>0.2832</v>
       </c>
       <c r="J336" t="n">
-        <v>6.825</v>
+        <v>7.08</v>
       </c>
     </row>
     <row r="337">
@@ -15369,10 +15369,10 @@
         <v>1.12</v>
       </c>
       <c r="I337" t="n">
-        <v>0.3006</v>
+        <v>0.3011</v>
       </c>
       <c r="J337" t="n">
-        <v>7.515</v>
+        <v>7.5275</v>
       </c>
     </row>
     <row r="338">
@@ -15409,10 +15409,10 @@
         <v>1.06</v>
       </c>
       <c r="I338" t="n">
-        <v>0.1734</v>
+        <v>0.1785</v>
       </c>
       <c r="J338" t="n">
-        <v>4.335</v>
+        <v>4.4625</v>
       </c>
     </row>
     <row r="339">
@@ -15449,10 +15449,10 @@
         <v>0.98</v>
       </c>
       <c r="I339" t="n">
-        <v>-0.0325</v>
+        <v>-0.0401</v>
       </c>
       <c r="J339" t="n">
-        <v>-0.8125</v>
+        <v>-1.0025</v>
       </c>
     </row>
     <row r="340">
@@ -15489,10 +15489,10 @@
         <v>0.82</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.2131</v>
+        <v>-0.2279</v>
       </c>
       <c r="J340" t="n">
-        <v>-5.3275</v>
+        <v>-5.6975</v>
       </c>
     </row>
     <row r="341">
@@ -15529,10 +15529,10 @@
         <v>0.78</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.2532</v>
+        <v>-0.2676</v>
       </c>
       <c r="J341" t="n">
-        <v>-6.33</v>
+        <v>-6.69</v>
       </c>
     </row>
     <row r="342">
@@ -15569,10 +15569,10 @@
         <v>1.28</v>
       </c>
       <c r="I342" t="n">
-        <v>0.5736</v>
+        <v>0.5593</v>
       </c>
       <c r="J342" t="n">
-        <v>24.0912</v>
+        <v>23.4906</v>
       </c>
     </row>
     <row r="343">
@@ -15609,10 +15609,10 @@
         <v>1.19</v>
       </c>
       <c r="I343" t="n">
-        <v>0.413</v>
+        <v>0.4113</v>
       </c>
       <c r="J343" t="n">
-        <v>17.346</v>
+        <v>17.2746</v>
       </c>
     </row>
     <row r="344">
@@ -15649,10 +15649,10 @@
         <v>1.13</v>
       </c>
       <c r="I344" t="n">
-        <v>0.3</v>
+        <v>0.3051</v>
       </c>
       <c r="J344" t="n">
-        <v>12.6</v>
+        <v>12.8142</v>
       </c>
     </row>
     <row r="345">
@@ -15689,10 +15689,10 @@
         <v>0.76</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.2813</v>
+        <v>-0.2935</v>
       </c>
       <c r="J345" t="n">
-        <v>-11.8146</v>
+        <v>-12.327</v>
       </c>
     </row>
     <row r="346">
@@ -15729,10 +15729,10 @@
         <v>0.76</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.2813</v>
+        <v>-0.2935</v>
       </c>
       <c r="J346" t="n">
-        <v>-11.8146</v>
+        <v>-12.327</v>
       </c>
     </row>
     <row r="347">
@@ -15769,10 +15769,10 @@
         <v>1.35</v>
       </c>
       <c r="I347" t="n">
-        <v>0.946</v>
+        <v>0.8814</v>
       </c>
       <c r="J347" t="n">
-        <v>39.732</v>
+        <v>37.0188</v>
       </c>
     </row>
     <row r="348">
@@ -15809,10 +15809,10 @@
         <v>1.28</v>
       </c>
       <c r="I348" t="n">
-        <v>0.7824</v>
+        <v>0.7366</v>
       </c>
       <c r="J348" t="n">
-        <v>32.8608</v>
+        <v>30.9372</v>
       </c>
     </row>
     <row r="349">
@@ -15849,10 +15849,10 @@
         <v>1.24</v>
       </c>
       <c r="I349" t="n">
-        <v>0.6851</v>
+        <v>0.651</v>
       </c>
       <c r="J349" t="n">
-        <v>28.7742</v>
+        <v>27.342</v>
       </c>
     </row>
     <row r="350">
@@ -15889,10 +15889,10 @@
         <v>0.85</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.515</v>
+        <v>-0.4875</v>
       </c>
       <c r="J350" t="n">
-        <v>-21.63</v>
+        <v>-20.475</v>
       </c>
     </row>
     <row r="351">
@@ -15929,10 +15929,10 @@
         <v>0.74</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.8002</v>
+        <v>-0.7406</v>
       </c>
       <c r="J351" t="n">
-        <v>-33.6084</v>
+        <v>-31.1052</v>
       </c>
     </row>
     <row r="352">
@@ -15969,10 +15969,10 @@
         <v>1.62</v>
       </c>
       <c r="I352" t="n">
-        <v>1.3022</v>
+        <v>1.2741</v>
       </c>
       <c r="J352" t="n">
-        <v>35.1594</v>
+        <v>34.4007</v>
       </c>
     </row>
     <row r="353">
@@ -16009,10 +16009,10 @@
         <v>1.56</v>
       </c>
       <c r="I353" t="n">
-        <v>1.2261</v>
+        <v>1.1933</v>
       </c>
       <c r="J353" t="n">
-        <v>33.1047</v>
+        <v>32.2191</v>
       </c>
     </row>
     <row r="354">
@@ -16049,10 +16049,10 @@
         <v>1.18</v>
       </c>
       <c r="I354" t="n">
-        <v>0.5164</v>
+        <v>0.5046</v>
       </c>
       <c r="J354" t="n">
-        <v>13.9428</v>
+        <v>13.6242</v>
       </c>
     </row>
     <row r="355">
@@ -16089,10 +16089,10 @@
         <v>0.77</v>
       </c>
       <c r="I355" t="n">
-        <v>-0.7445000000000001</v>
+        <v>-0.6882</v>
       </c>
       <c r="J355" t="n">
-        <v>-20.1015</v>
+        <v>-18.5814</v>
       </c>
     </row>
     <row r="356">
@@ -16129,10 +16129,10 @@
         <v>0.72</v>
       </c>
       <c r="I356" t="n">
-        <v>-0.869</v>
+        <v>-0.7976</v>
       </c>
       <c r="J356" t="n">
-        <v>-23.463</v>
+        <v>-21.5352</v>
       </c>
     </row>
     <row r="357">
@@ -16169,10 +16169,10 @@
         <v>1.03</v>
       </c>
       <c r="I357" t="n">
-        <v>0.1128</v>
+        <v>0.1151</v>
       </c>
       <c r="J357" t="n">
-        <v>3.0456</v>
+        <v>3.1077</v>
       </c>
     </row>
     <row r="358">
@@ -16209,10 +16209,10 @@
         <v>0.99</v>
       </c>
       <c r="I358" t="n">
-        <v>-0.0118</v>
+        <v>-0.0186</v>
       </c>
       <c r="J358" t="n">
-        <v>-0.3186</v>
+        <v>-0.5022</v>
       </c>
     </row>
     <row r="359">
@@ -16249,10 +16249,10 @@
         <v>0.97</v>
       </c>
       <c r="I359" t="n">
-        <v>-0.0421</v>
+        <v>-0.0522</v>
       </c>
       <c r="J359" t="n">
-        <v>-1.1367</v>
+        <v>-1.4094</v>
       </c>
     </row>
     <row r="360">
@@ -16289,10 +16289,10 @@
         <v>0.93</v>
       </c>
       <c r="I360" t="n">
-        <v>-0.09229999999999999</v>
+        <v>-0.1057</v>
       </c>
       <c r="J360" t="n">
-        <v>-2.4921</v>
+        <v>-2.8539</v>
       </c>
     </row>
     <row r="361">
@@ -16329,10 +16329,10 @@
         <v>0.64</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.3823</v>
+        <v>-0.394</v>
       </c>
       <c r="J361" t="n">
-        <v>-10.3221</v>
+        <v>-10.638</v>
       </c>
     </row>
     <row r="362">
@@ -16369,10 +16369,10 @@
         <v>1.35</v>
       </c>
       <c r="I362" t="n">
-        <v>0.7524</v>
+        <v>0.7116</v>
       </c>
       <c r="J362" t="n">
-        <v>19.5624</v>
+        <v>18.5016</v>
       </c>
     </row>
     <row r="363">
@@ -16409,10 +16409,10 @@
         <v>0.83</v>
       </c>
       <c r="I363" t="n">
-        <v>-0.1965</v>
+        <v>-0.2128</v>
       </c>
       <c r="J363" t="n">
-        <v>-5.109</v>
+        <v>-5.5328</v>
       </c>
     </row>
     <row r="364">
@@ -16449,10 +16449,10 @@
         <v>0.8</v>
       </c>
       <c r="I364" t="n">
-        <v>-0.2266</v>
+        <v>-0.2428</v>
       </c>
       <c r="J364" t="n">
-        <v>-5.8916</v>
+        <v>-6.3128</v>
       </c>
     </row>
     <row r="365">
@@ -16489,10 +16489,10 @@
         <v>0.76</v>
       </c>
       <c r="I365" t="n">
-        <v>-0.2661</v>
+        <v>-0.2816</v>
       </c>
       <c r="J365" t="n">
-        <v>-6.9186</v>
+        <v>-7.3216</v>
       </c>
     </row>
     <row r="366">
@@ -16529,10 +16529,10 @@
         <v>0.75</v>
       </c>
       <c r="I366" t="n">
-        <v>-0.2758</v>
+        <v>-0.2912</v>
       </c>
       <c r="J366" t="n">
-        <v>-7.1708</v>
+        <v>-7.5712</v>
       </c>
     </row>
     <row r="367">
@@ -16569,10 +16569,10 @@
         <v>1.51</v>
       </c>
       <c r="I367" t="n">
-        <v>1.1642</v>
+        <v>1.1267</v>
       </c>
       <c r="J367" t="n">
-        <v>30.2692</v>
+        <v>29.2942</v>
       </c>
     </row>
     <row r="368">
@@ -16609,10 +16609,10 @@
         <v>1.25</v>
       </c>
       <c r="I368" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.657</v>
       </c>
       <c r="J368" t="n">
-        <v>17.862</v>
+        <v>17.082</v>
       </c>
     </row>
     <row r="369">
@@ -16649,10 +16649,10 @@
         <v>1.09</v>
       </c>
       <c r="I369" t="n">
-        <v>0.2829</v>
+        <v>0.29</v>
       </c>
       <c r="J369" t="n">
-        <v>7.3554</v>
+        <v>7.54</v>
       </c>
     </row>
     <row r="370">
@@ -16689,10 +16689,10 @@
         <v>1.05</v>
       </c>
       <c r="I370" t="n">
-        <v>0.1617</v>
+        <v>0.176</v>
       </c>
       <c r="J370" t="n">
-        <v>4.2042</v>
+        <v>4.576</v>
       </c>
     </row>
     <row r="371">
@@ -16729,10 +16729,10 @@
         <v>0.91</v>
       </c>
       <c r="I371" t="n">
-        <v>-0.3645</v>
+        <v>-0.3464</v>
       </c>
       <c r="J371" t="n">
-        <v>-9.477</v>
+        <v>-9.006399999999999</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/4566/event_4566_evp_summary.xlsx
+++ b/database/event/4566/event_4566_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.0229</v>
+        <v>9.1106</v>
       </c>
       <c r="C2" t="n">
-        <v>2.0373</v>
+        <v>2.0571</v>
       </c>
       <c r="D2" t="n">
-        <v>3.4832</v>
+        <v>3.5445</v>
       </c>
       <c r="E2" t="n">
-        <v>9.0229</v>
+        <v>9.1106</v>
       </c>
       <c r="F2" t="n">
-        <v>4.5807</v>
+        <v>4.605</v>
       </c>
       <c r="G2" t="n">
-        <v>4.4423</v>
+        <v>4.5056</v>
       </c>
       <c r="H2" t="n">
-        <v>12.3807</v>
+        <v>11.4108</v>
       </c>
       <c r="I2" t="n">
-        <v>6.6855</v>
+        <v>6.4068</v>
       </c>
       <c r="J2" t="n">
-        <v>4.4423</v>
+        <v>4.5056</v>
       </c>
       <c r="K2" t="n">
         <v>286</v>
@@ -529,7 +529,7 @@
         <v>142</v>
       </c>
       <c r="M2" t="n">
-        <v>11.1278</v>
+        <v>10.9124</v>
       </c>
       <c r="N2" t="n">
         <v>428</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.7861</v>
+        <v>5.4267</v>
       </c>
       <c r="C3" t="n">
-        <v>1.3065</v>
+        <v>1.2253</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0097</v>
+        <v>1.8663</v>
       </c>
       <c r="E3" t="n">
-        <v>5.7861</v>
+        <v>5.4267</v>
       </c>
       <c r="F3" t="n">
-        <v>4.3852</v>
+        <v>4.075</v>
       </c>
       <c r="G3" t="n">
-        <v>1.4009</v>
+        <v>1.3517</v>
       </c>
       <c r="H3" t="n">
-        <v>9.574199999999999</v>
+        <v>8.8566</v>
       </c>
       <c r="I3" t="n">
-        <v>5.17</v>
+        <v>4.9727</v>
       </c>
       <c r="J3" t="n">
-        <v>1.4009</v>
+        <v>1.3517</v>
       </c>
       <c r="K3" t="n">
         <v>257</v>
@@ -575,7 +575,7 @@
         <v>102</v>
       </c>
       <c r="M3" t="n">
-        <v>6.5709</v>
+        <v>6.3244</v>
       </c>
       <c r="N3" t="n">
         <v>359</v>
@@ -584,47 +584,47 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>sergej</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.0311</v>
+        <v>3.9589</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9102</v>
+        <v>0.8939</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2108</v>
+        <v>1.1977</v>
       </c>
       <c r="E4" t="n">
-        <v>4.0311</v>
+        <v>3.9589</v>
       </c>
       <c r="F4" t="n">
-        <v>2.7267</v>
+        <v>2.3837</v>
       </c>
       <c r="G4" t="n">
-        <v>1.3044</v>
+        <v>1.5752</v>
       </c>
       <c r="H4" t="n">
-        <v>4.1023</v>
+        <v>2.5068</v>
       </c>
       <c r="I4" t="n">
-        <v>2.2152</v>
+        <v>1.4075</v>
       </c>
       <c r="J4" t="n">
-        <v>1.3044</v>
+        <v>1.5752</v>
       </c>
       <c r="K4" t="n">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="L4" t="n">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="M4" t="n">
-        <v>3.5196</v>
+        <v>2.9827</v>
       </c>
       <c r="N4" t="n">
-        <v>343</v>
+        <v>359</v>
       </c>
     </row>
     <row r="5">
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.0043</v>
+        <v>3.8611</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9041</v>
+        <v>0.8718</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1986</v>
+        <v>1.1531</v>
       </c>
       <c r="E5" t="n">
-        <v>4.0043</v>
+        <v>3.8611</v>
       </c>
       <c r="F5" t="n">
-        <v>3.3208</v>
+        <v>3.2456</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6835</v>
+        <v>0.6155</v>
       </c>
       <c r="H5" t="n">
-        <v>6.0625</v>
+        <v>5.7428</v>
       </c>
       <c r="I5" t="n">
-        <v>3.2737</v>
+        <v>3.2244</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6835</v>
+        <v>0.6155</v>
       </c>
       <c r="K5" t="n">
         <v>286</v>
@@ -667,7 +667,7 @@
         <v>142</v>
       </c>
       <c r="M5" t="n">
-        <v>3.9572</v>
+        <v>3.8399</v>
       </c>
       <c r="N5" t="n">
         <v>428</v>
@@ -676,47 +676,47 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>sergej</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.9624</v>
+        <v>3.7705</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8947000000000001</v>
+        <v>0.8514</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1796</v>
+        <v>1.1119</v>
       </c>
       <c r="E6" t="n">
-        <v>3.9624</v>
+        <v>3.7705</v>
       </c>
       <c r="F6" t="n">
-        <v>2.3984</v>
+        <v>2.5817</v>
       </c>
       <c r="G6" t="n">
-        <v>1.564</v>
+        <v>1.1888</v>
       </c>
       <c r="H6" t="n">
-        <v>3.0189</v>
+        <v>3.2502</v>
       </c>
       <c r="I6" t="n">
-        <v>1.6302</v>
+        <v>1.8249</v>
       </c>
       <c r="J6" t="n">
-        <v>1.564</v>
+        <v>1.1888</v>
       </c>
       <c r="K6" t="n">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="L6" t="n">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="M6" t="n">
-        <v>3.1942</v>
+        <v>3.0137</v>
       </c>
       <c r="N6" t="n">
-        <v>359</v>
+        <v>343</v>
       </c>
     </row>
     <row r="7">
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.6154</v>
+        <v>3.6489</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8163</v>
+        <v>0.8239</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0216</v>
+        <v>1.0565</v>
       </c>
       <c r="E7" t="n">
-        <v>3.6154</v>
+        <v>3.6489</v>
       </c>
       <c r="F7" t="n">
-        <v>2.4031</v>
+        <v>2.4129</v>
       </c>
       <c r="G7" t="n">
-        <v>1.2123</v>
+        <v>1.236</v>
       </c>
       <c r="H7" t="n">
-        <v>3.0345</v>
+        <v>2.6165</v>
       </c>
       <c r="I7" t="n">
-        <v>1.6386</v>
+        <v>1.4691</v>
       </c>
       <c r="J7" t="n">
-        <v>1.2123</v>
+        <v>1.236</v>
       </c>
       <c r="K7" t="n">
         <v>286</v>
@@ -759,7 +759,7 @@
         <v>142</v>
       </c>
       <c r="M7" t="n">
-        <v>2.8509</v>
+        <v>2.7051</v>
       </c>
       <c r="N7" t="n">
         <v>428</v>
@@ -768,35 +768,35 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CeRq</t>
+          <t>Brehze</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.5941</v>
+        <v>3.4966</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8115</v>
+        <v>0.7895</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0119</v>
+        <v>0.9871</v>
       </c>
       <c r="E8" t="n">
-        <v>3.5941</v>
+        <v>3.4966</v>
       </c>
       <c r="F8" t="n">
-        <v>3.5172</v>
+        <v>3.131</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0769</v>
+        <v>0.3656</v>
       </c>
       <c r="H8" t="n">
-        <v>6.7105</v>
+        <v>5.3125</v>
       </c>
       <c r="I8" t="n">
-        <v>3.6236</v>
+        <v>2.9828</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0769</v>
+        <v>0.3656</v>
       </c>
       <c r="K8" t="n">
         <v>269</v>
@@ -805,7 +805,7 @@
         <v>48</v>
       </c>
       <c r="M8" t="n">
-        <v>3.7005</v>
+        <v>3.3484</v>
       </c>
       <c r="N8" t="n">
         <v>317</v>
@@ -814,93 +814,93 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Brehze</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.535</v>
+        <v>3.3814</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7982</v>
+        <v>0.7635</v>
       </c>
       <c r="D9" t="n">
-        <v>0.985</v>
+        <v>0.9346</v>
       </c>
       <c r="E9" t="n">
-        <v>3.535</v>
+        <v>3.3814</v>
       </c>
       <c r="F9" t="n">
-        <v>3.1577</v>
+        <v>3.006</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3773</v>
+        <v>0.3754</v>
       </c>
       <c r="H9" t="n">
-        <v>5.5243</v>
+        <v>4.8434</v>
       </c>
       <c r="I9" t="n">
-        <v>2.9831</v>
+        <v>2.7194</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3773</v>
+        <v>0.3754</v>
       </c>
       <c r="K9" t="n">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="L9" t="n">
-        <v>48</v>
+        <v>102</v>
       </c>
       <c r="M9" t="n">
-        <v>3.3604</v>
+        <v>3.0948</v>
       </c>
       <c r="N9" t="n">
-        <v>317</v>
+        <v>359</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>CeRq</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.4636</v>
+        <v>3.3559</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7821</v>
+        <v>0.7577</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9525</v>
+        <v>0.923</v>
       </c>
       <c r="E10" t="n">
-        <v>3.4636</v>
+        <v>3.3559</v>
       </c>
       <c r="F10" t="n">
-        <v>3.0912</v>
+        <v>3.3121</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3724</v>
+        <v>0.0438</v>
       </c>
       <c r="H10" t="n">
-        <v>5.3047</v>
+        <v>5.9923</v>
       </c>
       <c r="I10" t="n">
-        <v>2.8645</v>
+        <v>3.3645</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3724</v>
+        <v>0.0438</v>
       </c>
       <c r="K10" t="n">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="L10" t="n">
-        <v>102</v>
+        <v>48</v>
       </c>
       <c r="M10" t="n">
-        <v>3.2369</v>
+        <v>3.4083</v>
       </c>
       <c r="N10" t="n">
-        <v>359</v>
+        <v>317</v>
       </c>
     </row>
     <row r="11">
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.4322</v>
+        <v>3.3078</v>
       </c>
       <c r="C11" t="n">
-        <v>0.775</v>
+        <v>0.7469</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9382</v>
+        <v>0.9011</v>
       </c>
       <c r="E11" t="n">
-        <v>3.4322</v>
+        <v>3.3078</v>
       </c>
       <c r="F11" t="n">
-        <v>2.1444</v>
+        <v>2.095</v>
       </c>
       <c r="G11" t="n">
-        <v>1.2878</v>
+        <v>1.2128</v>
       </c>
       <c r="H11" t="n">
-        <v>2.181</v>
+        <v>2.095</v>
       </c>
       <c r="I11" t="n">
-        <v>1.1777</v>
+        <v>1.1763</v>
       </c>
       <c r="J11" t="n">
-        <v>1.2878</v>
+        <v>1.2128</v>
       </c>
       <c r="K11" t="n">
         <v>257</v>
@@ -943,7 +943,7 @@
         <v>102</v>
       </c>
       <c r="M11" t="n">
-        <v>2.4655</v>
+        <v>2.3891</v>
       </c>
       <c r="N11" t="n">
         <v>359</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.3099</v>
+        <v>3.1973</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7474</v>
+        <v>0.7219</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8825</v>
+        <v>0.8507</v>
       </c>
       <c r="E12" t="n">
-        <v>3.3099</v>
+        <v>3.1973</v>
       </c>
       <c r="F12" t="n">
-        <v>3.5928</v>
+        <v>3.4578</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.2829</v>
+        <v>-0.2605</v>
       </c>
       <c r="H12" t="n">
-        <v>6.9597</v>
+        <v>6.5396</v>
       </c>
       <c r="I12" t="n">
-        <v>3.7582</v>
+        <v>3.6718</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.2829</v>
+        <v>-0.2605</v>
       </c>
       <c r="K12" t="n">
         <v>269</v>
@@ -989,7 +989,7 @@
         <v>48</v>
       </c>
       <c r="M12" t="n">
-        <v>3.4753</v>
+        <v>3.4113</v>
       </c>
       <c r="N12" t="n">
         <v>317</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.2921</v>
+        <v>3.1821</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7433</v>
+        <v>0.7185</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8744</v>
+        <v>0.8438</v>
       </c>
       <c r="E13" t="n">
-        <v>3.2921</v>
+        <v>3.1821</v>
       </c>
       <c r="F13" t="n">
-        <v>3.7401</v>
+        <v>3.5741</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.448</v>
+        <v>-0.392</v>
       </c>
       <c r="H13" t="n">
-        <v>7.4459</v>
+        <v>6.976</v>
       </c>
       <c r="I13" t="n">
-        <v>4.0207</v>
+        <v>3.9168</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.448</v>
+        <v>-0.392</v>
       </c>
       <c r="K13" t="n">
         <v>286</v>
@@ -1035,7 +1035,7 @@
         <v>142</v>
       </c>
       <c r="M13" t="n">
-        <v>3.5727</v>
+        <v>3.5248</v>
       </c>
       <c r="N13" t="n">
         <v>428</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.564</v>
+        <v>2.6462</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5789</v>
+        <v>0.5975</v>
       </c>
       <c r="D14" t="n">
-        <v>0.543</v>
+        <v>0.5997</v>
       </c>
       <c r="E14" t="n">
-        <v>2.564</v>
+        <v>2.6462</v>
       </c>
       <c r="F14" t="n">
-        <v>2.2994</v>
+        <v>2.4224</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2646</v>
+        <v>0.2238</v>
       </c>
       <c r="H14" t="n">
-        <v>2.6923</v>
+        <v>2.6522</v>
       </c>
       <c r="I14" t="n">
-        <v>1.4538</v>
+        <v>1.4891</v>
       </c>
       <c r="J14" t="n">
-        <v>0.2646</v>
+        <v>0.2238</v>
       </c>
       <c r="K14" t="n">
         <v>286</v>
@@ -1081,7 +1081,7 @@
         <v>142</v>
       </c>
       <c r="M14" t="n">
-        <v>1.7184</v>
+        <v>1.7129</v>
       </c>
       <c r="N14" t="n">
         <v>428</v>
@@ -1090,93 +1090,93 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>jks</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.3424</v>
+        <v>2.1787</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5289</v>
+        <v>0.4919</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4421</v>
+        <v>0.3867</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3424</v>
+        <v>2.1787</v>
       </c>
       <c r="F15" t="n">
-        <v>2.3424</v>
+        <v>2.7695</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>-0.5908</v>
       </c>
       <c r="H15" t="n">
-        <v>2.4019</v>
+        <v>3.9552</v>
       </c>
       <c r="I15" t="n">
-        <v>2.4019</v>
+        <v>2.2207</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>-0.5908</v>
       </c>
       <c r="K15" t="n">
-        <v>280</v>
+        <v>269</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M15" t="n">
-        <v>2.4019</v>
+        <v>1.6299</v>
       </c>
       <c r="N15" t="n">
-        <v>280</v>
+        <v>317</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>allu</t>
+          <t>jks</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.2824</v>
+        <v>2.0674</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5154</v>
+        <v>0.4668</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4148</v>
+        <v>0.336</v>
       </c>
       <c r="E16" t="n">
-        <v>2.2824</v>
+        <v>2.0674</v>
       </c>
       <c r="F16" t="n">
-        <v>2.1995</v>
+        <v>2.0674</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0829</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.3628</v>
+        <v>2.0674</v>
       </c>
       <c r="I16" t="n">
-        <v>1.2759</v>
+        <v>2.0674</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0829</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>255</v>
+        <v>280</v>
       </c>
       <c r="L16" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.3588</v>
+        <v>2.0674</v>
       </c>
       <c r="N16" t="n">
-        <v>343</v>
+        <v>280</v>
       </c>
     </row>
     <row r="17">
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.262</v>
+        <v>1.9764</v>
       </c>
       <c r="C17" t="n">
-        <v>0.5107</v>
+        <v>0.4463</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4055</v>
+        <v>0.2946</v>
       </c>
       <c r="E17" t="n">
-        <v>2.262</v>
+        <v>1.9764</v>
       </c>
       <c r="F17" t="n">
-        <v>2.262</v>
+        <v>1.9764</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>2.262</v>
+        <v>1.9764</v>
       </c>
       <c r="I17" t="n">
-        <v>2.262</v>
+        <v>1.9764</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>2.262</v>
+        <v>1.9764</v>
       </c>
       <c r="N17" t="n">
         <v>277</v>
@@ -1228,231 +1228,231 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>allu</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.2279</v>
+        <v>1.8411</v>
       </c>
       <c r="C18" t="n">
-        <v>0.503</v>
+        <v>0.4157</v>
       </c>
       <c r="D18" t="n">
-        <v>0.39</v>
+        <v>0.2329</v>
       </c>
       <c r="E18" t="n">
-        <v>2.2279</v>
+        <v>1.8411</v>
       </c>
       <c r="F18" t="n">
-        <v>2.8498</v>
+        <v>1.7777</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.6219</v>
+        <v>0.0634</v>
       </c>
       <c r="H18" t="n">
-        <v>4.5082</v>
+        <v>1.7777</v>
       </c>
       <c r="I18" t="n">
-        <v>2.4344</v>
+        <v>0.9981</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.6219</v>
+        <v>0.0634</v>
       </c>
       <c r="K18" t="n">
-        <v>269</v>
+        <v>255</v>
       </c>
       <c r="L18" t="n">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="M18" t="n">
-        <v>1.8125</v>
+        <v>1.0615</v>
       </c>
       <c r="N18" t="n">
-        <v>317</v>
+        <v>343</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Aerial</t>
+          <t>smooya</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8749</v>
+        <v>0.6064000000000001</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1975</v>
+        <v>0.1369</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2259</v>
+        <v>-0.3295</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8749</v>
+        <v>0.6064000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6526</v>
+        <v>0.6064000000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2223</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6526</v>
+        <v>0.6064000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3524</v>
+        <v>0.6064000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>0.2223</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>255</v>
+        <v>280</v>
       </c>
       <c r="L19" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.5747</v>
+        <v>0.6064000000000001</v>
       </c>
       <c r="N19" t="n">
-        <v>343</v>
+        <v>280</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>smooya</t>
+          <t>Aerial</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8007</v>
+        <v>0.4123</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1808</v>
+        <v>0.0931</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2597</v>
+        <v>-0.418</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8007</v>
+        <v>0.4123</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8007</v>
+        <v>0.2485</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>0.1638</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8007</v>
+        <v>0.2485</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8007</v>
+        <v>0.1395</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>0.1638</v>
       </c>
       <c r="K20" t="n">
-        <v>280</v>
+        <v>255</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="M20" t="n">
-        <v>0.8007</v>
+        <v>0.3033</v>
       </c>
       <c r="N20" t="n">
-        <v>280</v>
+        <v>343</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>jkaem</t>
+          <t>daps</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.5145</v>
+        <v>0.322</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1162</v>
+        <v>0.0727</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.39</v>
+        <v>-0.4591</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5145</v>
+        <v>0.322</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5145</v>
+        <v>1.0013</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>-0.6793</v>
       </c>
       <c r="H21" t="n">
-        <v>0.5145</v>
+        <v>1.0013</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5145</v>
+        <v>0.5622</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>-0.6793</v>
       </c>
       <c r="K21" t="n">
-        <v>280</v>
+        <v>269</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M21" t="n">
-        <v>0.5145</v>
+        <v>-0.1171</v>
       </c>
       <c r="N21" t="n">
-        <v>280</v>
+        <v>317</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>daps</t>
+          <t>jkaem</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.4174</v>
+        <v>0.2931</v>
       </c>
       <c r="C22" t="n">
-        <v>0.09420000000000001</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.4342</v>
+        <v>-0.4723</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4174</v>
+        <v>0.2931</v>
       </c>
       <c r="F22" t="n">
-        <v>1.1211</v>
+        <v>0.2931</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.7037</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.1211</v>
+        <v>0.2931</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6054</v>
+        <v>0.2931</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.7037</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="L22" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.09829999999999994</v>
+        <v>0.2931</v>
       </c>
       <c r="N22" t="n">
-        <v>317</v>
+        <v>280</v>
       </c>
     </row>
     <row r="23">
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.3036</v>
+        <v>0.195</v>
       </c>
       <c r="C23" t="n">
-        <v>0.06859999999999999</v>
+        <v>0.044</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.486</v>
+        <v>-0.517</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3036</v>
+        <v>0.195</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3036</v>
+        <v>0.195</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3036</v>
+        <v>0.195</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3036</v>
+        <v>0.195</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.3036</v>
+        <v>0.195</v>
       </c>
       <c r="N23" t="n">
         <v>277</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.2887</v>
+        <v>0.159</v>
       </c>
       <c r="C24" t="n">
-        <v>0.06519999999999999</v>
+        <v>0.0359</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4928</v>
+        <v>-0.5334</v>
       </c>
       <c r="E24" t="n">
-        <v>0.2887</v>
+        <v>0.159</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2887</v>
+        <v>0.159</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2887</v>
+        <v>0.159</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2887</v>
+        <v>0.159</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.2887</v>
+        <v>0.159</v>
       </c>
       <c r="N24" t="n">
         <v>280</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.2373</v>
+        <v>0.0327</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0536</v>
+        <v>0.0074</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.5162</v>
+        <v>-0.5909</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2373</v>
+        <v>0.0327</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2373</v>
+        <v>0.0327</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2373</v>
+        <v>0.0327</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2373</v>
+        <v>0.0327</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.2373</v>
+        <v>0.0327</v>
       </c>
       <c r="N25" t="n">
         <v>277</v>
@@ -1596,93 +1596,93 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>xseveN</t>
+          <t>AZR</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.0005</v>
+        <v>-0.143</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0001</v>
+        <v>-0.0323</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.6244</v>
+        <v>-0.6709000000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.0005</v>
+        <v>-0.143</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0839</v>
+        <v>-0.143</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.0844</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0839</v>
+        <v>-0.143</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0453</v>
+        <v>-0.143</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.0844</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>255</v>
+        <v>280</v>
       </c>
       <c r="L26" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.0391</v>
+        <v>-0.143</v>
       </c>
       <c r="N26" t="n">
-        <v>343</v>
+        <v>280</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AZR</t>
+          <t>xseveN</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.0706</v>
+        <v>-0.2206</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.0159</v>
+        <v>-0.0498</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.6563</v>
+        <v>-0.7063</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.0706</v>
+        <v>-0.2206</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.0706</v>
+        <v>-0.1083</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>-0.1123</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.0706</v>
+        <v>-0.1083</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.0706</v>
+        <v>-0.0608</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>-0.1123</v>
       </c>
       <c r="K27" t="n">
-        <v>280</v>
+        <v>255</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.0706</v>
+        <v>-0.1731</v>
       </c>
       <c r="N27" t="n">
-        <v>280</v>
+        <v>343</v>
       </c>
     </row>
     <row r="28">
@@ -1692,31 +1692,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.2543</v>
+        <v>-0.3663</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0574</v>
+        <v>-0.0827</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.74</v>
+        <v>-0.7727000000000001</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.2543</v>
+        <v>-0.3663</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.8887</v>
+        <v>-0.8823</v>
       </c>
       <c r="G28" t="n">
-        <v>0.6344</v>
+        <v>0.516</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.8887</v>
+        <v>-0.8823</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.4799</v>
+        <v>-0.4954</v>
       </c>
       <c r="J28" t="n">
-        <v>0.6344</v>
+        <v>0.516</v>
       </c>
       <c r="K28" t="n">
         <v>257</v>
@@ -1725,7 +1725,7 @@
         <v>102</v>
       </c>
       <c r="M28" t="n">
-        <v>0.1545</v>
+        <v>0.02060000000000001</v>
       </c>
       <c r="N28" t="n">
         <v>359</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.9989</v>
+        <v>-0.9847</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.2255</v>
+        <v>-0.2223</v>
       </c>
       <c r="D29" t="n">
-        <v>-1.0789</v>
+        <v>-1.0544</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.9989</v>
+        <v>-0.9847</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.9989</v>
+        <v>-0.9847</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.9989</v>
+        <v>-0.9847</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.9989</v>
+        <v>-0.9847</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.9989</v>
+        <v>-0.9847</v>
       </c>
       <c r="N29" t="n">
         <v>277</v>
@@ -1784,31 +1784,31 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-2.397</v>
+        <v>-2.3092</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.5412</v>
+        <v>-0.5214</v>
       </c>
       <c r="D30" t="n">
-        <v>-1.7154</v>
+        <v>-1.6577</v>
       </c>
       <c r="E30" t="n">
-        <v>-2.397</v>
+        <v>-2.3092</v>
       </c>
       <c r="F30" t="n">
-        <v>-2.0432</v>
+        <v>-1.9153</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.3538</v>
+        <v>-0.3939</v>
       </c>
       <c r="H30" t="n">
-        <v>-2.0432</v>
+        <v>-1.9153</v>
       </c>
       <c r="I30" t="n">
-        <v>-1.1033</v>
+        <v>-1.0754</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.3538</v>
+        <v>-0.3939</v>
       </c>
       <c r="K30" t="n">
         <v>255</v>
@@ -1817,7 +1817,7 @@
         <v>88</v>
       </c>
       <c r="M30" t="n">
-        <v>-1.4571</v>
+        <v>-1.4693</v>
       </c>
       <c r="N30" t="n">
         <v>343</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-2.8064</v>
+        <v>-2.6071</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.6337</v>
+        <v>-0.5887</v>
       </c>
       <c r="D31" t="n">
-        <v>-1.9017</v>
+        <v>-1.7934</v>
       </c>
       <c r="E31" t="n">
-        <v>-2.8064</v>
+        <v>-2.6071</v>
       </c>
       <c r="F31" t="n">
-        <v>-2.8064</v>
+        <v>-2.6071</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-2.8064</v>
+        <v>-2.6071</v>
       </c>
       <c r="I31" t="n">
-        <v>-2.8064</v>
+        <v>-2.6071</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-2.8064</v>
+        <v>-2.6071</v>
       </c>
       <c r="N31" t="n">
         <v>277</v>
@@ -1969,10 +1969,10 @@
         <v>1.61</v>
       </c>
       <c r="I2" t="n">
-        <v>1.3276</v>
+        <v>1.3588</v>
       </c>
       <c r="J2" t="n">
-        <v>33.19</v>
+        <v>33.97</v>
       </c>
     </row>
     <row r="3">
@@ -2009,10 +2009,10 @@
         <v>1.29</v>
       </c>
       <c r="I3" t="n">
-        <v>0.726</v>
+        <v>0.6994</v>
       </c>
       <c r="J3" t="n">
-        <v>18.15</v>
+        <v>17.485</v>
       </c>
     </row>
     <row r="4">
@@ -2049,10 +2049,10 @@
         <v>1.19</v>
       </c>
       <c r="I4" t="n">
-        <v>0.519</v>
+        <v>0.4865</v>
       </c>
       <c r="J4" t="n">
-        <v>12.975</v>
+        <v>12.1625</v>
       </c>
     </row>
     <row r="5">
@@ -2089,10 +2089,10 @@
         <v>1.06</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1929</v>
+        <v>0.1651</v>
       </c>
       <c r="J5" t="n">
-        <v>4.8225</v>
+        <v>4.1275</v>
       </c>
     </row>
     <row r="6">
@@ -2129,10 +2129,10 @@
         <v>1.05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1627</v>
+        <v>0.1368</v>
       </c>
       <c r="J6" t="n">
-        <v>4.0675</v>
+        <v>3.42</v>
       </c>
     </row>
     <row r="7">
@@ -2169,10 +2169,10 @@
         <v>1.04</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1695</v>
+        <v>0.136</v>
       </c>
       <c r="J7" t="n">
-        <v>4.2375</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="8">
@@ -2209,10 +2209,10 @@
         <v>0.99</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0038</v>
+        <v>0.0013</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.095</v>
+        <v>0.0325</v>
       </c>
     </row>
     <row r="9">
@@ -2249,10 +2249,10 @@
         <v>0.86</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.175</v>
+        <v>-0.1584</v>
       </c>
       <c r="J9" t="n">
-        <v>-4.375</v>
+        <v>-3.96</v>
       </c>
     </row>
     <row r="10">
@@ -2289,10 +2289,10 @@
         <v>0.68</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3468</v>
+        <v>-0.3316</v>
       </c>
       <c r="J10" t="n">
-        <v>-8.67</v>
+        <v>-8.289999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -2329,10 +2329,10 @@
         <v>0.47</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5322</v>
+        <v>-0.5359</v>
       </c>
       <c r="J11" t="n">
-        <v>-13.305</v>
+        <v>-13.3975</v>
       </c>
     </row>
     <row r="12">
@@ -2369,10 +2369,10 @@
         <v>1.3</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7975</v>
+        <v>0.771</v>
       </c>
       <c r="J12" t="n">
-        <v>23.1275</v>
+        <v>22.359</v>
       </c>
     </row>
     <row r="13">
@@ -2409,10 +2409,10 @@
         <v>1.26</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7116</v>
+        <v>0.6787</v>
       </c>
       <c r="J13" t="n">
-        <v>20.6364</v>
+        <v>19.6823</v>
       </c>
     </row>
     <row r="14">
@@ -2449,10 +2449,10 @@
         <v>0.93</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2656</v>
+        <v>-0.2261</v>
       </c>
       <c r="J14" t="n">
-        <v>-7.7024</v>
+        <v>-6.5569</v>
       </c>
     </row>
     <row r="15">
@@ -2489,10 +2489,10 @@
         <v>0.87</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4259</v>
+        <v>-0.3828</v>
       </c>
       <c r="J15" t="n">
-        <v>-12.3511</v>
+        <v>-11.1012</v>
       </c>
     </row>
     <row r="16">
@@ -2529,10 +2529,10 @@
         <v>0.8</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5941</v>
+        <v>-0.5553</v>
       </c>
       <c r="J16" t="n">
-        <v>-17.2289</v>
+        <v>-16.1037</v>
       </c>
     </row>
     <row r="17">
@@ -2569,10 +2569,10 @@
         <v>1.28</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5603</v>
+        <v>0.5008</v>
       </c>
       <c r="J17" t="n">
-        <v>16.2487</v>
+        <v>14.5232</v>
       </c>
     </row>
     <row r="18">
@@ -2609,10 +2609,10 @@
         <v>1.2</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4292</v>
+        <v>0.3718</v>
       </c>
       <c r="J18" t="n">
-        <v>12.4468</v>
+        <v>10.7822</v>
       </c>
     </row>
     <row r="19">
@@ -2649,10 +2649,10 @@
         <v>0.92</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1253</v>
+        <v>-0.1065</v>
       </c>
       <c r="J19" t="n">
-        <v>-3.6337</v>
+        <v>-3.0885</v>
       </c>
     </row>
     <row r="20">
@@ -2689,10 +2689,10 @@
         <v>0.87</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.182</v>
+        <v>-0.1614</v>
       </c>
       <c r="J20" t="n">
-        <v>-5.278</v>
+        <v>-4.6806</v>
       </c>
     </row>
     <row r="21">
@@ -2729,10 +2729,10 @@
         <v>0.83</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.224</v>
+        <v>-0.2035</v>
       </c>
       <c r="J21" t="n">
-        <v>-6.496</v>
+        <v>-5.9015</v>
       </c>
     </row>
     <row r="22">
@@ -2769,10 +2769,10 @@
         <v>1.6</v>
       </c>
       <c r="I22" t="n">
-        <v>1.0963</v>
+        <v>1.0883</v>
       </c>
       <c r="J22" t="n">
-        <v>26.3112</v>
+        <v>26.1192</v>
       </c>
     </row>
     <row r="23">
@@ -2809,10 +2809,10 @@
         <v>1.17</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4702</v>
+        <v>0.446</v>
       </c>
       <c r="J23" t="n">
-        <v>11.2848</v>
+        <v>10.704</v>
       </c>
     </row>
     <row r="24">
@@ -2849,10 +2849,10 @@
         <v>1.09</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2864</v>
+        <v>0.2541</v>
       </c>
       <c r="J24" t="n">
-        <v>6.8736</v>
+        <v>6.0984</v>
       </c>
     </row>
     <row r="25">
@@ -2889,10 +2889,10 @@
         <v>1.03</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1069</v>
+        <v>0.0863</v>
       </c>
       <c r="J25" t="n">
-        <v>2.5656</v>
+        <v>2.0712</v>
       </c>
     </row>
     <row r="26">
@@ -2929,10 +2929,10 @@
         <v>1.03</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1069</v>
+        <v>0.0863</v>
       </c>
       <c r="J26" t="n">
-        <v>2.5656</v>
+        <v>2.0712</v>
       </c>
     </row>
     <row r="27">
@@ -2969,10 +2969,10 @@
         <v>1.34</v>
       </c>
       <c r="I27" t="n">
-        <v>0.6068</v>
+        <v>0.5793</v>
       </c>
       <c r="J27" t="n">
-        <v>14.5632</v>
+        <v>13.9032</v>
       </c>
     </row>
     <row r="28">
@@ -3009,10 +3009,10 @@
         <v>1.11</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2758</v>
+        <v>0.227</v>
       </c>
       <c r="J28" t="n">
-        <v>6.6192</v>
+        <v>5.448</v>
       </c>
     </row>
     <row r="29">
@@ -3049,10 +3049,10 @@
         <v>0.99</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.0244</v>
+        <v>-0.0178</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.5856</v>
+        <v>-0.4272</v>
       </c>
     </row>
     <row r="30">
@@ -3089,10 +3089,10 @@
         <v>0.84</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2101</v>
+        <v>-0.1895</v>
       </c>
       <c r="J30" t="n">
-        <v>-5.0424</v>
+        <v>-4.548</v>
       </c>
     </row>
     <row r="31">
@@ -3129,10 +3129,10 @@
         <v>0.62</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.418</v>
+        <v>-0.4094</v>
       </c>
       <c r="J31" t="n">
-        <v>-10.032</v>
+        <v>-9.8256</v>
       </c>
     </row>
     <row r="32">
@@ -3169,10 +3169,10 @@
         <v>1.51</v>
       </c>
       <c r="I32" t="n">
-        <v>0.9432</v>
+        <v>0.9311</v>
       </c>
       <c r="J32" t="n">
-        <v>22.6368</v>
+        <v>22.3464</v>
       </c>
     </row>
     <row r="33">
@@ -3209,10 +3209,10 @@
         <v>1.43</v>
       </c>
       <c r="I33" t="n">
-        <v>0.8363</v>
+        <v>0.8242</v>
       </c>
       <c r="J33" t="n">
-        <v>20.0712</v>
+        <v>19.7808</v>
       </c>
     </row>
     <row r="34">
@@ -3249,10 +3249,10 @@
         <v>1.4</v>
       </c>
       <c r="I34" t="n">
-        <v>0.7956</v>
+        <v>0.7841</v>
       </c>
       <c r="J34" t="n">
-        <v>19.0944</v>
+        <v>18.8184</v>
       </c>
     </row>
     <row r="35">
@@ -3289,10 +3289,10 @@
         <v>1.26</v>
       </c>
       <c r="I35" t="n">
-        <v>0.5968</v>
+        <v>0.5921</v>
       </c>
       <c r="J35" t="n">
-        <v>14.3232</v>
+        <v>14.2104</v>
       </c>
     </row>
     <row r="36">
@@ -3329,10 +3329,10 @@
         <v>1.17</v>
       </c>
       <c r="I36" t="n">
-        <v>0.451</v>
+        <v>0.426</v>
       </c>
       <c r="J36" t="n">
-        <v>10.824</v>
+        <v>10.224</v>
       </c>
     </row>
     <row r="37">
@@ -3369,10 +3369,10 @@
         <v>0.83</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.1989</v>
+        <v>-0.1832</v>
       </c>
       <c r="J37" t="n">
-        <v>-4.7736</v>
+        <v>-4.3968</v>
       </c>
     </row>
     <row r="38">
@@ -3409,10 +3409,10 @@
         <v>0.8</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.2295</v>
+        <v>-0.2137</v>
       </c>
       <c r="J38" t="n">
-        <v>-5.508</v>
+        <v>-5.1288</v>
       </c>
     </row>
     <row r="39">
@@ -3449,10 +3449,10 @@
         <v>0.77</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.2585</v>
+        <v>-0.2427</v>
       </c>
       <c r="J39" t="n">
-        <v>-6.204</v>
+        <v>-5.8248</v>
       </c>
     </row>
     <row r="40">
@@ -3489,10 +3489,10 @@
         <v>0.74</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.2857</v>
+        <v>-0.2699</v>
       </c>
       <c r="J40" t="n">
-        <v>-6.8568</v>
+        <v>-6.4776</v>
       </c>
     </row>
     <row r="41">
@@ -3529,10 +3529,10 @@
         <v>0.6</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.4118</v>
+        <v>-0.4013</v>
       </c>
       <c r="J41" t="n">
-        <v>-9.8832</v>
+        <v>-9.6312</v>
       </c>
     </row>
     <row r="42">
@@ -3569,10 +3569,10 @@
         <v>1.15</v>
       </c>
       <c r="I42" t="n">
-        <v>0.2818</v>
+        <v>0.2687</v>
       </c>
       <c r="J42" t="n">
-        <v>8.454000000000001</v>
+        <v>8.061</v>
       </c>
     </row>
     <row r="43">
@@ -3609,10 +3609,10 @@
         <v>1.06</v>
       </c>
       <c r="I43" t="n">
-        <v>0.1414</v>
+        <v>0.1243</v>
       </c>
       <c r="J43" t="n">
-        <v>4.242</v>
+        <v>3.729</v>
       </c>
     </row>
     <row r="44">
@@ -3649,10 +3649,10 @@
         <v>1.03</v>
       </c>
       <c r="I44" t="n">
-        <v>0.0854</v>
+        <v>0.0707</v>
       </c>
       <c r="J44" t="n">
-        <v>2.562</v>
+        <v>2.121</v>
       </c>
     </row>
     <row r="45">
@@ -3689,10 +3689,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.2371</v>
+        <v>-0.2169</v>
       </c>
       <c r="J45" t="n">
-        <v>-7.113</v>
+        <v>-6.507</v>
       </c>
     </row>
     <row r="46">
@@ -3729,10 +3729,10 @@
         <v>0.66</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.3788</v>
+        <v>-0.3661</v>
       </c>
       <c r="J46" t="n">
-        <v>-11.364</v>
+        <v>-10.983</v>
       </c>
     </row>
     <row r="47">
@@ -3769,10 +3769,10 @@
         <v>1.28</v>
       </c>
       <c r="I47" t="n">
-        <v>0.3972</v>
+        <v>0.3346</v>
       </c>
       <c r="J47" t="n">
-        <v>11.916</v>
+        <v>10.038</v>
       </c>
     </row>
     <row r="48">
@@ -3809,10 +3809,10 @@
         <v>1.22</v>
       </c>
       <c r="I48" t="n">
-        <v>0.3273</v>
+        <v>0.2705</v>
       </c>
       <c r="J48" t="n">
-        <v>9.819000000000001</v>
+        <v>8.115</v>
       </c>
     </row>
     <row r="49">
@@ -3849,10 +3849,10 @@
         <v>1.19</v>
       </c>
       <c r="I49" t="n">
-        <v>0.2911</v>
+        <v>0.238</v>
       </c>
       <c r="J49" t="n">
-        <v>8.733000000000001</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="50">
@@ -3889,10 +3889,10 @@
         <v>1.04</v>
       </c>
       <c r="I50" t="n">
-        <v>0.08110000000000001</v>
+        <v>0.0595</v>
       </c>
       <c r="J50" t="n">
-        <v>2.433</v>
+        <v>1.785</v>
       </c>
     </row>
     <row r="51">
@@ -3929,10 +3929,10 @@
         <v>0.98</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.0535</v>
+        <v>-0.0413</v>
       </c>
       <c r="J51" t="n">
-        <v>-1.605</v>
+        <v>-1.239</v>
       </c>
     </row>
     <row r="52">
@@ -3969,10 +3969,10 @@
         <v>2.18</v>
       </c>
       <c r="I52" t="n">
-        <v>1.7759</v>
+        <v>1.8296</v>
       </c>
       <c r="J52" t="n">
-        <v>42.6216</v>
+        <v>43.9104</v>
       </c>
     </row>
     <row r="53">
@@ -4009,10 +4009,10 @@
         <v>1.27</v>
       </c>
       <c r="I53" t="n">
-        <v>0.6149</v>
+        <v>0.6086</v>
       </c>
       <c r="J53" t="n">
-        <v>14.7576</v>
+        <v>14.6064</v>
       </c>
     </row>
     <row r="54">
@@ -4049,10 +4049,10 @@
         <v>1.14</v>
       </c>
       <c r="I54" t="n">
-        <v>0.3906</v>
+        <v>0.3587</v>
       </c>
       <c r="J54" t="n">
-        <v>9.3744</v>
+        <v>8.6088</v>
       </c>
     </row>
     <row r="55">
@@ -4089,10 +4089,10 @@
         <v>1.05</v>
       </c>
       <c r="I55" t="n">
-        <v>0.1488</v>
+        <v>0.1225</v>
       </c>
       <c r="J55" t="n">
-        <v>3.5712</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="56">
@@ -4129,10 +4129,10 @@
         <v>0.98</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.1556</v>
+        <v>-0.1304</v>
       </c>
       <c r="J56" t="n">
-        <v>-3.7344</v>
+        <v>-3.1296</v>
       </c>
     </row>
     <row r="57">
@@ -4169,10 +4169,10 @@
         <v>1.23</v>
       </c>
       <c r="I57" t="n">
-        <v>0.5155999999999999</v>
+        <v>0.4917</v>
       </c>
       <c r="J57" t="n">
-        <v>12.3744</v>
+        <v>11.8008</v>
       </c>
     </row>
     <row r="58">
@@ -4209,10 +4209,10 @@
         <v>0.89</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.1442</v>
+        <v>-0.1282</v>
       </c>
       <c r="J58" t="n">
-        <v>-3.4608</v>
+        <v>-3.0768</v>
       </c>
     </row>
     <row r="59">
@@ -4249,10 +4249,10 @@
         <v>0.79</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.2457</v>
+        <v>-0.2274</v>
       </c>
       <c r="J59" t="n">
-        <v>-5.8968</v>
+        <v>-5.4576</v>
       </c>
     </row>
     <row r="60">
@@ -4289,10 +4289,10 @@
         <v>0.68</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.3488</v>
+        <v>-0.3336</v>
       </c>
       <c r="J60" t="n">
-        <v>-8.3712</v>
+        <v>-8.006399999999999</v>
       </c>
     </row>
     <row r="61">
@@ -4329,10 +4329,10 @@
         <v>0.54</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4735</v>
+        <v>-0.4696</v>
       </c>
       <c r="J61" t="n">
-        <v>-11.364</v>
+        <v>-11.2704</v>
       </c>
     </row>
     <row r="62">
@@ -4369,10 +4369,10 @@
         <v>1.38</v>
       </c>
       <c r="I62" t="n">
-        <v>0.8206</v>
+        <v>0.8053</v>
       </c>
       <c r="J62" t="n">
-        <v>27.9004</v>
+        <v>27.3802</v>
       </c>
     </row>
     <row r="63">
@@ -4409,10 +4409,10 @@
         <v>1.16</v>
       </c>
       <c r="I63" t="n">
-        <v>0.4684</v>
+        <v>0.4375</v>
       </c>
       <c r="J63" t="n">
-        <v>15.9256</v>
+        <v>14.875</v>
       </c>
     </row>
     <row r="64">
@@ -4449,10 +4449,10 @@
         <v>0.97</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.1448</v>
+        <v>-0.1146</v>
       </c>
       <c r="J64" t="n">
-        <v>-4.9232</v>
+        <v>-3.8964</v>
       </c>
     </row>
     <row r="65">
@@ -4489,10 +4489,10 @@
         <v>0.97</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.1448</v>
+        <v>-0.1146</v>
       </c>
       <c r="J65" t="n">
-        <v>-4.9232</v>
+        <v>-3.8964</v>
       </c>
     </row>
     <row r="66">
@@ -4529,10 +4529,10 @@
         <v>0.79</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.6215000000000001</v>
+        <v>-0.5843</v>
       </c>
       <c r="J66" t="n">
-        <v>-21.131</v>
+        <v>-19.8662</v>
       </c>
     </row>
     <row r="67">
@@ -4569,10 +4569,10 @@
         <v>1.26</v>
       </c>
       <c r="I67" t="n">
-        <v>0.4977</v>
+        <v>0.4591</v>
       </c>
       <c r="J67" t="n">
-        <v>16.9218</v>
+        <v>15.6094</v>
       </c>
     </row>
     <row r="68">
@@ -4609,10 +4609,10 @@
         <v>1.18</v>
       </c>
       <c r="I68" t="n">
-        <v>0.3869</v>
+        <v>0.3317</v>
       </c>
       <c r="J68" t="n">
-        <v>13.1546</v>
+        <v>11.2778</v>
       </c>
     </row>
     <row r="69">
@@ -4649,10 +4649,10 @@
         <v>1.12</v>
       </c>
       <c r="I69" t="n">
-        <v>0.2806</v>
+        <v>0.2329</v>
       </c>
       <c r="J69" t="n">
-        <v>9.5404</v>
+        <v>7.9186</v>
       </c>
     </row>
     <row r="70">
@@ -4689,10 +4689,10 @@
         <v>0.97</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.0629</v>
+        <v>-0.0492</v>
       </c>
       <c r="J70" t="n">
-        <v>-2.1386</v>
+        <v>-1.6728</v>
       </c>
     </row>
     <row r="71">
@@ -4729,10 +4729,10 @@
         <v>0.78</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.2775</v>
+        <v>-0.2589</v>
       </c>
       <c r="J71" t="n">
-        <v>-9.435</v>
+        <v>-8.8026</v>
       </c>
     </row>
     <row r="72">
@@ -4769,10 +4769,10 @@
         <v>1.63</v>
       </c>
       <c r="I72" t="n">
-        <v>0.7657</v>
+        <v>0.6956</v>
       </c>
       <c r="J72" t="n">
-        <v>22.2053</v>
+        <v>20.1724</v>
       </c>
     </row>
     <row r="73">
@@ -4809,10 +4809,10 @@
         <v>1.41</v>
       </c>
       <c r="I73" t="n">
-        <v>0.5396</v>
+        <v>0.4699</v>
       </c>
       <c r="J73" t="n">
-        <v>15.6484</v>
+        <v>13.6271</v>
       </c>
     </row>
     <row r="74">
@@ -4849,10 +4849,10 @@
         <v>1.1</v>
       </c>
       <c r="I74" t="n">
-        <v>0.1747</v>
+        <v>0.137</v>
       </c>
       <c r="J74" t="n">
-        <v>5.0663</v>
+        <v>3.973</v>
       </c>
     </row>
     <row r="75">
@@ -4889,10 +4889,10 @@
         <v>0.89</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.1707</v>
+        <v>-0.1506</v>
       </c>
       <c r="J75" t="n">
-        <v>-4.9503</v>
+        <v>-4.3674</v>
       </c>
     </row>
     <row r="76">
@@ -4929,10 +4929,10 @@
         <v>0.71</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.3503</v>
+        <v>-0.3373</v>
       </c>
       <c r="J76" t="n">
-        <v>-10.1587</v>
+        <v>-9.781700000000001</v>
       </c>
     </row>
     <row r="77">
@@ -4969,10 +4969,10 @@
         <v>1.43</v>
       </c>
       <c r="I77" t="n">
-        <v>0.8008999999999999</v>
+        <v>0.7503</v>
       </c>
       <c r="J77" t="n">
-        <v>23.2261</v>
+        <v>21.7587</v>
       </c>
     </row>
     <row r="78">
@@ -5009,10 +5009,10 @@
         <v>1.06</v>
       </c>
       <c r="I78" t="n">
-        <v>0.1724</v>
+        <v>0.1346</v>
       </c>
       <c r="J78" t="n">
-        <v>4.9996</v>
+        <v>3.9034</v>
       </c>
     </row>
     <row r="79">
@@ -5049,10 +5049,10 @@
         <v>0.88</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.1681</v>
+        <v>-0.1479</v>
       </c>
       <c r="J79" t="n">
-        <v>-4.8749</v>
+        <v>-4.2891</v>
       </c>
     </row>
     <row r="80">
@@ -5089,10 +5089,10 @@
         <v>0.84</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.2106</v>
+        <v>-0.1901</v>
       </c>
       <c r="J80" t="n">
-        <v>-6.1074</v>
+        <v>-5.5129</v>
       </c>
     </row>
     <row r="81">
@@ -5129,10 +5129,10 @@
         <v>0.72</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.3279</v>
+        <v>-0.3116</v>
       </c>
       <c r="J81" t="n">
-        <v>-9.5091</v>
+        <v>-9.0364</v>
       </c>
     </row>
     <row r="82">
@@ -5169,10 +5169,10 @@
         <v>1.37</v>
       </c>
       <c r="I82" t="n">
-        <v>0.5057</v>
+        <v>0.4372</v>
       </c>
       <c r="J82" t="n">
-        <v>14.1596</v>
+        <v>12.2416</v>
       </c>
     </row>
     <row r="83">
@@ -5209,10 +5209,10 @@
         <v>1.21</v>
       </c>
       <c r="I83" t="n">
-        <v>0.321</v>
+        <v>0.2639</v>
       </c>
       <c r="J83" t="n">
-        <v>8.988</v>
+        <v>7.3892</v>
       </c>
     </row>
     <row r="84">
@@ -5249,10 +5249,10 @@
         <v>1.05</v>
       </c>
       <c r="I84" t="n">
-        <v>0.1029</v>
+        <v>0.0764</v>
       </c>
       <c r="J84" t="n">
-        <v>2.8812</v>
+        <v>2.1392</v>
       </c>
     </row>
     <row r="85">
@@ -5289,10 +5289,10 @@
         <v>1</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.0061</v>
+        <v>-0.0042</v>
       </c>
       <c r="J85" t="n">
-        <v>-0.1708</v>
+        <v>-0.1176</v>
       </c>
     </row>
     <row r="86">
@@ -5329,10 +5329,10 @@
         <v>0.83</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.2302</v>
+        <v>-0.2101</v>
       </c>
       <c r="J86" t="n">
-        <v>-6.4456</v>
+        <v>-5.8828</v>
       </c>
     </row>
     <row r="87">
@@ -5369,10 +5369,10 @@
         <v>1.49</v>
       </c>
       <c r="I87" t="n">
-        <v>0.8702</v>
+        <v>0.8212</v>
       </c>
       <c r="J87" t="n">
-        <v>24.3656</v>
+        <v>22.9936</v>
       </c>
     </row>
     <row r="88">
@@ -5409,10 +5409,10 @@
         <v>1.06</v>
       </c>
       <c r="I88" t="n">
-        <v>0.1649</v>
+        <v>0.1296</v>
       </c>
       <c r="J88" t="n">
-        <v>4.6172</v>
+        <v>3.6288</v>
       </c>
     </row>
     <row r="89">
@@ -5449,10 +5449,10 @@
         <v>1</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.0023</v>
+        <v>-0.0013</v>
       </c>
       <c r="J89" t="n">
-        <v>-0.0644</v>
+        <v>-0.0364</v>
       </c>
     </row>
     <row r="90">
@@ -5489,10 +5489,10 @@
         <v>0.97</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.0611</v>
+        <v>-0.0478</v>
       </c>
       <c r="J90" t="n">
-        <v>-1.7108</v>
+        <v>-1.3384</v>
       </c>
     </row>
     <row r="91">
@@ -5529,10 +5529,10 @@
         <v>0.68</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.3694</v>
+        <v>-0.3567</v>
       </c>
       <c r="J91" t="n">
-        <v>-10.3432</v>
+        <v>-9.9876</v>
       </c>
     </row>
     <row r="92">
@@ -5569,10 +5569,10 @@
         <v>1.08</v>
       </c>
       <c r="I92" t="n">
-        <v>0.2403</v>
+        <v>0.1957</v>
       </c>
       <c r="J92" t="n">
-        <v>6.4881</v>
+        <v>5.2839</v>
       </c>
     </row>
     <row r="93">
@@ -5609,10 +5609,10 @@
         <v>0.86</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.1802</v>
+        <v>-0.1616</v>
       </c>
       <c r="J93" t="n">
-        <v>-4.8654</v>
+        <v>-4.3632</v>
       </c>
     </row>
     <row r="94">
@@ -5649,10 +5649,10 @@
         <v>0.85</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.1905</v>
+        <v>-0.1716</v>
       </c>
       <c r="J94" t="n">
-        <v>-5.1435</v>
+        <v>-4.6332</v>
       </c>
     </row>
     <row r="95">
@@ -5689,10 +5689,10 @@
         <v>0.8</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.2406</v>
+        <v>-0.2213</v>
       </c>
       <c r="J95" t="n">
-        <v>-6.4962</v>
+        <v>-5.9751</v>
       </c>
     </row>
     <row r="96">
@@ -5729,10 +5729,10 @@
         <v>0.79</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.2504</v>
+        <v>-0.2311</v>
       </c>
       <c r="J96" t="n">
-        <v>-6.7608</v>
+        <v>-6.2397</v>
       </c>
     </row>
     <row r="97">
@@ -5769,10 +5769,10 @@
         <v>1.72</v>
       </c>
       <c r="I97" t="n">
-        <v>1.4074</v>
+        <v>1.4367</v>
       </c>
       <c r="J97" t="n">
-        <v>37.9998</v>
+        <v>38.7909</v>
       </c>
     </row>
     <row r="98">
@@ -5809,10 +5809,10 @@
         <v>1.21</v>
       </c>
       <c r="I98" t="n">
-        <v>0.5707</v>
+        <v>0.5352</v>
       </c>
       <c r="J98" t="n">
-        <v>15.4089</v>
+        <v>14.4504</v>
       </c>
     </row>
     <row r="99">
@@ -5849,10 +5849,10 @@
         <v>1.01</v>
       </c>
       <c r="I99" t="n">
-        <v>0.0322</v>
+        <v>0.0223</v>
       </c>
       <c r="J99" t="n">
-        <v>0.8694</v>
+        <v>0.6021</v>
       </c>
     </row>
     <row r="100">
@@ -5889,10 +5889,10 @@
         <v>0.98</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.1288</v>
+        <v>-0.1015</v>
       </c>
       <c r="J100" t="n">
-        <v>-3.4776</v>
+        <v>-2.7405</v>
       </c>
     </row>
     <row r="101">
@@ -5929,10 +5929,10 @@
         <v>0.91</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.3471</v>
+        <v>-0.3057</v>
       </c>
       <c r="J101" t="n">
-        <v>-9.371700000000001</v>
+        <v>-8.2539</v>
       </c>
     </row>
     <row r="102">
@@ -5969,10 +5969,10 @@
         <v>1.43</v>
       </c>
       <c r="I102" t="n">
-        <v>0.9912</v>
+        <v>0.9876</v>
       </c>
       <c r="J102" t="n">
-        <v>23.7888</v>
+        <v>23.7024</v>
       </c>
     </row>
     <row r="103">
@@ -6009,10 +6009,10 @@
         <v>1.39</v>
       </c>
       <c r="I103" t="n">
-        <v>0.9203</v>
+        <v>0.9067</v>
       </c>
       <c r="J103" t="n">
-        <v>22.0872</v>
+        <v>21.7608</v>
       </c>
     </row>
     <row r="104">
@@ -6049,10 +6049,10 @@
         <v>1.2</v>
       </c>
       <c r="I104" t="n">
-        <v>0.5402</v>
+        <v>0.5083</v>
       </c>
       <c r="J104" t="n">
-        <v>12.9648</v>
+        <v>12.1992</v>
       </c>
     </row>
     <row r="105">
@@ -6089,10 +6089,10 @@
         <v>1.15</v>
       </c>
       <c r="I105" t="n">
-        <v>0.4267</v>
+        <v>0.3937</v>
       </c>
       <c r="J105" t="n">
-        <v>10.2408</v>
+        <v>9.4488</v>
       </c>
     </row>
     <row r="106">
@@ -6129,10 +6129,10 @@
         <v>1.06</v>
       </c>
       <c r="I106" t="n">
-        <v>0.1919</v>
+        <v>0.1641</v>
       </c>
       <c r="J106" t="n">
-        <v>4.6056</v>
+        <v>3.9384</v>
       </c>
     </row>
     <row r="107">
@@ -6169,10 +6169,10 @@
         <v>1.1</v>
       </c>
       <c r="I107" t="n">
-        <v>0.2913</v>
+        <v>0.2442</v>
       </c>
       <c r="J107" t="n">
-        <v>6.9912</v>
+        <v>5.8608</v>
       </c>
     </row>
     <row r="108">
@@ -6209,10 +6209,10 @@
         <v>1.02</v>
       </c>
       <c r="I108" t="n">
-        <v>0.1039</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="J108" t="n">
-        <v>2.4936</v>
+        <v>1.8768</v>
       </c>
     </row>
     <row r="109">
@@ -6249,10 +6249,10 @@
         <v>0.87</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.1681</v>
+        <v>-0.1508</v>
       </c>
       <c r="J109" t="n">
-        <v>-4.0344</v>
+        <v>-3.6192</v>
       </c>
     </row>
     <row r="110">
@@ -6289,10 +6289,10 @@
         <v>0.74</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.2953</v>
+        <v>-0.2774</v>
       </c>
       <c r="J110" t="n">
-        <v>-7.0872</v>
+        <v>-6.6576</v>
       </c>
     </row>
     <row r="111">
@@ -6329,10 +6329,10 @@
         <v>0.5</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.5102</v>
+        <v>-0.5112</v>
       </c>
       <c r="J111" t="n">
-        <v>-12.2448</v>
+        <v>-12.2688</v>
       </c>
     </row>
     <row r="112">
@@ -6369,10 +6369,10 @@
         <v>1.33</v>
       </c>
       <c r="I112" t="n">
-        <v>0.4547</v>
+        <v>0.3883</v>
       </c>
       <c r="J112" t="n">
-        <v>13.1863</v>
+        <v>11.2607</v>
       </c>
     </row>
     <row r="113">
@@ -6409,10 +6409,10 @@
         <v>1.2</v>
       </c>
       <c r="I113" t="n">
-        <v>0.304</v>
+        <v>0.2494</v>
       </c>
       <c r="J113" t="n">
-        <v>8.816000000000001</v>
+        <v>7.2326</v>
       </c>
     </row>
     <row r="114">
@@ -6449,10 +6449,10 @@
         <v>1.17</v>
       </c>
       <c r="I114" t="n">
-        <v>0.2671</v>
+        <v>0.2166</v>
       </c>
       <c r="J114" t="n">
-        <v>7.7459</v>
+        <v>6.2814</v>
       </c>
     </row>
     <row r="115">
@@ -6489,10 +6489,10 @@
         <v>1.07</v>
       </c>
       <c r="I115" t="n">
-        <v>0.1314</v>
+        <v>0.1004</v>
       </c>
       <c r="J115" t="n">
-        <v>3.8106</v>
+        <v>2.9116</v>
       </c>
     </row>
     <row r="116">
@@ -6529,10 +6529,10 @@
         <v>0.9</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.1582</v>
+        <v>-0.1383</v>
       </c>
       <c r="J116" t="n">
-        <v>-4.5878</v>
+        <v>-4.0107</v>
       </c>
     </row>
     <row r="117">
@@ -6569,10 +6569,10 @@
         <v>1.21</v>
       </c>
       <c r="I117" t="n">
-        <v>0.4556</v>
+        <v>0.3977</v>
       </c>
       <c r="J117" t="n">
-        <v>13.2124</v>
+        <v>11.5333</v>
       </c>
     </row>
     <row r="118">
@@ -6609,10 +6609,10 @@
         <v>1.18</v>
       </c>
       <c r="I118" t="n">
-        <v>0.404</v>
+        <v>0.3475</v>
       </c>
       <c r="J118" t="n">
-        <v>11.716</v>
+        <v>10.0775</v>
       </c>
     </row>
     <row r="119">
@@ -6649,10 +6649,10 @@
         <v>1.01</v>
       </c>
       <c r="I119" t="n">
-        <v>0.0456</v>
+        <v>0.0305</v>
       </c>
       <c r="J119" t="n">
-        <v>1.3224</v>
+        <v>0.8845</v>
       </c>
     </row>
     <row r="120">
@@ -6689,10 +6689,10 @@
         <v>0.8</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.2506</v>
+        <v>-0.2306</v>
       </c>
       <c r="J120" t="n">
-        <v>-7.2674</v>
+        <v>-6.6874</v>
       </c>
     </row>
     <row r="121">
@@ -6729,10 +6729,10 @@
         <v>0.7</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.3459</v>
+        <v>-0.3308</v>
       </c>
       <c r="J121" t="n">
-        <v>-10.0311</v>
+        <v>-9.5932</v>
       </c>
     </row>
     <row r="122">
@@ -6769,10 +6769,10 @@
         <v>1.34</v>
       </c>
       <c r="I122" t="n">
-        <v>0.464</v>
+        <v>0.3973</v>
       </c>
       <c r="J122" t="n">
-        <v>13.92</v>
+        <v>11.919</v>
       </c>
     </row>
     <row r="123">
@@ -6809,10 +6809,10 @@
         <v>1.18</v>
       </c>
       <c r="I123" t="n">
-        <v>0.2785</v>
+        <v>0.2269</v>
       </c>
       <c r="J123" t="n">
-        <v>8.355</v>
+        <v>6.807</v>
       </c>
     </row>
     <row r="124">
@@ -6849,10 +6849,10 @@
         <v>1.14</v>
       </c>
       <c r="I124" t="n">
-        <v>0.2287</v>
+        <v>0.1833</v>
       </c>
       <c r="J124" t="n">
-        <v>6.861</v>
+        <v>5.499</v>
       </c>
     </row>
     <row r="125">
@@ -6889,10 +6889,10 @@
         <v>1.08</v>
       </c>
       <c r="I125" t="n">
-        <v>0.1457</v>
+        <v>0.1125</v>
       </c>
       <c r="J125" t="n">
-        <v>4.371</v>
+        <v>3.375</v>
       </c>
     </row>
     <row r="126">
@@ -6929,10 +6929,10 @@
         <v>0.99</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.036</v>
+        <v>-0.0267</v>
       </c>
       <c r="J126" t="n">
-        <v>-1.08</v>
+        <v>-0.801</v>
       </c>
     </row>
     <row r="127">
@@ -6969,10 +6969,10 @@
         <v>1.08</v>
       </c>
       <c r="I127" t="n">
-        <v>0.2254</v>
+        <v>0.1812</v>
       </c>
       <c r="J127" t="n">
-        <v>6.762</v>
+        <v>5.436</v>
       </c>
     </row>
     <row r="128">
@@ -7009,10 +7009,10 @@
         <v>1.01</v>
       </c>
       <c r="I128" t="n">
-        <v>0.0527</v>
+        <v>0.0355</v>
       </c>
       <c r="J128" t="n">
-        <v>1.581</v>
+        <v>1.065</v>
       </c>
     </row>
     <row r="129">
@@ -7049,10 +7049,10 @@
         <v>0.98</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.0386</v>
+        <v>-0.0301</v>
       </c>
       <c r="J129" t="n">
-        <v>-1.158</v>
+        <v>-0.903</v>
       </c>
     </row>
     <row r="130">
@@ -7089,10 +7089,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.2363</v>
+        <v>-0.2162</v>
       </c>
       <c r="J130" t="n">
-        <v>-7.089</v>
+        <v>-6.486</v>
       </c>
     </row>
     <row r="131">
@@ -7129,10 +7129,10 @@
         <v>0.79</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.2561</v>
+        <v>-0.2364</v>
       </c>
       <c r="J131" t="n">
-        <v>-7.683</v>
+        <v>-7.092</v>
       </c>
     </row>
     <row r="132">
@@ -7169,10 +7169,10 @@
         <v>1.48</v>
       </c>
       <c r="I132" t="n">
-        <v>0.6137</v>
+        <v>0.5425</v>
       </c>
       <c r="J132" t="n">
-        <v>18.411</v>
+        <v>16.275</v>
       </c>
     </row>
     <row r="133">
@@ -7209,10 +7209,10 @@
         <v>1.18</v>
       </c>
       <c r="I133" t="n">
-        <v>0.2785</v>
+        <v>0.2269</v>
       </c>
       <c r="J133" t="n">
-        <v>8.355</v>
+        <v>6.807</v>
       </c>
     </row>
     <row r="134">
@@ -7249,10 +7249,10 @@
         <v>1.1</v>
       </c>
       <c r="I134" t="n">
-        <v>0.1748</v>
+        <v>0.1371</v>
       </c>
       <c r="J134" t="n">
-        <v>5.244</v>
+        <v>4.113</v>
       </c>
     </row>
     <row r="135">
@@ -7289,10 +7289,10 @@
         <v>1.02</v>
       </c>
       <c r="I135" t="n">
-        <v>0.0423</v>
+        <v>0.0292</v>
       </c>
       <c r="J135" t="n">
-        <v>1.269</v>
+        <v>0.876</v>
       </c>
     </row>
     <row r="136">
@@ -7329,10 +7329,10 @@
         <v>0.95</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.0978</v>
+        <v>-0.0808</v>
       </c>
       <c r="J136" t="n">
-        <v>-2.934</v>
+        <v>-2.424</v>
       </c>
     </row>
     <row r="137">
@@ -7369,10 +7369,10 @@
         <v>1.24</v>
       </c>
       <c r="I137" t="n">
-        <v>0.4963</v>
+        <v>0.4372</v>
       </c>
       <c r="J137" t="n">
-        <v>14.889</v>
+        <v>13.116</v>
       </c>
     </row>
     <row r="138">
@@ -7409,10 +7409,10 @@
         <v>1.11</v>
       </c>
       <c r="I138" t="n">
-        <v>0.2687</v>
+        <v>0.221</v>
       </c>
       <c r="J138" t="n">
-        <v>8.061</v>
+        <v>6.63</v>
       </c>
     </row>
     <row r="139">
@@ -7449,10 +7449,10 @@
         <v>1.09</v>
       </c>
       <c r="I139" t="n">
-        <v>0.2297</v>
+        <v>0.1858</v>
       </c>
       <c r="J139" t="n">
-        <v>6.891</v>
+        <v>5.574</v>
       </c>
     </row>
     <row r="140">
@@ -7489,10 +7489,10 @@
         <v>0.95</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.08749999999999999</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="J140" t="n">
-        <v>-2.625</v>
+        <v>-2.142</v>
       </c>
     </row>
     <row r="141">
@@ -7529,10 +7529,10 @@
         <v>0.7</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.3492</v>
+        <v>-0.3347</v>
       </c>
       <c r="J141" t="n">
-        <v>-10.476</v>
+        <v>-10.041</v>
       </c>
     </row>
     <row r="142">
@@ -7569,10 +7569,10 @@
         <v>1.91</v>
       </c>
       <c r="I142" t="n">
-        <v>0.9798</v>
+        <v>0.9177</v>
       </c>
       <c r="J142" t="n">
-        <v>21.5556</v>
+        <v>20.1894</v>
       </c>
     </row>
     <row r="143">
@@ -7609,10 +7609,10 @@
         <v>1.68</v>
       </c>
       <c r="I143" t="n">
-        <v>0.7743</v>
+        <v>0.7027</v>
       </c>
       <c r="J143" t="n">
-        <v>17.0346</v>
+        <v>15.4594</v>
       </c>
     </row>
     <row r="144">
@@ -7649,10 +7649,10 @@
         <v>1.18</v>
       </c>
       <c r="I144" t="n">
-        <v>0.261</v>
+        <v>0.2151</v>
       </c>
       <c r="J144" t="n">
-        <v>5.742</v>
+        <v>4.7322</v>
       </c>
     </row>
     <row r="145">
@@ -7689,10 +7689,10 @@
         <v>1.17</v>
       </c>
       <c r="I145" t="n">
-        <v>0.2484</v>
+        <v>0.2037</v>
       </c>
       <c r="J145" t="n">
-        <v>5.4648</v>
+        <v>4.4814</v>
       </c>
     </row>
     <row r="146">
@@ -7729,10 +7729,10 @@
         <v>0.96</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.1008</v>
+        <v>-0.0866</v>
       </c>
       <c r="J146" t="n">
-        <v>-2.2176</v>
+        <v>-1.9052</v>
       </c>
     </row>
     <row r="147">
@@ -7769,10 +7769,10 @@
         <v>0.93</v>
       </c>
       <c r="I147" t="n">
-        <v>-0.081</v>
+        <v>-0.0667</v>
       </c>
       <c r="J147" t="n">
-        <v>-1.782</v>
+        <v>-1.4674</v>
       </c>
     </row>
     <row r="148">
@@ -7809,10 +7809,10 @@
         <v>0.9</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.1186</v>
+        <v>-0.1034</v>
       </c>
       <c r="J148" t="n">
-        <v>-2.6092</v>
+        <v>-2.2748</v>
       </c>
     </row>
     <row r="149">
@@ -7849,10 +7849,10 @@
         <v>0.74</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.285</v>
+        <v>-0.2697</v>
       </c>
       <c r="J149" t="n">
-        <v>-6.27</v>
+        <v>-5.9334</v>
       </c>
     </row>
     <row r="150">
@@ -7889,10 +7889,10 @@
         <v>0.58</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.4281</v>
+        <v>-0.419</v>
       </c>
       <c r="J150" t="n">
-        <v>-9.418200000000001</v>
+        <v>-9.218</v>
       </c>
     </row>
     <row r="151">
@@ -7929,10 +7929,10 @@
         <v>0.53</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.4722</v>
+        <v>-0.4675</v>
       </c>
       <c r="J151" t="n">
-        <v>-10.3884</v>
+        <v>-10.285</v>
       </c>
     </row>
     <row r="152">
@@ -7969,10 +7969,10 @@
         <v>1.52</v>
       </c>
       <c r="I152" t="n">
-        <v>0.9344</v>
+        <v>0.8952</v>
       </c>
       <c r="J152" t="n">
-        <v>23.36</v>
+        <v>22.38</v>
       </c>
     </row>
     <row r="153">
@@ -8009,10 +8009,10 @@
         <v>0.98</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.0417</v>
+        <v>-0.032</v>
       </c>
       <c r="J153" t="n">
-        <v>-1.0425</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="154">
@@ -8049,10 +8049,10 @@
         <v>0.98</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.0417</v>
+        <v>-0.032</v>
       </c>
       <c r="J154" t="n">
-        <v>-1.0425</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="155">
@@ -8089,10 +8089,10 @@
         <v>0.77</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.2799</v>
+        <v>-0.261</v>
       </c>
       <c r="J155" t="n">
-        <v>-6.9975</v>
+        <v>-6.525</v>
       </c>
     </row>
     <row r="156">
@@ -8129,10 +8129,10 @@
         <v>0.65</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.3913</v>
+        <v>-0.38</v>
       </c>
       <c r="J156" t="n">
-        <v>-9.782500000000001</v>
+        <v>-9.5</v>
       </c>
     </row>
     <row r="157">
@@ -8169,10 +8169,10 @@
         <v>1.66</v>
       </c>
       <c r="I157" t="n">
-        <v>0.7906</v>
+        <v>0.7206</v>
       </c>
       <c r="J157" t="n">
-        <v>19.765</v>
+        <v>18.015</v>
       </c>
     </row>
     <row r="158">
@@ -8209,10 +8209,10 @@
         <v>1.31</v>
       </c>
       <c r="I158" t="n">
-        <v>0.4276</v>
+        <v>0.3633</v>
       </c>
       <c r="J158" t="n">
-        <v>10.69</v>
+        <v>9.0825</v>
       </c>
     </row>
     <row r="159">
@@ -8249,10 +8249,10 @@
         <v>1.29</v>
       </c>
       <c r="I159" t="n">
-        <v>0.4052</v>
+        <v>0.3424</v>
       </c>
       <c r="J159" t="n">
-        <v>10.13</v>
+        <v>8.56</v>
       </c>
     </row>
     <row r="160">
@@ -8289,10 +8289,10 @@
         <v>0.8</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.2665</v>
+        <v>-0.2484</v>
       </c>
       <c r="J160" t="n">
-        <v>-6.6625</v>
+        <v>-6.21</v>
       </c>
     </row>
     <row r="161">
@@ -8329,10 +8329,10 @@
         <v>0.79</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.2763</v>
+        <v>-0.2586</v>
       </c>
       <c r="J161" t="n">
-        <v>-6.9075</v>
+        <v>-6.465</v>
       </c>
     </row>
     <row r="162">
@@ -8369,10 +8369,10 @@
         <v>1.15</v>
       </c>
       <c r="I162" t="n">
-        <v>0.3895</v>
+        <v>0.3381</v>
       </c>
       <c r="J162" t="n">
-        <v>8.958500000000001</v>
+        <v>7.7763</v>
       </c>
     </row>
     <row r="163">
@@ -8409,10 +8409,10 @@
         <v>0.97</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.0442</v>
+        <v>-0.035</v>
       </c>
       <c r="J163" t="n">
-        <v>-1.0166</v>
+        <v>-0.805</v>
       </c>
     </row>
     <row r="164">
@@ -8449,10 +8449,10 @@
         <v>0.97</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.0442</v>
+        <v>-0.035</v>
       </c>
       <c r="J164" t="n">
-        <v>-1.0166</v>
+        <v>-0.805</v>
       </c>
     </row>
     <row r="165">
@@ -8489,10 +8489,10 @@
         <v>0.67</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.3601</v>
+        <v>-0.3455</v>
       </c>
       <c r="J165" t="n">
-        <v>-8.282299999999999</v>
+        <v>-7.9465</v>
       </c>
     </row>
     <row r="166">
@@ -8529,10 +8529,10 @@
         <v>0.47</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.5358000000000001</v>
+        <v>-0.5405</v>
       </c>
       <c r="J166" t="n">
-        <v>-12.3234</v>
+        <v>-12.4315</v>
       </c>
     </row>
     <row r="167">
@@ -8569,10 +8569,10 @@
         <v>1.46</v>
       </c>
       <c r="I167" t="n">
-        <v>0.5722</v>
+        <v>0.5024999999999999</v>
       </c>
       <c r="J167" t="n">
-        <v>13.1606</v>
+        <v>11.5575</v>
       </c>
     </row>
     <row r="168">
@@ -8609,10 +8609,10 @@
         <v>1.37</v>
       </c>
       <c r="I168" t="n">
-        <v>0.4797</v>
+        <v>0.4144</v>
       </c>
       <c r="J168" t="n">
-        <v>11.0331</v>
+        <v>9.5312</v>
       </c>
     </row>
     <row r="169">
@@ -8649,10 +8649,10 @@
         <v>1.35</v>
       </c>
       <c r="I169" t="n">
-        <v>0.4587</v>
+        <v>0.3948</v>
       </c>
       <c r="J169" t="n">
-        <v>10.5501</v>
+        <v>9.080399999999999</v>
       </c>
     </row>
     <row r="170">
@@ -8689,10 +8689,10 @@
         <v>1.3</v>
       </c>
       <c r="I170" t="n">
-        <v>0.4058</v>
+        <v>0.3457</v>
       </c>
       <c r="J170" t="n">
-        <v>9.333399999999999</v>
+        <v>7.9511</v>
       </c>
     </row>
     <row r="171">
@@ -8729,10 +8729,10 @@
         <v>0.97</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.0803</v>
+        <v>-0.0665</v>
       </c>
       <c r="J171" t="n">
-        <v>-1.8469</v>
+        <v>-1.5295</v>
       </c>
     </row>
     <row r="172">
@@ -8769,10 +8769,10 @@
         <v>1.12</v>
       </c>
       <c r="I172" t="n">
-        <v>0.3876</v>
+        <v>0.3455</v>
       </c>
       <c r="J172" t="n">
-        <v>11.2404</v>
+        <v>10.0195</v>
       </c>
     </row>
     <row r="173">
@@ -8809,10 +8809,10 @@
         <v>1.08</v>
       </c>
       <c r="I173" t="n">
-        <v>0.2822</v>
+        <v>0.2434</v>
       </c>
       <c r="J173" t="n">
-        <v>8.1838</v>
+        <v>7.0586</v>
       </c>
     </row>
     <row r="174">
@@ -8849,10 +8849,10 @@
         <v>1.07</v>
       </c>
       <c r="I174" t="n">
-        <v>0.2543</v>
+        <v>0.217</v>
       </c>
       <c r="J174" t="n">
-        <v>7.3747</v>
+        <v>6.293</v>
       </c>
     </row>
     <row r="175">
@@ -8889,10 +8889,10 @@
         <v>0.95</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.205</v>
+        <v>-0.1695</v>
       </c>
       <c r="J175" t="n">
-        <v>-5.945</v>
+        <v>-4.9155</v>
       </c>
     </row>
     <row r="176">
@@ -8929,10 +8929,10 @@
         <v>0.91</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.3203</v>
+        <v>-0.2786</v>
       </c>
       <c r="J176" t="n">
-        <v>-9.2887</v>
+        <v>-8.0794</v>
       </c>
     </row>
     <row r="177">
@@ -8969,10 +8969,10 @@
         <v>1.25</v>
       </c>
       <c r="I177" t="n">
-        <v>0.4854</v>
+        <v>0.4283</v>
       </c>
       <c r="J177" t="n">
-        <v>14.0766</v>
+        <v>12.4207</v>
       </c>
     </row>
     <row r="178">
@@ -9009,10 +9009,10 @@
         <v>1.18</v>
       </c>
       <c r="I178" t="n">
-        <v>0.3734</v>
+        <v>0.322</v>
       </c>
       <c r="J178" t="n">
-        <v>10.8286</v>
+        <v>9.337999999999999</v>
       </c>
     </row>
     <row r="179">
@@ -9049,10 +9049,10 @@
         <v>1.18</v>
       </c>
       <c r="I179" t="n">
-        <v>0.3734</v>
+        <v>0.322</v>
       </c>
       <c r="J179" t="n">
-        <v>10.8286</v>
+        <v>9.337999999999999</v>
       </c>
     </row>
     <row r="180">
@@ -9089,10 +9089,10 @@
         <v>1.12</v>
       </c>
       <c r="I180" t="n">
-        <v>0.2711</v>
+        <v>0.2277</v>
       </c>
       <c r="J180" t="n">
-        <v>7.8619</v>
+        <v>6.6033</v>
       </c>
     </row>
     <row r="181">
@@ -9129,10 +9129,10 @@
         <v>1.07</v>
       </c>
       <c r="I181" t="n">
-        <v>0.1738</v>
+        <v>0.1405</v>
       </c>
       <c r="J181" t="n">
-        <v>5.0402</v>
+        <v>4.0745</v>
       </c>
     </row>
     <row r="182">
@@ -9169,10 +9169,10 @@
         <v>1.49</v>
       </c>
       <c r="I182" t="n">
-        <v>0.844</v>
+        <v>0.7906</v>
       </c>
       <c r="J182" t="n">
-        <v>25.32</v>
+        <v>23.718</v>
       </c>
     </row>
     <row r="183">
@@ -9209,10 +9209,10 @@
         <v>1.32</v>
       </c>
       <c r="I183" t="n">
-        <v>0.5977</v>
+        <v>0.538</v>
       </c>
       <c r="J183" t="n">
-        <v>17.931</v>
+        <v>16.14</v>
       </c>
     </row>
     <row r="184">
@@ -9249,10 +9249,10 @@
         <v>1.07</v>
       </c>
       <c r="I184" t="n">
-        <v>0.1774</v>
+        <v>0.1432</v>
       </c>
       <c r="J184" t="n">
-        <v>5.322</v>
+        <v>4.296</v>
       </c>
     </row>
     <row r="185">
@@ -9289,10 +9289,10 @@
         <v>0.92</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.1344</v>
+        <v>-0.1152</v>
       </c>
       <c r="J185" t="n">
-        <v>-4.032</v>
+        <v>-3.456</v>
       </c>
     </row>
     <row r="186">
@@ -9329,10 +9329,10 @@
         <v>0.85</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.2126</v>
+        <v>-0.1924</v>
       </c>
       <c r="J186" t="n">
-        <v>-6.378</v>
+        <v>-5.772</v>
       </c>
     </row>
     <row r="187">
@@ -9369,10 +9369,10 @@
         <v>1.22</v>
       </c>
       <c r="I187" t="n">
-        <v>0.6352</v>
+        <v>0.5982</v>
       </c>
       <c r="J187" t="n">
-        <v>19.056</v>
+        <v>17.946</v>
       </c>
     </row>
     <row r="188">
@@ -9409,10 +9409,10 @@
         <v>1.14</v>
       </c>
       <c r="I188" t="n">
-        <v>0.446</v>
+        <v>0.403</v>
       </c>
       <c r="J188" t="n">
-        <v>13.38</v>
+        <v>12.09</v>
       </c>
     </row>
     <row r="189">
@@ -9449,10 +9449,10 @@
         <v>1.08</v>
       </c>
       <c r="I189" t="n">
-        <v>0.2891</v>
+        <v>0.2489</v>
       </c>
       <c r="J189" t="n">
-        <v>8.673</v>
+        <v>7.467</v>
       </c>
     </row>
     <row r="190">
@@ -9489,10 +9489,10 @@
         <v>0.78</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.6319</v>
+        <v>-0.5946</v>
       </c>
       <c r="J190" t="n">
-        <v>-18.957</v>
+        <v>-17.838</v>
       </c>
     </row>
     <row r="191">
@@ -9529,10 +9529,10 @@
         <v>0.75</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.6991000000000001</v>
+        <v>-0.6657999999999999</v>
       </c>
       <c r="J191" t="n">
-        <v>-20.973</v>
+        <v>-19.974</v>
       </c>
     </row>
     <row r="192">
@@ -9569,10 +9569,10 @@
         <v>1.09</v>
       </c>
       <c r="I192" t="n">
-        <v>0.2562</v>
+        <v>0.2098</v>
       </c>
       <c r="J192" t="n">
-        <v>6.405</v>
+        <v>5.245</v>
       </c>
     </row>
     <row r="193">
@@ -9609,10 +9609,10 @@
         <v>0.9</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.1391</v>
+        <v>-0.1218</v>
       </c>
       <c r="J193" t="n">
-        <v>-3.4775</v>
+        <v>-3.045</v>
       </c>
     </row>
     <row r="194">
@@ -9649,10 +9649,10 @@
         <v>0.86</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.1816</v>
+        <v>-0.1625</v>
       </c>
       <c r="J194" t="n">
-        <v>-4.54</v>
+        <v>-4.0625</v>
       </c>
     </row>
     <row r="195">
@@ -9689,10 +9689,10 @@
         <v>0.84</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.2022</v>
+        <v>-0.1827</v>
       </c>
       <c r="J195" t="n">
-        <v>-5.055</v>
+        <v>-4.5675</v>
       </c>
     </row>
     <row r="196">
@@ -9729,10 +9729,10 @@
         <v>0.78</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.2619</v>
+        <v>-0.2426</v>
       </c>
       <c r="J196" t="n">
-        <v>-6.5475</v>
+        <v>-6.065</v>
       </c>
     </row>
     <row r="197">
@@ -9769,10 +9769,10 @@
         <v>1.94</v>
       </c>
       <c r="I197" t="n">
-        <v>1.6452</v>
+        <v>1.6917</v>
       </c>
       <c r="J197" t="n">
-        <v>41.13</v>
+        <v>42.2925</v>
       </c>
     </row>
     <row r="198">
@@ -9809,10 +9809,10 @@
         <v>1.27</v>
       </c>
       <c r="I198" t="n">
-        <v>0.6802</v>
+        <v>0.6546999999999999</v>
       </c>
       <c r="J198" t="n">
-        <v>17.005</v>
+        <v>16.3675</v>
       </c>
     </row>
     <row r="199">
@@ -9849,10 +9849,10 @@
         <v>1.11</v>
       </c>
       <c r="I199" t="n">
-        <v>0.3202</v>
+        <v>0.2883</v>
       </c>
       <c r="J199" t="n">
-        <v>8.005000000000001</v>
+        <v>7.2075</v>
       </c>
     </row>
     <row r="200">
@@ -9889,10 +9889,10 @@
         <v>1.1</v>
       </c>
       <c r="I200" t="n">
-        <v>0.2943</v>
+        <v>0.2627</v>
       </c>
       <c r="J200" t="n">
-        <v>7.3575</v>
+        <v>6.5675</v>
       </c>
     </row>
     <row r="201">
@@ -9929,10 +9929,10 @@
         <v>1.07</v>
       </c>
       <c r="I201" t="n">
-        <v>0.2124</v>
+        <v>0.1832</v>
       </c>
       <c r="J201" t="n">
-        <v>5.31</v>
+        <v>4.58</v>
       </c>
     </row>
     <row r="202">
@@ -9969,10 +9969,10 @@
         <v>1.52</v>
       </c>
       <c r="I202" t="n">
-        <v>1.1128</v>
+        <v>1.1253</v>
       </c>
       <c r="J202" t="n">
-        <v>23.3688</v>
+        <v>23.6313</v>
       </c>
     </row>
     <row r="203">
@@ -10009,10 +10009,10 @@
         <v>1.44</v>
       </c>
       <c r="I203" t="n">
-        <v>0.9984</v>
+        <v>0.9973</v>
       </c>
       <c r="J203" t="n">
-        <v>20.9664</v>
+        <v>20.9433</v>
       </c>
     </row>
     <row r="204">
@@ -10049,10 +10049,10 @@
         <v>1.41</v>
       </c>
       <c r="I204" t="n">
-        <v>0.9475</v>
+        <v>0.9389</v>
       </c>
       <c r="J204" t="n">
-        <v>19.8975</v>
+        <v>19.7169</v>
       </c>
     </row>
     <row r="205">
@@ -10089,10 +10089,10 @@
         <v>1.18</v>
       </c>
       <c r="I205" t="n">
-        <v>0.4885</v>
+        <v>0.4574</v>
       </c>
       <c r="J205" t="n">
-        <v>10.2585</v>
+        <v>9.605399999999999</v>
       </c>
     </row>
     <row r="206">
@@ -10129,10 +10129,10 @@
         <v>0.93</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.3133</v>
+        <v>-0.276</v>
       </c>
       <c r="J206" t="n">
-        <v>-6.5793</v>
+        <v>-5.796</v>
       </c>
     </row>
     <row r="207">
@@ -10169,10 +10169,10 @@
         <v>1.16</v>
       </c>
       <c r="I207" t="n">
-        <v>0.4061</v>
+        <v>0.3539</v>
       </c>
       <c r="J207" t="n">
-        <v>8.5281</v>
+        <v>7.4319</v>
       </c>
     </row>
     <row r="208">
@@ -10209,10 +10209,10 @@
         <v>1.07</v>
       </c>
       <c r="I208" t="n">
-        <v>0.2257</v>
+        <v>0.1834</v>
       </c>
       <c r="J208" t="n">
-        <v>4.7397</v>
+        <v>3.8514</v>
       </c>
     </row>
     <row r="209">
@@ -10249,10 +10249,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.0871</v>
+        <v>-0.074</v>
       </c>
       <c r="J209" t="n">
-        <v>-1.8291</v>
+        <v>-1.554</v>
       </c>
     </row>
     <row r="210">
@@ -10289,10 +10289,10 @@
         <v>0.55</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.4675</v>
+        <v>-0.4631</v>
       </c>
       <c r="J210" t="n">
-        <v>-9.817500000000001</v>
+        <v>-9.725099999999999</v>
       </c>
     </row>
     <row r="211">
@@ -10329,10 +10329,10 @@
         <v>0.54</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.4762</v>
+        <v>-0.4729</v>
       </c>
       <c r="J211" t="n">
-        <v>-10.0002</v>
+        <v>-9.930899999999999</v>
       </c>
     </row>
     <row r="212">
@@ -10369,10 +10369,10 @@
         <v>0.88</v>
       </c>
       <c r="I212" t="n">
-        <v>-0.1317</v>
+        <v>-0.1152</v>
       </c>
       <c r="J212" t="n">
-        <v>-2.5023</v>
+        <v>-2.1888</v>
       </c>
     </row>
     <row r="213">
@@ -10409,10 +10409,10 @@
         <v>0.76</v>
       </c>
       <c r="I213" t="n">
-        <v>-0.2603</v>
+        <v>-0.2462</v>
       </c>
       <c r="J213" t="n">
-        <v>-4.9457</v>
+        <v>-4.6778</v>
       </c>
     </row>
     <row r="214">
@@ -10449,10 +10449,10 @@
         <v>0.68</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.3336</v>
+        <v>-0.3207</v>
       </c>
       <c r="J214" t="n">
-        <v>-6.3384</v>
+        <v>-6.0933</v>
       </c>
     </row>
     <row r="215">
@@ -10489,10 +10489,10 @@
         <v>0.62</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.3863</v>
+        <v>-0.375</v>
       </c>
       <c r="J215" t="n">
-        <v>-7.3397</v>
+        <v>-7.125</v>
       </c>
     </row>
     <row r="216">
@@ -10529,10 +10529,10 @@
         <v>0.49</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.501</v>
+        <v>-0.4993</v>
       </c>
       <c r="J216" t="n">
-        <v>-9.519</v>
+        <v>-9.486700000000001</v>
       </c>
     </row>
     <row r="217">
@@ -10569,10 +10569,10 @@
         <v>1.71</v>
       </c>
       <c r="I217" t="n">
-        <v>0.7874</v>
+        <v>0.7171999999999999</v>
       </c>
       <c r="J217" t="n">
-        <v>14.9606</v>
+        <v>13.6268</v>
       </c>
     </row>
     <row r="218">
@@ -10609,10 +10609,10 @@
         <v>1.66</v>
       </c>
       <c r="I218" t="n">
-        <v>0.742</v>
+        <v>0.6721</v>
       </c>
       <c r="J218" t="n">
-        <v>14.098</v>
+        <v>12.7699</v>
       </c>
     </row>
     <row r="219">
@@ -10649,10 +10649,10 @@
         <v>1.44</v>
       </c>
       <c r="I219" t="n">
-        <v>0.5367</v>
+        <v>0.4734</v>
       </c>
       <c r="J219" t="n">
-        <v>10.1973</v>
+        <v>8.9946</v>
       </c>
     </row>
     <row r="220">
@@ -10689,10 +10689,10 @@
         <v>1.37</v>
       </c>
       <c r="I220" t="n">
-        <v>0.4659</v>
+        <v>0.4061</v>
       </c>
       <c r="J220" t="n">
-        <v>8.8521</v>
+        <v>7.7159</v>
       </c>
     </row>
     <row r="221">
@@ -10729,10 +10729,10 @@
         <v>1.35</v>
       </c>
       <c r="I221" t="n">
-        <v>0.4449</v>
+        <v>0.3863</v>
       </c>
       <c r="J221" t="n">
-        <v>8.453099999999999</v>
+        <v>7.3397</v>
       </c>
     </row>
     <row r="222">
@@ -10769,10 +10769,10 @@
         <v>1.17</v>
       </c>
       <c r="I222" t="n">
-        <v>0.4082</v>
+        <v>0.3535</v>
       </c>
       <c r="J222" t="n">
-        <v>11.8378</v>
+        <v>10.2515</v>
       </c>
     </row>
     <row r="223">
@@ -10809,10 +10809,10 @@
         <v>0.89</v>
       </c>
       <c r="I223" t="n">
-        <v>-0.1501</v>
+        <v>-0.1321</v>
       </c>
       <c r="J223" t="n">
-        <v>-4.3529</v>
+        <v>-3.8309</v>
       </c>
     </row>
     <row r="224">
@@ -10849,10 +10849,10 @@
         <v>0.88</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.1609</v>
+        <v>-0.1424</v>
       </c>
       <c r="J224" t="n">
-        <v>-4.6661</v>
+        <v>-4.1296</v>
       </c>
     </row>
     <row r="225">
@@ -10889,10 +10889,10 @@
         <v>0.79</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.2528</v>
+        <v>-0.2332</v>
       </c>
       <c r="J225" t="n">
-        <v>-7.3312</v>
+        <v>-6.7628</v>
       </c>
     </row>
     <row r="226">
@@ -10929,10 +10929,10 @@
         <v>0.77</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.2722</v>
+        <v>-0.2531</v>
       </c>
       <c r="J226" t="n">
-        <v>-7.8938</v>
+        <v>-7.3399</v>
       </c>
     </row>
     <row r="227">
@@ -10969,10 +10969,10 @@
         <v>1.48</v>
       </c>
       <c r="I227" t="n">
-        <v>0.6163</v>
+        <v>0.5451</v>
       </c>
       <c r="J227" t="n">
-        <v>17.8727</v>
+        <v>15.8079</v>
       </c>
     </row>
     <row r="228">
@@ -11009,10 +11009,10 @@
         <v>1.37</v>
       </c>
       <c r="I228" t="n">
-        <v>0.499</v>
+        <v>0.4306</v>
       </c>
       <c r="J228" t="n">
-        <v>14.471</v>
+        <v>12.4874</v>
       </c>
     </row>
     <row r="229">
@@ -11049,10 +11049,10 @@
         <v>1.27</v>
       </c>
       <c r="I229" t="n">
-        <v>0.387</v>
+        <v>0.325</v>
       </c>
       <c r="J229" t="n">
-        <v>11.223</v>
+        <v>9.425000000000001</v>
       </c>
     </row>
     <row r="230">
@@ -11089,10 +11089,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.2537</v>
+        <v>-0.2346</v>
       </c>
       <c r="J230" t="n">
-        <v>-7.3573</v>
+        <v>-6.8034</v>
       </c>
     </row>
     <row r="231">
@@ -11129,10 +11129,10 @@
         <v>0.73</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.3307</v>
+        <v>-0.3159</v>
       </c>
       <c r="J231" t="n">
-        <v>-9.590299999999999</v>
+        <v>-9.161099999999999</v>
       </c>
     </row>
     <row r="232">
@@ -11169,10 +11169,10 @@
         <v>1.05</v>
       </c>
       <c r="I232" t="n">
-        <v>0.2316</v>
+        <v>0.2016</v>
       </c>
       <c r="J232" t="n">
-        <v>4.4004</v>
+        <v>3.8304</v>
       </c>
     </row>
     <row r="233">
@@ -11209,10 +11209,10 @@
         <v>0.79</v>
       </c>
       <c r="I233" t="n">
-        <v>-0.2354</v>
+        <v>-0.2204</v>
       </c>
       <c r="J233" t="n">
-        <v>-4.4726</v>
+        <v>-4.1876</v>
       </c>
     </row>
     <row r="234">
@@ -11249,10 +11249,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.3277</v>
+        <v>-0.3135</v>
       </c>
       <c r="J234" t="n">
-        <v>-6.2263</v>
+        <v>-5.9565</v>
       </c>
     </row>
     <row r="235">
@@ -11289,10 +11289,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.4435</v>
+        <v>-0.4359</v>
       </c>
       <c r="J235" t="n">
-        <v>-8.426500000000001</v>
+        <v>-8.2821</v>
       </c>
     </row>
     <row r="236">
@@ -11329,10 +11329,10 @@
         <v>0.5</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.4963</v>
+        <v>-0.4942</v>
       </c>
       <c r="J236" t="n">
-        <v>-9.4297</v>
+        <v>-9.389799999999999</v>
       </c>
     </row>
     <row r="237">
@@ -11369,10 +11369,10 @@
         <v>2.34</v>
       </c>
       <c r="I237" t="n">
-        <v>1.2537</v>
+        <v>1.22</v>
       </c>
       <c r="J237" t="n">
-        <v>23.8203</v>
+        <v>23.18</v>
       </c>
     </row>
     <row r="238">
@@ -11409,10 +11409,10 @@
         <v>1.51</v>
       </c>
       <c r="I238" t="n">
-        <v>0.6073</v>
+        <v>0.5393</v>
       </c>
       <c r="J238" t="n">
-        <v>11.5387</v>
+        <v>10.2467</v>
       </c>
     </row>
     <row r="239">
@@ -11449,10 +11449,10 @@
         <v>1.27</v>
       </c>
       <c r="I239" t="n">
-        <v>0.3626</v>
+        <v>0.3086</v>
       </c>
       <c r="J239" t="n">
-        <v>6.8894</v>
+        <v>5.8634</v>
       </c>
     </row>
     <row r="240">
@@ -11489,10 +11489,10 @@
         <v>1.12</v>
       </c>
       <c r="I240" t="n">
-        <v>0.1775</v>
+        <v>0.1404</v>
       </c>
       <c r="J240" t="n">
-        <v>3.3725</v>
+        <v>2.6676</v>
       </c>
     </row>
     <row r="241">
@@ -11529,10 +11529,10 @@
         <v>0.96</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.1045</v>
+        <v>-0.091</v>
       </c>
       <c r="J241" t="n">
-        <v>-1.9855</v>
+        <v>-1.729</v>
       </c>
     </row>
     <row r="242">
@@ -11569,10 +11569,10 @@
         <v>1.25</v>
       </c>
       <c r="I242" t="n">
-        <v>0.5187</v>
+        <v>0.4596</v>
       </c>
       <c r="J242" t="n">
-        <v>15.561</v>
+        <v>13.788</v>
       </c>
     </row>
     <row r="243">
@@ -11609,10 +11609,10 @@
         <v>1.08</v>
       </c>
       <c r="I243" t="n">
-        <v>0.2134</v>
+        <v>0.1708</v>
       </c>
       <c r="J243" t="n">
-        <v>6.402</v>
+        <v>5.124</v>
       </c>
     </row>
     <row r="244">
@@ -11649,10 +11649,10 @@
         <v>1.04</v>
       </c>
       <c r="I244" t="n">
-        <v>0.1254</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="J244" t="n">
-        <v>3.762</v>
+        <v>2.841</v>
       </c>
     </row>
     <row r="245">
@@ -11689,10 +11689,10 @@
         <v>0.97</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.0578</v>
+        <v>-0.0454</v>
       </c>
       <c r="J245" t="n">
-        <v>-1.734</v>
+        <v>-1.362</v>
       </c>
     </row>
     <row r="246">
@@ -11729,10 +11729,10 @@
         <v>0.63</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.4103</v>
+        <v>-0.4011</v>
       </c>
       <c r="J246" t="n">
-        <v>-12.309</v>
+        <v>-12.033</v>
       </c>
     </row>
     <row r="247">
@@ -11769,10 +11769,10 @@
         <v>1.17</v>
       </c>
       <c r="I247" t="n">
-        <v>0.271</v>
+        <v>0.219</v>
       </c>
       <c r="J247" t="n">
-        <v>8.130000000000001</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="248">
@@ -11809,10 +11809,10 @@
         <v>1.15</v>
       </c>
       <c r="I248" t="n">
-        <v>0.2453</v>
+        <v>0.1964</v>
       </c>
       <c r="J248" t="n">
-        <v>7.359</v>
+        <v>5.892</v>
       </c>
     </row>
     <row r="249">
@@ -11849,10 +11849,10 @@
         <v>1.1</v>
       </c>
       <c r="I249" t="n">
-        <v>0.1782</v>
+        <v>0.1387</v>
       </c>
       <c r="J249" t="n">
-        <v>5.346</v>
+        <v>4.161</v>
       </c>
     </row>
     <row r="250">
@@ -11889,10 +11889,10 @@
         <v>1.09</v>
       </c>
       <c r="I250" t="n">
-        <v>0.1642</v>
+        <v>0.1269</v>
       </c>
       <c r="J250" t="n">
-        <v>4.926</v>
+        <v>3.807</v>
       </c>
     </row>
     <row r="251">
@@ -11929,10 +11929,10 @@
         <v>0.96</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.0799</v>
+        <v>-0.0643</v>
       </c>
       <c r="J251" t="n">
-        <v>-2.397</v>
+        <v>-1.929</v>
       </c>
     </row>
     <row r="252">
@@ -11969,10 +11969,10 @@
         <v>1.79</v>
       </c>
       <c r="I252" t="n">
-        <v>1.5257</v>
+        <v>1.5716</v>
       </c>
       <c r="J252" t="n">
-        <v>42.7196</v>
+        <v>44.0048</v>
       </c>
     </row>
     <row r="253">
@@ -12009,10 +12009,10 @@
         <v>1.01</v>
       </c>
       <c r="I253" t="n">
-        <v>0.0457</v>
+        <v>0.0343</v>
       </c>
       <c r="J253" t="n">
-        <v>1.2796</v>
+        <v>0.9604</v>
       </c>
     </row>
     <row r="254">
@@ -12049,10 +12049,10 @@
         <v>0.97</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.1515</v>
+        <v>-0.1204</v>
       </c>
       <c r="J254" t="n">
-        <v>-4.242</v>
+        <v>-3.3712</v>
       </c>
     </row>
     <row r="255">
@@ -12089,10 +12089,10 @@
         <v>0.88</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.412</v>
+        <v>-0.3691</v>
       </c>
       <c r="J255" t="n">
-        <v>-11.536</v>
+        <v>-10.3348</v>
       </c>
     </row>
     <row r="256">
@@ -12129,10 +12129,10 @@
         <v>0.8</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.6056</v>
+        <v>-0.5682</v>
       </c>
       <c r="J256" t="n">
-        <v>-16.9568</v>
+        <v>-15.9096</v>
       </c>
     </row>
     <row r="257">
@@ -12169,10 +12169,10 @@
         <v>1.21</v>
       </c>
       <c r="I257" t="n">
-        <v>0.461</v>
+        <v>0.4032</v>
       </c>
       <c r="J257" t="n">
-        <v>12.908</v>
+        <v>11.2896</v>
       </c>
     </row>
     <row r="258">
@@ -12209,10 +12209,10 @@
         <v>1.15</v>
       </c>
       <c r="I258" t="n">
-        <v>0.3552</v>
+        <v>0.3011</v>
       </c>
       <c r="J258" t="n">
-        <v>9.945600000000001</v>
+        <v>8.4308</v>
       </c>
     </row>
     <row r="259">
@@ -12249,10 +12249,10 @@
         <v>0.97</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.0561</v>
+        <v>-0.0446</v>
       </c>
       <c r="J259" t="n">
-        <v>-1.5708</v>
+        <v>-1.2488</v>
       </c>
     </row>
     <row r="260">
@@ -12289,10 +12289,10 @@
         <v>0.83</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.2185</v>
+        <v>-0.1981</v>
       </c>
       <c r="J260" t="n">
-        <v>-6.118</v>
+        <v>-5.5468</v>
       </c>
     </row>
     <row r="261">
@@ -12329,10 +12329,10 @@
         <v>0.64</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.3984</v>
+        <v>-0.3877</v>
       </c>
       <c r="J261" t="n">
-        <v>-11.1552</v>
+        <v>-10.8556</v>
       </c>
     </row>
     <row r="262">
@@ -12369,10 +12369,10 @@
         <v>0.67</v>
       </c>
       <c r="I262" t="n">
-        <v>-0.3287</v>
+        <v>-0.319</v>
       </c>
       <c r="J262" t="n">
-        <v>-6.2453</v>
+        <v>-6.061</v>
       </c>
     </row>
     <row r="263">
@@ -12409,10 +12409,10 @@
         <v>0.67</v>
       </c>
       <c r="I263" t="n">
-        <v>-0.3287</v>
+        <v>-0.319</v>
       </c>
       <c r="J263" t="n">
-        <v>-6.2453</v>
+        <v>-6.061</v>
       </c>
     </row>
     <row r="264">
@@ -12449,10 +12449,10 @@
         <v>0.66</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.3382</v>
+        <v>-0.329</v>
       </c>
       <c r="J264" t="n">
-        <v>-6.4258</v>
+        <v>-6.251</v>
       </c>
     </row>
     <row r="265">
@@ -12489,10 +12489,10 @@
         <v>0.55</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.4341</v>
+        <v>-0.428</v>
       </c>
       <c r="J265" t="n">
-        <v>-8.2479</v>
+        <v>-8.132</v>
       </c>
     </row>
     <row r="266">
@@ -12529,10 +12529,10 @@
         <v>0.37</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.5925</v>
+        <v>-0.6025</v>
       </c>
       <c r="J266" t="n">
-        <v>-11.2575</v>
+        <v>-11.4475</v>
       </c>
     </row>
     <row r="267">
@@ -12569,10 +12569,10 @@
         <v>2.18</v>
       </c>
       <c r="I267" t="n">
-        <v>1.8613</v>
+        <v>1.9249</v>
       </c>
       <c r="J267" t="n">
-        <v>35.3647</v>
+        <v>36.5731</v>
       </c>
     </row>
     <row r="268">
@@ -12609,10 +12609,10 @@
         <v>2.01</v>
       </c>
       <c r="I268" t="n">
-        <v>1.6689</v>
+        <v>1.7136</v>
       </c>
       <c r="J268" t="n">
-        <v>31.7091</v>
+        <v>32.5584</v>
       </c>
     </row>
     <row r="269">
@@ -12649,10 +12649,10 @@
         <v>1.46</v>
       </c>
       <c r="I269" t="n">
-        <v>1.0012</v>
+        <v>1.0116</v>
       </c>
       <c r="J269" t="n">
-        <v>19.0228</v>
+        <v>19.2204</v>
       </c>
     </row>
     <row r="270">
@@ -12689,10 +12689,10 @@
         <v>1.42</v>
       </c>
       <c r="I270" t="n">
-        <v>0.9349</v>
+        <v>0.9365</v>
       </c>
       <c r="J270" t="n">
-        <v>17.7631</v>
+        <v>17.7935</v>
       </c>
     </row>
     <row r="271">
@@ -12729,10 +12729,10 @@
         <v>0.72</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.8478</v>
+        <v>-0.8428</v>
       </c>
       <c r="J271" t="n">
-        <v>-16.1082</v>
+        <v>-16.0132</v>
       </c>
     </row>
     <row r="272">
@@ -12769,10 +12769,10 @@
         <v>1.35</v>
       </c>
       <c r="I272" t="n">
-        <v>0.7493</v>
+        <v>0.7114</v>
       </c>
       <c r="J272" t="n">
-        <v>17.9832</v>
+        <v>17.0736</v>
       </c>
     </row>
     <row r="273">
@@ -12809,10 +12809,10 @@
         <v>0.95</v>
       </c>
       <c r="I273" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.0572</v>
       </c>
       <c r="J273" t="n">
-        <v>-1.656</v>
+        <v>-1.3728</v>
       </c>
     </row>
     <row r="274">
@@ -12849,10 +12849,10 @@
         <v>0.78</v>
       </c>
       <c r="I274" t="n">
-        <v>-0.2545</v>
+        <v>-0.2364</v>
       </c>
       <c r="J274" t="n">
-        <v>-6.108</v>
+        <v>-5.6736</v>
       </c>
     </row>
     <row r="275">
@@ -12889,10 +12889,10 @@
         <v>0.61</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.411</v>
+        <v>-0.4005</v>
       </c>
       <c r="J275" t="n">
-        <v>-9.864000000000001</v>
+        <v>-9.612</v>
       </c>
     </row>
     <row r="276">
@@ -12929,10 +12929,10 @@
         <v>0.4</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.5927</v>
+        <v>-0.6061</v>
       </c>
       <c r="J276" t="n">
-        <v>-14.2248</v>
+        <v>-14.5464</v>
       </c>
     </row>
     <row r="277">
@@ -12969,10 +12969,10 @@
         <v>1.61</v>
       </c>
       <c r="I277" t="n">
-        <v>1.228</v>
+        <v>1.2441</v>
       </c>
       <c r="J277" t="n">
-        <v>29.472</v>
+        <v>29.8584</v>
       </c>
     </row>
     <row r="278">
@@ -13009,10 +13009,10 @@
         <v>1.58</v>
       </c>
       <c r="I278" t="n">
-        <v>1.1889</v>
+        <v>1.2037</v>
       </c>
       <c r="J278" t="n">
-        <v>28.5336</v>
+        <v>28.8888</v>
       </c>
     </row>
     <row r="279">
@@ -13049,10 +13049,10 @@
         <v>1.36</v>
       </c>
       <c r="I279" t="n">
-        <v>0.8518</v>
+        <v>0.8359</v>
       </c>
       <c r="J279" t="n">
-        <v>20.4432</v>
+        <v>20.0616</v>
       </c>
     </row>
     <row r="280">
@@ -13089,10 +13089,10 @@
         <v>1.11</v>
       </c>
       <c r="I280" t="n">
-        <v>0.3176</v>
+        <v>0.2858</v>
       </c>
       <c r="J280" t="n">
-        <v>7.6224</v>
+        <v>6.8592</v>
       </c>
     </row>
     <row r="281">
@@ -13129,10 +13129,10 @@
         <v>0.91</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.3721</v>
+        <v>-0.3342</v>
       </c>
       <c r="J281" t="n">
-        <v>-8.930400000000001</v>
+        <v>-8.020799999999999</v>
       </c>
     </row>
     <row r="282">
@@ -13169,10 +13169,10 @@
         <v>1.23</v>
       </c>
       <c r="I282" t="n">
-        <v>0.6364</v>
+        <v>0.5994</v>
       </c>
       <c r="J282" t="n">
-        <v>18.4556</v>
+        <v>17.3826</v>
       </c>
     </row>
     <row r="283">
@@ -13209,10 +13209,10 @@
         <v>1.16</v>
       </c>
       <c r="I283" t="n">
-        <v>0.4768</v>
+        <v>0.4355</v>
       </c>
       <c r="J283" t="n">
-        <v>13.8272</v>
+        <v>12.6295</v>
       </c>
     </row>
     <row r="284">
@@ -13249,10 +13249,10 @@
         <v>1.01</v>
       </c>
       <c r="I284" t="n">
-        <v>0.0502</v>
+        <v>0.0378</v>
       </c>
       <c r="J284" t="n">
-        <v>1.4558</v>
+        <v>1.0962</v>
       </c>
     </row>
     <row r="285">
@@ -13289,10 +13289,10 @@
         <v>0.98</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.1102</v>
+        <v>-0.0843</v>
       </c>
       <c r="J285" t="n">
-        <v>-3.1958</v>
+        <v>-2.4447</v>
       </c>
     </row>
     <row r="286">
@@ -13329,10 +13329,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.2425</v>
+        <v>-0.204</v>
       </c>
       <c r="J286" t="n">
-        <v>-7.0325</v>
+        <v>-5.916</v>
       </c>
     </row>
     <row r="287">
@@ -13369,10 +13369,10 @@
         <v>1.27</v>
       </c>
       <c r="I287" t="n">
-        <v>0.5409</v>
+        <v>0.4813</v>
       </c>
       <c r="J287" t="n">
-        <v>15.6861</v>
+        <v>13.9577</v>
       </c>
     </row>
     <row r="288">
@@ -13409,10 +13409,10 @@
         <v>1.05</v>
       </c>
       <c r="I288" t="n">
-        <v>0.1437</v>
+        <v>0.1113</v>
       </c>
       <c r="J288" t="n">
-        <v>4.1673</v>
+        <v>3.2277</v>
       </c>
     </row>
     <row r="289">
@@ -13449,10 +13449,10 @@
         <v>0.99</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.0274</v>
+        <v>-0.0194</v>
       </c>
       <c r="J289" t="n">
-        <v>-0.7946</v>
+        <v>-0.5626</v>
       </c>
     </row>
     <row r="290">
@@ -13489,10 +13489,10 @@
         <v>0.98</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.0451</v>
+        <v>-0.034</v>
       </c>
       <c r="J290" t="n">
-        <v>-1.3079</v>
+        <v>-0.986</v>
       </c>
     </row>
     <row r="291">
@@ -13529,10 +13529,10 @@
         <v>0.88</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.1723</v>
+        <v>-0.1518</v>
       </c>
       <c r="J291" t="n">
-        <v>-4.9967</v>
+        <v>-4.4022</v>
       </c>
     </row>
     <row r="292">
@@ -13569,10 +13569,10 @@
         <v>1.21</v>
       </c>
       <c r="I292" t="n">
-        <v>0.4479</v>
+        <v>0.3899</v>
       </c>
       <c r="J292" t="n">
-        <v>12.5412</v>
+        <v>10.9172</v>
       </c>
     </row>
     <row r="293">
@@ -13609,10 +13609,10 @@
         <v>1.11</v>
       </c>
       <c r="I293" t="n">
-        <v>0.2697</v>
+        <v>0.2218</v>
       </c>
       <c r="J293" t="n">
-        <v>7.5516</v>
+        <v>6.2104</v>
       </c>
     </row>
     <row r="294">
@@ -13649,10 +13649,10 @@
         <v>1.01</v>
       </c>
       <c r="I294" t="n">
-        <v>0.0425</v>
+        <v>0.029</v>
       </c>
       <c r="J294" t="n">
-        <v>1.19</v>
+        <v>0.8120000000000001</v>
       </c>
     </row>
     <row r="295">
@@ -13689,10 +13689,10 @@
         <v>0.93</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.1125</v>
+        <v>-0.0945</v>
       </c>
       <c r="J295" t="n">
-        <v>-3.15</v>
+        <v>-2.646</v>
       </c>
     </row>
     <row r="296">
@@ -13729,10 +13729,10 @@
         <v>0.8</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.2535</v>
+        <v>-0.2337</v>
       </c>
       <c r="J296" t="n">
-        <v>-7.098</v>
+        <v>-6.5436</v>
       </c>
     </row>
     <row r="297">
@@ -13769,10 +13769,10 @@
         <v>1.36</v>
       </c>
       <c r="I297" t="n">
-        <v>0.4936</v>
+        <v>0.4255</v>
       </c>
       <c r="J297" t="n">
-        <v>13.8208</v>
+        <v>11.914</v>
       </c>
     </row>
     <row r="298">
@@ -13809,10 +13809,10 @@
         <v>1.34</v>
       </c>
       <c r="I298" t="n">
-        <v>0.4714</v>
+        <v>0.4041</v>
       </c>
       <c r="J298" t="n">
-        <v>13.1992</v>
+        <v>11.3148</v>
       </c>
     </row>
     <row r="299">
@@ -13849,10 +13849,10 @@
         <v>1.03</v>
       </c>
       <c r="I299" t="n">
-        <v>0.0668</v>
+        <v>0.0479</v>
       </c>
       <c r="J299" t="n">
-        <v>1.8704</v>
+        <v>1.3412</v>
       </c>
     </row>
     <row r="300">
@@ -13889,10 +13889,10 @@
         <v>1.02</v>
       </c>
       <c r="I300" t="n">
-        <v>0.0469</v>
+        <v>0.0327</v>
       </c>
       <c r="J300" t="n">
-        <v>1.3132</v>
+        <v>0.9156</v>
       </c>
     </row>
     <row r="301">
@@ -13929,10 +13929,10 @@
         <v>0.74</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.3187</v>
+        <v>-0.3027</v>
       </c>
       <c r="J301" t="n">
-        <v>-8.9236</v>
+        <v>-8.4756</v>
       </c>
     </row>
     <row r="302">
@@ -13969,10 +13969,10 @@
         <v>1.07</v>
       </c>
       <c r="I302" t="n">
-        <v>0.1957</v>
+        <v>0.1549</v>
       </c>
       <c r="J302" t="n">
-        <v>5.871</v>
+        <v>4.647</v>
       </c>
     </row>
     <row r="303">
@@ -14009,10 +14009,10 @@
         <v>1.07</v>
       </c>
       <c r="I303" t="n">
-        <v>0.1957</v>
+        <v>0.1549</v>
       </c>
       <c r="J303" t="n">
-        <v>5.871</v>
+        <v>4.647</v>
       </c>
     </row>
     <row r="304">
@@ -14049,10 +14049,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.09719999999999999</v>
+        <v>-0.0809</v>
       </c>
       <c r="J304" t="n">
-        <v>-2.916</v>
+        <v>-2.427</v>
       </c>
     </row>
     <row r="305">
@@ -14089,10 +14089,10 @@
         <v>0.93</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.1096</v>
+        <v>-0.09229999999999999</v>
       </c>
       <c r="J305" t="n">
-        <v>-3.288</v>
+        <v>-2.769</v>
       </c>
     </row>
     <row r="306">
@@ -14129,10 +14129,10 @@
         <v>0.87</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.1781</v>
+        <v>-0.1578</v>
       </c>
       <c r="J306" t="n">
-        <v>-5.343</v>
+        <v>-4.734</v>
       </c>
     </row>
     <row r="307">
@@ -14169,10 +14169,10 @@
         <v>1.26</v>
       </c>
       <c r="I307" t="n">
-        <v>0.3729</v>
+        <v>0.3123</v>
       </c>
       <c r="J307" t="n">
-        <v>11.187</v>
+        <v>9.369</v>
       </c>
     </row>
     <row r="308">
@@ -14209,10 +14209,10 @@
         <v>1.21</v>
       </c>
       <c r="I308" t="n">
-        <v>0.3142</v>
+        <v>0.2589</v>
       </c>
       <c r="J308" t="n">
-        <v>9.426</v>
+        <v>7.767</v>
       </c>
     </row>
     <row r="309">
@@ -14249,10 +14249,10 @@
         <v>1.19</v>
       </c>
       <c r="I309" t="n">
-        <v>0.2901</v>
+        <v>0.2374</v>
       </c>
       <c r="J309" t="n">
-        <v>8.702999999999999</v>
+        <v>7.122</v>
       </c>
     </row>
     <row r="310">
@@ -14289,10 +14289,10 @@
         <v>1.08</v>
       </c>
       <c r="I310" t="n">
-        <v>0.145</v>
+        <v>0.112</v>
       </c>
       <c r="J310" t="n">
-        <v>4.35</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="311">
@@ -14329,10 +14329,10 @@
         <v>1.03</v>
       </c>
       <c r="I311" t="n">
-        <v>0.0615</v>
+        <v>0.044</v>
       </c>
       <c r="J311" t="n">
-        <v>1.845</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="312">
@@ -14369,10 +14369,10 @@
         <v>1.7</v>
       </c>
       <c r="I312" t="n">
-        <v>1.3405</v>
+        <v>1.3619</v>
       </c>
       <c r="J312" t="n">
-        <v>30.8315</v>
+        <v>31.3237</v>
       </c>
     </row>
     <row r="313">
@@ -14409,10 +14409,10 @@
         <v>1.34</v>
       </c>
       <c r="I313" t="n">
-        <v>0.8124</v>
+        <v>0.7949000000000001</v>
       </c>
       <c r="J313" t="n">
-        <v>18.6852</v>
+        <v>18.2827</v>
       </c>
     </row>
     <row r="314">
@@ -14449,10 +14449,10 @@
         <v>1.29</v>
       </c>
       <c r="I314" t="n">
-        <v>0.7167</v>
+        <v>0.6942</v>
       </c>
       <c r="J314" t="n">
-        <v>16.4841</v>
+        <v>15.9666</v>
       </c>
     </row>
     <row r="315">
@@ -14489,10 +14489,10 @@
         <v>1.21</v>
       </c>
       <c r="I315" t="n">
-        <v>0.5503</v>
+        <v>0.5215</v>
       </c>
       <c r="J315" t="n">
-        <v>12.6569</v>
+        <v>11.9945</v>
       </c>
     </row>
     <row r="316">
@@ -14529,10 +14529,10 @@
         <v>1.1</v>
       </c>
       <c r="I316" t="n">
-        <v>0.2895</v>
+        <v>0.2579</v>
       </c>
       <c r="J316" t="n">
-        <v>6.6585</v>
+        <v>5.9317</v>
       </c>
     </row>
     <row r="317">
@@ -14569,10 +14569,10 @@
         <v>1.12</v>
       </c>
       <c r="I317" t="n">
-        <v>0.3373</v>
+        <v>0.2887</v>
       </c>
       <c r="J317" t="n">
-        <v>7.7579</v>
+        <v>6.6401</v>
       </c>
     </row>
     <row r="318">
@@ -14609,10 +14609,10 @@
         <v>0.88</v>
       </c>
       <c r="I318" t="n">
-        <v>-0.1557</v>
+        <v>-0.1393</v>
       </c>
       <c r="J318" t="n">
-        <v>-3.5811</v>
+        <v>-3.2039</v>
       </c>
     </row>
     <row r="319">
@@ -14649,10 +14649,10 @@
         <v>0.78</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.2557</v>
+        <v>-0.2373</v>
       </c>
       <c r="J319" t="n">
-        <v>-5.8811</v>
+        <v>-5.4579</v>
       </c>
     </row>
     <row r="320">
@@ -14689,10 +14689,10 @@
         <v>0.73</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.303</v>
+        <v>-0.2856</v>
       </c>
       <c r="J320" t="n">
-        <v>-6.969</v>
+        <v>-6.5688</v>
       </c>
     </row>
     <row r="321">
@@ -14729,10 +14729,10 @@
         <v>0.64</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.3855</v>
+        <v>-0.3728</v>
       </c>
       <c r="J321" t="n">
-        <v>-8.8665</v>
+        <v>-8.574400000000001</v>
       </c>
     </row>
     <row r="322">
@@ -14769,10 +14769,10 @@
         <v>1.11</v>
       </c>
       <c r="I322" t="n">
-        <v>0.273</v>
+        <v>0.2246</v>
       </c>
       <c r="J322" t="n">
-        <v>11.466</v>
+        <v>9.433199999999999</v>
       </c>
     </row>
     <row r="323">
@@ -14809,10 +14809,10 @@
         <v>1.06</v>
       </c>
       <c r="I323" t="n">
-        <v>0.1711</v>
+        <v>0.1336</v>
       </c>
       <c r="J323" t="n">
-        <v>7.1862</v>
+        <v>5.6112</v>
       </c>
     </row>
     <row r="324">
@@ -14849,10 +14849,10 @@
         <v>1.02</v>
       </c>
       <c r="I324" t="n">
-        <v>0.0741</v>
+        <v>0.0528</v>
       </c>
       <c r="J324" t="n">
-        <v>3.1122</v>
+        <v>2.2176</v>
       </c>
     </row>
     <row r="325">
@@ -14889,10 +14889,10 @@
         <v>1</v>
       </c>
       <c r="I325" t="n">
-        <v>0.0004</v>
+        <v>0.0001</v>
       </c>
       <c r="J325" t="n">
-        <v>0.0168</v>
+        <v>0.0042</v>
       </c>
     </row>
     <row r="326">
@@ -14929,10 +14929,10 @@
         <v>0.78</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.2715</v>
+        <v>-0.2523</v>
       </c>
       <c r="J326" t="n">
-        <v>-11.403</v>
+        <v>-10.5966</v>
       </c>
     </row>
     <row r="327">
@@ -14969,10 +14969,10 @@
         <v>1.31</v>
       </c>
       <c r="I327" t="n">
-        <v>0.8011</v>
+        <v>0.7746</v>
       </c>
       <c r="J327" t="n">
-        <v>33.6462</v>
+        <v>32.5332</v>
       </c>
     </row>
     <row r="328">
@@ -15009,10 +15009,10 @@
         <v>1.09</v>
       </c>
       <c r="I328" t="n">
-        <v>0.2999</v>
+        <v>0.2632</v>
       </c>
       <c r="J328" t="n">
-        <v>12.5958</v>
+        <v>11.0544</v>
       </c>
     </row>
     <row r="329">
@@ -15049,10 +15049,10 @@
         <v>1.08</v>
       </c>
       <c r="I329" t="n">
-        <v>0.2739</v>
+        <v>0.2384</v>
       </c>
       <c r="J329" t="n">
-        <v>11.5038</v>
+        <v>10.0128</v>
       </c>
     </row>
     <row r="330">
@@ -15089,10 +15089,10 @@
         <v>1.01</v>
       </c>
       <c r="I330" t="n">
-        <v>0.0464</v>
+        <v>0.0349</v>
       </c>
       <c r="J330" t="n">
-        <v>1.9488</v>
+        <v>1.4658</v>
       </c>
     </row>
     <row r="331">
@@ -15129,10 +15129,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.2467</v>
+        <v>-0.208</v>
       </c>
       <c r="J331" t="n">
-        <v>-10.3614</v>
+        <v>-8.736000000000001</v>
       </c>
     </row>
     <row r="332">
@@ -15169,10 +15169,10 @@
         <v>1.35</v>
       </c>
       <c r="I332" t="n">
-        <v>0.8519</v>
+        <v>0.8312</v>
       </c>
       <c r="J332" t="n">
-        <v>21.2975</v>
+        <v>20.78</v>
       </c>
     </row>
     <row r="333">
@@ -15209,10 +15209,10 @@
         <v>1.22</v>
       </c>
       <c r="I333" t="n">
-        <v>0.587</v>
+        <v>0.5538999999999999</v>
       </c>
       <c r="J333" t="n">
-        <v>14.675</v>
+        <v>13.8475</v>
       </c>
     </row>
     <row r="334">
@@ -15249,10 +15249,10 @@
         <v>1.21</v>
       </c>
       <c r="I334" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.5324</v>
       </c>
       <c r="J334" t="n">
-        <v>14.15</v>
+        <v>13.31</v>
       </c>
     </row>
     <row r="335">
@@ -15289,10 +15289,10 @@
         <v>1.15</v>
       </c>
       <c r="I335" t="n">
-        <v>0.433</v>
+        <v>0.3986</v>
       </c>
       <c r="J335" t="n">
-        <v>10.825</v>
+        <v>9.965</v>
       </c>
     </row>
     <row r="336">
@@ -15329,10 +15329,10 @@
         <v>1.09</v>
       </c>
       <c r="I336" t="n">
-        <v>0.2832</v>
+        <v>0.2513</v>
       </c>
       <c r="J336" t="n">
-        <v>7.08</v>
+        <v>6.2825</v>
       </c>
     </row>
     <row r="337">
@@ -15369,10 +15369,10 @@
         <v>1.12</v>
       </c>
       <c r="I337" t="n">
-        <v>0.3011</v>
+        <v>0.2504</v>
       </c>
       <c r="J337" t="n">
-        <v>7.5275</v>
+        <v>6.26</v>
       </c>
     </row>
     <row r="338">
@@ -15409,10 +15409,10 @@
         <v>1.06</v>
       </c>
       <c r="I338" t="n">
-        <v>0.1785</v>
+        <v>0.1396</v>
       </c>
       <c r="J338" t="n">
-        <v>4.4625</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="339">
@@ -15449,10 +15449,10 @@
         <v>0.98</v>
       </c>
       <c r="I339" t="n">
-        <v>-0.0401</v>
+        <v>-0.0311</v>
       </c>
       <c r="J339" t="n">
-        <v>-1.0025</v>
+        <v>-0.7775</v>
       </c>
     </row>
     <row r="340">
@@ -15489,10 +15489,10 @@
         <v>0.82</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.2279</v>
+        <v>-0.2076</v>
       </c>
       <c r="J340" t="n">
-        <v>-5.6975</v>
+        <v>-5.19</v>
       </c>
     </row>
     <row r="341">
@@ -15529,10 +15529,10 @@
         <v>0.78</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.2676</v>
+        <v>-0.2482</v>
       </c>
       <c r="J341" t="n">
-        <v>-6.69</v>
+        <v>-6.205</v>
       </c>
     </row>
     <row r="342">
@@ -15569,10 +15569,10 @@
         <v>1.28</v>
       </c>
       <c r="I342" t="n">
-        <v>0.5593</v>
+        <v>0.4997</v>
       </c>
       <c r="J342" t="n">
-        <v>23.4906</v>
+        <v>20.9874</v>
       </c>
     </row>
     <row r="343">
@@ -15609,10 +15609,10 @@
         <v>1.19</v>
       </c>
       <c r="I343" t="n">
-        <v>0.4113</v>
+        <v>0.3546</v>
       </c>
       <c r="J343" t="n">
-        <v>17.2746</v>
+        <v>14.8932</v>
       </c>
     </row>
     <row r="344">
@@ -15649,10 +15649,10 @@
         <v>1.13</v>
       </c>
       <c r="I344" t="n">
-        <v>0.3051</v>
+        <v>0.2545</v>
       </c>
       <c r="J344" t="n">
-        <v>12.8142</v>
+        <v>10.689</v>
       </c>
     </row>
     <row r="345">
@@ -15689,10 +15689,10 @@
         <v>0.76</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.2935</v>
+        <v>-0.2754</v>
       </c>
       <c r="J345" t="n">
-        <v>-12.327</v>
+        <v>-11.5668</v>
       </c>
     </row>
     <row r="346">
@@ -15729,10 +15729,10 @@
         <v>0.76</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.2935</v>
+        <v>-0.2754</v>
       </c>
       <c r="J346" t="n">
-        <v>-12.327</v>
+        <v>-11.5668</v>
       </c>
     </row>
     <row r="347">
@@ -15769,10 +15769,10 @@
         <v>1.35</v>
       </c>
       <c r="I347" t="n">
-        <v>0.8814</v>
+        <v>0.8616</v>
       </c>
       <c r="J347" t="n">
-        <v>37.0188</v>
+        <v>36.1872</v>
       </c>
     </row>
     <row r="348">
@@ -15809,10 +15809,10 @@
         <v>1.28</v>
       </c>
       <c r="I348" t="n">
-        <v>0.7366</v>
+        <v>0.7055</v>
       </c>
       <c r="J348" t="n">
-        <v>30.9372</v>
+        <v>29.631</v>
       </c>
     </row>
     <row r="349">
@@ -15849,10 +15849,10 @@
         <v>1.24</v>
       </c>
       <c r="I349" t="n">
-        <v>0.651</v>
+        <v>0.6152</v>
       </c>
       <c r="J349" t="n">
-        <v>27.342</v>
+        <v>25.8384</v>
       </c>
     </row>
     <row r="350">
@@ -15889,10 +15889,10 @@
         <v>0.85</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.4875</v>
+        <v>-0.4456</v>
       </c>
       <c r="J350" t="n">
-        <v>-20.475</v>
+        <v>-18.7152</v>
       </c>
     </row>
     <row r="351">
@@ -15929,10 +15929,10 @@
         <v>0.74</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.7406</v>
+        <v>-0.7121</v>
       </c>
       <c r="J351" t="n">
-        <v>-31.1052</v>
+        <v>-29.9082</v>
       </c>
     </row>
     <row r="352">
@@ -15969,10 +15969,10 @@
         <v>1.62</v>
       </c>
       <c r="I352" t="n">
-        <v>1.2741</v>
+        <v>1.2937</v>
       </c>
       <c r="J352" t="n">
-        <v>34.4007</v>
+        <v>34.9299</v>
       </c>
     </row>
     <row r="353">
@@ -16009,10 +16009,10 @@
         <v>1.56</v>
       </c>
       <c r="I353" t="n">
-        <v>1.1933</v>
+        <v>1.2085</v>
       </c>
       <c r="J353" t="n">
-        <v>32.2191</v>
+        <v>32.6295</v>
       </c>
     </row>
     <row r="354">
@@ -16049,10 +16049,10 @@
         <v>1.18</v>
       </c>
       <c r="I354" t="n">
-        <v>0.5046</v>
+        <v>0.4685</v>
       </c>
       <c r="J354" t="n">
-        <v>13.6242</v>
+        <v>12.6495</v>
       </c>
     </row>
     <row r="355">
@@ -16089,10 +16089,10 @@
         <v>0.77</v>
       </c>
       <c r="I355" t="n">
-        <v>-0.6882</v>
+        <v>-0.6577</v>
       </c>
       <c r="J355" t="n">
-        <v>-18.5814</v>
+        <v>-17.7579</v>
       </c>
     </row>
     <row r="356">
@@ -16129,10 +16129,10 @@
         <v>0.72</v>
       </c>
       <c r="I356" t="n">
-        <v>-0.7976</v>
+        <v>-0.7761</v>
       </c>
       <c r="J356" t="n">
-        <v>-21.5352</v>
+        <v>-20.9547</v>
       </c>
     </row>
     <row r="357">
@@ -16169,10 +16169,10 @@
         <v>1.03</v>
       </c>
       <c r="I357" t="n">
-        <v>0.1151</v>
+        <v>0.08550000000000001</v>
       </c>
       <c r="J357" t="n">
-        <v>3.1077</v>
+        <v>2.3085</v>
       </c>
     </row>
     <row r="358">
@@ -16209,10 +16209,10 @@
         <v>0.99</v>
       </c>
       <c r="I358" t="n">
-        <v>-0.0186</v>
+        <v>-0.0137</v>
       </c>
       <c r="J358" t="n">
-        <v>-0.5022</v>
+        <v>-0.3699</v>
       </c>
     </row>
     <row r="359">
@@ -16249,10 +16249,10 @@
         <v>0.97</v>
       </c>
       <c r="I359" t="n">
-        <v>-0.0522</v>
+        <v>-0.042</v>
       </c>
       <c r="J359" t="n">
-        <v>-1.4094</v>
+        <v>-1.134</v>
       </c>
     </row>
     <row r="360">
@@ -16289,10 +16289,10 @@
         <v>0.93</v>
       </c>
       <c r="I360" t="n">
-        <v>-0.1057</v>
+        <v>-0.0901</v>
       </c>
       <c r="J360" t="n">
-        <v>-2.8539</v>
+        <v>-2.4327</v>
       </c>
     </row>
     <row r="361">
@@ -16329,10 +16329,10 @@
         <v>0.64</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.394</v>
+        <v>-0.3824</v>
       </c>
       <c r="J361" t="n">
-        <v>-10.638</v>
+        <v>-10.3248</v>
       </c>
     </row>
     <row r="362">
@@ -16369,10 +16369,10 @@
         <v>1.35</v>
       </c>
       <c r="I362" t="n">
-        <v>0.7116</v>
+        <v>0.6621</v>
       </c>
       <c r="J362" t="n">
-        <v>18.5016</v>
+        <v>17.2146</v>
       </c>
     </row>
     <row r="363">
@@ -16409,10 +16409,10 @@
         <v>0.83</v>
       </c>
       <c r="I363" t="n">
-        <v>-0.2128</v>
+        <v>-0.193</v>
       </c>
       <c r="J363" t="n">
-        <v>-5.5328</v>
+        <v>-5.018</v>
       </c>
     </row>
     <row r="364">
@@ -16449,10 +16449,10 @@
         <v>0.8</v>
       </c>
       <c r="I364" t="n">
-        <v>-0.2428</v>
+        <v>-0.2231</v>
       </c>
       <c r="J364" t="n">
-        <v>-6.3128</v>
+        <v>-5.8006</v>
       </c>
     </row>
     <row r="365">
@@ -16489,10 +16489,10 @@
         <v>0.76</v>
       </c>
       <c r="I365" t="n">
-        <v>-0.2816</v>
+        <v>-0.2629</v>
       </c>
       <c r="J365" t="n">
-        <v>-7.3216</v>
+        <v>-6.8354</v>
       </c>
     </row>
     <row r="366">
@@ -16529,10 +16529,10 @@
         <v>0.75</v>
       </c>
       <c r="I366" t="n">
-        <v>-0.2912</v>
+        <v>-0.2727</v>
       </c>
       <c r="J366" t="n">
-        <v>-7.5712</v>
+        <v>-7.0902</v>
       </c>
     </row>
     <row r="367">
@@ -16569,10 +16569,10 @@
         <v>1.51</v>
       </c>
       <c r="I367" t="n">
-        <v>1.1267</v>
+        <v>1.1394</v>
       </c>
       <c r="J367" t="n">
-        <v>29.2942</v>
+        <v>29.6244</v>
       </c>
     </row>
     <row r="368">
@@ -16609,10 +16609,10 @@
         <v>1.25</v>
       </c>
       <c r="I368" t="n">
-        <v>0.657</v>
+        <v>0.6237</v>
       </c>
       <c r="J368" t="n">
-        <v>17.082</v>
+        <v>16.2162</v>
       </c>
     </row>
     <row r="369">
@@ -16649,10 +16649,10 @@
         <v>1.09</v>
       </c>
       <c r="I369" t="n">
-        <v>0.29</v>
+        <v>0.2569</v>
       </c>
       <c r="J369" t="n">
-        <v>7.54</v>
+        <v>6.6794</v>
       </c>
     </row>
     <row r="370">
@@ -16689,10 +16689,10 @@
         <v>1.05</v>
       </c>
       <c r="I370" t="n">
-        <v>0.176</v>
+        <v>0.1492</v>
       </c>
       <c r="J370" t="n">
-        <v>4.576</v>
+        <v>3.8792</v>
       </c>
     </row>
     <row r="371">
@@ -16729,10 +16729,10 @@
         <v>0.91</v>
       </c>
       <c r="I371" t="n">
-        <v>-0.3464</v>
+        <v>-0.3049</v>
       </c>
       <c r="J371" t="n">
-        <v>-9.006399999999999</v>
+        <v>-7.9274</v>
       </c>
     </row>
   </sheetData>
